--- a/Thư mục KQ/VB sau tóm tắt/test_results.xlsx
+++ b/Thư mục KQ/VB sau tóm tắt/test_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,88 +453,213 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Taste Studio của Regent Hotels &amp; Resorts tổ chức với chủ đề 'Dáng hình của biển', giới hạn 20 khách mời mỗi tối. Sự kiện quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, từ Mr. Dripping (drip art) đến Francesco (Milan), Huân Trần (Regent Phú Quốc) và Andy Huỳnh (Oku). Regent Phú Quốc mong muốn tiếp tục kiến tạo trải nghiệm đưa nét bản địa đặc sắc lên bản đồ thế giới cho khách hàng hạng sang.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{
+  "id": 1,
+  "style": "news_brief",
+  "article": "Taste Studio do thương hiệu Regent Hotels &amp; Resorts tổ chức nhằm mang đến trải nghiệm đa giác quan qua ẩm thực và nghệ thuật. Sự kiện này quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, từ nhà thiết kế thời trang đến nhạc sĩ, kết hợp cùng các thương hiệu hàng đầu như Vietnam Airlines. Sự kiện hướng đến phân khúc khách hàng sang trọng. Mùa một và hai diễn ra lần được vào tháng 4, tháng 11 năm ngoái. Taste Studio năm nay với chủ đề 'Dáng hình của biển', giới hạn 20 khách mời mỗi tối. Các khách mời được tham gia vào chuỗi khám phá gồm 7 chương đặc sắc về vẻ đẹp của biển, qua lăng kính nghệ sĩ tài hoa Mr. Dripping - nghệ sĩ vẽ tranh bằng phương pháp nhỏ giọt (drip art). Không gian nhà hàng, nơi diễn ra sự kiện với nội thất dùng tre, mây và tầm vông do kiến trúc sư Nguyễn Trung Nghĩa thiết kế. Ngoài hai nghệ sĩ này, Taste Studio còn có sự tham gia của bếp trưởng Francesco đến từ Milan, với 20 năm kinh nghiệm làm việc tại các khách sạn danh tiếng thế giới, đang bắt đầu hành trình mới tại Việt Nam. Ông đảm nhận vai trò cố vấn ẩm thực tại Regent Phú Quốc, mang đến trải nghiệm độc đáo cho thực khách. Bên cạnh đó, phó bếp trưởng điều hành Huân Trần tại chương trình mong muốn chinh phục các hương vị vùng miền khác nhau. Được nếm nhiều nguyên liệu địa phương và các loại gia vị đặc biệt, vị đầu bếp để lại điểm nhấn riêng trong cách giữ gìn, nâng tầm phong vị của quê hương tại Regent Phú Quốc. Chương trình có sự góp mặt của bếp trưởng nhà hàng Oku - Andy Huỳnh. Trước khi gia nhập Regent Phú Quốc, anh phát triển kỹ thuật nấu ăn Nhật Bản tại Nobu, San Diego và Nassau. Các món ăn của Andy luôn mang ý nghĩa hướng về cội nguồn. Bếp trưởng nhà hàng Ocean Club Daniel và bếp trưởng Duyến Nguyễn của khu nghỉ dưỡng này cũng tham gia, sáng tạo một số hương vị độc đáo từ nguyên liệu địa phương. Đại diện Regent Phú Quốc cho biết, thông qua Taste Studio, đơn vị mong muốn tiếp tục kiến tạo trải nghiệm đưa nét bản địa đặc sắc của Việt Nam lên bản đồ thế giới, từ đó chinh phục khách hàng hạng sang và giới chuyên gia. Thanh Thư",
+  "summary": "Taste Studio của Regent Hotels &amp; Resorts tổ chức với chủ đề 'Dáng hình của biển', giới hạn 20 khách mời mỗi tối. Sự kiện quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, từ Mr. Dripping (drip art) đến Francesco (Milan), Huân Trần (Regent Phú Quốc) và Andy Huỳnh (Oku). Regent Phú Quốc mong muốn tiếp tục kiến tạo trải nghiệm đưa nét bản địa đặc sắc lên bản đồ thế giới cho khách hàng hạng sang.",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, nhưng có bỏ sót một số chi tiết quan trọng như sự tham gia của các thương hiệu hàng đầu và kiến trúc sư Nguyễn Trung Nghĩa",
+  "relevance_score": 0.8,
+  "relevance_reason": "Bản tóm tắt bao hàm các ý chính quan trọng, nhưng bỏ sót thông điệp về việc Regent Phú Quốc muốn chinh phục khách hàng hạng sang và giới chuyên gia",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, nhưng có thể rút gọn một số chi tiết để tăng tính súc tích"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hai giải thưởng gồm 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới'. Đây cũng là năm thứ tư liên tiếp đơn vị đạt giải thưởng này, sau quá trình thẩm định từ hội đồng chuyên môn toàn cầu và bình chọn bởi hàng nghìn du khách, khách sạn quốc tế khác. 'Giải thưởng góp phần khẳng định Amiana Resort Nha Trang là điểm đến lý tưởng cho du khách tìm kiếm không gian riêng tư, gần gũi thiên nhiên với kiến trúc cao cấp, mang lại trải nghiệm sang trọng, độc đáo', đại diện resort chia sẻ. Amiana có kiến trúc hòa hợp thiên nhiên, kết hợp yếu tố truyền thống và hiện đại, tạo nên không gian thư giãn, sang trọng nhưng vẫn giữ được cảm giác gần gũi, yên bình. Bãi biển riêng tư với hàng dừa rợp bóng xanh mát là nơi du khách có thể thư giãn, nghỉ ngơi thoải mái. Resort còn tận dụng địa hình tự nhiên để bố trí các công trình công cộng như hồ bơi, nhà hàng, phòng hội nghị, spa... Các yếu tố đậm chất nhiệt đới như dừa xanh, sóng biển, đá và gỗ được lồng ghép khéo léo trong từng chi tiết thiết kế nội ngoại thất. Biệt thự, phòng nghỉ, nhà hàng đều có sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại. Mỗi căn biệt thự đều mang kiến trúc mở, sử dụng nội thất chủ yếu từ gỗ, đá tự nhiên. Tất cả phòng đều có cửa sổ lớn và ban công rộng, tối ưu tầm nhìn hướng biển với cảnh quan thiên nhiên vây quanh. Biệt thự còn có hồ bơi riêng, không gian vườn với các loại cây nhiệt đới, đảm bảo yếu tố riêng tư cho khách hàng. Resort không chỉ chú trọng xây dựng công trình tiện ích, mà còn đặc biệt lưu ý việc bảo vệ môi trường, sử dụng các giải pháp bền vững. Những không gian xanh, vườn cây, hồ nước đều được bố trí hợp lý, tạo nên hệ sinh thái tự nhiên trong lòng khu nghỉ dưỡng. Theo đại diện Amiana Resort Nha Trang, những chi tiết kiến trúc thông minh cùng không gian mở, vật liệu tự nhiên, sự khéo léo trong thiết kế tại đây góp phần tạo nên khu nghỉ dưỡng lý tưởng cho những ai tìm kiếm sự an yên, lãng mạn và xa hoa. Á Hiên</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Amiana Resort Nha Trang tiếp tục nhận hai giải thưởng quốc tế: 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới', nổi bật với kiến trúc tự nhiên kết hợp công nghệ, bãi biển riêng tư xanh mát, hồ bơi và vườn bảo vệ môi trường.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{
+  "id": 2,
+  "style": "news_brief",
+  "article": "Hai giải thưởng gồm 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới'. Đây cũng là năm thứ tư liên tiếp đơn vị đạt giải thưởng này, sau quá trình thẩm định từ hội đồng chuyên môn toàn cầu và bình chọn bởi hàng nghìn du khách, khách sạn quốc tế khác. 'Giải thưởng góp phần khẳng định Amiana Resort Nha Trang là điểm đến lý tưởng cho du khách tìm kiếm không gian riêng tư, gần gũi thiên nhiên với kiến trúc cao cấp, mang lại trải nghiệm sang trọng, độc đáo', đại diện resort chia sẻ. Amiana có kiến trúc hòa hợp thiên nhiên, kết hợp yếu tố truyền thống và hiện đại, tạo nên không gian thư giãn, sang trọng nhưng vẫn giữ được cảm giác gần gũi, yên bình. Bãi biển riêng tư với hàng dừa rợp bóng xanh mát là nơi du khách có thể thư giãn, nghỉ ngơi thoải mái. Resort còn tận dụng địa hình tự nhiên để bố trí các công trình công cộng như hồ bơi, nhà hàng, phòng hội nghị, spa... Các yếu tố đậm chất nhiệt đới như dừa xanh, sóng biển, đá và gỗ được lồng ghép khéo léo trong từng chi tiết thiết kế nội ngoại thất. Biệt thự, phòng nghỉ, nhà hàng đều có sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại. Mỗi căn biệt thự đều mang kiến trúc mở, sử dụng nội thất chủ yếu từ gỗ, đá tự nhiên. Tất cả phòng đều có cửa sổ lớn và ban công rộng, tối ưu tầm nhìn hướng biển với cảnh quan thiên nhiên vây quanh. Biệt thự còn có hồ bơi riêng, không gian vườn với các loại cây nhiệt đới, đảm bảo yếu tố riêng tư cho khách hàng. Resort không chỉ chú trọng xây dựng công trình tiện ích, mà còn đặc biệt lưu ý việc bảo vệ môi trường, sử dụng các giải pháp bền vững. Những không gian xanh, vườn cây, hồ nước đều được bố trí hợp lý, tạo nên hệ sinh thái tự nhiên trong lòng khu nghỉ dưỡng. Theo đại diện Amiana Resort Nha Trang, những chi tiết kiến trúc thông minh cùng không gian mở, vật liệu tự nhiên, sự khéo léo trong thiết kế tại đây góp phần tạo nên khu nghỉ dưỡng lý tưởng cho những ai tìm kiếm sự an yên, lãng mạn và xa hoa. Á Hiên",
+  "summary": "Amiana Resort Nha Trang tiếp tục nhận hai giải thưởng quốc tế: 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới', nổi bật với kiến trúc tự nhiên kết hợp công nghệ, bãi biển riêng tư xanh mát, hồ bơi và vườn bảo vệ môi trường.",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, nhưng có thể thiếu một số chi tiết quan trọng như việc Amiana Resort Nha Trang đạt giải thưởng này lần thứ tư liên tiếp và quá trình thẩm định từ hội đồng chuyên môn toàn cầu",
+  "relevance_score": 0.8,
+  "relevance_reason": "Bản tóm tắt bao hàm các ý chính quan trọng như giải thưởng, kiến trúc và môi trường, nhưng có thể bỏ sót thông điệp cốt lõi về sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, nhưng có thể loại bỏ một số từ ngữ không cần thiết để tăng tính súc tích"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ, rộng hơn 300 ha. Nơi đây ngoài là điểm đến ngắm dòng Tiền Giang, đón gió sông mát dịu, còn là địa chỉ thu hút khách với bộ sưu tập gỗ lũa nội thất độc đáo của khu du lịch trên cồn. Gỗ lũa tức những thân cây khủng, vớt từ đáy sông, bên ngoài bị dòng nước bào mòn, chỉ còn phần lõi bền chắc. Hàng nghìn thân gỗ lũa được người chủ tuyển chọn làm vật liệu chính xây Khu du lịch sinh thái Cồn Én từ tiểu cảnh, nhà đến đài quan sát. Hơn 20 năm trước, ông Nguyễn Văn Nghỉ ở huyện Chợ Mới đã sưu tập rất nhiều gỗ lũa. Ban đầu ông trục vớt chúng để khơi thông dòng chảy, hạn chế tình trạng lưới đánh cá mắc vào thân cây. Lâu dần, ông yêu mến và muốn lưu giữ những thân gỗ trầm thủy này. Ba năm trước, ông Nghỉ dùng số gỗ lũa để xây khu du lịch ven sông Tiền rộng 6 ha. Đặc sắc trong các vật liệu từ gỗ lũa là bức tranh điêu khắc về phong cảnh làng quê Việt Nam xưa dài hơn 24 m, nặng 20 tấn. Bức tranh do nghệ nhân ở Huế thực hiện trong 7 năm, trên khúc gỗ trầm thủy khủng, tùy từng đoạn có chiều cao từ 1,5 - 1,8 m. Cạnh bức tranh là bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ như tứ quý, sảnh tiến tới của nhiều dòng xe nổi tiếng. Dọc các lối đi là những tiểu cảnh làm từ gỗ lũa. Một số được điêu khắc thành các con vật, chim muông. Những cây gỗ lũa kích thước lớn được tận dụng làm đài quan sát cao 26 m, hoặc móng trụ để xây nhà nghỉ, cầu vượt. Khuôn viên cũng được phủ bởi nhiều cây kiểng, dừa cùng dãy nhà sàn ven sông. Tại đây du khách được ngắm hoàng hôn trên sông, tắm sông và thưởng thức ẩm thực miền Tây. Chị Phúc Điền, du khách ở TP HCM, cho biết khá thích với khung cảnh miền Tây yên bình ở Cồn Én. Chị cũng bất ngờ với sự kỳ công của người đã sưu tập hàng nghìn thân gỗ lũa và biến chúng thành điểm tham quan độc đáo. Cồn Én, nằm cách TP HCM 170 km, du khách có thể đến đây từ hướng quốc lộ 30 của tỉnh Đồng Tháp hoặc lên phà Tấn Long vượt sông Tiền từ phía huyện Chợ Mới. Giá vé vào cổng là 80.000 đồng. Ngọc Tài</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gỗ lũa từ sông Tiền tạo nên khu du lịch Cồn Én, với tiểu cảnh, đài quan sát và bức tranh điêu khắc dài 24 m. Du khách đến TP HCM qua quốc lộ 30 hoặc phà Tấn Long thăm đảo này với giá vé 80.000 đồng, nơi người dân đã biến hàng nghìn thân gỗ lũa thành điểm tham quan yên bình.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{
+  "id": 3,
+  "style": "news_brief",
+  "article": "Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ, rộng hơn 300 ha. Nơi đây ngoài là điểm đến ngắm dòng Tiền Giang, đón gió sông mát dịu, còn là địa chỉ thu hút khách với bộ sưu tập gỗ lũa nội thất độc đáo của khu du lịch trên cồn. Gỗ lũa tức những thân cây khủng, vớt từ đáy sông, bên ngoài bị dòng nước bào mòn, chỉ còn phần lõi bền chắc. Hàng nghìn thân gỗ lũa được người chủ tuyển chọn làm vật liệu chính xây Khu du lịch sinh thái Cồn Én từ tiểu cảnh, nhà đến đài quan sát. Hơn 20 năm trước, ông Nguyễn Văn Nghỉ ở huyện Chợ Mới đã sưu tập rất nhiều gỗ lũa. Ban đầu ông trục vớt chúng để khơi thông dòng chảy, hạn chế tình trạng lưới đánh cá mắc vào thân cây. Lâu dần, ông yêu mến và muốn lưu giữ những thân gỗ trầm thủy này. Ba năm trước, ông Nghỉ dùng số gỗ lũa để xây khu du lịch ven sông Tiền rộng 6 ha. Đặc sắc trong các vật liệu từ gỗ lũa là bức tranh điêu khắc về phong cảnh làng quê Việt Nam xưa dài hơn 24 m, nặng 20 tấn. Bức tranh do nghệ nhân ở Huế thực hiện trong 7 năm, trên khúc gỗ trầm thủy khủng, tùy từng đoạn có chiều cao từ 1,5 - 1,8 m. Cạnh bức tranh là bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ như tứ quý, sảnh tiến tới của nhiều dòng xe nổi tiếng. Dọc các lối đi là những tiểu cảnh làm từ gỗ lũa. Một số được điêu khắc thành các con vật, chim muông. Những cây gỗ lũa kích thước lớn được tận dụng làm đài quan sát cao 26 m, hoặc móng trụ để xây nhà nghỉ, cầu vượt. Khuôn viên cũng được phủ bởi nhiều cây kiểng, dừa cùng dãy nhà sàn ven sông. Tại đây du khách được ngắm hoàng hôn trên sông, tắm sông và thưởng thức ẩm thực miền Tây. Chị Phúc Điền, du khách ở TP HCM, cho biết khá thích với khung cảnh miền Tây yên bình ở Cồn Én. Chị cũng bất ngờ với sự kỳ công của người đã sưu tập hàng nghìn thân gỗ lũa và biến chúng thành điểm tham quan độc đáo. Cồn Én, nằm cách TP HCM 170 km, du khách có thể đến đây từ hướng quốc lộ 30 của tỉnh Đồng Tháp hoặc lên phà Tấn Long vượt sông Tiền từ phía huyện Chợ Mới. Giá vé vào cổng là 80.000 đồng. Ngọc Tài",
+  "summary": "Gỗ lũa từ sông Tiền tạo nên khu du lịch Cồn Én, với tiểu cảnh, đài quan sát và bức tranh điêu khắc dài 24 m. Du khách đến TP HCM qua quốc lộ 30 hoặc phà Tấn Long thăm đảo này với giá vé 80.000 đồng, nơi người dân đã biến hàng nghìn thân gỗ lũa thành điểm tham quan yên bình.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin nhưng có thiếu sót một số chi tiết quan trọng như vị trí của Cồn Én, diện tích khu du lịch và một số hoạt động du lịch khác",
+  "relevance_score": 0.7,
+  "relevance_reason": "Bản tóm tắt chưa bao hàm đủ các ý chính quan trọng nhất như vị trí địa lý, các hoạt động du lịch và đặc điểm nổi bật của khu du lịch Cồn Én",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt có mạch lạc, logic và dễ đọc, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng và tránh trùng lặp thông tin"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Văn phòng mới của MayTrip tại địa chỉ 833 Lê Hồng Phong, quận 10, nhằm mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Văn phòng mới được kỳ vọng là điểm đến thuận tiện cho khách hàng trong việc tìm hiểu và sử dụng dịch vụ của công ty. Trong ngày khai trương, MayTrip trao tặng nhiều quà tặng và ưu đãi cho khách tham dự. Các voucher gồm: 2 triệu đồng cho khách đăng ký tour Bắc Á trong ba ngày khai trương, 1 triệu đồng cho tour Đông Nam Á trong ba tháng từ ngày khai trương, 500.000 đồng cho dịch vụ tour nội địa trong một năm, 200.000 đồng dịch vụ đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và 100.000 đồng với dịch vụ vé máy bay trong 6 tháng. Buổi lễ khai trương văn phòng tại Sài Gòn còn giới thiệu các chương trìnhtour Nhật Bảndịp Tết Âm lịch như cung đường vàng trải nghiệm trượt tuyết, Hokkaido - miền tuyết trắng. Những chuyến đi này được MayTrip thiết kế kỹ lưỡng, phù hợp với không khí đón xuân cho gia đình và cặp đôi Việt trong dịp Tết Nguyên đán. Năm nay, MayTrip xác định tour Hokkaido là sản phẩm 'đinh' trong dịp Tết Nguyên đán. Hokkaido nằm ở miền Bắc Nhật Bản, nổi tiếng với những đợt tuyết dày và phong cảnh mùa đông đặc trưng. Tour Hokkaido dịp Tết là hành trình lý tưởng để du khách tận hưởng kỳ nghỉ theo cách mới mẻ và ấn tượng trong tuyết trắng. Bên cạnh đó, tour Hokkaido của MayTrip cũng mang đến trải nghiệm suối nước nóng onsen giữa băng tuyết, giúp du khách thư giãn sau những hoạt động trong ngày. Bên cạnh đó, MayTrip cũng cung cấp các tour du lịch khác với lịch khởi hành linh hoạt kéo dài đến hết năm 2025, gồm hành trình ngắm hoa anh đào, hoa mơ, mận và nghỉ lễ 30/4 và 1/5. Các hành trình này dựa trên xu hướng và sở thích của du khách Việt Nam. Theo đại diện công ty, sự kiện khai trương văn phòng mới tại TP HCM đánh dấu bước phát triển mới của MayTrip. Với mục tiêu ưu tiên trải nghiệm khách hàng, đơn vị hy vọng nhận được sự ủng hộ từ khách hàng để trở thành công ty lữ hành hàng đầu, hướng mục tiêu thương hiệu toàn cầu vào năm 2030. Ngoài TP HCM, MayTrip còn có văn phòng tại Hải Phòng và TP Vinh. Các văn phòng này giúp MayTrip dễ dàng tiếp cận và đáp ứng nhu cầu đa dạng của khách hàng. Công ty cam kết đảm bảo chất lượng dịch vụ để mang lại chuyến đi an toàn, trọn vẹn cho khách hàng. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MayTrip khai trương văn phòng mới tại 833 Lê Hồng Phong, quận 10 (TP HCM), với ưu đãi và tour Hokkaido dịp Tết Nguyên đán. Công ty đặt mục tiêu trở thành công ty lữ hành hàng đầu toàn cầu vào năm 2030, cam kết chất lượng dịch vụ an toàn cho khách.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{
+  "id": 4,
+  "style": "news_brief",
+  "article": "Văn phòng mới của MayTrip tại địa chỉ 833 Lê Hồng Phong, quận 10, nhằm mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Văn phòng mới được kỳ vọng là điểm đến thuận tiện cho khách hàng trong việc tìm hiểu và sử dụng dịch vụ của công ty. Trong ngày khai trương, MayTrip trao tặng nhiều quà tặng và ưu đãi cho khách tham dự. Các voucher gồm: 2 triệu đồng cho khách đăng ký tour Bắc Á trong ba ngày khai trương, 1 triệu đồng cho tour Đông Nam Á trong ba tháng từ ngày khai trương, 500.000 đồng cho dịch vụ tour nội địa trong một năm, 200.000 đồng dịch vụ đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và 100.000 đồng với dịch vụ vé máy bay trong 6 tháng. Buổi lễ khai trương văn phòng tại Sài Gòn còn giới thiệu các chương trìnhtour Nhật Bảndịp Tết Âm lịch như cung đường vàng trải nghiệm trượt tuyết, Hokkaido - miền tuyết trắng. Những chuyến đi này được MayTrip thiết kế kỹ lưỡng, phù hợp với không khí đón xuân cho gia đình và cặp đôi Việt trong dịp Tết Nguyên đán. Năm nay, MayTrip xác định tour Hokkaido là sản phẩm 'đinh' trong dịp Tết Nguyên đán. Hokkaido nằm ở miền Bắc Nhật Bản, nổi tiếng với những đợt tuyết dày và phong cảnh mùa đông đặc trưng. Tour Hokkaido dịp Tết là hành trình lý tưởng để du khách tận hưởng kỳ nghỉ theo cách mới mẻ và ấn tượng trong tuyết trắng. Bên cạnh đó, tour Hokkaido của MayTrip cũng mang đến trải nghiệm suối nước nóng onsen giữa băng tuyết, giúp du khách thư giãn sau những hoạt động trong ngày. Bên cạnh đó, MayTrip cũng cung cấp các tour du lịch khác với lịch khởi hành linh hoạt kéo dài đến hết năm 2025, gồm hành trình ngắm hoa anh đào, hoa mơ, mận và nghỉ lễ 30/4 và 1/5. Các hành trình này dựa trên xu hướng và sở thích của du khách Việt Nam. Theo đại diện công ty, sự kiện khai trương văn phòng mới tại TP HCM đánh dấu bước phát triển mới của MayTrip. Với mục tiêu ưu tiên trải nghiệm khách hàng, đơn vị hy vọng nhận được sự ủng hộ từ khách hàng để trở thành công ty lữ hành hàng đầu, hướng mục tiêu thương hiệu toàn cầu vào năm 2030. Ngoài TP HCM, MayTrip còn có văn phòng tại Hải Phòng và TP Vinh. Các văn phòng này giúp MayTrip dễ dàng tiếp cận và đáp ứng nhu cầu đa dạng của khách hàng. Công ty cam kết đảm bảo chất lượng dịch vụ để mang lại chuyến đi an toàn, trọn vẹn cho khách hàng. Thanh Thư",
+  "summary": "MayTrip khai trương văn phòng mới tại 833 Lê Hồng Phong, quận 10 (TP HCM), với ưu đãi và tour Hokkaido dịp Tết Nguyên đán. Công ty đặt mục tiêu trở thành công ty lữ hành hàng đầu toàn cầu vào năm 2030, cam kết chất lượng dịch vụ an toàn cho khách.",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, nhưng có thể thêm chi tiết về các ưu đãi và tour du lịch để tăng tính trung thực",
+  "relevance_score": 0.8,
+  "relevance_reason": "Bản tóm tắt bao gồm các ý chính quan trọng, nhưng có thể bỏ sót thông điệp cốt lõi về mục tiêu của công ty và các văn phòng khác",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, nhưng có thể rút gọn một số chi tiết để tăng tính súc tích"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ngày 29/10, tại Khu du lịch Sun World Fansipan Legend, Hiệp hội Du lịch tỉnh Lào Cai công bố chương trình kích cầu du lịch lớn nhất năm với chủ đề 'Chạm Sa Pa - Chạm những tầng mây', diễn ra từ 2/11 đến 30/12. Trong thời gian này, 130 doanh nghiệp tại Sa Pa sẽ cung cấp nhiều ưu đãi lên đến 50% và cam kết đảm bảo chất lượng dịch vụ. Theo đó, Công ty Cáp treo Fansipan Sa Pa (Khu du lịch Sun World Fansipan Legend) áp dụng đồng giá vé cáp treo hai chiều Fansipan chỉ còn 550.000 đồng cho du khách Việt Nam. Mức giá này giảm 30% so với giá gốc. Du khách có thể khám phá đỉnh Fansipan, chiêm ngưỡng kiến trúc tâm linh và tham gia các hoạt động văn hóa của 7 dân tộc thiểu số Tây Bắc tại Bản Mây. Nhiều điểm du lịch khác tại Sa Pa cũng miễn phí vé tham quan và cung cấp ưu đãi hấp dẫn. Trong đó, vườn đá Tả Phìn và vườn hồng Mộng Mơ miễn phí vé, Khu du lịch Cát Cát miễn phí trải nghiệm ẩm thực Tây Bắc cùng các hoạt động vẽ sáp ong, xe lanh, dệt vải... với bà con dân bản. Các khách sạn như Chaulong Sapa, Amazing Sapa, Vườn Sa Pa, Arista Sa Pa và Le Bordeaux Sapa áp dụng giảm giá phòng trực tiếp tới 50%. Hotel de la Coupole và Lady Hill Sapa Resort có nhiều ưu đãi về dịch vụ ăn uống, spa. Một số nhà xe như Inter Bus Lines và Eco Sa Pa cũng giảm giá vé xe khứ hồi đến 30%, cung cấp đa dạng hình thức di chuyển từ xe limousine đến xe lớn. Ông Phạm Cao Vỹ, đại diện Hiệp hội Du lịch tỉnh Lào Cai nhấn mạnh sự cần thiết của việc kích cầu du lịch để phục hồi ngành sau ảnh hưởng nặng nề của bão lũ. Ông kêu gọi tất cả doanh nghiệp du lịch trên địa bàn tham gia nhằm tạo sức bật cho du lịch Sa Pa phát triển mạnh mẽ vào giai đoạn cuối năm 2024. Ông Nguyễn Xuân Chiến, Phó chủ tịch Sun Group Vùng Miền Bắc, cho biết trước đây chương trình kích cầu 'Đến Sa Pa - Bay giữa mùa hoa' thành công ngoài mong đợi. 'Lần này, thông qua chính sách ưu đãi sâu, chúng tôi hy vọng thu hút đông đảo du khách đến Sa Pa để khám phá vẻ đẹp độc đáo của mùa mây', ông Chiến nói. Ngoài chính sách ưu đãi sâu, tỉnh Lào Cai và thị xã Sa Pa tổ chức nhiều sự kiện văn hóa đặc sắc nhằm mang đến trải nghiệm độc đáo cho du khách. Các hoạt động bao gồm lễ hội truyền thống, triển lãm nghệ thuật, thể thao và giải trí. Đặc biệt là sự kiện ánh sáng 3D Mapping và lễ hội hoa sen đá lần đầu tiên được tổ chức tại Sun World Fansipan Legend. Sa Pa đang trong mùa mây - thời điểm lý tưởng để vui chơi ngoài trời. Ban tổ chức kỳ vọng chương trình kích cầu sẽ tăng sức hút của Sa Pa và củng cố vị thế là điểm đến hàng đầu miền Bắc. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{
+  "id": 5,
+  "style": "news_brief",
+  "article": "Ngày 29/10, tại Khu du lịch Sun World Fansipan Legend, Hiệp hội Du lịch tỉnh Lào Cai công bố chương trình kích cầu du lịch lớn nhất năm với chủ đề 'Chạm Sa Pa - Chạm những tầng mây', diễn ra từ 2/11 đến 30/12. Trong thời gian này, 130 doanh nghiệp tại Sa Pa sẽ cung cấp nhiều ưu đãi lên đến 50% và cam kết đảm bảo chất lượng dịch vụ. Theo đó, Công ty Cáp treo Fansipan Sa Pa (Khu du lịch Sun World Fansipan Legend) áp dụng đồng giá vé cáp treo hai chiều Fansipan chỉ còn 550.000 đồng cho du khách Việt Nam. Mức giá này giảm 30% so với giá gốc. Du khách có thể khám phá đỉnh Fansipan, chiêm ngưỡng kiến trúc tâm linh và tham gia các hoạt động văn hóa của 7 dân tộc thiểu số Tây Bắc tại Bản Mây. Nhiều điểm du lịch khác tại Sa Pa cũng miễn phí vé tham quan và cung cấp ưu đãi hấp dẫn. Trong đó, vườn đá Tả Phìn và vườn hồng Mộng Mơ miễn phí vé, Khu du lịch Cát Cát miễn phí trải nghiệm ẩm thực Tây Bắc cùng các hoạt động vẽ sáp ong, xe lanh, dệt vải... với bà con dân bản. Các khách sạn như Chaulong Sapa, Amazing Sapa, Vườn Sa Pa, Arista Sa Pa và Le Bordeaux Sapa áp dụng giảm giá phòng trực tiếp tới 50%. Hotel de la Coupole và Lady Hill Sapa Resort có nhiều ưu đãi về dịch vụ ăn uống, spa. Một số nhà xe như Inter Bus Lines và Eco Sa Pa cũng giảm giá vé xe khứ hồi đến 30%, cung cấp đa dạng hình thức di chuyển từ xe limousine đến xe lớn. Ông Phạm Cao Vỹ, đại diện Hiệp hội Du lịch tỉnh Lào Cai nhấn mạnh sự cần thiết của việc kích cầu du lịch để phục hồi ngành sau ảnh hưởng nặng nề của bão lũ. Ông kêu gọi tất cả doanh nghiệp du lịch trên địa bàn tham gia nhằm tạo sức bật cho du lịch Sa Pa phát triển mạnh mẽ vào giai đoạn cuối năm 2024. Ông Nguyễn Xuân Chiến, Phó chủ tịch Sun Group Vùng Miền Bắc, cho biết trước đây chương trình kích cầu 'Đến Sa Pa - Bay giữa mùa hoa' thành công ngoài mong đợi. 'Lần này, thông qua chính sách ưu đãi sâu, chúng tôi hy vọng thu hút đông đảo du khách đến Sa Pa để khám phá vẻ đẹp độc đáo của mùa mây', ông Chiến nói. Ngoài chính sách ưu đãi sâu, tỉnh Lào Cai và thị xã Sa Pa tổ chức nhiều sự kiện văn hóa đặc sắc nhằm mang đến trải nghiệm độc đáo cho du khách. Các hoạt động bao gồm lễ hội truyền thống, triển lãm nghệ thuật, thể thao và giải trí. Đặc biệt là sự kiện ánh sáng 3D Mapping và lễ hội hoa sen đá lần đầu tiên được tổ chức tại Sun World Fansipan Legend. Sa Pa đang trong mùa mây - thời điểm lý tưởng để vui chơi ngoài trời. Ban tổ chức kỳ vọng chương trình kích cầu sẽ tăng sức hút của Sa Pa và củng cố vị thế là điểm đến hàng đầu miền Bắc. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 1.0,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, không sai số liệu và không xuyên tạc ý nghĩa của văn bản gốc.",
+  "relevance_score": 1.0,
+  "relevance_reason": "Bản tóm tắt bao hàm đủ các ý chính quan trọng nhất, không bỏ sót thông điệp cốt lõi nào.",
+  "coherence_conciseness_score": 1.0,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic, dễ đọc và loại bỏ được các chi tiết rườm rà/lặp từ không."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brisbane nằm phía đông nam bang Queensland, là thành phố lớn thứ ba tại Australia. Do gần đường xích đạo, khí hậu nơi đây ôn hòa, quanh năm nắng ấm. Trung tâm Brisbane không chỉ có những khối bê tông, khu mua sắm, mà còn bao phủ bởi mảng xanh, với 5 công viên và vườn thực vật nổi tiếng. Dưới đây là 5 điểm đến hút du khách ở Brisbane. South Bank Parklands Nằm bên bờ sông Brisbane, South Bank Parklands được ví như 'ốc đảo xanh' giữa lòng thành phố sôi động, nổi bật với rừng mưa nhiệt đới và loạt hoạt động giải trí cho mọi lứa tuổi. Ngay cửa ngõ công viên là thảm cỏ, hàng cây rợp bóng và vườn hoa. Nhiều người dân thường picnic, dã ngoại, vui chơi tại bãi biển nhân tạo Streets Beach, River Quay Green, Rainforest Green hay Liana Lounge. Ngoài ra, Wheel of Brisbane - vòng đu quay cao tới 60 m - là biểu tượng tại South Bank Parklands, dễ dàng ngắm toàn cảnh Brisbane từ trên cao. Roma Street Parkland Nằm cạnh ga xe lửa Roma Street, công viên cùng tên cũng được người dân lẫn du khách gọi là 'ốc đảo xanh mát' giữa Brisbane, ghi dấu với những khu vườn và bãi cỏ rộng lớn. Tại đây, du khách hòa mình vào khu vườn Spectacle - nơi trồng hàng nghìn gốc violets, cẩm chướng, delphiniums và foxgloves. Khí hậu ôn hòa thu hút chim kookaburras, gà lôi, vẹt. Bạn cũng có thể tổ chức tiệc BBQ ngoài trời, cho con khám phá công viên trẻ em. Brisbane City Botanic Gardens Nằm trên trục đường Alice, Brisbane City Botanic Gardens bảo tồn hàng nghìn loài thực vật quý hiếm, nổi bật với vẻ nguyên sơ. Khu vườn này là một trong những điểm đến lý tưởng cho người chuộng nét thanh bình giữa lòng đô thị. Tại đây, du khách có thể khám phá con đường dạo bộ ven sông, chiêm ngưỡng rặng thông Bunya được trồng từ năm 1858. Điểm đến tiếp theo là Bamboo Grove - con đường tre rợp mát, được ví như 'khu rừng xa xôi giữa thành phố hiện đại'. Vườn bách thảo tổ chức sự kiện quanh năm như biểu diễn Riverstage, lễ hội đa văn hóa, trưng bày nghệ thuật cùng hoạt động cộng đồng miễn phí. Trong đó, chợ Riverside Sunday Market hút hàng nghìn du khách nhờ gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden Tại Epicurious, du khách có thể khám phá ẩm thực bang Queensland đa dạng, nhất là rau, củ, quả, thảo mộc hữu cơ theo mùa. 14 chuyên viên tình nguyện chăm sóc khu vườn kỹ lưỡng, mong truyền cảm hứng cho người yêu nấu ăn và trồng trọt. 'Tới Epicurious, tôi và bạn bè được hướng dẫn cách chăm sóc rau củ, trái cây, thảo mộc và thưởng thức miễn phí', một du khách viết trên Facebook, nhận hàng trăm nghìn lượt thích. Mount Coot-tha Botanic Gardens Mở cửa đón khách từ năm 1976, Mount Coot-tha Botanic Gardens tọa lạc chân núi Coot-tha, là vườn thực vật nhiệt đới hàng đầu Brisbane, diện tích đến 56 ha. Dạo quanh khu vườn, du khách có thể chiêm ngưỡng hoa xuân, các loài cây nhiệt đới và khu thảo dược. Nơi đây là điểm đến quen thuộc của người yêu thiên nhiên, picnic, mê hoạt động thể chất, với đường chạy bộ thoáng đãng. Để khám phá thành thủ phủ bang Queensland, bạn có thể chọn đường bay thẳng từ TP HCM đến Brisbane của Vietjet, với 9 giờ trên máy bay thân rộng, thoải mái cùng loạt dịch vụ tiện ích, ưu đãi như: bảo hiểm Sky Care miễn phí, chương trình tích điểm SkyJoy, đổi quà từ hơn 250 thương hiệu lớn toàn cầu. Trước đó ngày14-15/9, Vietjet đồng hành lễ hội thả diều Vietjet Redcliffe KiteFest tại Redcliffe, Queensland. Hãng hàng không Việt còn áp dụng nhiều chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu. Đông Vệ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brisbane, thành phố lớn thứ ba của Australia với khí hậu ôn hòa quanh năm. Thành phố có nhiều công viên và vườn thực vật nổi tiếng như South Bank Parklands, Roma Street Parkland và Brisbane City Botanic Gardens bảo tồn hàng nghìn loài cây quý hiếm trên trục đường Alice. Hội chợ Riverside Sunday Market hút du khách với gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden giới thiệu ẩm thực Queensland đa dạng. Mount Coot-tha Botanic Gardens nằm trên núi Coot-tha, là vườn thực vật lớn của Brisbane. Vietjet cung cấp đường bay thẳng TP HCM - Brisbane với nhiều dịch vụ tiện ích và chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{
+  "id": 6,
+  "style": "news_brief",
+  "article": "Brisbane nằm phía đông nam bang Queensland, là thành phố lớn thứ ba tại Australia. Do gần đường xích đạo, khí hậu nơi đây ôn hòa, quanh năm nắng ấm. Trung tâm Brisbane không chỉ có những khối bê tông, khu mua sắm, mà còn bao phủ bởi mảng xanh, với 5 công viên và vườn thực vật nổi tiếng. Dưới đây là 5 điểm đến hút du khách ở Brisbane. South Bank Parklands Nằm bên bờ sông Brisbane, South Bank Parklands được ví như 'ốc đảo xanh' giữa lòng thành phố sôi động, nổi bật với rừng mưa nhiệt đới và loạt hoạt động giải trí cho mọi lứa tuổi. Ngay cửa ngõ công viên là thảm cỏ, hàng cây rợp bóng và vườn hoa. Nhiều người dân thường picnic, dã ngoại, vui chơi tại bãi biển nhân tạo Streets Beach, River Quay Green, Rainforest Green hay Liana Lounge. Ngoài ra, Wheel of Brisbane - vòng đu quay cao tới 60 m - là biểu tượng tại South Bank Parklands, dễ dàng ngắm toàn cảnh Brisbane từ trên cao. Roma Street Parkland Nằm cạnh ga xe lửa Roma Street, công viên cùng tên cũng được người dân lẫn du khách gọi là 'ốc đảo xanh mát' giữa Brisbane, ghi dấu với những khu vườn và bãi cỏ rộng lớn. Tại đây, du khách hòa mình vào khu vườn Spectacle - nơi trồng hàng nghìn gốc violets, cẩm chướng, delphiniums và foxgloves. Khí hậu ôn hòa thu hút chim kookaburras, gà lôi, vẹt. Bạn cũng có thể tổ chức tiệc BBQ ngoài trời, cho con khám phá công viên trẻ em. Brisbane City Botanic Gardens Nằm trên trục đường Alice, Brisbane City Botanic Gardens bảo tồn hàng nghìn loài thực vật quý hiếm, nổi bật với vẻ nguyên sơ. Khu vườn này là một trong những điểm đến lý tưởng cho người chuộng nét thanh bình giữa lòng đô thị. Tại đây, du khách có thể khám phá con đường dạo bộ ven sông, chiêm ngưỡng rặng thông Bunya được trồng từ năm 1858. Điểm đến tiếp theo là Bamboo Grove - con đường tre rợp mát, được ví như 'khu rừng xa xôi giữa thành phố hiện đại'. Vườn bách thảo tổ chức sự kiện quanh năm như biểu diễn Riverstage, lễ hội đa văn hóa, trưng bày nghệ thuật cùng hoạt động cộng đồng miễn phí. Trong đó, chợ Riverside Sunday Market hút hàng nghìn du khách nhờ gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden Tại Epicurious, du khách có thể khám phá ẩm thực bang Queensland đa dạng, nhất là rau, củ, quả, thảo mộc hữu cơ theo mùa. 14 chuyên viên tình nguyện chăm sóc khu vườn kỹ lưỡng, mong truyền cảm hứng cho người yêu nấu ăn và trồng trọt. 'Tới Epicurious, tôi và bạn bè được hướng dẫn cách chăm sóc rau củ, trái cây, thảo mộc và thưởng thức miễn phí', một du khách viết trên Facebook, nhận hàng trăm nghìn lượt thích. Mount Coot-tha Botanic Gardens Mở cửa đón khách từ năm 1976, Mount Coot-tha Botanic Gardens tọa lạc chân núi Coot-tha, là vườn thực vật nhiệt đới hàng đầu Brisbane, diện tích đến 56 ha. Dạo quanh khu vườn, du khách có thể chiêm ngưỡng hoa xuân, các loài cây nhiệt đới và khu thảo dược. Nơi đây là điểm đến quen thuộc của người yêu thiên nhiên, picnic, mê hoạt động thể chất, với đường chạy bộ thoáng đãng. Để khám phá thành thủ phủ bang Queensland, bạn có thể chọn đường bay thẳng từ TP HCM đến Brisbane của Vietjet, với 9 giờ trên máy bay thân rộng, thoải mái cùng loạt dịch vụ tiện ích, ưu đãi như: bảo hiểm Sky Care miễn phí, chương trình tích điểm SkyJoy, đổi quà từ hơn 250 thương hiệu lớn toàn cầu. Trước đó ngày14-15/9, Vietjet đồng hành lễ hội thả diều Vietjet Redcliffe KiteFest tại Redcliffe, Queensland. Hãng hàng không Việt còn áp dụng nhiều chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu. Đông Vệ",
+  "summary": "Brisbane, thành phố lớn thứ ba của Australia với khí hậu ôn hòa quanh năm. Thành phố có nhiều công viên và vườn thực vật nổi tiếng như South Bank Parklands, Roma Street Parkland và Brisbane City Botanic Gardens bảo tồn hàng nghìn loài cây quý hiếm trên trục đường Alice. Hội chợ Riverside Sunday Market hút du khách với gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden giới thiệu ẩm thực Queensland đa dạng. Mount Coot-tha Botanic Gardens nằm trên núi Coot-tha, là vườn thực vật lớn của Brisbane. Vietjet cung cấp đường bay thẳng TP HCM - Brisbane với nhiều dịch vụ tiện ích và chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng có bỏ sót một số chi tiết quan trọng như mô tả cụ thể về các hoạt động giải trí tại South Bank Parklands và Roma Street Parkland",
+  "relevance_score": 0.9,
+  "relevance_reason": "Bản tóm tắt bao hàm đủ các ý chính quan trọng nhất về các điểm đến hút du khách ở Brisbane, tuy nhiên có thể thêm thông tin về các sự kiện và hoạt động tại các công viên",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Bản tóm tắt có logic và dễ đọc nhưng có thể cải thiện bằng cách loại bỏ các từ ngữ lặp từ và sắp xếp lại cấu trúc câu cho rõ ràng hơn"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Công ty du lịch NhatbanAZ mở bán chùm tour Nhật Bản khởi hành dịp Tết Dương lịch và Âm lịch từ đầu tháng 10. Trong đó, các tour truyền thống đến Osaka, Kyoto và Tokyo được làm mới bằng những hoạt động phù hợp với mùa đông xuân như trượt tuyết tại Fujiten Resort, ngắm tuyết làng cổ Oshino Hakkai và tham gia lễ hội ánh sáng Nabana no sato. NhatbanAZ cũng mở rộng các cung đường mới cho du khách trải nghiệm trong dịp Tết 2025. Cụ thể, tour Hokkaido gồm Asahikawa, Monbetsu và Sapporo với giá 55,9 triệu đồng mỗi khách. Du khách sẽ tham gia câu cá trên băng, đi tàu phá băng và thưởng thức bia hơi tại Sapporo, cùng dịch vụ hàng không 5 sao và lưu trú khách sạn 4 sao quốc tế. Tour thứ hai là chuyến thăm làng cổ Shirakawago, núi Phú Sĩ và Tokyo trong 6 ngày 5 đêm với giá 31,9 triệu đồng mỗi khách. Du khách sẽ được chiêm ngưỡng tuyết trắng tại Shirakawago, một Di sản Văn hóa Thế giới của UNESCO từ năm 1995. Tour cũng gồm tham quan lâu đài Matsumoto - di tích bảo vật quốc gia của Nhật Bản và trải nghiệm trượt tuyết tại Fujiten Snow Resort - top 3 khu trượt tuyết nổi tiếng. Bà Hồ Như Thảo, Giám đốc Điều hành NhatbanAZ Văn phòng TP HCM cho biết sản phẩm mới này nhận được sự quan tâm lớn từ du khách, đặc biệt là những người từng đi Nhật và muốn trở lại với hành trình mới. Khu vực Hokkaido được biết đến với tuyết rơi dày đặc hơn Tokyo hay Osaka, nên lịch khởi hành tour Hokkaido dịp Tết Âm lịch nhận được nhiều đăng ký giữ chỗ. Trong dịp Tết Nguyên đán 2025, NhatbanAZ cung cấp các hành trình từ 5 đến 6 ngày với mức giá cơ bản đến cao cấp, khoảng 31,9 - 55,9 triệu đồng mỗi khách để đáp ứng nhu cầu đa dạng. Giá tour Tết có phần chênh lệch so với ngày thường và tăng so với cùng kỳ năm trước. Do đó, NhatbanAZ chủ động gặp gỡ và làm việc với các đối tác cung cấp dịch vụ, từ đó xây dựng chương trình, đưa ra chính sách ưu đãi tốt nhất cho khách hàng. Với kinh nghiệm hơn 15 năm trong ngành du lịch chuyên thị trường Nhật Bản, NhatbanAZ thuộc danh sách công ty chỉ định nộp visa bởi Đại sứ quán Nhật Bản đề xuất. Đồng thời là đối tác chiến lược của các hãng hàng không, khách sạn và đối tác land tour uy tín tại Nhật Bản. Công ty cũng là nhà tư vấn và tổ chức những chuyến Famtrip kết nối các công ty du lịch Việt Nam tới tham quan xúc tiến đầu tư, hợp tác tại Nhật Bản. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{
+  "id": 7,
+  "style": "news_brief",
+  "article": "Công ty du lịch NhatbanAZ mở bán chùm tour Nhật Bản khởi hành dịp Tết Dương lịch và Âm lịch từ đầu tháng 10. Trong đó, các tour truyền thống đến Osaka, Kyoto và Tokyo được làm mới bằng những hoạt động phù hợp với mùa đông xuân như trượt tuyết tại Fujiten Resort, ngắm tuyết làng cổ Oshino Hakkai và tham gia lễ hội ánh sáng Nabana no sato. NhatbanAZ cũng mở rộng các cung đường mới cho du khách trải nghiệm trong dịp Tết 2025. Cụ thể, tour Hokkaido gồm Asahikawa, Monbetsu và Sapporo với giá 55,9 triệu đồng mỗi khách. Du khách sẽ tham gia câu cá trên băng, đi tàu phá băng và thưởng thức bia hơi tại Sapporo, cùng dịch vụ hàng không 5 sao và lưu trú khách sạn 4 sao quốc tế. Tour thứ hai là chuyến thăm làng cổ Shirakawago, núi Phú Sĩ và Tokyo trong 6 ngày 5 đêm với giá 31,9 triệu đồng mỗi khách. Du khách sẽ được chiêm ngưỡng tuyết trắng tại Shirakawago, một Di sản Văn hóa Thế giới của UNESCO từ năm 1995. Tour cũng gồm tham quan lâu đài Matsumoto - di tích bảo vật quốc gia của Nhật Bản và trải nghiệm trượt tuyết tại Fujiten Snow Resort - top 3 khu trượt tuyết nổi tiếng. Bà Hồ Như Thảo, Giám đốc Điều hành NhatbanAZ Văn phòng TP HCM cho biết sản phẩm mới này nhận được sự quan tâm lớn từ du khách, đặc biệt là những người từng đi Nhật và muốn trở lại với hành trình mới. Khu vực Hokkaido được biết đến với tuyết rơi dày đặc hơn Tokyo hay Osaka, nên lịch khởi hành tour Hokkaido dịp Tết Âm lịch nhận được nhiều đăng ký giữ chỗ. Trong dịp Tết Nguyên đán 2025, NhatbanAZ cung cấp các hành trình từ 5 đến 6 ngày với mức giá cơ bản đến cao cấp, khoảng 31,9 - 55,9 triệu đồng mỗi khách để đáp ứng nhu cầu đa dạng. Giá tour Tết có phần chênh lệch so với ngày thường và tăng so với cùng kỳ năm trước. Do đó, NhatbanAZ chủ động gặp gỡ và làm việc với các đối tác cung cấp dịch vụ, từ đó xây dựng chương trình, đưa ra chính sách ưu đãi tốt nhất cho khách hàng. Với kinh nghiệm hơn 15 năm trong ngành du lịch chuyên thị trường Nhật Bản, NhatbanAZ thuộc danh sách công ty chỉ định nộp visa bởi Đại sứ quán Nhật Bản đề xuất. Đồng thời là đối tác chiến lược của các hãng hàng không, khách sạn và đối tác land tour uy tín tại Nhật Bản. Công ty cũng là nhà tư vấn và tổ chức những chuyến Famtrip kết nối các công ty du lịch Việt Nam tới tham quan xúc tiến đầu tư, hợp tác tại Nhật Bản. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 1.0,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, sai số liệu, hay xuyên tạc ý nghĩa của văn bản gốc",
+  "relevance_score": 1.0,
+  "relevance_reason": "Bản tóm tắt bao hàm đủ các ý chính quan trọng nhất và không bỏ sót thông điệp cốt lõi nào",
+  "coherence_conciseness_score": 1.0,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic, dễ đọc và loại bỏ được các chi tiết rườm rà/lặp từ không"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Theo bảng xếp hạng 20 quốc gia tốt nhất thế giới năm 2024 (The Best Countries in the World) do tạp chí du lịch Mỹ Condé Nast Traveler công bố vào tháng 10, Việt Nam ở vị trí 15 với 89 điểm. Một điểm đến khác thuộc Đông Nam Á có mặt trong danh sách này là Thái Lan, xếp thứ ba với 92,29 điểm. Đứng đầu top 20 là Nhật Bản với 95,32 điểm. Xếp hạng nằm trong giải thưởng thường niênReaders' Choice Awards của tạp chí Mỹ, dựa trên đánh giá của hơn 575.000 độc giả về các trải nghiệm du lịch ở mỗi quốc gia, xét theo các tiêu chí văn hóa, cảnh quan, dịch vụ du lịch và cơ sở hạ tầng. Độc giả của Condé Nast Traveler nhận xét Việt Nam thu hút du khách nhờ vẻ đẹp mộc mạc và quyến rũ. 'Với lượng khách nước ngoài đang trên đà tăng từ 2019 đến nay, Việt Nam không còn là điểm đến đáng chú ý mà thành điểm đến đáng ghé thăm', biên tập tờ Condé Nast Traveler viết. Theo số liệu từ Tổng cục Thống kê, trong 9 tháng đầu năm, Việt Nam đón hơn 12,7 triệu lượt khách quốc tế, vượt lượng khách cả năm 2023 là 12,6 triệu lượt. Lượng khách quốc tế đến Việt Nam tăng trưởng tích cực 9 tháng đầu năm 2024, với một số thị trường phục hồi hoàn toàn, tăng mạnh so với 2019, theo Cục Du lịch Quốc gia. Cục cũng dự đoán với đà tăng trường như hiện nay, Việt Nam sẽ hoàn thành mục tiêu đón 17-18 triệu lượt khách quốc tế năm 2024. Thái Lan được tạp chí Mỹ nhận xét là quốc gia đa dạng cảnh quan, giao thông thuận tiện với nhiều tàu thuyền, xe buýt đêm và chuyến bay nội địa giá rẻ. Ẩm thực cũng là điểm sáng của xứ chùa Vàng khi có nhiều khu chợ đêm nhộn nhịp, bày bán đặc sản địa phương. 8 tháng đầu năm 2024, Thái Lan đón hơn 20 triệu lượt khách quốc tế, tăng 34% so với cùng kỳ năm trước. Quốc gia này đặt mục tiêu đón ít nhất 36-37 triệu lượt khách nước ngoài trong cả năm nay, kỳ vọng thu về khoảng 3.500 tỷ baht (95,5 tỷ USD). Condé Nast Traveler là tạp chí du lịch nổi tiếng toàn cầu, ra mắt vào năm 1987. Các bảng xếp hạng của Condé Nast Traveler như Readers' Choice Awards được chuyên gia du lịch đánh giá là uy tín vì dựa trên ý kiến từ hàng triệu độc giả quốc tế. Bích Phương(TheoCNTraveller)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>LỖI: 'NoneType' object is not iterable</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{
-  "id": 1,
-  "style": "news_brief",
-  "article": "Taste Studio do thương hiệu Regent Hotels &amp; Resorts tổ chức nhằm mang đến trải nghiệm đa giác quan qua ẩm thực và nghệ thuật. Sự kiện này quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, từ nhà thiết kế thời trang đến nhạc sĩ, kết hợp cùng các thương hiệu hàng đầu như Vietnam Airlines. Sự kiện hướng đến phân khúc khách hàng sang trọng. Mùa một và hai diễn ra lần được vào tháng 4, tháng 11 năm ngoái. Taste Studio năm nay với chủ đề 'Dáng hình của biển', giới hạn 20 khách mời mỗi tối. Các khách mời được tham gia vào chuỗi khám phá gồm 7 chương đặc sắc về vẻ đẹp của biển, qua lăng kính nghệ sĩ tài hoa Mr. Dripping - nghệ sĩ vẽ tranh bằng phương pháp nhỏ giọt (drip art). Không gian nhà hàng, nơi diễn ra sự kiện với nội thất dùng tre, mây và tầm vông do kiến trúc sư Nguyễn Trung Nghĩa thiết kế. Ngoài hai nghệ sĩ này, Taste Studio còn có sự tham gia của bếp trưởng Francesco đến từ Milan, với 20 năm kinh nghiệm làm việc tại các khách sạn danh tiếng thế giới, đang bắt đầu hành trình mới tại Việt Nam. Ông đảm nhận vai trò cố vấn ẩm thực tại Regent Phú Quốc, mang đến trải nghiệm độc đáo cho thực khách. Bên cạnh đó, phó bếp trưởng điều hành Huân Trần tại chương trình mong muốn chinh phục các hương vị vùng miền khác nhau. Được nếm nhiều nguyên liệu địa phương và các loại gia vị đặc biệt, vị đầu bếp để lại điểm nhấn riêng trong cách giữ gìn, nâng tầm phong vị của quê hương tại Regent Phú Quốc. Chương trình có sự góp mặt của bếp trưởng nhà hàng Oku - Andy Huỳnh. Trước khi gia nhập Regent Phú Quốc, anh phát triển kỹ thuật nấu ăn Nhật Bản tại Nobu, San Diego và Nassau. Các món ăn của Andy luôn mang ý nghĩa hướng về cội nguồn. Bếp trưởng nhà hàng Ocean Club Daniel và bếp trưởng Duyến Nguyễn của khu nghỉ dưỡng này cũng tham gia, sáng tạo một số hương vị độc đáo từ nguyên liệu địa phương. Đại diện Regent Phú Quốc cho biết, thông qua Taste Studio, đơn vị mong muốn tiếp tục kiến tạo trải nghiệm đưa nét bản địa đặc sắc của Việt Nam lên bản đồ thế giới, từ đó chinh phục khách hàng hạng sang và giới chuyên gia. Thanh Thư",
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{
+  "id": 8,
+  "style": "news_brief",
+  "article": "Theo bảng xếp hạng 20 quốc gia tốt nhất thế giới năm 2024 (The Best Countries in the World) do tạp chí du lịch Mỹ Condé Nast Traveler công bố vào tháng 10, Việt Nam ở vị trí 15 với 89 điểm. Một điểm đến khác thuộc Đông Nam Á có mặt trong danh sách này là Thái Lan, xếp thứ ba với 92,29 điểm. Đứng đầu top 20 là Nhật Bản với 95,32 điểm. Xếp hạng nằm trong giải thưởng thường niênReaders' Choice Awards của tạp chí Mỹ, dựa trên đánh giá của hơn 575.000 độc giả về các trải nghiệm du lịch ở mỗi quốc gia, xét theo các tiêu chí văn hóa, cảnh quan, dịch vụ du lịch và cơ sở hạ tầng. Độc giả của Condé Nast Traveler nhận xét Việt Nam thu hút du khách nhờ vẻ đẹp mộc mạc và quyến rũ. 'Với lượng khách nước ngoài đang trên đà tăng từ 2019 đến nay, Việt Nam không còn là điểm đến đáng chú ý mà thành điểm đến đáng ghé thăm', biên tập tờ Condé Nast Traveler viết. Theo số liệu từ Tổng cục Thống kê, trong 9 tháng đầu năm, Việt Nam đón hơn 12,7 triệu lượt khách quốc tế, vượt lượng khách cả năm 2023 là 12,6 triệu lượt. Lượng khách quốc tế đến Việt Nam tăng trưởng tích cực 9 tháng đầu năm 2024, với một số thị trường phục hồi hoàn toàn, tăng mạnh so với 2019, theo Cục Du lịch Quốc gia. Cục cũng dự đoán với đà tăng trường như hiện nay, Việt Nam sẽ hoàn thành mục tiêu đón 17-18 triệu lượt khách quốc tế năm 2024. Thái Lan được tạp chí Mỹ nhận xét là quốc gia đa dạng cảnh quan, giao thông thuận tiện với nhiều tàu thuyền, xe buýt đêm và chuyến bay nội địa giá rẻ. Ẩm thực cũng là điểm sáng của xứ chùa Vàng khi có nhiều khu chợ đêm nhộn nhịp, bày bán đặc sản địa phương. 8 tháng đầu năm 2024, Thái Lan đón hơn 20 triệu lượt khách quốc tế, tăng 34% so với cùng kỳ năm trước. Quốc gia này đặt mục tiêu đón ít nhất 36-37 triệu lượt khách nước ngoài trong cả năm nay, kỳ vọng thu về khoảng 3.500 tỷ baht (95,5 tỷ USD). Condé Nast Traveler là tạp chí du lịch nổi tiếng toàn cầu, ra mắt vào năm 1987. Các bảng xếp hạng của Condé Nast Traveler như Readers' Choice Awards được chuyên gia du lịch đánh giá là uy tín vì dựa trên ý kiến từ hàng triệu độc giả quốc tế. Bích Phương(TheoCNTraveller)",
   "summary": "LỖI: 'NoneType' object is not iterable",
   "faithfulness_score": 0.0,
-  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không phản ánh nội dung của sự kiện Taste Studio",
+  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin gì về văn bản gốc, không có nội dung để đánh giá tính trung thực.",
   "relevance_score": 0.0,
-  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào về sự kiện, không đề cập đến chủ đề, khách mời, hoặc mục đích của sự kiện",
+  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không thể đánh giá tính bao quát.",
   "coherence_conciseness_score": 0.0,
-  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá về tính mạch lạc và súc tích"
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hai giải thưởng gồm 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới'. Đây cũng là năm thứ tư liên tiếp đơn vị đạt giải thưởng này, sau quá trình thẩm định từ hội đồng chuyên môn toàn cầu và bình chọn bởi hàng nghìn du khách, khách sạn quốc tế khác. 'Giải thưởng góp phần khẳng định Amiana Resort Nha Trang là điểm đến lý tưởng cho du khách tìm kiếm không gian riêng tư, gần gũi thiên nhiên với kiến trúc cao cấp, mang lại trải nghiệm sang trọng, độc đáo', đại diện resort chia sẻ. Amiana có kiến trúc hòa hợp thiên nhiên, kết hợp yếu tố truyền thống và hiện đại, tạo nên không gian thư giãn, sang trọng nhưng vẫn giữ được cảm giác gần gũi, yên bình. Bãi biển riêng tư với hàng dừa rợp bóng xanh mát là nơi du khách có thể thư giãn, nghỉ ngơi thoải mái. Resort còn tận dụng địa hình tự nhiên để bố trí các công trình công cộng như hồ bơi, nhà hàng, phòng hội nghị, spa... Các yếu tố đậm chất nhiệt đới như dừa xanh, sóng biển, đá và gỗ được lồng ghép khéo léo trong từng chi tiết thiết kế nội ngoại thất. Biệt thự, phòng nghỉ, nhà hàng đều có sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại. Mỗi căn biệt thự đều mang kiến trúc mở, sử dụng nội thất chủ yếu từ gỗ, đá tự nhiên. Tất cả phòng đều có cửa sổ lớn và ban công rộng, tối ưu tầm nhìn hướng biển với cảnh quan thiên nhiên vây quanh. Biệt thự còn có hồ bơi riêng, không gian vườn với các loại cây nhiệt đới, đảm bảo yếu tố riêng tư cho khách hàng. Resort không chỉ chú trọng xây dựng công trình tiện ích, mà còn đặc biệt lưu ý việc bảo vệ môi trường, sử dụng các giải pháp bền vững. Những không gian xanh, vườn cây, hồ nước đều được bố trí hợp lý, tạo nên hệ sinh thái tự nhiên trong lòng khu nghỉ dưỡng. Theo đại diện Amiana Resort Nha Trang, những chi tiết kiến trúc thông minh cùng không gian mở, vật liệu tự nhiên, sự khéo léo trong thiết kế tại đây góp phần tạo nên khu nghỉ dưỡng lý tưởng cho những ai tìm kiếm sự an yên, lãng mạn và xa hoa. Á Hiên</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ, rộng hơn 300 ha. Nơi đây ngoài là điểm đến ngắm dòng Tiền Giang, đón gió sông mát dịu, còn là địa chỉ thu hút khách với bộ sưu tập gỗ lũa nội thất độc đáo của khu du lịch trên cồn. Gỗ lũa tức những thân cây khủng, vớt từ đáy sông, bên ngoài bị dòng nước bào mòn, chỉ còn phần lõi bền chắc. Hàng nghìn thân gỗ lũa được người chủ tuyển chọn làm vật liệu chính xây Khu du lịch sinh thái Cồn Én từ tiểu cảnh, nhà đến đài quan sát. Hơn 20 năm trước, ông Nguyễn Văn Nghỉ ở huyện Chợ Mới đã sưu tập rất nhiều gỗ lũa. Ban đầu ông trục vớt chúng để khơi thông dòng chảy, hạn chế tình trạng lưới đánh cá mắc vào thân cây. Lâu dần, ông yêu mến và muốn lưu giữ những thân gỗ trầm thủy này. Ba năm trước, ông Nghỉ dùng số gỗ lũa để xây khu du lịch ven sông Tiền rộng 6 ha. Đặc sắc trong các vật liệu từ gỗ lũa là bức tranh điêu khắc về phong cảnh làng quê Việt Nam xưa dài hơn 24 m, nặng 20 tấn. Bức tranh do nghệ nhân ở Huế thực hiện trong 7 năm, trên khúc gỗ trầm thủy khủng, tùy từng đoạn có chiều cao từ 1,5 - 1,8 m. Cạnh bức tranh là bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ như tứ quý, sảnh tiến tới của nhiều dòng xe nổi tiếng. Dọc các lối đi là những tiểu cảnh làm từ gỗ lũa. Một số được điêu khắc thành các con vật, chim muông. Những cây gỗ lũa kích thước lớn được tận dụng làm đài quan sát cao 26 m, hoặc móng trụ để xây nhà nghỉ, cầu vượt. Khuôn viên cũng được phủ bởi nhiều cây kiểng, dừa cùng dãy nhà sàn ven sông. Tại đây du khách được ngắm hoàng hôn trên sông, tắm sông và thưởng thức ẩm thực miền Tây. Chị Phúc Điền, du khách ở TP HCM, cho biết khá thích với khung cảnh miền Tây yên bình ở Cồn Én. Chị cũng bất ngờ với sự kỳ công của người đã sưu tập hàng nghìn thân gỗ lũa và biến chúng thành điểm tham quan độc đáo. Cồn Én, nằm cách TP HCM 170 km, du khách có thể đến đây từ hướng quốc lộ 30 của tỉnh Đồng Tháp hoặc lên phà Tấn Long vượt sông Tiền từ phía huyện Chợ Mới. Giá vé vào cổng là 80.000 đồng. Ngọc Tài</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Văn phòng mới của MayTrip tại địa chỉ 833 Lê Hồng Phong, quận 10, nhằm mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Văn phòng mới được kỳ vọng là điểm đến thuận tiện cho khách hàng trong việc tìm hiểu và sử dụng dịch vụ của công ty. Trong ngày khai trương, MayTrip trao tặng nhiều quà tặng và ưu đãi cho khách tham dự. Các voucher gồm: 2 triệu đồng cho khách đăng ký tour Bắc Á trong ba ngày khai trương, 1 triệu đồng cho tour Đông Nam Á trong ba tháng từ ngày khai trương, 500.000 đồng cho dịch vụ tour nội địa trong một năm, 200.000 đồng dịch vụ đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và 100.000 đồng với dịch vụ vé máy bay trong 6 tháng. Buổi lễ khai trương văn phòng tại Sài Gòn còn giới thiệu các chương trìnhtour Nhật Bảndịp Tết Âm lịch như cung đường vàng trải nghiệm trượt tuyết, Hokkaido - miền tuyết trắng. Những chuyến đi này được MayTrip thiết kế kỹ lưỡng, phù hợp với không khí đón xuân cho gia đình và cặp đôi Việt trong dịp Tết Nguyên đán. Năm nay, MayTrip xác định tour Hokkaido là sản phẩm 'đinh' trong dịp Tết Nguyên đán. Hokkaido nằm ở miền Bắc Nhật Bản, nổi tiếng với những đợt tuyết dày và phong cảnh mùa đông đặc trưng. Tour Hokkaido dịp Tết là hành trình lý tưởng để du khách tận hưởng kỳ nghỉ theo cách mới mẻ và ấn tượng trong tuyết trắng. Bên cạnh đó, tour Hokkaido của MayTrip cũng mang đến trải nghiệm suối nước nóng onsen giữa băng tuyết, giúp du khách thư giãn sau những hoạt động trong ngày. Bên cạnh đó, MayTrip cũng cung cấp các tour du lịch khác với lịch khởi hành linh hoạt kéo dài đến hết năm 2025, gồm hành trình ngắm hoa anh đào, hoa mơ, mận và nghỉ lễ 30/4 và 1/5. Các hành trình này dựa trên xu hướng và sở thích của du khách Việt Nam. Theo đại diện công ty, sự kiện khai trương văn phòng mới tại TP HCM đánh dấu bước phát triển mới của MayTrip. Với mục tiêu ưu tiên trải nghiệm khách hàng, đơn vị hy vọng nhận được sự ủng hộ từ khách hàng để trở thành công ty lữ hành hàng đầu, hướng mục tiêu thương hiệu toàn cầu vào năm 2030. Ngoài TP HCM, MayTrip còn có văn phòng tại Hải Phòng và TP Vinh. Các văn phòng này giúp MayTrip dễ dàng tiếp cận và đáp ứng nhu cầu đa dạng của khách hàng. Công ty cam kết đảm bảo chất lượng dịch vụ để mang lại chuyến đi an toàn, trọn vẹn cho khách hàng. Thanh Thư</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ngày 29/10, tại Khu du lịch Sun World Fansipan Legend, Hiệp hội Du lịch tỉnh Lào Cai công bố chương trình kích cầu du lịch lớn nhất năm với chủ đề 'Chạm Sa Pa - Chạm những tầng mây', diễn ra từ 2/11 đến 30/12. Trong thời gian này, 130 doanh nghiệp tại Sa Pa sẽ cung cấp nhiều ưu đãi lên đến 50% và cam kết đảm bảo chất lượng dịch vụ. Theo đó, Công ty Cáp treo Fansipan Sa Pa (Khu du lịch Sun World Fansipan Legend) áp dụng đồng giá vé cáp treo hai chiều Fansipan chỉ còn 550.000 đồng cho du khách Việt Nam. Mức giá này giảm 30% so với giá gốc. Du khách có thể khám phá đỉnh Fansipan, chiêm ngưỡng kiến trúc tâm linh và tham gia các hoạt động văn hóa của 7 dân tộc thiểu số Tây Bắc tại Bản Mây. Nhiều điểm du lịch khác tại Sa Pa cũng miễn phí vé tham quan và cung cấp ưu đãi hấp dẫn. Trong đó, vườn đá Tả Phìn và vườn hồng Mộng Mơ miễn phí vé, Khu du lịch Cát Cát miễn phí trải nghiệm ẩm thực Tây Bắc cùng các hoạt động vẽ sáp ong, xe lanh, dệt vải... với bà con dân bản. Các khách sạn như Chaulong Sapa, Amazing Sapa, Vườn Sa Pa, Arista Sa Pa và Le Bordeaux Sapa áp dụng giảm giá phòng trực tiếp tới 50%. Hotel de la Coupole và Lady Hill Sapa Resort có nhiều ưu đãi về dịch vụ ăn uống, spa. Một số nhà xe như Inter Bus Lines và Eco Sa Pa cũng giảm giá vé xe khứ hồi đến 30%, cung cấp đa dạng hình thức di chuyển từ xe limousine đến xe lớn. Ông Phạm Cao Vỹ, đại diện Hiệp hội Du lịch tỉnh Lào Cai nhấn mạnh sự cần thiết của việc kích cầu du lịch để phục hồi ngành sau ảnh hưởng nặng nề của bão lũ. Ông kêu gọi tất cả doanh nghiệp du lịch trên địa bàn tham gia nhằm tạo sức bật cho du lịch Sa Pa phát triển mạnh mẽ vào giai đoạn cuối năm 2024. Ông Nguyễn Xuân Chiến, Phó chủ tịch Sun Group Vùng Miền Bắc, cho biết trước đây chương trình kích cầu 'Đến Sa Pa - Bay giữa mùa hoa' thành công ngoài mong đợi. 'Lần này, thông qua chính sách ưu đãi sâu, chúng tôi hy vọng thu hút đông đảo du khách đến Sa Pa để khám phá vẻ đẹp độc đáo của mùa mây', ông Chiến nói. Ngoài chính sách ưu đãi sâu, tỉnh Lào Cai và thị xã Sa Pa tổ chức nhiều sự kiện văn hóa đặc sắc nhằm mang đến trải nghiệm độc đáo cho du khách. Các hoạt động bao gồm lễ hội truyền thống, triển lãm nghệ thuật, thể thao và giải trí. Đặc biệt là sự kiện ánh sáng 3D Mapping và lễ hội hoa sen đá lần đầu tiên được tổ chức tại Sun World Fansipan Legend. Sa Pa đang trong mùa mây - thời điểm lý tưởng để vui chơi ngoài trời. Ban tổ chức kỳ vọng chương trình kích cầu sẽ tăng sức hút của Sa Pa và củng cố vị thế là điểm đến hàng đầu miền Bắc. Thanh Thư</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Brisbane nằm phía đông nam bang Queensland, là thành phố lớn thứ ba tại Australia. Do gần đường xích đạo, khí hậu nơi đây ôn hòa, quanh năm nắng ấm. Trung tâm Brisbane không chỉ có những khối bê tông, khu mua sắm, mà còn bao phủ bởi mảng xanh, với 5 công viên và vườn thực vật nổi tiếng. Dưới đây là 5 điểm đến hút du khách ở Brisbane. South Bank Parklands Nằm bên bờ sông Brisbane, South Bank Parklands được ví như 'ốc đảo xanh' giữa lòng thành phố sôi động, nổi bật với rừng mưa nhiệt đới và loạt hoạt động giải trí cho mọi lứa tuổi. Ngay cửa ngõ công viên là thảm cỏ, hàng cây rợp bóng và vườn hoa. Nhiều người dân thường picnic, dã ngoại, vui chơi tại bãi biển nhân tạo Streets Beach, River Quay Green, Rainforest Green hay Liana Lounge. Ngoài ra, Wheel of Brisbane - vòng đu quay cao tới 60 m - là biểu tượng tại South Bank Parklands, dễ dàng ngắm toàn cảnh Brisbane từ trên cao. Roma Street Parkland Nằm cạnh ga xe lửa Roma Street, công viên cùng tên cũng được người dân lẫn du khách gọi là 'ốc đảo xanh mát' giữa Brisbane, ghi dấu với những khu vườn và bãi cỏ rộng lớn. Tại đây, du khách hòa mình vào khu vườn Spectacle - nơi trồng hàng nghìn gốc violets, cẩm chướng, delphiniums và foxgloves. Khí hậu ôn hòa thu hút chim kookaburras, gà lôi, vẹt. Bạn cũng có thể tổ chức tiệc BBQ ngoài trời, cho con khám phá công viên trẻ em. Brisbane City Botanic Gardens Nằm trên trục đường Alice, Brisbane City Botanic Gardens bảo tồn hàng nghìn loài thực vật quý hiếm, nổi bật với vẻ nguyên sơ. Khu vườn này là một trong những điểm đến lý tưởng cho người chuộng nét thanh bình giữa lòng đô thị. Tại đây, du khách có thể khám phá con đường dạo bộ ven sông, chiêm ngưỡng rặng thông Bunya được trồng từ năm 1858. Điểm đến tiếp theo là Bamboo Grove - con đường tre rợp mát, được ví như 'khu rừng xa xôi giữa thành phố hiện đại'. Vườn bách thảo tổ chức sự kiện quanh năm như biểu diễn Riverstage, lễ hội đa văn hóa, trưng bày nghệ thuật cùng hoạt động cộng đồng miễn phí. Trong đó, chợ Riverside Sunday Market hút hàng nghìn du khách nhờ gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden Tại Epicurious, du khách có thể khám phá ẩm thực bang Queensland đa dạng, nhất là rau, củ, quả, thảo mộc hữu cơ theo mùa. 14 chuyên viên tình nguyện chăm sóc khu vườn kỹ lưỡng, mong truyền cảm hứng cho người yêu nấu ăn và trồng trọt. 'Tới Epicurious, tôi và bạn bè được hướng dẫn cách chăm sóc rau củ, trái cây, thảo mộc và thưởng thức miễn phí', một du khách viết trên Facebook, nhận hàng trăm nghìn lượt thích. Mount Coot-tha Botanic Gardens Mở cửa đón khách từ năm 1976, Mount Coot-tha Botanic Gardens tọa lạc chân núi Coot-tha, là vườn thực vật nhiệt đới hàng đầu Brisbane, diện tích đến 56 ha. Dạo quanh khu vườn, du khách có thể chiêm ngưỡng hoa xuân, các loài cây nhiệt đới và khu thảo dược. Nơi đây là điểm đến quen thuộc của người yêu thiên nhiên, picnic, mê hoạt động thể chất, với đường chạy bộ thoáng đãng. Để khám phá thành thủ phủ bang Queensland, bạn có thể chọn đường bay thẳng từ TP HCM đến Brisbane của Vietjet, với 9 giờ trên máy bay thân rộng, thoải mái cùng loạt dịch vụ tiện ích, ưu đãi như: bảo hiểm Sky Care miễn phí, chương trình tích điểm SkyJoy, đổi quà từ hơn 250 thương hiệu lớn toàn cầu. Trước đó ngày14-15/9, Vietjet đồng hành lễ hội thả diều Vietjet Redcliffe KiteFest tại Redcliffe, Queensland. Hãng hàng không Việt còn áp dụng nhiều chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu. Đông Vệ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Công ty du lịch NhatbanAZ mở bán chùm tour Nhật Bản khởi hành dịp Tết Dương lịch và Âm lịch từ đầu tháng 10. Trong đó, các tour truyền thống đến Osaka, Kyoto và Tokyo được làm mới bằng những hoạt động phù hợp với mùa đông xuân như trượt tuyết tại Fujiten Resort, ngắm tuyết làng cổ Oshino Hakkai và tham gia lễ hội ánh sáng Nabana no sato. NhatbanAZ cũng mở rộng các cung đường mới cho du khách trải nghiệm trong dịp Tết 2025. Cụ thể, tour Hokkaido gồm Asahikawa, Monbetsu và Sapporo với giá 55,9 triệu đồng mỗi khách. Du khách sẽ tham gia câu cá trên băng, đi tàu phá băng và thưởng thức bia hơi tại Sapporo, cùng dịch vụ hàng không 5 sao và lưu trú khách sạn 4 sao quốc tế. Tour thứ hai là chuyến thăm làng cổ Shirakawago, núi Phú Sĩ và Tokyo trong 6 ngày 5 đêm với giá 31,9 triệu đồng mỗi khách. Du khách sẽ được chiêm ngưỡng tuyết trắng tại Shirakawago, một Di sản Văn hóa Thế giới của UNESCO từ năm 1995. Tour cũng gồm tham quan lâu đài Matsumoto - di tích bảo vật quốc gia của Nhật Bản và trải nghiệm trượt tuyết tại Fujiten Snow Resort - top 3 khu trượt tuyết nổi tiếng. Bà Hồ Như Thảo, Giám đốc Điều hành NhatbanAZ Văn phòng TP HCM cho biết sản phẩm mới này nhận được sự quan tâm lớn từ du khách, đặc biệt là những người từng đi Nhật và muốn trở lại với hành trình mới. Khu vực Hokkaido được biết đến với tuyết rơi dày đặc hơn Tokyo hay Osaka, nên lịch khởi hành tour Hokkaido dịp Tết Âm lịch nhận được nhiều đăng ký giữ chỗ. Trong dịp Tết Nguyên đán 2025, NhatbanAZ cung cấp các hành trình từ 5 đến 6 ngày với mức giá cơ bản đến cao cấp, khoảng 31,9 - 55,9 triệu đồng mỗi khách để đáp ứng nhu cầu đa dạng. Giá tour Tết có phần chênh lệch so với ngày thường và tăng so với cùng kỳ năm trước. Do đó, NhatbanAZ chủ động gặp gỡ và làm việc với các đối tác cung cấp dịch vụ, từ đó xây dựng chương trình, đưa ra chính sách ưu đãi tốt nhất cho khách hàng. Với kinh nghiệm hơn 15 năm trong ngành du lịch chuyên thị trường Nhật Bản, NhatbanAZ thuộc danh sách công ty chỉ định nộp visa bởi Đại sứ quán Nhật Bản đề xuất. Đồng thời là đối tác chiến lược của các hãng hàng không, khách sạn và đối tác land tour uy tín tại Nhật Bản. Công ty cũng là nhà tư vấn và tổ chức những chuyến Famtrip kết nối các công ty du lịch Việt Nam tới tham quan xúc tiến đầu tư, hợp tác tại Nhật Bản. Thanh Thư</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Theo bảng xếp hạng 20 quốc gia tốt nhất thế giới năm 2024 (The Best Countries in the World) do tạp chí du lịch Mỹ Condé Nast Traveler công bố vào tháng 10, Việt Nam ở vị trí 15 với 89 điểm. Một điểm đến khác thuộc Đông Nam Á có mặt trong danh sách này là Thái Lan, xếp thứ ba với 92,29 điểm. Đứng đầu top 20 là Nhật Bản với 95,32 điểm. Xếp hạng nằm trong giải thưởng thường niênReaders' Choice Awards của tạp chí Mỹ, dựa trên đánh giá của hơn 575.000 độc giả về các trải nghiệm du lịch ở mỗi quốc gia, xét theo các tiêu chí văn hóa, cảnh quan, dịch vụ du lịch và cơ sở hạ tầng. Độc giả của Condé Nast Traveler nhận xét Việt Nam thu hút du khách nhờ vẻ đẹp mộc mạc và quyến rũ. 'Với lượng khách nước ngoài đang trên đà tăng từ 2019 đến nay, Việt Nam không còn là điểm đến đáng chú ý mà thành điểm đến đáng ghé thăm', biên tập tờ Condé Nast Traveler viết. Theo số liệu từ Tổng cục Thống kê, trong 9 tháng đầu năm, Việt Nam đón hơn 12,7 triệu lượt khách quốc tế, vượt lượng khách cả năm 2023 là 12,6 triệu lượt. Lượng khách quốc tế đến Việt Nam tăng trưởng tích cực 9 tháng đầu năm 2024, với một số thị trường phục hồi hoàn toàn, tăng mạnh so với 2019, theo Cục Du lịch Quốc gia. Cục cũng dự đoán với đà tăng trường như hiện nay, Việt Nam sẽ hoàn thành mục tiêu đón 17-18 triệu lượt khách quốc tế năm 2024. Thái Lan được tạp chí Mỹ nhận xét là quốc gia đa dạng cảnh quan, giao thông thuận tiện với nhiều tàu thuyền, xe buýt đêm và chuyến bay nội địa giá rẻ. Ẩm thực cũng là điểm sáng của xứ chùa Vàng khi có nhiều khu chợ đêm nhộn nhịp, bày bán đặc sản địa phương. 8 tháng đầu năm 2024, Thái Lan đón hơn 20 triệu lượt khách quốc tế, tăng 34% so với cùng kỳ năm trước. Quốc gia này đặt mục tiêu đón ít nhất 36-37 triệu lượt khách nước ngoài trong cả năm nay, kỳ vọng thu về khoảng 3.500 tỷ baht (95,5 tỷ USD). Condé Nast Traveler là tạp chí du lịch nổi tiếng toàn cầu, ra mắt vào năm 1987. Các bảng xếp hạng của Condé Nast Traveler như Readers' Choice Awards được chuyên gia du lịch đánh giá là uy tín vì dựa trên ý kiến từ hàng triệu độc giả quốc tế. Bích Phương(TheoCNTraveller)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá tính mạch lạc và súc tích."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -542,8 +667,27 @@
           <t>Theo KTO Việt Nam, 8 tháng năm nay, Hàn Quốc đón 389.000 lượt khách Việt, tăng 27% so với cùng kỳ năm 2023. Số lượng khách Việt Nam đến Hàn Quốc dự kiến tăng mạnh hơn bởi đất nước này đang bước vào mùa lá vàng đẹp nhất năm. Đại diện KTO khẳng định, Việt Nam là thị trường quan trọng với ngành du lịch Hàn Quốc với nhiều sự kiện tổ chức thành công. Cụ thể, trong năm nay, KTO Việt Nam xúc tiến các chương trình quảng bá, phát triển sản phẩm du lịch Hàn Quốc phù hợp với nhu cầu du khách Việt. Kết quả, nhiều sản phẩm du lịch mới được ra mắt thị trường trong nước như: tour du lịch Hàn Quốc kết hợp giải chạy Marathon tại Gyeongju và Jeju, tour trải nghiệm Esports, tour lễ hội đèn lồng truyền thống Yeondeunghoe hay tour đạp xe đạp đường dài khám phá Hàn Quốc... Chương trình Năm du lịch Hàn Quốc 2023-2024 (Visit Korea Year 2023-2024) do Tổng cục du lịch Hàn Quốc (KTO) triển khai cũng mang đến những hoạt động mới mẻ, quảng bá du lịch Hàn Quốc đến cộng đồng quốc tế. Bên cạnh đó, nhằm mang đến những trải nghiệm chân thực và đậm chất bản địa, KTO tổ chức nhiều famtour. Nổi bật là famtour trải nghiệm Esports cùng các KOL hàng đầu làng thể thao điện tử như: SofM, reviewer Duy Thẩm, Hải Triều, streamer Hà Tiều Phu, BLV Esports nổi tiếng Văn Tùng, Hoàng Luân, kết hợp Box Esports. Làn sóng văn hóa Hallyu cũng được lồng ghép vào sản phẩm du lịch, khi hàng loạt tên tuổi lớn đến Việt Nam trong khuôn khổ sự kiện Korea Travel Festa, tổ chức tháng 5 vừa qua. Mới nhất, KTO Việt Nam có mặt tại Hội chợ Du lịch Quốc tế (ITE) TP HCM, mang theo không gian đặc trưng Hàn Quốc cùng nhiều trải nghiệm mới mẻ, độc đáo. Nắm bắt nhu cầu du lịch Hàn Quốc tăng cao trong mùa cuối năm của du khách Việt, KTO Việt Nam tiếp tục đẩy mạnh các chương trình ưu đãi đặc biệt. Cùng các đối tác, công ty du lịch hàng đầu Việt Nam, KTO góp phần phát triển nhiều tuyến điểm mới trong hành trình du lịch Hàn Quốc, mang đến đa dạng lựa chọn và nhiều trải nghiệm cho khách hàng. Hồi tháng 5, KTO Việt Nam ký kết thỏa thuận hợp tác cùng Tập đoàn Vingroup, nhằm thúc đẩy hơn nữa sự giao lưu, trao đổi du lịch giữa hai nước. Theo đó, KTO triển khai chiến dịch hỗ trợ dành riêng cho khách hàng thuộc hệ sinh thái Vingroup khi mua tour du lịch Hàn Quốc từ tháng 10 đến tháng 12 Cụ thể, chủ sở hữu xe Vinfast, cư dân Vinhomes, nhân viên Vingroup) và hội viên Vinclub (gọi chung là Vintizen) sẽ nhận được mức giá ưu đãi đặc biệt từ các công ty du lịch và KTO Việt Nam. Bên cạnh mức giá ưu đãi từ các công ty du lịch, Vintizen có cơ hội áp dụng đồng thời voucher trị giá một triệu đồng mỗi khách hàng, mua tối đa 5 tour du lịch Hàn Quốc để nhận voucher lên đến 5 triệu đồng từ KTO Việt Nam, trong thời gian 1-10/10. Ngoài thời gian trên, du khách mua tour tại các đối tác du lịch sẽ nhận được nhiều phần quà Hàn Quốc từ KTO Việt Nam. Thanh Thư</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hàn Quốc đón 389.000 lượt khách Việt Nam tăng 27% nhờ mùa lá vàng đẹp nhất năm và chương trình quảng bá du lịch mới, trong đó Vintizen hưởng ưu đãi giảm giá tour từ tháng 10 đến tháng 12 với voucher trị giá một triệu đồng mỗi khách hàng.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{
+  "id": 9,
+  "style": "news_brief",
+  "article": "Theo KTO Việt Nam, 8 tháng năm nay, Hàn Quốc đón 389.000 lượt khách Việt, tăng 27% so với cùng kỳ năm 2023. Số lượng khách Việt Nam đến Hàn Quốc dự kiến tăng mạnh hơn bởi đất nước này đang bước vào mùa lá vàng đẹp nhất năm. Đại diện KTO khẳng định, Việt Nam là thị trường quan trọng với ngành du lịch Hàn Quốc với nhiều sự kiện tổ chức thành công. Cụ thể, trong năm nay, KTO Việt Nam xúc tiến các chương trình quảng bá, phát triển sản phẩm du lịch Hàn Quốc phù hợp với nhu cầu du khách Việt. Kết quả, nhiều sản phẩm du lịch mới được ra mắt thị trường trong nước như: tour du lịch Hàn Quốc kết hợp giải chạy Marathon tại Gyeongju và Jeju, tour trải nghiệm Esports, tour lễ hội đèn lồng truyền thống Yeondeunghoe hay tour đạp xe đạp đường dài khám phá Hàn Quốc... Chương trình Năm du lịch Hàn Quốc 2023-2024 (Visit Korea Year 2023-2024) do Tổng cục du lịch Hàn Quốc (KTO) triển khai cũng mang đến những hoạt động mới mẻ, quảng bá du lịch Hàn Quốc đến cộng đồng quốc tế. Bên cạnh đó, nhằm mang đến những trải nghiệm chân thực và đậm chất bản địa, KTO tổ chức nhiều famtour. Nổi bật là famtour trải nghiệm Esports cùng các KOL hàng đầu làng thể thao điện tử như: SofM, reviewer Duy Thẩm, Hải Triều, streamer Hà Tiều Phu, BLV Esports nổi tiếng Văn Tùng, Hoàng Luân, kết hợp Box Esports. Làn sóng văn hóa Hallyu cũng được lồng ghép vào sản phẩm du lịch, khi hàng loạt tên tuổi lớn đến Việt Nam trong khuôn khổ sự kiện Korea Travel Festa, tổ chức tháng 5 vừa qua. Mới nhất, KTO Việt Nam có mặt tại Hội chợ Du lịch Quốc tế (ITE) TP HCM, mang theo không gian đặc trưng Hàn Quốc cùng nhiều trải nghiệm mới mẻ, độc đáo. Nắm bắt nhu cầu du lịch Hàn Quốc tăng cao trong mùa cuối năm của du khách Việt, KTO Việt Nam tiếp tục đẩy mạnh các chương trình ưu đãi đặc biệt. Cùng các đối tác, công ty du lịch hàng đầu Việt Nam, KTO góp phần phát triển nhiều tuyến điểm mới trong hành trình du lịch Hàn Quốc, mang đến đa dạng lựa chọn và nhiều trải nghiệm cho khách hàng. Hồi tháng 5, KTO Việt Nam ký kết thỏa thuận hợp tác cùng Tập đoàn Vingroup, nhằm thúc đẩy hơn nữa sự giao lưu, trao đổi du lịch giữa hai nước. Theo đó, KTO triển khai chiến dịch hỗ trợ dành riêng cho khách hàng thuộc hệ sinh thái Vingroup khi mua tour du lịch Hàn Quốc từ tháng 10 đến tháng 12 Cụ thể, chủ sở hữu xe Vinfast, cư dân Vinhomes, nhân viên Vingroup) và hội viên Vinclub (gọi chung là Vintizen) sẽ nhận được mức giá ưu đãi đặc biệt từ các công ty du lịch và KTO Việt Nam. Bên cạnh mức giá ưu đãi từ các công ty du lịch, Vintizen có cơ hội áp dụng đồng thời voucher trị giá một triệu đồng mỗi khách hàng, mua tối đa 5 tour du lịch Hàn Quốc để nhận voucher lên đến 5 triệu đồng từ KTO Việt Nam, trong thời gian 1-10/10. Ngoài thời gian trên, du khách mua tour tại các đối tác du lịch sẽ nhận được nhiều phần quà Hàn Quốc từ KTO Việt Nam. Thanh Thư",
+  "summary": "Hàn Quốc đón 389.000 lượt khách Việt Nam tăng 27% nhờ mùa lá vàng đẹp nhất năm và chương trình quảng bá du lịch mới, trong đó Vintizen hưởng ưu đãi giảm giá tour từ tháng 10 đến tháng 12 với voucher trị giá một triệu đồng mỗi khách hàng.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng có thể thiếu chính xác khi không đề cập đầy đủ đến các chương trình quảng bá du lịch và sự kiện cụ thể",
+  "relevance_score": 0.7,
+  "relevance_reason": "Bản tóm tắt bao gồm một số ý chính nhưng bỏ sót thông tin quan trọng về các sản phẩm du lịch mới và chương trình Năm du lịch Hàn Quốc 2023-2024",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, tuy nhiên có thể rút gọn một số chi tiết để tăng tính súc tích"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -551,8 +695,27 @@
           <t>Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) là đơn vị phụ trách tổ chức. Với chủ đề 'Liên kết cùng phát triển - Kiên Giang 2024', diễn đàn hướng đến tăng cường hợp tác, liên kết giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với các Bộ, ngành Trung ương, các địa phương khác trên cả nước. Từ đó, các bên có thêm cơ sở đẩy mạnh, phát huy tiềm năng về sản phẩm OCOP của vùng. Đến nay, đã có trên 35 tỉnh, thành phố đăng ký tham gia diễn đàn cùng hơn 300 nhà đầu tư đến tìm hiểu cơ hội, xúc tiến hợp tác kinh doanh. Diễn đàn dự kiến thu hút khoảng 50.000-100.000 khách tham quan suốt thời gian diễn ra. Hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước sẽ cùng trưng bày, giới thiệu các sản phẩm OCOP tiêu biểu, công nghiệp nông thôn, đặc sản địa phương. Ngoài chương trình chính, sự kiện còn bao gồm chuỗi hoạt động khác như: triển lãm sản phẩm OCOP; hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024'; các hội nghị, hội thảo, ký kết biên bản hợp tác... Đặc biệt, khách tham dự còn được tìm hiểu quy trình sản xuất nước mắm truyền thống Phú Quốc, một trong những đặc sản nổi tiếng của Kiên Giang. Buổi tối, diễn dàn có các chương trình ca nhạc với sự góp mặt của các ca sĩ, nghệ sĩ nổi tiếng. Diễn đàn kết nối sản phẩm OCOP là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh, thành phố vùng Đồng bằng sông Cửu Long tổ chức quy mô cấp vùng. Đây vừa là nơi giao lưu, kết nối kinh doanh, vừa là cơ hội để các sản phẩm này vươn ra thế giới, góp phần phát triển kinh tế nông nghiệp, xây dựng nông thôn mới bền vững. Á Hiên</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp với Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) phụ trách việc tổ chức. Chủ đề của diễn đàn là 'Liên kết cùng phát triển - Kiên Giang 2024', hướng đến tăng cường hợp tác giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với Bộ ngành Trung ương và địa phương khác trên cả nước. Diễn đàn đã thu hút hơn 35 tỉnh/thành phố đăng ký tham gia cùng gần 300 nhà đầu tư tìm hiểu cơ hội xúc tiến hợp tác kinh doanh, dự kiến sẽ có khoảng 50-100 nghìn khách tham quan và trưng bày hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước. Ngoài chương trình chính như triển lãm sản phẩm OCOP, hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024', diễn đàn còn có chuỗi hoạt động khác gồm: ký kết biên bản hợp tác, ca nhạc với sự góp mặt của các nghệ sĩ nổi tiếng. Đây là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh/thành phố vùng Đồng bằng sông Cửu Long tổ chức, vừa giúp giao lưu kinh doanh vừa tạo cơ hội cho sản phẩm OCOP vươn ra thế giới.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{
+  "id": 10,
+  "style": "news_brief",
+  "article": "Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) là đơn vị phụ trách tổ chức. Với chủ đề 'Liên kết cùng phát triển - Kiên Giang 2024', diễn đàn hướng đến tăng cường hợp tác, liên kết giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với các Bộ, ngành Trung ương, các địa phương khác trên cả nước. Từ đó, các bên có thêm cơ sở đẩy mạnh, phát huy tiềm năng về sản phẩm OCOP của vùng. Đến nay, đã có trên 35 tỉnh, thành phố đăng ký tham gia diễn đàn cùng hơn 300 nhà đầu tư đến tìm hiểu cơ hội, xúc tiến hợp tác kinh doanh. Diễn đàn dự kiến thu hút khoảng 50.000-100.000 khách tham quan suốt thời gian diễn ra. Hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước sẽ cùng trưng bày, giới thiệu các sản phẩm OCOP tiêu biểu, công nghiệp nông thôn, đặc sản địa phương. Ngoài chương trình chính, sự kiện còn bao gồm chuỗi hoạt động khác như: triển lãm sản phẩm OCOP; hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024'; các hội nghị, hội thảo, ký kết biên bản hợp tác... Đặc biệt, khách tham dự còn được tìm hiểu quy trình sản xuất nước mắm truyền thống Phú Quốc, một trong những đặc sản nổi tiếng của Kiên Giang. Buổi tối, diễn dàn có các chương trình ca nhạc với sự góp mặt của các ca sĩ, nghệ sĩ nổi tiếng. Diễn đàn kết nối sản phẩm OCOP là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh, thành phố vùng Đồng bằng sông Cửu Long tổ chức quy mô cấp vùng. Đây vừa là nơi giao lưu, kết nối kinh doanh, vừa là cơ hội để các sản phẩm này vươn ra thế giới, góp phần phát triển kinh tế nông nghiệp, xây dựng nông thôn mới bền vững. Á Hiên",
+  "summary": "Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp với Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) phụ trách việc tổ chức. Chủ đề của diễn đàn là 'Liên kết cùng phát triển - Kiên Giang 2024', hướng đến tăng cường hợp tác giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với Bộ ngành Trung ương và địa phương khác trên cả nước. Diễn đàn đã thu hút hơn 35 tỉnh/thành phố đăng ký tham gia cùng gần 300 nhà đầu tư tìm hiểu cơ hội xúc tiến hợp tác kinh doanh, dự kiến sẽ có khoảng 50-100 nghìn khách tham quan và trưng bày hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước. Ngoài chương trình chính như triển lãm sản phẩm OCOP, hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024', diễn đàn còn có chuỗi hoạt động khác gồm: ký kết biên bản hợp tác, ca nhạc với sự góp mặt của các nghệ sĩ nổi tiếng. Đây là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh/thành phố vùng Đồng bằng sông Cửu Long tổ chức, vừa giúp giao lưu kinh doanh vừa tạo cơ hội cho sản phẩm OCOP vươn ra thế giới.",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, nhưng có một số chi tiết được tóm tắt không đầy đủ như việc khách tham dự có thể tìm hiểu quy trình sản xuất nước mắm truyền thống Phú Quốc",
+  "relevance_score": 0.8,
+  "relevance_reason": "Bản tóm tắt bao hàm đủ các ý chính quan trọng, nhưng có thể thêm thông tin về mục tiêu của diễn đàn và ý nghĩa của việc tăng cường hợp tác giữa các tỉnh, thành phố",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, nhưng có thể rút gọn một số câu để tăng tính súc tích"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -560,8 +723,27 @@
           <t>Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Hoàng Giang</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LỖI: 'NoneType' object is not iterable</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{
+  "id": 11,
+  "style": "news_brief",
+  "article": "Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Hoàng Giang",
+  "summary": "LỖI: 'NoneType' object is not iterable",
+  "faithfulness_score": 0.0,
+  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không phản ánh nội dung của văn bản.",
+  "relevance_score": 0.0,
+  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không đề cập đến các sự kiện, tình huống hoặc thông điệp chính.",
+  "coherence_conciseness_score": 0.0,
+  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá về tính mạch lạc và súc tích."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -569,8 +751,27 @@
           <t>Bếp trưởng Christian Le Squer nổi tiếng với 22 năm liên tiếp đạt 3 sao Michelin, hiện đảm nhiệm vai trò bếp trưởng tại La Maison 1888. Nhà hàng là điểm đến ẩm thực Pháp cao cấp, nằm ngay trong khuôn viên resort InterContinental Danang Sun Peninsula Resort. Tháng 7 vừa qua đánh dấu cột mốc quan trọng khi La Maison 1888 gia nhập 'bản đồ' Michelin Guide với ngôi sao đầu tiên. Với sự điều hành của bếp trưởng Christian Le Squer, thực khách sẽ được trải nghiệm ẩm thực Pháp cao cấp giao hòa giữa nghệ thuật và thẩm mỹ cao cấp, mang đậm dấu ấn cá nhân của ông. Ông Seif Hamdy, Tổng giám đốc khu nghỉ dưỡng cho biết sự góp mặt của bếp trưởng Christian tại InterContinental Danang là bước tiến quan trọng. Sự sáng tạo trong ẩm thực cùng khả năng của ông là điều đã được chứng minh bằng 22 năm liên tục được trao tặng ba sao Michelin. Christian Le Squer còn từng đạt danh hiệu 'Bếp trưởng của năm' do Gault &amp; Millau trao tặng năm 2023. 'Christian Le Squer sẽ mang đến làn gió mới cùng tầm nhìn sáng tạo, góp phần nâng tầm trải nghiệm ẩm thực cho thực khách tại La Maison 1888 với phong cách 'haute couture' đặc trưng do chính ông tạo ra', ông Seif Hamdy nói. Sinh ra và lớn lên bên bờ biển Brittany (Pháp), bếp trưởng Christian có nhiều trải nghiệm tuổi thơ gắn liền với ẩm thực. Những ký ức thuở nhỏ gieo cho ông đam mê ẩm thực sâu sắc và dẫn lối ông đến kinh đô ánh sáng và thời trang Paris. Đến năm 34 tuổi, ông được trao sao Michelin đầu tiên tại nhà hàng Café de la Paix. Thành công này đã thôi thúc ông tiếp tục hành trình chinh phục những đỉnh cao ẩm thực kế tiếp. Sau đó, ông gia nhập nhà hàng Pavillon Ledoyen năm 1999, giúp nơi này giành được ba sao Michelin không lâu sau đó. Thành tích này được ông Christian lặp lại tại Le Cinq, nhà hàng Pháp biểu tượng tại khách sạn Four Seasons Hotel George V ở Paris. Bếp trưởng Christian ví von phong cách ẩm thực độc đáo của mình như những tác phẩm thời trang nghệ thuật cao cấp 'haute couture' trên bàn ăn. Ông cho biết mỗi món đều mang dấu ấn riêng biệt, sở hữu hương vị và diện mạo thanh lịch như một bộ trang phục sang trọng hay một chai nước hoa độc bản được giới thiệu tại Tuần lễ Thời trang Paris. Sau nhiều chuyến ghé thăm Việt Nam, đặc biệt là Đà Nẵng, ông hiểu hơn về nhu cầu của thực khách nơi đây. Nhiều người ông gặp cho biết họ tìm kiếm sự kết hợp hài hòa giữa truyền thống và hiện đại trong ẩm thực Pháp. Việc khám phá các hương vị, nguyên liệu, văn hóa ẩm thực đặc sắc của Việt Nam đã trở thành nguồn cảm hứng để ông phác họa nên bức tranh ẩm thực riêng cho La Maison 1888. 'Tôi rất mong chờ được cùng làm việc với đội ngũ tài năng tại La Maison 1888, đặc biệt là Bếp trưởng Florian Stein', Christian nói. Nằm trong một dinh thự theo phong cách Đông Dương thanh lịch do Bill Bensley thiết kế, La Maison 1888 là một trong những điểm đến ẩm thực quốc tế đáng cân nhắc tại Đông Nam Á. Nhà hàng sở hữu hầm rượu vang với bộ sưu tập phong phú cùng tầm nhìn đẹp hướng biển. Nơi đây chinh phục thực khách bằng ẩm thực cao cấp với chất lượng được Michelin công nhận cùng không gian sang trọng đậm chất Pháp. Sắp tới, bếp trưởng Christian hứa hẹn mang đến nhiều bất ngờ thú vị, góp phần nâng tầm trải nghiệm ẩm thực của thực khách tại đây. Á Hiên</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LỖI: 'NoneType' object is not iterable</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{
+  "id": 12,
+  "style": "news_brief",
+  "article": "Bếp trưởng Christian Le Squer nổi tiếng với 22 năm liên tiếp đạt 3 sao Michelin, hiện đảm nhiệm vai trò bếp trưởng tại La Maison 1888. Nhà hàng là điểm đến ẩm thực Pháp cao cấp, nằm ngay trong khuôn viên resort InterContinental Danang Sun Peninsula Resort. Tháng 7 vừa qua đánh dấu cột mốc quan trọng khi La Maison 1888 gia nhập 'bản đồ' Michelin Guide với ngôi sao đầu tiên. Với sự điều hành của bếp trưởng Christian Le Squer, thực khách sẽ được trải nghiệm ẩm thực Pháp cao cấp giao hòa giữa nghệ thuật và thẩm mỹ cao cấp, mang đậm dấu ấn cá nhân của ông. Ông Seif Hamdy, Tổng giám đốc khu nghỉ dưỡng cho biết sự góp mặt của bếp trưởng Christian tại InterContinental Danang là bước tiến quan trọng. Sự sáng tạo trong ẩm thực cùng khả năng của ông là điều đã được chứng minh bằng 22 năm liên tục được trao tặng ba sao Michelin. Christian Le Squer còn từng đạt danh hiệu 'Bếp trưởng của năm' do Gault &amp; Millau trao tặng năm 2023. 'Christian Le Squer sẽ mang đến làn gió mới cùng tầm nhìn sáng tạo, góp phần nâng tầm trải nghiệm ẩm thực cho thực khách tại La Maison 1888 với phong cách 'haute couture' đặc trưng do chính ông tạo ra', ông Seif Hamdy nói. Sinh ra và lớn lên bên bờ biển Brittany (Pháp), bếp trưởng Christian có nhiều trải nghiệm tuổi thơ gắn liền với ẩm thực. Những ký ức thuở nhỏ gieo cho ông đam mê ẩm thực sâu sắc và dẫn lối ông đến kinh đô ánh sáng và thời trang Paris. Đến năm 34 tuổi, ông được trao sao Michelin đầu tiên tại nhà hàng Café de la Paix. Thành công này đã thôi thúc ông tiếp tục hành trình chinh phục những đỉnh cao ẩm thực kế tiếp. Sau đó, ông gia nhập nhà hàng Pavillon Ledoyen năm 1999, giúp nơi này giành được ba sao Michelin không lâu sau đó. Thành tích này được ông Christian lặp lại tại Le Cinq, nhà hàng Pháp biểu tượng tại khách sạn Four Seasons Hotel George V ở Paris. Bếp trưởng Christian ví von phong cách ẩm thực độc đáo của mình như những tác phẩm thời trang nghệ thuật cao cấp 'haute couture' trên bàn ăn. Ông cho biết mỗi món đều mang dấu ấn riêng biệt, sở hữu hương vị và diện mạo thanh lịch như một bộ trang phục sang trọng hay một chai nước hoa độc bản được giới thiệu tại Tuần lễ Thời trang Paris. Sau nhiều chuyến ghé thăm Việt Nam, đặc biệt là Đà Nẵng, ông hiểu hơn về nhu cầu của thực khách nơi đây. Nhiều người ông gặp cho biết họ tìm kiếm sự kết hợp hài hòa giữa truyền thống và hiện đại trong ẩm thực Pháp. Việc khám phá các hương vị, nguyên liệu, văn hóa ẩm thực đặc sắc của Việt Nam đã trở thành nguồn cảm hứng để ông phác họa nên bức tranh ẩm thực riêng cho La Maison 1888. 'Tôi rất mong chờ được cùng làm việc với đội ngũ tài năng tại La Maison 1888, đặc biệt là Bếp trưởng Florian Stein', Christian nói. Nằm trong một dinh thự theo phong cách Đông Dương thanh lịch do Bill Bensley thiết kế, La Maison 1888 là một trong những điểm đến ẩm thực quốc tế đáng cân nhắc tại Đông Nam Á. Nhà hàng sở hữu hầm rượu vang với bộ sưu tập phong phú cùng tầm nhìn đẹp hướng biển. Nơi đây chinh phục thực khách bằng ẩm thực cao cấp với chất lượng được Michelin công nhận cùng không gian sang trọng đậm chất Pháp. Sắp tới, bếp trưởng Christian hứa hẹn mang đến nhiều bất ngờ thú vị, góp phần nâng tầm trải nghiệm ẩm thực của thực khách tại đây. Á Hiên",
+  "summary": "LỖI: 'NoneType' object is not iterable",
+  "faithfulness_score": 0.0,
+  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không có nội dung để đánh giá tính trung thực.",
+  "relevance_score": 0.0,
+  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không có nội dung để đánh giá tính bao quát.",
+  "coherence_conciseness_score": 0.0,
+  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá tính mạch lạc và súc tích."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -578,8 +779,27 @@
           <t>Đại diện Sun World Sầm Sơn cho biết chương trình ưu đãi nhằm tri ân khách hàng đã ủng hộ suốt thời gian công viên nước ra mắt. Từ ngày 3/9, giá 100.000 đồng áp dụng chung cho mọi lứa tuổi. Trước đó, giá gốc 200.000 đồng (khách ngoại tỉnh) và 150.000 đồng (người Thanh Hóa). Riêng bé dưới 1 m được miễn phí vé. Khai trương đúng dịp cao điểm hè 30/6, Sun World Sầm Sơn - công viên nước quy mô nhất miền Bắc cùng tổ hợp trò chơi đạt kỷ lục châu Á - Thái Bình Dương - là 'cú hích' cho du lịch Sầm Sơn năm nay, hút hàng nghìn lượt khách mỗi ngày. Công viên nước thuộc phường Quảng Châu, Quảng Tiến, ngay đại lộ Nam sông Mã - cửa ngõ Sầm Sơn, cách trung tâm TP Thanh Hóa13 km và bãi biển Sầm Sơn 1,5 km. Thiết kế không gian lấy cảm hứng từ truyện dân gian Việt Nam, kết hợp hài hòa kiến trúc truyền thống và hiện đại. Các trò chơi cùng cảnh quan vừa gần gũi, vừa mới mẻ. Công viên nước chia ba phân khu riêng biệt dành cho mọi lứa tuổi: gia đình, trẻ em và khu cảm giác mạnh. Trong đó, trò 'Vịnh sóng thần' có diện tích 6.100 m2, chiều dài bờ biển nhân tạo đến 179 m. Cụ thể, phân khu cảm giác mạnh tập hợp những trò tốc độ, kích thích, góp phần giúp du khách giải tỏa áp lực công việc, cuộc sống. Điển hình là tổ hợp hàm cá mập, với các đường trượt uốn lượn, độ dốc cao chủ đề 'cá mập hung tàn' hay 'cá mập siêu bạo chúa'. Nhằm đáp ứng nhu cầu vui chơi của gia đình lẫn nhóm bạn trẻ, ban tổ chức kiến tạo mê cung quy mô lớn, nhấn vào các đường trượt đan chéo và vực lốc xoáy (tổ hợp ống trượt uốn lượn, xoắn ốc như các xoáy nước dành cho phao đôi đầu tiên tại châu Á - Thái Bình Dương). Du khách có thể khám phá đa dạng đường trượt gồm: 'cá đuối vượt sóng', 'cá trê vượt thác' hay 8 làn trượt thảm bạch tuộc. Chủ dự án cũng bố trí phân khu bến tuổi thơ cho trẻ, với 3 tổ hợp nhỏ mô hình sinh vật dưới nước quen thuộc. Bao quanh khu trò chơi là sông lười, gợi nhớ dòng Đơ tại Sầm Sơn. Tại đây, du khách có thể lênh đênh theo dòng nước, thư giãn và tận hưởng cảm giác sảng khoái như trẻ thơ. Nếu muốn khám phá trọn vẹn công viên nước, du khách nên đến từ 10h hoặc 15h bởi nắng không quá gắt, thích hợp với cả người già lẫn trẻ nhỏ. Vạn Phát</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sun World Sầm Sơn giảm giá vé 100.000 đồng từ ngày 3/9, miễn phí cho trẻ dưới 1m. Công viên nước quy mô lớn nằm gần trung tâm TP Thanh Hóa, hấp dẫn du khách nhờ nhiều trò chơi kết hợp giữa truyền thống và hiện đại.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{
+  "id": 13,
+  "style": "news_brief",
+  "article": "Đại diện Sun World Sầm Sơn cho biết chương trình ưu đãi nhằm tri ân khách hàng đã ủng hộ suốt thời gian công viên nước ra mắt. Từ ngày 3/9, giá 100.000 đồng áp dụng chung cho mọi lứa tuổi. Trước đó, giá gốc 200.000 đồng (khách ngoại tỉnh) và 150.000 đồng (người Thanh Hóa). Riêng bé dưới 1 m được miễn phí vé. Khai trương đúng dịp cao điểm hè 30/6, Sun World Sầm Sơn - công viên nước quy mô nhất miền Bắc cùng tổ hợp trò chơi đạt kỷ lục châu Á - Thái Bình Dương - là 'cú hích' cho du lịch Sầm Sơn năm nay, hút hàng nghìn lượt khách mỗi ngày. Công viên nước thuộc phường Quảng Châu, Quảng Tiến, ngay đại lộ Nam sông Mã - cửa ngõ Sầm Sơn, cách trung tâm TP Thanh Hóa13 km và bãi biển Sầm Sơn 1,5 km. Thiết kế không gian lấy cảm hứng từ truyện dân gian Việt Nam, kết hợp hài hòa kiến trúc truyền thống và hiện đại. Các trò chơi cùng cảnh quan vừa gần gũi, vừa mới mẻ. Công viên nước chia ba phân khu riêng biệt dành cho mọi lứa tuổi: gia đình, trẻ em và khu cảm giác mạnh. Trong đó, trò 'Vịnh sóng thần' có diện tích 6.100 m2, chiều dài bờ biển nhân tạo đến 179 m. Cụ thể, phân khu cảm giác mạnh tập hợp những trò tốc độ, kích thích, góp phần giúp du khách giải tỏa áp lực công việc, cuộc sống. Điển hình là tổ hợp hàm cá mập, với các đường trượt uốn lượn, độ dốc cao chủ đề 'cá mập hung tàn' hay 'cá mập siêu bạo chúa'. Nhằm đáp ứng nhu cầu vui chơi của gia đình lẫn nhóm bạn trẻ, ban tổ chức kiến tạo mê cung quy mô lớn, nhấn vào các đường trượt đan chéo và vực lốc xoáy (tổ hợp ống trượt uốn lượn, xoắn ốc như các xoáy nước dành cho phao đôi đầu tiên tại châu Á - Thái Bình Dương). Du khách có thể khám phá đa dạng đường trượt gồm: 'cá đuối vượt sóng', 'cá trê vượt thác' hay 8 làn trượt thảm bạch tuộc. Chủ dự án cũng bố trí phân khu bến tuổi thơ cho trẻ, với 3 tổ hợp nhỏ mô hình sinh vật dưới nước quen thuộc. Bao quanh khu trò chơi là sông lười, gợi nhớ dòng Đơ tại Sầm Sơn. Tại đây, du khách có thể lênh đênh theo dòng nước, thư giãn và tận hưởng cảm giác sảng khoái như trẻ thơ. Nếu muốn khám phá trọn vẹn công viên nước, du khách nên đến từ 10h hoặc 15h bởi nắng không quá gắt, thích hợp với cả người già lẫn trẻ nhỏ. Vạn Phát",
+  "summary": "Sun World Sầm Sơn giảm giá vé 100.000 đồng từ ngày 3/9, miễn phí cho trẻ dưới 1m. Công viên nước quy mô lớn nằm gần trung tâm TP Thanh Hóa, hấp dẫn du khách nhờ nhiều trò chơi kết hợp giữa truyền thống và hiện đại.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng thiếu sót một số chi tiết quan trọng như thời gian khai trương, các phân khu trong công viên nước và một số trò chơi đặc biệt",
+  "relevance_score": 0.7,
+  "relevance_reason": "Bản tóm tắt chưa bao hàm đủ các ý chính quan trọng như mục đích của chương trình ưu đãi, vị trí và thiết kế của công viên nước",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt có logic, dễ đọc và súc tích, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng mà không làm cho bản tóm tắt trở nên rườm rà"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -587,8 +807,27 @@
           <t>Chiều 28/8, khách sạn Grand Mercure Hanoi đón hơn 200 vị khách thuộc đoàn 4.500 du khách từ Ấn Độ sang Việt Nam. Theo ông Remi Faubel, tổng quản lý khách sạn, đây là cơ hội lớn để quảng bá nét đẹp văn hóa, truyền thống tới khách quốc tế. 'Chúng tôi tự tin các yếu tố như lối kiến trúc Đông Dương, hệ thống cửa Bức Bàn, các chi tiết nội thất lấy cảm hứng từ hoa sen, trống đồng, hạt gạo, ruộng bậc thang,... sẽ góp phần để lại ấn tượng tốt đẹp trong lòng du khách', ông Faubel nói. Do nhu cầu của khách, Grand Mercure Hanoi vẫn phục vụ chủ yếu các món Ấn. Bếp trưởng - Nguyễn Minh Nguyện lý giải, du khách Ấn Độ luôn có nhu cầu thưởng thức ẩm thực đất nước họ để có cảm giác gần gũi và thoải mái khi đi du lịch. Đó cũng là cách họ gìn giữ văn hóa và chế độ ăn truyền thống. 'Khi lên kế hoạch, chúng tôi phải trao đổi với phía đại diện đoàn để nắm thông tin về chế độ ăn, suất ăn tôn giáo, yêu cầu đặc biệt, từ đó lựa chọn các loại gia vị đặc trưng của Ấn Độ để các món ăn giữ được hương vị', vị bếp trưởng nói. Tuy nhiên, khách sạn cũng chuẩn bị thêm một số món ăn đặc trưng của Việt Nam như gà, bánh cuốn, xôi, hoa quả nhiệt đới... để giới thiệu đến đoàn khách. Từ ngày 27/8 đến 3/9, Việt Nam đón 4.500 du khách thuộc tập đoàn dược phẩm lớn đến từ Ấn Độ. Dự kiến, họ sẽ chia thành các nhóm nhỏ tới Hà Nội - Ninh Bình - Hạ Long và sử dụng các dịch vụ lưu trú, ăn uống tại các khách sạn 5 sao trên địa bàn thủ đô. Ấn Độ là một trong 10 thị trường khách du lịch quốc tế lớn nhất Việt Nam. Theo số liệu từ Cục Du lịch Quốc gia, trong 6 tháng đầu năm, nước ta đã đón 231.000 lượt khách Ấn Độ, tăng 164% so với cùng kỳ năm 2023. Việt Nam có nhiều thế mạnh để thu hút và phát triển thị trường này. Các đường bay thẳng giữa hai nước được khai thác trong thời gian gần đây khiến thời gian di chuyển rút ngắn chỉ còn khoảng 4 - 5 tiếng. Theo Outlook Traveller, Việt Nam sở hữu những cảnh quan đẹp, nền văn hóa đa dạng và chiều sâu lịch sử. Giá thành dịch vụ cạnh tranh khiến nước ta trở thành điểm đến lý tưởng cho du khách Ấn Độ. Lan Anh</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hàng nghìn du khách Ấn Độ đến Grand Mercure Hanoi, nơi lối kiến trúc Đông Dương và ẩm thực truyền thống tạo ấn tượng tốt. Việt Nam với cảnh quan đẹp đa dạng văn hóa lịch sử thu hút du khách do giá cả hợp lý.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{
+  "id": 14,
+  "style": "news_brief",
+  "article": "Chiều 28/8, khách sạn Grand Mercure Hanoi đón hơn 200 vị khách thuộc đoàn 4.500 du khách từ Ấn Độ sang Việt Nam. Theo ông Remi Faubel, tổng quản lý khách sạn, đây là cơ hội lớn để quảng bá nét đẹp văn hóa, truyền thống tới khách quốc tế. 'Chúng tôi tự tin các yếu tố như lối kiến trúc Đông Dương, hệ thống cửa Bức Bàn, các chi tiết nội thất lấy cảm hứng từ hoa sen, trống đồng, hạt gạo, ruộng bậc thang,... sẽ góp phần để lại ấn tượng tốt đẹp trong lòng du khách', ông Faubel nói. Do nhu cầu của khách, Grand Mercure Hanoi vẫn phục vụ chủ yếu các món Ấn. Bếp trưởng - Nguyễn Minh Nguyện lý giải, du khách Ấn Độ luôn có nhu cầu thưởng thức ẩm thực đất nước họ để có cảm giác gần gũi và thoải mái khi đi du lịch. Đó cũng là cách họ gìn giữ văn hóa và chế độ ăn truyền thống. 'Khi lên kế hoạch, chúng tôi phải trao đổi với phía đại diện đoàn để nắm thông tin về chế độ ăn, suất ăn tôn giáo, yêu cầu đặc biệt, từ đó lựa chọn các loại gia vị đặc trưng của Ấn Độ để các món ăn giữ được hương vị', vị bếp trưởng nói. Tuy nhiên, khách sạn cũng chuẩn bị thêm một số món ăn đặc trưng của Việt Nam như gà, bánh cuốn, xôi, hoa quả nhiệt đới... để giới thiệu đến đoàn khách. Từ ngày 27/8 đến 3/9, Việt Nam đón 4.500 du khách thuộc tập đoàn dược phẩm lớn đến từ Ấn Độ. Dự kiến, họ sẽ chia thành các nhóm nhỏ tới Hà Nội - Ninh Bình - Hạ Long và sử dụng các dịch vụ lưu trú, ăn uống tại các khách sạn 5 sao trên địa bàn thủ đô. Ấn Độ là một trong 10 thị trường khách du lịch quốc tế lớn nhất Việt Nam. Theo số liệu từ Cục Du lịch Quốc gia, trong 6 tháng đầu năm, nước ta đã đón 231.000 lượt khách Ấn Độ, tăng 164% so với cùng kỳ năm 2023. Việt Nam có nhiều thế mạnh để thu hút và phát triển thị trường này. Các đường bay thẳng giữa hai nước được khai thác trong thời gian gần đây khiến thời gian di chuyển rút ngắn chỉ còn khoảng 4 - 5 tiếng. Theo Outlook Traveller, Việt Nam sở hữu những cảnh quan đẹp, nền văn hóa đa dạng và chiều sâu lịch sử. Giá thành dịch vụ cạnh tranh khiến nước ta trở thành điểm đến lý tưởng cho du khách Ấn Độ. Lan Anh",
+  "summary": "Hàng nghìn du khách Ấn Độ đến Grand Mercure Hanoi, nơi lối kiến trúc Đông Dương và ẩm thực truyền thống tạo ấn tượng tốt. Việt Nam với cảnh quan đẹp đa dạng văn hóa lịch sử thu hút du khách do giá cả hợp lý.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng thiếu sót một số chi tiết quan trọng như số lượng du khách và các hoạt động cụ thể tại khách sạn",
+  "relevance_score": 0.7,
+  "relevance_reason": "Bản tóm tắt chưa bao hàm đủ các ý chính quan trọng như nhu cầu ẩm thực của du khách Ấn Độ và việc giới thiệu văn hóa Việt Nam",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, tuy nhiên có thể rút gọn một số từ ngữ để tăng tính súc tích"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -596,8 +835,27 @@
           <t>Theo Báo cáo Hạnh phúc Thế giới (World Happiness Report) 2024 của Liên Hợp Quốc công bố hồi tháng 3, Lithuania là quốc gia 'hạnh phúc nhất thế giới dành cho những người dưới 30 tuổi (gen Z)'. Hai nhà sáng tạo nội dung Ammar Kandil và Staffan Taylor đến từ Yes Theory, kênh truyền thông nổi tiếng của Canada, quyết định đến thủ đô Vilnius để tìm hiểu xem liệu báo cáo có nói đúng. Khi hạ cánh xuống Vilnius, Amma và Staffan bắt đầu nói chuyện với người dân địa phương. Hầu hết người trẻ đều đồng ý quốc gia họ đang sống là nơi tốt nhờ 'đồ ăn tuyệt vời, người dân thân thiện, nhiều cơ hội nghề nghiệp và nền kinh tế đang phát triển'. Nhiều người trong số đó cho rằng các khó khăn mà thế hệ trước chịu đựng đã dạy thế hệ trẻ ngày nay cách tận hưởng cuộc sống trong từng khoảnh khắc và 'tìm thấy vẻ đẹp trong những điều giản dị'. Để thu hút nhiều người trẻ đến nói chuyện hơn, Amma và Staffan đã tổ chức một buổi gặp gỡ. Tại sự kiện, những người tham dự lần lượt bày tỏ quan điểm. 'Sau một năm sống tại Mỹ, tôi đánh giá cao cuộc sống ở Lithuania vì tính kết nối với thiên nhiên', một thanh niên chia sẻ. Người này nói thêm du khách có thể dễ dàng tiếp cận một hồ nước hay khu rừng tại Lithuania và chiêm ngưỡng khung cảnh thiên nhiên tuyệt đẹp ở đó. 'Lithuania chưa bao giờ tốt như hiện nay', một phụ nữ trẻ khác thừa nhận. Khi nói về hạnh phúc, một người dân địa phương cho biết dù người trẻ sống ở đất nước này 'khá vui vẻ' nhưng không có nghĩa họ không phải đối mặt với nhiều vấn đề, áp lực cuộc sống. Sau buổi gặp gỡ, Ammar và Staffan dành phần còn lại của chuyến đi để giao lưu với người dân địa phương, ghé thăm các điểm du lịch như nhà tù cũ Lukiškės giờ là địa điểm văn hóa và tượng đài Hill of Crosses. 'Đây là một trong những trải nghiệm du lịch hạnh phúc nhất tôi từng có', Ammar, người từng đi khắp thế giới, chia sẻ với độc giả trên kênh Yes Theory khi đang tham gia một bữa tiệc tối. Steffan đồng tình khi nhận định Lithuania chắc chắn là một trong những quốc gia cởi mở, hào phóng, tử tế nhất mà anh từng đến. Video của hai du khách đến từ Canada đã thu hút gần một triệu lượt xem và bình luận chỉ sau vài ngày đăng tải. Một người từng đến Vilnius học theo diện trao đổi sinh viên chia sẻ thời gian ở Liathuania là quãng thời gian hạnh phúc nhất của mình. 'Cảm ơn Liathuania đã chào đón tôi', người này nói. 'Tình yêu, sự sáng tạo và lòng tốt có thể giúp chúng ta vượt qua quá khứ đen tối, biến tiêu cực thành ánh sáng và giúp đỡ người khác', một người dân địa phương bày tỏ sau khi xem video của Ammar và Steffan. Anh Minh(TheoYes Theory, DM)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lithuania được đánh giá cao về sự cởi mở, hào phóng và đồ ăn ngon. Tuy nhiên, cuộc sống vẫn có áp lực từ thế hệ trước đã dạy trẻ tận hưởng từng khoảnh khắc và tìm thấy vẻ đẹp trong giản dị.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{
+  "id": 15,
+  "style": "news_brief",
+  "article": "Theo Báo cáo Hạnh phúc Thế giới (World Happiness Report) 2024 của Liên Hợp Quốc công bố hồi tháng 3, Lithuania là quốc gia 'hạnh phúc nhất thế giới dành cho những người dưới 30 tuổi (gen Z)'. Hai nhà sáng tạo nội dung Ammar Kandil và Staffan Taylor đến từ Yes Theory, kênh truyền thông nổi tiếng của Canada, quyết định đến thủ đô Vilnius để tìm hiểu xem liệu báo cáo có nói đúng. Khi hạ cánh xuống Vilnius, Amma và Staffan bắt đầu nói chuyện với người dân địa phương. Hầu hết người trẻ đều đồng ý quốc gia họ đang sống là nơi tốt nhờ 'đồ ăn tuyệt vời, người dân thân thiện, nhiều cơ hội nghề nghiệp và nền kinh tế đang phát triển'. Nhiều người trong số đó cho rằng các khó khăn mà thế hệ trước chịu đựng đã dạy thế hệ trẻ ngày nay cách tận hưởng cuộc sống trong từng khoảnh khắc và 'tìm thấy vẻ đẹp trong những điều giản dị'. Để thu hút nhiều người trẻ đến nói chuyện hơn, Amma và Staffan đã tổ chức một buổi gặp gỡ. Tại sự kiện, những người tham dự lần lượt bày tỏ quan điểm. 'Sau một năm sống tại Mỹ, tôi đánh giá cao cuộc sống ở Lithuania vì tính kết nối với thiên nhiên', một thanh niên chia sẻ. Người này nói thêm du khách có thể dễ dàng tiếp cận một hồ nước hay khu rừng tại Lithuania và chiêm ngưỡng khung cảnh thiên nhiên tuyệt đẹp ở đó. 'Lithuania chưa bao giờ tốt như hiện nay', một phụ nữ trẻ khác thừa nhận. Khi nói về hạnh phúc, một người dân địa phương cho biết dù người trẻ sống ở đất nước này 'khá vui vẻ' nhưng không có nghĩa họ không phải đối mặt với nhiều vấn đề, áp lực cuộc sống. Sau buổi gặp gỡ, Ammar và Staffan dành phần còn lại của chuyến đi để giao lưu với người dân địa phương, ghé thăm các điểm du lịch như nhà tù cũ Lukiškės giờ là địa điểm văn hóa và tượng đài Hill of Crosses. 'Đây là một trong những trải nghiệm du lịch hạnh phúc nhất tôi từng có', Ammar, người từng đi khắp thế giới, chia sẻ với độc giả trên kênh Yes Theory khi đang tham gia một bữa tiệc tối. Steffan đồng tình khi nhận định Lithuania chắc chắn là một trong những quốc gia cởi mở, hào phóng, tử tế nhất mà anh từng đến. Video của hai du khách đến từ Canada đã thu hút gần một triệu lượt xem và bình luận chỉ sau vài ngày đăng tải. Một người từng đến Vilnius học theo diện trao đổi sinh viên chia sẻ thời gian ở Liathuania là quãng thời gian hạnh phúc nhất của mình. 'Cảm ơn Liathuania đã chào đón tôi', người này nói. 'Tình yêu, sự sáng tạo và lòng tốt có thể giúp chúng ta vượt qua quá khứ đen tối, biến tiêu cực thành ánh sáng và giúp đỡ người khác', một người dân địa phương bày tỏ sau khi xem video của Ammar và Steffan. Anh Minh(TheoYes Theory, DM)",
+  "summary": "Lithuania được đánh giá cao về sự cởi mở, hào phóng và đồ ăn ngon. Tuy nhiên, cuộc sống vẫn có áp lực từ thế hệ trước đã dạy trẻ tận hưởng từng khoảnh khắc và tìm thấy vẻ đẹp trong giản dị.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng thiếu sót một số chi tiết quan trọng như việc Lithuania được đánh giá là quốc gia hạnh phúc nhất thế giới dành cho người dưới 30 tuổi và các hoạt động của Ammar và Staffan khi đến Vilnius",
+  "relevance_score": 0.7,
+  "relevance_reason": "Bản tóm tắt không bao hàm đủ các ý chính quan trọng như việc người dân Lithuania đánh giá cao cuộc sống ở đây vì đồ ăn tuyệt vời, người dân thân thiện, nhiều cơ hội nghề nghiệp và nền kinh tế đang phát triển",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, tuy nhiên có thể rút gọn một số chi tiết để tăng tính súc tích"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -605,8 +863,27 @@
           <t>Đi dạo trong khuôn viên lâu đài của mình ở Pháp vào một buổi tối mùa hè 2023, Philippa Girling cảm thấy nhẹ nhõm khi nghe thấy tiếng cười của những du khách nữ đang lưu trú tại đây. Tiếng cười là mục tiêu mà CEO Camp Château, nơi tổ chức trại hè dành riêng cho phụ nữ, mong muốn khi mở dịch vụ này. Tuy mới thành lập được hai năm, danh sách khách đăng ký đến nghỉ dưỡng tại lâu đài cổ nằm trên đỉnh đồi ở vùng Quercy, tây nam nước Pháp, năm nay đã kín chỗ. Lượng khách chờ cho mùa hè 2025 đã lên đến 11.000 người. Philippa rất vui khi được mọi người yêu thích dịch vụ cũng nhưng cảm thấy rất tiếc cho những người trong danh sách chờ khi nhiều du khách sẽ phải đợi 20 năm mới đến lượt. Cô đang xem xét để mở rộng trại hè, giúp nhiều du khách nữ có thể sử dụng dịch vụ hơn. Philippa nói mục đích tồn tại của Camp Château rất đơn giản: mang đến cho phụ nữ trải nghiệm vui vẻ. Philippa từng làm 30 năm trong ngành ngân hàng nên thấu hiểu áp lực mà phụ nữ ngày nay phải đối mặt. Do đó, cô cùng các đồng sáng lập tạo ra Camp Château để giúp các khách hàng nữ của mình thư giãn, mang lại cho họ sự chăm sóc sức khỏe tinh thần và thể chất, không gian yên tĩnh và thời gian để hồi phục trước khi quay về cuộc sống thường ngày. Kỳ nghỉ trong trại hè kéo dài sáu ngày năm đêm với nhiều hoạt động để hội viên tham gia như làm nến, nếm thử phô mai, cưỡi ngựa, yoga. Một số phụ nữ hào hứng tham gia mọi hoạt động, số khác thích dành phần lớn thời gian nằm bên hồ bơi. Mỗi đợt đón khách khoảng 50 người. Girling, người lớn lên ở miền nam nước Anh, thường đi nghỉ ở Quercy và hiện sống ở California, Mỹ, nhận thấy 'phụ nữ khi ở bên nhau thật tuyệt vời'. Những người phụ nữ đều rất hòa đồng. Họ nằm giường tầng trong các căn phòng tại lâu đài hoặc trong lều dành cho hai người. Tất cả cùng dùng chung bữa tối tại sảnh lớn và có khung giờ phục vụ đồ uống riêng. Trọng tâm của chương trình trại hè này là trao cho phụ nữ quyền tự quyết, làm mọi thứ họ muốn và chỉ cần đối xử tử tế với nhau. Toàn bộ thiết kế của Camp Château đều hướng tới mục đích giúp mọi người có thể gặp gỡ, trò chuyện nhiều hơn một cách tự nhiên nhất. Điều duy nhất khách cần quyết định tại Camp Château là muốn nghỉ ngơi hay vui chơi. Tất cả phụ nữ đều được chào đón tại trại hè. Từ tháng 7 trở về trước, phần lớn khách đến đây là người Mỹ. Nhưng từ đầu tháng 8, số lượng quốc tịch đa dạng hơn khi có thêm các khách đến từ Andorra, Canada, Ai Cập, Anh và Nigeria. Độ tuổi từ 19 đến ngoài 70 tuổi. Nhiều người đến một mình và không ít người gọi trại hè này là 'môi trường an toàn phục vụ niềm đam mê du lịch' của họ. Ngoài ra, trại hè cũng đón các nhóm khách nhỏ gồm mẹ và con gái. Giá một kỳ nghỉ là 2.178 euro, gồm mọi chi phí ăn ở, vui chơi và không tính đưa đón sân bay, dịch vụ massage. Philippa nói số tiền này không nhỏ nhưng cô và các cộng sự đã phải tính toán để đưa ra mức giá phải chăng nhất có thể. Càng ngày, lượng khách đăng ký càng đông. Nhưng Philippa nói sẽ không tăng giá vì muốn nhiều người có thể tiếp cận trải nghiệm này thay vì hướng tới tệp khách nhà giàu. Anh Minh(TheoEuro News)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Du khách nữ đến Camp Château, lâu đài cổ ở Quercy, Tây Nam Pháp với các hoạt động như làm nến, yoga hoặc thư giãn bên hồ bơi. Mục tiêu trại hè là mang lại trải nghiệm vui vẻ và chăm sóc sức khỏe tinh thần thể chất cho phụ nữ tự quyết định mọi thứ trong sự tôn trọng lẫn nhau. Camp Château đón khách đa dạng từ Mỹ đến Andorra với 11.000 người đăng ký mùa hè năm nay, nhưng nhiều du khách phải đợi hai thập kỷ mới được phục vụ. Philippa Girling tăng giá không vì muốn tiếp cận rộng rãi hơn mà nhằm tập trung vào tệp khách giàu có; tuy nhiên, cô cũng nhận ra rằng cần mở rộng dịch vụ để giúp phụ nữ sử dụng nó dễ dàng hơn. Camp Château tạo điều kiện cho các phụ nữ thư giãn và hồi phục sau khi quay về cuộc sống thường ngày, nhấn mạnh quyền tự quyết định của họ trong sự tôn trọng lẫn nhau.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{
+  "id": 16,
+  "style": "news_brief",
+  "article": "Đi dạo trong khuôn viên lâu đài của mình ở Pháp vào một buổi tối mùa hè 2023, Philippa Girling cảm thấy nhẹ nhõm khi nghe thấy tiếng cười của những du khách nữ đang lưu trú tại đây. Tiếng cười là mục tiêu mà CEO Camp Château, nơi tổ chức trại hè dành riêng cho phụ nữ, mong muốn khi mở dịch vụ này. Tuy mới thành lập được hai năm, danh sách khách đăng ký đến nghỉ dưỡng tại lâu đài cổ nằm trên đỉnh đồi ở vùng Quercy, tây nam nước Pháp, năm nay đã kín chỗ. Lượng khách chờ cho mùa hè 2025 đã lên đến 11.000 người. Philippa rất vui khi được mọi người yêu thích dịch vụ cũng nhưng cảm thấy rất tiếc cho những người trong danh sách chờ khi nhiều du khách sẽ phải đợi 20 năm mới đến lượt. Cô đang xem xét để mở rộng trại hè, giúp nhiều du khách nữ có thể sử dụng dịch vụ hơn. Philippa nói mục đích tồn tại của Camp Château rất đơn giản: mang đến cho phụ nữ trải nghiệm vui vẻ. Philippa từng làm 30 năm trong ngành ngân hàng nên thấu hiểu áp lực mà phụ nữ ngày nay phải đối mặt. Do đó, cô cùng các đồng sáng lập tạo ra Camp Château để giúp các khách hàng nữ của mình thư giãn, mang lại cho họ sự chăm sóc sức khỏe tinh thần và thể chất, không gian yên tĩnh và thời gian để hồi phục trước khi quay về cuộc sống thường ngày. Kỳ nghỉ trong trại hè kéo dài sáu ngày năm đêm với nhiều hoạt động để hội viên tham gia như làm nến, nếm thử phô mai, cưỡi ngựa, yoga. Một số phụ nữ hào hứng tham gia mọi hoạt động, số khác thích dành phần lớn thời gian nằm bên hồ bơi. Mỗi đợt đón khách khoảng 50 người. Girling, người lớn lên ở miền nam nước Anh, thường đi nghỉ ở Quercy và hiện sống ở California, Mỹ, nhận thấy 'phụ nữ khi ở bên nhau thật tuyệt vời'. Những người phụ nữ đều rất hòa đồng. Họ nằm giường tầng trong các căn phòng tại lâu đài hoặc trong lều dành cho hai người. Tất cả cùng dùng chung bữa tối tại sảnh lớn và có khung giờ phục vụ đồ uống riêng. Trọng tâm của chương trình trại hè này là trao cho phụ nữ quyền tự quyết, làm mọi thứ họ muốn và chỉ cần đối xử tử tế với nhau. Toàn bộ thiết kế của Camp Château đều hướng tới mục đích giúp mọi người có thể gặp gỡ, trò chuyện nhiều hơn một cách tự nhiên nhất. Điều duy nhất khách cần quyết định tại Camp Château là muốn nghỉ ngơi hay vui chơi. Tất cả phụ nữ đều được chào đón tại trại hè. Từ tháng 7 trở về trước, phần lớn khách đến đây là người Mỹ. Nhưng từ đầu tháng 8, số lượng quốc tịch đa dạng hơn khi có thêm các khách đến từ Andorra, Canada, Ai Cập, Anh và Nigeria. Độ tuổi từ 19 đến ngoài 70 tuổi. Nhiều người đến một mình và không ít người gọi trại hè này là 'môi trường an toàn phục vụ niềm đam mê du lịch' của họ. Ngoài ra, trại hè cũng đón các nhóm khách nhỏ gồm mẹ và con gái. Giá một kỳ nghỉ là 2.178 euro, gồm mọi chi phí ăn ở, vui chơi và không tính đưa đón sân bay, dịch vụ massage. Philippa nói số tiền này không nhỏ nhưng cô và các cộng sự đã phải tính toán để đưa ra mức giá phải chăng nhất có thể. Càng ngày, lượng khách đăng ký càng đông. Nhưng Philippa nói sẽ không tăng giá vì muốn nhiều người có thể tiếp cận trải nghiệm này thay vì hướng tới tệp khách nhà giàu. Anh Minh(TheoEuro News)",
+  "summary": "Du khách nữ đến Camp Château, lâu đài cổ ở Quercy, Tây Nam Pháp với các hoạt động như làm nến, yoga hoặc thư giãn bên hồ bơi. Mục tiêu trại hè là mang lại trải nghiệm vui vẻ và chăm sóc sức khỏe tinh thần thể chất cho phụ nữ tự quyết định mọi thứ trong sự tôn trọng lẫn nhau. Camp Château đón khách đa dạng từ Mỹ đến Andorra với 11.000 người đăng ký mùa hè năm nay, nhưng nhiều du khách phải đợi hai thập kỷ mới được phục vụ. Philippa Girling tăng giá không vì muốn tiếp cận rộng rãi hơn mà nhằm tập trung vào tệp khách giàu có; tuy nhiên, cô cũng nhận ra rằng cần mở rộng dịch vụ để giúp phụ nữ sử dụng nó dễ dàng hơn. Camp Château tạo điều kiện cho các phụ nữ thư giãn và hồi phục sau khi quay về cuộc sống thường ngày, nhấn mạnh quyền tự quyết định của họ trong sự tôn trọng lẫn nhau.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Bản tóm tắt có một số điểm không chính xác như việc Philippa Girling tăng giá không phải để tập trung vào tệp khách giàu có mà là không tăng giá để giúp nhiều người có thể tiếp cận trải nghiệm này",
+  "relevance_score": 0.9,
+  "relevance_reason": "Bản tóm tắt bao gồm hầu hết các ý chính quan trọng như mục tiêu của Camp Château, các hoạt động và đối tượng khách hàng, tuy nhiên có thể thêm một số chi tiết về lý do thành lập và không gian của lâu đài",
+  "coherence_conciseness_score": 0.8,
+  "coherence_conciseness_reason": "Bản tóm tắt có logic và dễ đọc, tuy nhiên có một số câu dài và phức tạp, cần được tinh gọn hơn để tăng tính súc tích"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -614,8 +891,27 @@
           <t>Thời gian này tại Malaysia cũng có nhiều sự kiện để du khách trải nghiệm như: lễ hội trò chơi dân gian tại Kuala Lumpur (13-16/9), lễ hội văn hóa Putrajaya (27-29/9), lễ hội bãi biển Tanjung Aru 2024 tại Kota Kinabalu (1 và 22/9)... Điểm đến phổ biến nhất tại Malaysia là thủ đô Kuala Lumpur - đô thị sầm uất với những di sản kiến trúc cùng các cao ốc hiện đại. Công trình nổi tiếng nhất là tháp đôi Petronas cao 88 tầng. Tại đây có đài quan sát toàn cảnh thành phố, cầu treo trên không, trung tâm khám phá khoa học Petrosains, thủy cung Aquaria KLCC và trung tâm mua sắm Suria KLCC. Quận trung tâm thành phố Kuala Lumpur là Bukit Bintang, khu vực nhộn nhịp bậc nhất với các khu mua sắm, khách sạn và nhà hàng cao cấp cùng nhiều tụ điểm vui chơi, giải trí. Đảo Penang lại mang đến không khí bình yên, nhẹ nhàng. Đặc biệt, George Town - thủ phủ của bang Penang là di sản thế giới, phản ánh rõ nét dấu vết lịch sử qua từng công trình kiến trúc lẫn đời sống văn hóa của cư dân, từ những ngõ nhỏ với căn nhà hai tầng của người Hoa đến tòa hội đồng thành phố, tháp đồng hồ từ thời thuộc địa Anh. Du khách đừng quên ghé đồi Penang Hill hay đền Kek Lok Si. Langkawi là quần đảo với 99 đảo nhỏ ngoài khơi biển Andaman. Vùng đất này có nhiều bãi biển hoang sơ với khu nghỉ dưỡng cao cấp, phù hợp cho kỳ nghỉ thư giãn sau những ngày bận rộn. Ngoài ra, hòn đảo này còn là điểm đến lý tưởng cho các môn thể thao dưới nước như lặn biển, dù kéo, mô tô nước hoặc khám phá công viên địa chất hàng triệu năm tuổi. Cao nguyên Cameron là địa danh nằm ở bang Pahang, được bao phủ một màu xanh dài bất tận bởi những đồi chè và loại cây ôn đới. Khí hậu của cao nguyên này mang đến cho du khách sự mát mẻ, dễ chịu như đang ở châu Âu. Khi đến đây, du khách đừng quên ghé thăm nông trại chế biến trà, vườn hoa oải hương, thung lũng hoa hồng hay thử trekking leo núi Batu Brinchang. Malaysia có nhiều món ăn hấp dẫn du khách, nổi bật là món cơm 'quốc dân' Nasi Lemak. Món cơm này gồm cơm, nấu từ gạo với nước cốt dừa, trứng luộc, gà chiên, lạc, dưa chuột thái lát, cá khô... ăn kèm xốt sambal. Món ăn tuy đơn giản song đủ dinh dưỡng và được nhiều người ưa thích. Char Kway Teow, món hủ tiếu xào nổi tiếng của cộng đồng người Hoa tại Malaysia được chế biến từ hủ tiếu bản to xào cùng tôm, chả cá, lạp xưởng, trứng, giá đỗ và hẹ. Ngoài ra, Roti Canai là món ăn của cộng đồng người Ấn. Đây là loại bánh dẹt, thơm, giòn và xốp, thường dùng kèm các loại cà ri. Thanh Thư</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LỖI: 'NoneType' object is not iterable</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>{
+  "id": 17,
+  "style": "news_brief",
+  "article": "Thời gian này tại Malaysia cũng có nhiều sự kiện để du khách trải nghiệm như: lễ hội trò chơi dân gian tại Kuala Lumpur (13-16/9), lễ hội văn hóa Putrajaya (27-29/9), lễ hội bãi biển Tanjung Aru 2024 tại Kota Kinabalu (1 và 22/9)... Điểm đến phổ biến nhất tại Malaysia là thủ đô Kuala Lumpur - đô thị sầm uất với những di sản kiến trúc cùng các cao ốc hiện đại. Công trình nổi tiếng nhất là tháp đôi Petronas cao 88 tầng. Tại đây có đài quan sát toàn cảnh thành phố, cầu treo trên không, trung tâm khám phá khoa học Petrosains, thủy cung Aquaria KLCC và trung tâm mua sắm Suria KLCC. Quận trung tâm thành phố Kuala Lumpur là Bukit Bintang, khu vực nhộn nhịp bậc nhất với các khu mua sắm, khách sạn và nhà hàng cao cấp cùng nhiều tụ điểm vui chơi, giải trí. Đảo Penang lại mang đến không khí bình yên, nhẹ nhàng. Đặc biệt, George Town - thủ phủ của bang Penang là di sản thế giới, phản ánh rõ nét dấu vết lịch sử qua từng công trình kiến trúc lẫn đời sống văn hóa của cư dân, từ những ngõ nhỏ với căn nhà hai tầng của người Hoa đến tòa hội đồng thành phố, tháp đồng hồ từ thời thuộc địa Anh. Du khách đừng quên ghé đồi Penang Hill hay đền Kek Lok Si. Langkawi là quần đảo với 99 đảo nhỏ ngoài khơi biển Andaman. Vùng đất này có nhiều bãi biển hoang sơ với khu nghỉ dưỡng cao cấp, phù hợp cho kỳ nghỉ thư giãn sau những ngày bận rộn. Ngoài ra, hòn đảo này còn là điểm đến lý tưởng cho các môn thể thao dưới nước như lặn biển, dù kéo, mô tô nước hoặc khám phá công viên địa chất hàng triệu năm tuổi. Cao nguyên Cameron là địa danh nằm ở bang Pahang, được bao phủ một màu xanh dài bất tận bởi những đồi chè và loại cây ôn đới. Khí hậu của cao nguyên này mang đến cho du khách sự mát mẻ, dễ chịu như đang ở châu Âu. Khi đến đây, du khách đừng quên ghé thăm nông trại chế biến trà, vườn hoa oải hương, thung lũng hoa hồng hay thử trekking leo núi Batu Brinchang. Malaysia có nhiều món ăn hấp dẫn du khách, nổi bật là món cơm 'quốc dân' Nasi Lemak. Món cơm này gồm cơm, nấu từ gạo với nước cốt dừa, trứng luộc, gà chiên, lạc, dưa chuột thái lát, cá khô... ăn kèm xốt sambal. Món ăn tuy đơn giản song đủ dinh dưỡng và được nhiều người ưa thích. Char Kway Teow, món hủ tiếu xào nổi tiếng của cộng đồng người Hoa tại Malaysia được chế biến từ hủ tiếu bản to xào cùng tôm, chả cá, lạp xưởng, trứng, giá đỗ và hẹ. Ngoài ra, Roti Canai là món ăn của cộng đồng người Ấn. Đây là loại bánh dẹt, thơm, giòn và xốp, thường dùng kèm các loại cà ri. Thanh Thư",
+  "summary": "LỖI: 'NoneType' object is not iterable",
+  "faithfulness_score": 0.0,
+  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin gì về văn bản gốc, không có nội dung để đánh giá tính trung thực.",
+  "relevance_score": 0.0,
+  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không phản ánh được nội dung chính.",
+  "coherence_conciseness_score": 0.0,
+  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá tính mạch lạc và súc tích."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -623,8 +919,27 @@
           <t>Lodo, 62 tuổi, hôm 6/8 đã có buổi sáng trải nghiệm đan võng cùng với nghệ nhân ở Cù Lao Chàm. Ông bất ngờ về độ bền chắc và sự khéo léo, kỳ công của nghệ nhân làm ra nó. Lodo đã mua một chiếc võng về làm kỷ niệm trong chuyến du lịch Việt Nam lần này. 'Tôi nghĩ đây là một vật liệu xanh giúp bảo vệ môi trường', du khách đến từ Pháp nói. Theo ông Lê Vĩnh Thuận, Phó giám đốc Ban quản lý khu bảo tồn biển Cù Lao Chàm, trong dịp Festival 'Cù Lao Chàm - mùa ngô đồng đỏ' năm 2024 diễn ra từ ngày 5 đến 11/8, lượng du khách đổ về Cù Lao Chàm tham gia lễ hội 'rất đông'. Đến đây, du khách được tìm hiểu về nguồn gốc và tham gia cùng với nghệ nhân đan loại võng truyền thống của đảo. Theo giới thiệu của Trung tâm Quản lý bảo tồn di sản Hội An, sợi võng được làm từ các mảng vỏ cây ngô đồng. Sau khi được tách ra từ thân cây, vỏ sẽ được gom lại thành từng bó rồi ngâm nước ở các khe, suối trên đảo như khe Ruộng Chùa, khe Ông Thơ, khe Xóm Mới. Sau một tháng, người thợ đem vỏ về tách chọn lớp bên trong có màu trắng đục, tước từng sợi nhỏ, phơi khô cho đến khi có màu trắng tinh mới có thể bắt tay vào đan võng. Công đoạn tước đòi hỏi sự tập trung cao của người thợ vì 'sợi càng mỏng đan võng càng chặt', nghệ nhân đan võng Ngô Thị Lê, 70 tuổi, cho biết. Vào khoảng tháng 7, người dân trên đảo đi chọn vỏ những cây ngô đồng làm nguyên liệu đan võng, khi cây ra hoa, rụng hết lá, vỏ đủ khô để thu hoạch. Cây ngô đồng dùng làm võng phải có dáng thẳng mới cho ra sợi suôn, mềm, dai và chịu lực tốt. Bà Lê cho biết khi đã chọn được cây, người dân khai thác bằng cách chỉ chặt ngang thân để cây còn nảy chồi, phát triển sinh sống trở lại. Bà Huỳnh Thị Út, 56 tuổi, cùng với bà Lê là hai trong số ít nghệ nhân ở Cù Lao Chàm duy trì nghề đan võng ngô đồng cho biết loại võng này được người xã đảo sáng tạo ra trong quá trình lao động sản xuất. 'Để làm ra chiếc võng đẹp, ngoài tước sợi mỏng còn yêu cầu thắt nút các mối mắt võng đều', bà Út nói. Lodo nói những nghệ nhân đan võng đã giúp ông phân biệt võng tư có bốn dây đan nối nhau và võng sáu có sáu dây dày hơn đan thành hình tứ giác. Võng ngô đồng dài 2,6 m, đan thủ công hơn một tháng, độ bền của võng có thể kéo dài từ 5 đến 10 năm, có giá từ 5 đến 10 triệu đồng. 'Mức giá này xứng đáng với công sức những người thợ bỏ ra', Lodo cho hay. Chị Hà Nhi, 45 tuổi, sống tại Hà Nội, cũng ấn tượng với loại võng không làm từ sợi công nghiệp mà hoàn toàn từ vỏ cây. 'Những sản phẩm thủ công truyền thống thẩm mỹ cao như thế này là điểm nhấn cho du khách khi du lịch trên đảo', chị Nhi nói. Ngô đồng gắn liền với đời sống hàng ngày của người dân Cù Lao Chàm từ hơn 300 năm trước, theo Ban quản lý khu bảo tồn biển Cù Lao Chàm. Trải qua nhiều đời gìn giữ và nỗ lực bảo tồn, phát huy giá trị văn hóa, nghề đan võng ngô đồng ở địa phương được Bộ Văn hóa Thể thao và Du lịch công nhận là Di sản văn hóa phi vật thể quốc gia hôm 6/8. Tuấn Anh</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LỖI: 'NoneType' object is not iterable</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{
+  "id": 18,
+  "style": "news_brief",
+  "article": "Lodo, 62 tuổi, hôm 6/8 đã có buổi sáng trải nghiệm đan võng cùng với nghệ nhân ở Cù Lao Chàm. Ông bất ngờ về độ bền chắc và sự khéo léo, kỳ công của nghệ nhân làm ra nó. Lodo đã mua một chiếc võng về làm kỷ niệm trong chuyến du lịch Việt Nam lần này. 'Tôi nghĩ đây là một vật liệu xanh giúp bảo vệ môi trường', du khách đến từ Pháp nói. Theo ông Lê Vĩnh Thuận, Phó giám đốc Ban quản lý khu bảo tồn biển Cù Lao Chàm, trong dịp Festival 'Cù Lao Chàm - mùa ngô đồng đỏ' năm 2024 diễn ra từ ngày 5 đến 11/8, lượng du khách đổ về Cù Lao Chàm tham gia lễ hội 'rất đông'. Đến đây, du khách được tìm hiểu về nguồn gốc và tham gia cùng với nghệ nhân đan loại võng truyền thống của đảo. Theo giới thiệu của Trung tâm Quản lý bảo tồn di sản Hội An, sợi võng được làm từ các mảng vỏ cây ngô đồng. Sau khi được tách ra từ thân cây, vỏ sẽ được gom lại thành từng bó rồi ngâm nước ở các khe, suối trên đảo như khe Ruộng Chùa, khe Ông Thơ, khe Xóm Mới. Sau một tháng, người thợ đem vỏ về tách chọn lớp bên trong có màu trắng đục, tước từng sợi nhỏ, phơi khô cho đến khi có màu trắng tinh mới có thể bắt tay vào đan võng. Công đoạn tước đòi hỏi sự tập trung cao của người thợ vì 'sợi càng mỏng đan võng càng chặt', nghệ nhân đan võng Ngô Thị Lê, 70 tuổi, cho biết. Vào khoảng tháng 7, người dân trên đảo đi chọn vỏ những cây ngô đồng làm nguyên liệu đan võng, khi cây ra hoa, rụng hết lá, vỏ đủ khô để thu hoạch. Cây ngô đồng dùng làm võng phải có dáng thẳng mới cho ra sợi suôn, mềm, dai và chịu lực tốt. Bà Lê cho biết khi đã chọn được cây, người dân khai thác bằng cách chỉ chặt ngang thân để cây còn nảy chồi, phát triển sinh sống trở lại. Bà Huỳnh Thị Út, 56 tuổi, cùng với bà Lê là hai trong số ít nghệ nhân ở Cù Lao Chàm duy trì nghề đan võng ngô đồng cho biết loại võng này được người xã đảo sáng tạo ra trong quá trình lao động sản xuất. 'Để làm ra chiếc võng đẹp, ngoài tước sợi mỏng còn yêu cầu thắt nút các mối mắt võng đều', bà Út nói. Lodo nói những nghệ nhân đan võng đã giúp ông phân biệt võng tư có bốn dây đan nối nhau và võng sáu có sáu dây dày hơn đan thành hình tứ giác. Võng ngô đồng dài 2,6 m, đan thủ công hơn một tháng, độ bền của võng có thể kéo dài từ 5 đến 10 năm, có giá từ 5 đến 10 triệu đồng. 'Mức giá này xứng đáng với công sức những người thợ bỏ ra', Lodo cho hay. Chị Hà Nhi, 45 tuổi, sống tại Hà Nội, cũng ấn tượng với loại võng không làm từ sợi công nghiệp mà hoàn toàn từ vỏ cây. 'Những sản phẩm thủ công truyền thống thẩm mỹ cao như thế này là điểm nhấn cho du khách khi du lịch trên đảo', chị Nhi nói. Ngô đồng gắn liền với đời sống hàng ngày của người dân Cù Lao Chàm từ hơn 300 năm trước, theo Ban quản lý khu bảo tồn biển Cù Lao Chàm. Trải qua nhiều đời gìn giữ và nỗ lực bảo tồn, phát huy giá trị văn hóa, nghề đan võng ngô đồng ở địa phương được Bộ Văn hóa Thể thao và Du lịch công nhận là Di sản văn hóa phi vật thể quốc gia hôm 6/8. Tuấn Anh",
+  "summary": "LỖI: 'NoneType' object is not iterable",
+  "faithfulness_score": 0.0,
+  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không phản ánh nội dung của bài viết.",
+  "relevance_score": 0.0,
+  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ ý chính quan trọng nào từ văn bản gốc, không đề cập đến chủ đề về nghề đan võng ngô đồng tại Cù Lao Chàm.",
+  "coherence_conciseness_score": 0.0,
+  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá về tính mạch lạc và súc tích."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -632,8 +947,27 @@
           <t>Với mục tiêu quảng bá du lịch mua sắm tại Singapore, Vietrantour cùng Tổng Cục du lịch Singapore giới thiệu những điểm đến mua sắm và check in hấp dẫn. Nếu du khách đang tìm kiếm những món đồ phiên bản giới hạn của các hãng thời trang cao cấp như Prada, Louis Vuitton, Hermes, ION Orchard và Scotts Square, nên tới trục đường Orchard Road. Đặc biệt, một số thời điểm, các cửa hàng thời trang tại khu vực này khuyến mại tới 70%. Ngoài ra, một số địa điểm mua sắm người dân địa phương hay tới là Tampines 1, Jem và Westgate với nhiều cửa hàng bán lẻ, thời trang phục vụ nhu cầu đời sống. Nếu đang trong chuyến đi cùng gia đình, du khách hãy ghé qua trung tâm thương mại Tanglin Mall hoặc House of Anli với hàng nghìn mặt hàng gia dụng, sản phẩm dành cho mẹ và bé. Trong khi đó, trung tâm mua sắm Mustafa - tụ điểm mua sắm đêm khuya quen thuộc của người dân địa phương cũng là nơi nổi tiếng với những món đồ công nghệ hàng đầu, đến các sản phẩm tiêu dùng với giá cả phải chăng. Khi mua sắm tại Singapore, khách hàng còn được hoàn thuế tới 7%. Là quốc gia phát triển mạnh về dịch vụ du lịch, Singapore chú trọng nhiều đến trải nghiệm khách hàng. Đất nước này cũng được đánh giá là trạm trung gian lý tưởng để bảo hành các sản phẩm đồ hiệu, 'thiên đường' mua hàng miễn thuế với nhiều thương hiệu quốc tế và các nhãn hàng địa phương như mỹ phẩm, nước hoa, bia rượu, đồng hồ, thực phẩm... Tại Singapore, một trong những trải nghiệm thú vị là du khách có thể tự tay hoàn thiện các sản phẩm thủ công truyền thống. Các cửa hàng sẽ có thợ thủ công lành nghề hướng dẫn du khách chưng cất rượu gin tại Brass Lion Distillery, làm đồ da tại Atelier Lodge hoặc học kỹ thuật thêu tranh hạt cườm truyền thống tại Rumah Bebe. Bạn cũng có thể dạo qua khu phố di sản Kampong Gelam, nơi sở hữu những cửa hàng bày bán đồ truyền thống như đồ gốm, đồ da thủ công,.. Trải nghiệm này sẽ giúp du khách hiểu rõ hơn về nét đẹp văn hóa Singapore, đồng thời thể hiện phong cách cá nhân trong từng sản phẩm. Du khách nêndạo các nhà sách như Books Actually và Huggs-Epigram Coffee Bookshop để khám phá văn học kinh điển từ một số nhà thơ, tiểu thuyết gia của Singapore. Thanh Thư</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LỖI: 'NoneType' object is not iterable</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{
+  "id": 19,
+  "style": "news_brief",
+  "article": "Với mục tiêu quảng bá du lịch mua sắm tại Singapore, Vietrantour cùng Tổng Cục du lịch Singapore giới thiệu những điểm đến mua sắm và check in hấp dẫn. Nếu du khách đang tìm kiếm những món đồ phiên bản giới hạn của các hãng thời trang cao cấp như Prada, Louis Vuitton, Hermes, ION Orchard và Scotts Square, nên tới trục đường Orchard Road. Đặc biệt, một số thời điểm, các cửa hàng thời trang tại khu vực này khuyến mại tới 70%. Ngoài ra, một số địa điểm mua sắm người dân địa phương hay tới là Tampines 1, Jem và Westgate với nhiều cửa hàng bán lẻ, thời trang phục vụ nhu cầu đời sống. Nếu đang trong chuyến đi cùng gia đình, du khách hãy ghé qua trung tâm thương mại Tanglin Mall hoặc House of Anli với hàng nghìn mặt hàng gia dụng, sản phẩm dành cho mẹ và bé. Trong khi đó, trung tâm mua sắm Mustafa - tụ điểm mua sắm đêm khuya quen thuộc của người dân địa phương cũng là nơi nổi tiếng với những món đồ công nghệ hàng đầu, đến các sản phẩm tiêu dùng với giá cả phải chăng. Khi mua sắm tại Singapore, khách hàng còn được hoàn thuế tới 7%. Là quốc gia phát triển mạnh về dịch vụ du lịch, Singapore chú trọng nhiều đến trải nghiệm khách hàng. Đất nước này cũng được đánh giá là trạm trung gian lý tưởng để bảo hành các sản phẩm đồ hiệu, 'thiên đường' mua hàng miễn thuế với nhiều thương hiệu quốc tế và các nhãn hàng địa phương như mỹ phẩm, nước hoa, bia rượu, đồng hồ, thực phẩm... Tại Singapore, một trong những trải nghiệm thú vị là du khách có thể tự tay hoàn thiện các sản phẩm thủ công truyền thống. Các cửa hàng sẽ có thợ thủ công lành nghề hướng dẫn du khách chưng cất rượu gin tại Brass Lion Distillery, làm đồ da tại Atelier Lodge hoặc học kỹ thuật thêu tranh hạt cườm truyền thống tại Rumah Bebe. Bạn cũng có thể dạo qua khu phố di sản Kampong Gelam, nơi sở hữu những cửa hàng bày bán đồ truyền thống như đồ gốm, đồ da thủ công,.. Trải nghiệm này sẽ giúp du khách hiểu rõ hơn về nét đẹp văn hóa Singapore, đồng thời thể hiện phong cách cá nhân trong từng sản phẩm. Du khách nêndạo các nhà sách như Books Actually và Huggs-Epigram Coffee Bookshop để khám phá văn học kinh điển từ một số nhà thơ, tiểu thuyết gia của Singapore. Thanh Thư",
+  "summary": "LỖI: 'NoneType' object is not iterable",
+  "faithfulness_score": 0.0,
+  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không có nội dung để đánh giá tính trung thực.",
+  "relevance_score": 0.0,
+  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không thể đánh giá tính bao quát.",
+  "coherence_conciseness_score": 0.0,
+  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá tính mạch lạc và súc tích."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -641,8 +975,27 @@
           <t>Chương trình lần này có sự đồng hành của diễn viên Ninh Dương Lan Ngọc. Thông qua Epic Sale, diễn viên mong muốn lan tỏa tinh thần du lịch thông minh, tiện lợi và tối ưu chi phí. Ông Iko Putera, Giám đốc Vận chuyển Traveloka, cho biết việc hợp tác cùng Lan Ngọc đánh dấu cột mốc quan trọng trên hành trình mang đến trải nghiệm du lịch tiện nghi tối ưu cho khách hàng. Tầm ảnh hưởng và đam mê du lịch của cô phù hợp với sứ mệnh nền tảng theo đuổi. Đôi bên đều muốn truyền cảm hứng khám phá thế giới qua những chuyến đi. Với Epic Sale lần này, Traveloka áp dụng ưu đãi đến 50% cho các sản phẩm du lịch, dịch vụ trên toàn thế giới. 'Đây là lời tri ân chúng tôi muốn gửi đến khách hàng đã luôn ủng hộ, gắn bó trên hành trình kiến tạo những chuyến đi đáng nhớ cùng Traveloka', ông Iko Putera cho biết. Từ khi trở thành đại sứ thương hiệu tại Việt Nam, diễn viên Ninh Dương Lan Ngọc đã có nhiều trải nghiệm du lịch chất lượng với nền tảng. Với loạt khuyến mại, ưu đãi, quà tặng trong Epic Sale 2024, cô nói sẽ tranh thủ săn vé, đặt phòng, chuẩn bị cho những chuyến đi sắp tới. Theo Lan Ngọc, chương trình mang lại cho du khách cơ hội du lịch tiện nghi với chi phí tiết kiệm, giúp khơi dậy mong muốn đi đây đi đó, khám phá thế giới. Cô đánh giá cao sự tiện lợi và các dịch vụ toàn diện của nền tảng, giúp việc lên kế hoạch cho các chuyến đi thêm dễ dàng, thú vị. Traveloka đã hợp tác cùng hàng nghìn đối tác để mang đến những deal giá ưu đãi sâu. Người dùng có thể truy cập nền tảng, theo dõi các ưu đãi hàng ngày trong các mục Vé máy bay, Khách sạn, Xperience và nhiều sản phẩm du lịch khác. 'Siêu ưu đãi Epic' (Super Epic Deal) sẽ được áp dụng cho các sản phẩm nhất định trong khung giờ giới hạn. Cụ thể, giờ vàng Epic Hour Deal ưu đãi vé máy bay mỗi thứ Bảy từ 14h-17h; đặt khách sạn giờ vàng EPIC Hotel Hour Deal diễn ra hàng ngày từ 18h-19h. Du khách có thể săn vé máy bay quốc nội và quốc tế với giá ưu đãi. Trong đó, vé nội địa Vietravel giá chỉ từ 781.925 đồng; vé China Southern Airlines đi Thâm Quyến từ 2,819 đồng; vé T'way Air đến Hàn Quốc và Nhật Bản lần lượt chỉ từ 2,667 triệu đồng và 2,682 triệu đồng. Khách hàng còn có cơ hội nghỉ dưỡng tại khách sạn 5 sao trong nước với giá từ 794.000 đồng. Hàng loạt khách sạn Hàn Quốc giá từ 1,858 triệu đồng, Nhật Bản từ 1,146 triệu đồng. Với dịch vụ giải trí, nền tảng áp dụng ưu đãi 'mua 1 tặng 1' vé tham quan Sun World, công viên nước The Amazing Bay, thủy cung Sea Life Bangkok Ocean World (Thái Lan). Để du khách có trải nghiệm du lịch trọn vẹn, Traveloka giới thiệu thêm nhiều tính năng khác như: hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt... Xem thêm thông tin chi tiết về chương trình Epic Sale trên ứng dụng, website và các tài khoản mạng xã hội của Traveloka. Á Hiên</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>781.925 đồng vé Vietravel, 2.819 triệu Thâm Quyến; 2.667 và 2.682 triệu Hàn Quốc-Nhật Bản. Khách sạn từ 794.000-1.858 triệu. Áp dụng 'mua 1 tặng 1' Sun World, The Amazing Bay, Sea Life Bangkok Ocean World. Hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt trên Traveloka. Epic Sale của Ninh Dương Lan Ngọc mong muốn lan tỏa tinh thần du lịch thông minh và áp dụng ưu đãi đến 50% cho các sản phẩm toàn thế giới nhằm tri ân khách hàng và khích lệ khám phá thế giới qua những chuyến đi tiện nghi với chi phí tiết kiệm.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{
+  "id": 20,
+  "style": "news_brief",
+  "article": "Chương trình lần này có sự đồng hành của diễn viên Ninh Dương Lan Ngọc. Thông qua Epic Sale, diễn viên mong muốn lan tỏa tinh thần du lịch thông minh, tiện lợi và tối ưu chi phí. Ông Iko Putera, Giám đốc Vận chuyển Traveloka, cho biết việc hợp tác cùng Lan Ngọc đánh dấu cột mốc quan trọng trên hành trình mang đến trải nghiệm du lịch tiện nghi tối ưu cho khách hàng. Tầm ảnh hưởng và đam mê du lịch của cô phù hợp với sứ mệnh nền tảng theo đuổi. Đôi bên đều muốn truyền cảm hứng khám phá thế giới qua những chuyến đi. Với Epic Sale lần này, Traveloka áp dụng ưu đãi đến 50% cho các sản phẩm du lịch, dịch vụ trên toàn thế giới. 'Đây là lời tri ân chúng tôi muốn gửi đến khách hàng đã luôn ủng hộ, gắn bó trên hành trình kiến tạo những chuyến đi đáng nhớ cùng Traveloka', ông Iko Putera cho biết. Từ khi trở thành đại sứ thương hiệu tại Việt Nam, diễn viên Ninh Dương Lan Ngọc đã có nhiều trải nghiệm du lịch chất lượng với nền tảng. Với loạt khuyến mại, ưu đãi, quà tặng trong Epic Sale 2024, cô nói sẽ tranh thủ săn vé, đặt phòng, chuẩn bị cho những chuyến đi sắp tới. Theo Lan Ngọc, chương trình mang lại cho du khách cơ hội du lịch tiện nghi với chi phí tiết kiệm, giúp khơi dậy mong muốn đi đây đi đó, khám phá thế giới. Cô đánh giá cao sự tiện lợi và các dịch vụ toàn diện của nền tảng, giúp việc lên kế hoạch cho các chuyến đi thêm dễ dàng, thú vị. Traveloka đã hợp tác cùng hàng nghìn đối tác để mang đến những deal giá ưu đãi sâu. Người dùng có thể truy cập nền tảng, theo dõi các ưu đãi hàng ngày trong các mục Vé máy bay, Khách sạn, Xperience và nhiều sản phẩm du lịch khác. 'Siêu ưu đãi Epic' (Super Epic Deal) sẽ được áp dụng cho các sản phẩm nhất định trong khung giờ giới hạn. Cụ thể, giờ vàng Epic Hour Deal ưu đãi vé máy bay mỗi thứ Bảy từ 14h-17h; đặt khách sạn giờ vàng EPIC Hotel Hour Deal diễn ra hàng ngày từ 18h-19h. Du khách có thể săn vé máy bay quốc nội và quốc tế với giá ưu đãi. Trong đó, vé nội địa Vietravel giá chỉ từ 781.925 đồng; vé China Southern Airlines đi Thâm Quyến từ 2,819 đồng; vé T'way Air đến Hàn Quốc và Nhật Bản lần lượt chỉ từ 2,667 triệu đồng và 2,682 triệu đồng. Khách hàng còn có cơ hội nghỉ dưỡng tại khách sạn 5 sao trong nước với giá từ 794.000 đồng. Hàng loạt khách sạn Hàn Quốc giá từ 1,858 triệu đồng, Nhật Bản từ 1,146 triệu đồng. Với dịch vụ giải trí, nền tảng áp dụng ưu đãi 'mua 1 tặng 1' vé tham quan Sun World, công viên nước The Amazing Bay, thủy cung Sea Life Bangkok Ocean World (Thái Lan). Để du khách có trải nghiệm du lịch trọn vẹn, Traveloka giới thiệu thêm nhiều tính năng khác như: hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt... Xem thêm thông tin chi tiết về chương trình Epic Sale trên ứng dụng, website và các tài khoản mạng xã hội của Traveloka. Á Hiên",
+  "summary": "781.925 đồng vé Vietravel, 2.819 triệu Thâm Quyến; 2.667 và 2.682 triệu Hàn Quốc-Nhật Bản. Khách sạn từ 794.000-1.858 triệu. Áp dụng 'mua 1 tặng 1' Sun World, The Amazing Bay, Sea Life Bangkok Ocean World. Hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt trên Traveloka. Epic Sale của Ninh Dương Lan Ngọc mong muốn lan tỏa tinh thần du lịch thông minh và áp dụng ưu đãi đến 50% cho các sản phẩm toàn thế giới nhằm tri ân khách hàng và khích lệ khám phá thế giới qua những chuyến đi tiện nghi với chi phí tiết kiệm.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng có thể thiếu một số chi tiết quan trọng như việc hợp tác giữa Traveloka và Ninh Dương Lan Ngọc, cũng như một số thông tin về các dịch vụ và ưu đãi cụ thể.",
+  "relevance_score": 0.7,
+  "relevance_reason": "Bản tóm tắt bao gồm một số ý chính như giá vé máy bay, khách sạn và các ưu đãi, nhưng có thể bỏ sót một số thông điệp cốt lõi như sứ mệnh của Traveloka và tầm ảnh hưởng của Ninh Dương Lan Ngọc.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, tuy nhiên có thể có một số từ ngữ lặp lại hoặc không cần thiết, nhưng tổng thể vẫn rõ ràng và súc tích."
+}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Thư mục KQ/VB sau tóm tắt/test_results.xlsx
+++ b/Thư mục KQ/VB sau tóm tắt/test_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taste Studio của Regent Hotels &amp; Resorts tổ chức với chủ đề 'Dáng hình của biển', giới hạn 20 khách mời mỗi tối. Sự kiện quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, từ Mr. Dripping (drip art) đến Francesco (Milan), Huân Trần (Regent Phú Quốc) và Andy Huỳnh (Oku). Regent Phú Quốc mong muốn tiếp tục kiến tạo trải nghiệm đưa nét bản địa đặc sắc lên bản đồ thế giới cho khách hàng hạng sang.</t>
+          <t>Regent Hotels &amp; Resorts tổ chức Taste Studio với chủ đề 'Dáng hình của biển', quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, giới hạn 20 khách mời mỗi tối.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -462,13 +462,13 @@
   "id": 1,
   "style": "news_brief",
   "article": "Taste Studio do thương hiệu Regent Hotels &amp; Resorts tổ chức nhằm mang đến trải nghiệm đa giác quan qua ẩm thực và nghệ thuật. Sự kiện này quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, từ nhà thiết kế thời trang đến nhạc sĩ, kết hợp cùng các thương hiệu hàng đầu như Vietnam Airlines. Sự kiện hướng đến phân khúc khách hàng sang trọng. Mùa một và hai diễn ra lần được vào tháng 4, tháng 11 năm ngoái. Taste Studio năm nay với chủ đề 'Dáng hình của biển', giới hạn 20 khách mời mỗi tối. Các khách mời được tham gia vào chuỗi khám phá gồm 7 chương đặc sắc về vẻ đẹp của biển, qua lăng kính nghệ sĩ tài hoa Mr. Dripping - nghệ sĩ vẽ tranh bằng phương pháp nhỏ giọt (drip art). Không gian nhà hàng, nơi diễn ra sự kiện với nội thất dùng tre, mây và tầm vông do kiến trúc sư Nguyễn Trung Nghĩa thiết kế. Ngoài hai nghệ sĩ này, Taste Studio còn có sự tham gia của bếp trưởng Francesco đến từ Milan, với 20 năm kinh nghiệm làm việc tại các khách sạn danh tiếng thế giới, đang bắt đầu hành trình mới tại Việt Nam. Ông đảm nhận vai trò cố vấn ẩm thực tại Regent Phú Quốc, mang đến trải nghiệm độc đáo cho thực khách. Bên cạnh đó, phó bếp trưởng điều hành Huân Trần tại chương trình mong muốn chinh phục các hương vị vùng miền khác nhau. Được nếm nhiều nguyên liệu địa phương và các loại gia vị đặc biệt, vị đầu bếp để lại điểm nhấn riêng trong cách giữ gìn, nâng tầm phong vị của quê hương tại Regent Phú Quốc. Chương trình có sự góp mặt của bếp trưởng nhà hàng Oku - Andy Huỳnh. Trước khi gia nhập Regent Phú Quốc, anh phát triển kỹ thuật nấu ăn Nhật Bản tại Nobu, San Diego và Nassau. Các món ăn của Andy luôn mang ý nghĩa hướng về cội nguồn. Bếp trưởng nhà hàng Ocean Club Daniel và bếp trưởng Duyến Nguyễn của khu nghỉ dưỡng này cũng tham gia, sáng tạo một số hương vị độc đáo từ nguyên liệu địa phương. Đại diện Regent Phú Quốc cho biết, thông qua Taste Studio, đơn vị mong muốn tiếp tục kiến tạo trải nghiệm đưa nét bản địa đặc sắc của Việt Nam lên bản đồ thế giới, từ đó chinh phục khách hàng hạng sang và giới chuyên gia. Thanh Thư",
-  "summary": "Taste Studio của Regent Hotels &amp; Resorts tổ chức với chủ đề 'Dáng hình của biển', giới hạn 20 khách mời mỗi tối. Sự kiện quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, từ Mr. Dripping (drip art) đến Francesco (Milan), Huân Trần (Regent Phú Quốc) và Andy Huỳnh (Oku). Regent Phú Quốc mong muốn tiếp tục kiến tạo trải nghiệm đưa nét bản địa đặc sắc lên bản đồ thế giới cho khách hàng hạng sang.",
-  "faithfulness_score": 0.9,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, nhưng có bỏ sót một số chi tiết quan trọng như sự tham gia của các thương hiệu hàng đầu và kiến trúc sư Nguyễn Trung Nghĩa",
-  "relevance_score": 0.8,
-  "relevance_reason": "Bản tóm tắt bao hàm các ý chính quan trọng, nhưng bỏ sót thông điệp về việc Regent Phú Quốc muốn chinh phục khách hàng hạng sang và giới chuyên gia",
+  "summary": "Regent Hotels &amp; Resorts tổ chức Taste Studio với chủ đề 'Dáng hình của biển', quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, giới hạn 20 khách mời mỗi tối.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như sự tham gia của các thương hiệu hàng đầu và nghệ sĩ tài năng",
+  "relevance_score": 0.6,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến chủ đề của sự kiện và giới hạn khách mời, nhưng bỏ qua các thông tin quan trọng về mục tiêu của chương trình và sự tham gia của các đầu bếp nổi tiếng",
   "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, nhưng có thể rút gọn một số chi tiết để tăng tính súc tích"
+  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và không có thông tin trùng lặp, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng để làm cho tóm tắt trở nên đầy đủ hơn"
 }</t>
         </is>
       </c>
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amiana Resort Nha Trang tiếp tục nhận hai giải thưởng quốc tế: 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới', nổi bật với kiến trúc tự nhiên kết hợp công nghệ, bãi biển riêng tư xanh mát, hồ bơi và vườn bảo vệ môi trường.</t>
+          <t>Amiana Resort Nha Trang tiếp tục nhận hai giải thưởng 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới', sau 4 năm liên tiếp. Phong cách hòa hợp giữa truyền thống và hiện đại tạo không gian thư giãn gần gũi thiên nhiên, biệt thự có cửa sổ lớn và ban công rộng, hồ bơi riêng tư và vườn nhiệt đới xanh mát. Resort chú trọng bảo vệ môi trường bằng giải pháp bền vững.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,13 +490,13 @@
   "id": 2,
   "style": "news_brief",
   "article": "Hai giải thưởng gồm 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới'. Đây cũng là năm thứ tư liên tiếp đơn vị đạt giải thưởng này, sau quá trình thẩm định từ hội đồng chuyên môn toàn cầu và bình chọn bởi hàng nghìn du khách, khách sạn quốc tế khác. 'Giải thưởng góp phần khẳng định Amiana Resort Nha Trang là điểm đến lý tưởng cho du khách tìm kiếm không gian riêng tư, gần gũi thiên nhiên với kiến trúc cao cấp, mang lại trải nghiệm sang trọng, độc đáo', đại diện resort chia sẻ. Amiana có kiến trúc hòa hợp thiên nhiên, kết hợp yếu tố truyền thống và hiện đại, tạo nên không gian thư giãn, sang trọng nhưng vẫn giữ được cảm giác gần gũi, yên bình. Bãi biển riêng tư với hàng dừa rợp bóng xanh mát là nơi du khách có thể thư giãn, nghỉ ngơi thoải mái. Resort còn tận dụng địa hình tự nhiên để bố trí các công trình công cộng như hồ bơi, nhà hàng, phòng hội nghị, spa... Các yếu tố đậm chất nhiệt đới như dừa xanh, sóng biển, đá và gỗ được lồng ghép khéo léo trong từng chi tiết thiết kế nội ngoại thất. Biệt thự, phòng nghỉ, nhà hàng đều có sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại. Mỗi căn biệt thự đều mang kiến trúc mở, sử dụng nội thất chủ yếu từ gỗ, đá tự nhiên. Tất cả phòng đều có cửa sổ lớn và ban công rộng, tối ưu tầm nhìn hướng biển với cảnh quan thiên nhiên vây quanh. Biệt thự còn có hồ bơi riêng, không gian vườn với các loại cây nhiệt đới, đảm bảo yếu tố riêng tư cho khách hàng. Resort không chỉ chú trọng xây dựng công trình tiện ích, mà còn đặc biệt lưu ý việc bảo vệ môi trường, sử dụng các giải pháp bền vững. Những không gian xanh, vườn cây, hồ nước đều được bố trí hợp lý, tạo nên hệ sinh thái tự nhiên trong lòng khu nghỉ dưỡng. Theo đại diện Amiana Resort Nha Trang, những chi tiết kiến trúc thông minh cùng không gian mở, vật liệu tự nhiên, sự khéo léo trong thiết kế tại đây góp phần tạo nên khu nghỉ dưỡng lý tưởng cho những ai tìm kiếm sự an yên, lãng mạn và xa hoa. Á Hiên",
-  "summary": "Amiana Resort Nha Trang tiếp tục nhận hai giải thưởng quốc tế: 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới', nổi bật với kiến trúc tự nhiên kết hợp công nghệ, bãi biển riêng tư xanh mát, hồ bơi và vườn bảo vệ môi trường.",
+  "summary": "Amiana Resort Nha Trang tiếp tục nhận hai giải thưởng 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới', sau 4 năm liên tiếp. Phong cách hòa hợp giữa truyền thống và hiện đại tạo không gian thư giãn gần gũi thiên nhiên, biệt thự có cửa sổ lớn và ban công rộng, hồ bơi riêng tư và vườn nhiệt đới xanh mát. Resort chú trọng bảo vệ môi trường bằng giải pháp bền vững.",
   "faithfulness_score": 0.9,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, nhưng có thể thiếu một số chi tiết quan trọng như việc Amiana Resort Nha Trang đạt giải thưởng này lần thứ tư liên tiếp và quá trình thẩm định từ hội đồng chuyên môn toàn cầu",
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể làm rõ hơn về quá trình thẩm định và bình chọn của hội đồng chuyên môn toàn cầu",
   "relevance_score": 0.8,
-  "relevance_reason": "Bản tóm tắt bao hàm các ý chính quan trọng như giải thưởng, kiến trúc và môi trường, nhưng có thể bỏ sót thông điệp cốt lõi về sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại",
+  "relevance_reason": "Tóm tắt đã bao gồm các điểm chính về giải thưởng và thiết kế của khu nghỉ dưỡng, nhưng bỏ qua một số chi tiết quan trọng như hệ sinh thái tự nhiên và sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại",
   "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, nhưng có thể loại bỏ một số từ ngữ không cần thiết để tăng tính súc tích"
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể rút gọn một số câu để tăng độ súc tích"
 }</t>
         </is>
       </c>
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gỗ lũa từ sông Tiền tạo nên khu du lịch Cồn Én, với tiểu cảnh, đài quan sát và bức tranh điêu khắc dài 24 m. Du khách đến TP HCM qua quốc lộ 30 hoặc phà Tấn Long thăm đảo này với giá vé 80.000 đồng, nơi người dân đã biến hàng nghìn thân gỗ lũa thành điểm tham quan yên bình.</t>
+          <t>Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ. Nơi đây là điểm đến ngắm dòng Tiền Giang và đón gió mát dịu. Du khách còn được tham quan khu du lịch sinh thái với bộ sưu tập gỗ lũa độc đáo. Gỗ lũa lấy từ đáy sông, sau khi bị bào mòn chỉ còn phần lõi bền chắc. Khu du lịch này có tiểu cảnh và nhà nghỉ làm bằng vật liệu chính là những thân cây khủng này. Một bức tranh điêu khắc dài hơn 24m nặng 20 tấn được thực hiện trên khúc gỗ trầm thủy, tùy từng đoạn chiều cao từ 1,5 - 1,8 m. Cạnh đó còn có bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ và tiểu cảnh làm từ gỗ lũa. Du khách cũng ngắm hoàng hôn trên sông tại đây. Giá vé vào cổng là 80.000 đồng.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,13 +518,13 @@
   "id": 3,
   "style": "news_brief",
   "article": "Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ, rộng hơn 300 ha. Nơi đây ngoài là điểm đến ngắm dòng Tiền Giang, đón gió sông mát dịu, còn là địa chỉ thu hút khách với bộ sưu tập gỗ lũa nội thất độc đáo của khu du lịch trên cồn. Gỗ lũa tức những thân cây khủng, vớt từ đáy sông, bên ngoài bị dòng nước bào mòn, chỉ còn phần lõi bền chắc. Hàng nghìn thân gỗ lũa được người chủ tuyển chọn làm vật liệu chính xây Khu du lịch sinh thái Cồn Én từ tiểu cảnh, nhà đến đài quan sát. Hơn 20 năm trước, ông Nguyễn Văn Nghỉ ở huyện Chợ Mới đã sưu tập rất nhiều gỗ lũa. Ban đầu ông trục vớt chúng để khơi thông dòng chảy, hạn chế tình trạng lưới đánh cá mắc vào thân cây. Lâu dần, ông yêu mến và muốn lưu giữ những thân gỗ trầm thủy này. Ba năm trước, ông Nghỉ dùng số gỗ lũa để xây khu du lịch ven sông Tiền rộng 6 ha. Đặc sắc trong các vật liệu từ gỗ lũa là bức tranh điêu khắc về phong cảnh làng quê Việt Nam xưa dài hơn 24 m, nặng 20 tấn. Bức tranh do nghệ nhân ở Huế thực hiện trong 7 năm, trên khúc gỗ trầm thủy khủng, tùy từng đoạn có chiều cao từ 1,5 - 1,8 m. Cạnh bức tranh là bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ như tứ quý, sảnh tiến tới của nhiều dòng xe nổi tiếng. Dọc các lối đi là những tiểu cảnh làm từ gỗ lũa. Một số được điêu khắc thành các con vật, chim muông. Những cây gỗ lũa kích thước lớn được tận dụng làm đài quan sát cao 26 m, hoặc móng trụ để xây nhà nghỉ, cầu vượt. Khuôn viên cũng được phủ bởi nhiều cây kiểng, dừa cùng dãy nhà sàn ven sông. Tại đây du khách được ngắm hoàng hôn trên sông, tắm sông và thưởng thức ẩm thực miền Tây. Chị Phúc Điền, du khách ở TP HCM, cho biết khá thích với khung cảnh miền Tây yên bình ở Cồn Én. Chị cũng bất ngờ với sự kỳ công của người đã sưu tập hàng nghìn thân gỗ lũa và biến chúng thành điểm tham quan độc đáo. Cồn Én, nằm cách TP HCM 170 km, du khách có thể đến đây từ hướng quốc lộ 30 của tỉnh Đồng Tháp hoặc lên phà Tấn Long vượt sông Tiền từ phía huyện Chợ Mới. Giá vé vào cổng là 80.000 đồng. Ngọc Tài",
-  "summary": "Gỗ lũa từ sông Tiền tạo nên khu du lịch Cồn Én, với tiểu cảnh, đài quan sát và bức tranh điêu khắc dài 24 m. Du khách đến TP HCM qua quốc lộ 30 hoặc phà Tấn Long thăm đảo này với giá vé 80.000 đồng, nơi người dân đã biến hàng nghìn thân gỗ lũa thành điểm tham quan yên bình.",
-  "faithfulness_score": 0.8,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin nhưng có thiếu sót một số chi tiết quan trọng như vị trí của Cồn Én, diện tích khu du lịch và một số hoạt động du lịch khác",
-  "relevance_score": 0.7,
-  "relevance_reason": "Bản tóm tắt chưa bao hàm đủ các ý chính quan trọng nhất như vị trí địa lý, các hoạt động du lịch và đặc điểm nổi bật của khu du lịch Cồn Én",
+  "summary": "Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ. Nơi đây là điểm đến ngắm dòng Tiền Giang và đón gió mát dịu. Du khách còn được tham quan khu du lịch sinh thái với bộ sưu tập gỗ lũa độc đáo. Gỗ lũa lấy từ đáy sông, sau khi bị bào mòn chỉ còn phần lõi bền chắc. Khu du lịch này có tiểu cảnh và nhà nghỉ làm bằng vật liệu chính là những thân cây khủng này. Một bức tranh điêu khắc dài hơn 24m nặng 20 tấn được thực hiện trên khúc gỗ trầm thủy, tùy từng đoạn chiều cao từ 1,5 - 1,8 m. Cạnh đó còn có bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ và tiểu cảnh làm từ gỗ lũa. Du khách cũng ngắm hoàng hôn trên sông tại đây. Giá vé vào cổng là 80.000 đồng.",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng thiếu một số chi tiết quan trọng như diện tích của khu du lịch và quá trình sưu tập gỗ lũa của ông Nguyễn Văn Nghỉ",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính như vị trí, đặc điểm của gỗ lũa và hoạt động du lịch, nhưng bỏ qua một số thông tin quan trọng như vị trí của Cồn Én so với TP HCM và cách di chuyển đến đó",
   "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt có mạch lạc, logic và dễ đọc, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng và tránh trùng lặp thông tin"
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể rút gọn một số câu để tăng độ súc tích"
 }</t>
         </is>
       </c>
@@ -535,27 +535,8 @@
           <t>Văn phòng mới của MayTrip tại địa chỉ 833 Lê Hồng Phong, quận 10, nhằm mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Văn phòng mới được kỳ vọng là điểm đến thuận tiện cho khách hàng trong việc tìm hiểu và sử dụng dịch vụ của công ty. Trong ngày khai trương, MayTrip trao tặng nhiều quà tặng và ưu đãi cho khách tham dự. Các voucher gồm: 2 triệu đồng cho khách đăng ký tour Bắc Á trong ba ngày khai trương, 1 triệu đồng cho tour Đông Nam Á trong ba tháng từ ngày khai trương, 500.000 đồng cho dịch vụ tour nội địa trong một năm, 200.000 đồng dịch vụ đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và 100.000 đồng với dịch vụ vé máy bay trong 6 tháng. Buổi lễ khai trương văn phòng tại Sài Gòn còn giới thiệu các chương trìnhtour Nhật Bảndịp Tết Âm lịch như cung đường vàng trải nghiệm trượt tuyết, Hokkaido - miền tuyết trắng. Những chuyến đi này được MayTrip thiết kế kỹ lưỡng, phù hợp với không khí đón xuân cho gia đình và cặp đôi Việt trong dịp Tết Nguyên đán. Năm nay, MayTrip xác định tour Hokkaido là sản phẩm 'đinh' trong dịp Tết Nguyên đán. Hokkaido nằm ở miền Bắc Nhật Bản, nổi tiếng với những đợt tuyết dày và phong cảnh mùa đông đặc trưng. Tour Hokkaido dịp Tết là hành trình lý tưởng để du khách tận hưởng kỳ nghỉ theo cách mới mẻ và ấn tượng trong tuyết trắng. Bên cạnh đó, tour Hokkaido của MayTrip cũng mang đến trải nghiệm suối nước nóng onsen giữa băng tuyết, giúp du khách thư giãn sau những hoạt động trong ngày. Bên cạnh đó, MayTrip cũng cung cấp các tour du lịch khác với lịch khởi hành linh hoạt kéo dài đến hết năm 2025, gồm hành trình ngắm hoa anh đào, hoa mơ, mận và nghỉ lễ 30/4 và 1/5. Các hành trình này dựa trên xu hướng và sở thích của du khách Việt Nam. Theo đại diện công ty, sự kiện khai trương văn phòng mới tại TP HCM đánh dấu bước phát triển mới của MayTrip. Với mục tiêu ưu tiên trải nghiệm khách hàng, đơn vị hy vọng nhận được sự ủng hộ từ khách hàng để trở thành công ty lữ hành hàng đầu, hướng mục tiêu thương hiệu toàn cầu vào năm 2030. Ngoài TP HCM, MayTrip còn có văn phòng tại Hải Phòng và TP Vinh. Các văn phòng này giúp MayTrip dễ dàng tiếp cận và đáp ứng nhu cầu đa dạng của khách hàng. Công ty cam kết đảm bảo chất lượng dịch vụ để mang lại chuyến đi an toàn, trọn vẹn cho khách hàng. Thanh Thư</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MayTrip khai trương văn phòng mới tại 833 Lê Hồng Phong, quận 10 (TP HCM), với ưu đãi và tour Hokkaido dịp Tết Nguyên đán. Công ty đặt mục tiêu trở thành công ty lữ hành hàng đầu toàn cầu vào năm 2030, cam kết chất lượng dịch vụ an toàn cho khách.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{
-  "id": 4,
-  "style": "news_brief",
-  "article": "Văn phòng mới của MayTrip tại địa chỉ 833 Lê Hồng Phong, quận 10, nhằm mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Văn phòng mới được kỳ vọng là điểm đến thuận tiện cho khách hàng trong việc tìm hiểu và sử dụng dịch vụ của công ty. Trong ngày khai trương, MayTrip trao tặng nhiều quà tặng và ưu đãi cho khách tham dự. Các voucher gồm: 2 triệu đồng cho khách đăng ký tour Bắc Á trong ba ngày khai trương, 1 triệu đồng cho tour Đông Nam Á trong ba tháng từ ngày khai trương, 500.000 đồng cho dịch vụ tour nội địa trong một năm, 200.000 đồng dịch vụ đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và 100.000 đồng với dịch vụ vé máy bay trong 6 tháng. Buổi lễ khai trương văn phòng tại Sài Gòn còn giới thiệu các chương trìnhtour Nhật Bảndịp Tết Âm lịch như cung đường vàng trải nghiệm trượt tuyết, Hokkaido - miền tuyết trắng. Những chuyến đi này được MayTrip thiết kế kỹ lưỡng, phù hợp với không khí đón xuân cho gia đình và cặp đôi Việt trong dịp Tết Nguyên đán. Năm nay, MayTrip xác định tour Hokkaido là sản phẩm 'đinh' trong dịp Tết Nguyên đán. Hokkaido nằm ở miền Bắc Nhật Bản, nổi tiếng với những đợt tuyết dày và phong cảnh mùa đông đặc trưng. Tour Hokkaido dịp Tết là hành trình lý tưởng để du khách tận hưởng kỳ nghỉ theo cách mới mẻ và ấn tượng trong tuyết trắng. Bên cạnh đó, tour Hokkaido của MayTrip cũng mang đến trải nghiệm suối nước nóng onsen giữa băng tuyết, giúp du khách thư giãn sau những hoạt động trong ngày. Bên cạnh đó, MayTrip cũng cung cấp các tour du lịch khác với lịch khởi hành linh hoạt kéo dài đến hết năm 2025, gồm hành trình ngắm hoa anh đào, hoa mơ, mận và nghỉ lễ 30/4 và 1/5. Các hành trình này dựa trên xu hướng và sở thích của du khách Việt Nam. Theo đại diện công ty, sự kiện khai trương văn phòng mới tại TP HCM đánh dấu bước phát triển mới của MayTrip. Với mục tiêu ưu tiên trải nghiệm khách hàng, đơn vị hy vọng nhận được sự ủng hộ từ khách hàng để trở thành công ty lữ hành hàng đầu, hướng mục tiêu thương hiệu toàn cầu vào năm 2030. Ngoài TP HCM, MayTrip còn có văn phòng tại Hải Phòng và TP Vinh. Các văn phòng này giúp MayTrip dễ dàng tiếp cận và đáp ứng nhu cầu đa dạng của khách hàng. Công ty cam kết đảm bảo chất lượng dịch vụ để mang lại chuyến đi an toàn, trọn vẹn cho khách hàng. Thanh Thư",
-  "summary": "MayTrip khai trương văn phòng mới tại 833 Lê Hồng Phong, quận 10 (TP HCM), với ưu đãi và tour Hokkaido dịp Tết Nguyên đán. Công ty đặt mục tiêu trở thành công ty lữ hành hàng đầu toàn cầu vào năm 2030, cam kết chất lượng dịch vụ an toàn cho khách.",
-  "faithfulness_score": 0.9,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, nhưng có thể thêm chi tiết về các ưu đãi và tour du lịch để tăng tính trung thực",
-  "relevance_score": 0.8,
-  "relevance_reason": "Bản tóm tắt bao gồm các ý chính quan trọng, nhưng có thể bỏ sót thông điệp cốt lõi về mục tiêu của công ty và các văn phòng khác",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, nhưng có thể rút gọn một số chi tiết để tăng tính súc tích"
-}</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -564,22 +545,7 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{
-  "id": 5,
-  "style": "news_brief",
-  "article": "Ngày 29/10, tại Khu du lịch Sun World Fansipan Legend, Hiệp hội Du lịch tỉnh Lào Cai công bố chương trình kích cầu du lịch lớn nhất năm với chủ đề 'Chạm Sa Pa - Chạm những tầng mây', diễn ra từ 2/11 đến 30/12. Trong thời gian này, 130 doanh nghiệp tại Sa Pa sẽ cung cấp nhiều ưu đãi lên đến 50% và cam kết đảm bảo chất lượng dịch vụ. Theo đó, Công ty Cáp treo Fansipan Sa Pa (Khu du lịch Sun World Fansipan Legend) áp dụng đồng giá vé cáp treo hai chiều Fansipan chỉ còn 550.000 đồng cho du khách Việt Nam. Mức giá này giảm 30% so với giá gốc. Du khách có thể khám phá đỉnh Fansipan, chiêm ngưỡng kiến trúc tâm linh và tham gia các hoạt động văn hóa của 7 dân tộc thiểu số Tây Bắc tại Bản Mây. Nhiều điểm du lịch khác tại Sa Pa cũng miễn phí vé tham quan và cung cấp ưu đãi hấp dẫn. Trong đó, vườn đá Tả Phìn và vườn hồng Mộng Mơ miễn phí vé, Khu du lịch Cát Cát miễn phí trải nghiệm ẩm thực Tây Bắc cùng các hoạt động vẽ sáp ong, xe lanh, dệt vải... với bà con dân bản. Các khách sạn như Chaulong Sapa, Amazing Sapa, Vườn Sa Pa, Arista Sa Pa và Le Bordeaux Sapa áp dụng giảm giá phòng trực tiếp tới 50%. Hotel de la Coupole và Lady Hill Sapa Resort có nhiều ưu đãi về dịch vụ ăn uống, spa. Một số nhà xe như Inter Bus Lines và Eco Sa Pa cũng giảm giá vé xe khứ hồi đến 30%, cung cấp đa dạng hình thức di chuyển từ xe limousine đến xe lớn. Ông Phạm Cao Vỹ, đại diện Hiệp hội Du lịch tỉnh Lào Cai nhấn mạnh sự cần thiết của việc kích cầu du lịch để phục hồi ngành sau ảnh hưởng nặng nề của bão lũ. Ông kêu gọi tất cả doanh nghiệp du lịch trên địa bàn tham gia nhằm tạo sức bật cho du lịch Sa Pa phát triển mạnh mẽ vào giai đoạn cuối năm 2024. Ông Nguyễn Xuân Chiến, Phó chủ tịch Sun Group Vùng Miền Bắc, cho biết trước đây chương trình kích cầu 'Đến Sa Pa - Bay giữa mùa hoa' thành công ngoài mong đợi. 'Lần này, thông qua chính sách ưu đãi sâu, chúng tôi hy vọng thu hút đông đảo du khách đến Sa Pa để khám phá vẻ đẹp độc đáo của mùa mây', ông Chiến nói. Ngoài chính sách ưu đãi sâu, tỉnh Lào Cai và thị xã Sa Pa tổ chức nhiều sự kiện văn hóa đặc sắc nhằm mang đến trải nghiệm độc đáo cho du khách. Các hoạt động bao gồm lễ hội truyền thống, triển lãm nghệ thuật, thể thao và giải trí. Đặc biệt là sự kiện ánh sáng 3D Mapping và lễ hội hoa sen đá lần đầu tiên được tổ chức tại Sun World Fansipan Legend. Sa Pa đang trong mùa mây - thời điểm lý tưởng để vui chơi ngoài trời. Ban tổ chức kỳ vọng chương trình kích cầu sẽ tăng sức hút của Sa Pa và củng cố vị thế là điểm đến hàng đầu miền Bắc. Thanh Thư",
-  "summary": "",
-  "faithfulness_score": 1.0,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, không sai số liệu và không xuyên tạc ý nghĩa của văn bản gốc.",
-  "relevance_score": 1.0,
-  "relevance_reason": "Bản tóm tắt bao hàm đủ các ý chính quan trọng nhất, không bỏ sót thông điệp cốt lõi nào.",
-  "coherence_conciseness_score": 1.0,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic, dễ đọc và loại bỏ được các chi tiết rườm rà/lặp từ không."
-}</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -587,27 +553,8 @@
           <t>Brisbane nằm phía đông nam bang Queensland, là thành phố lớn thứ ba tại Australia. Do gần đường xích đạo, khí hậu nơi đây ôn hòa, quanh năm nắng ấm. Trung tâm Brisbane không chỉ có những khối bê tông, khu mua sắm, mà còn bao phủ bởi mảng xanh, với 5 công viên và vườn thực vật nổi tiếng. Dưới đây là 5 điểm đến hút du khách ở Brisbane. South Bank Parklands Nằm bên bờ sông Brisbane, South Bank Parklands được ví như 'ốc đảo xanh' giữa lòng thành phố sôi động, nổi bật với rừng mưa nhiệt đới và loạt hoạt động giải trí cho mọi lứa tuổi. Ngay cửa ngõ công viên là thảm cỏ, hàng cây rợp bóng và vườn hoa. Nhiều người dân thường picnic, dã ngoại, vui chơi tại bãi biển nhân tạo Streets Beach, River Quay Green, Rainforest Green hay Liana Lounge. Ngoài ra, Wheel of Brisbane - vòng đu quay cao tới 60 m - là biểu tượng tại South Bank Parklands, dễ dàng ngắm toàn cảnh Brisbane từ trên cao. Roma Street Parkland Nằm cạnh ga xe lửa Roma Street, công viên cùng tên cũng được người dân lẫn du khách gọi là 'ốc đảo xanh mát' giữa Brisbane, ghi dấu với những khu vườn và bãi cỏ rộng lớn. Tại đây, du khách hòa mình vào khu vườn Spectacle - nơi trồng hàng nghìn gốc violets, cẩm chướng, delphiniums và foxgloves. Khí hậu ôn hòa thu hút chim kookaburras, gà lôi, vẹt. Bạn cũng có thể tổ chức tiệc BBQ ngoài trời, cho con khám phá công viên trẻ em. Brisbane City Botanic Gardens Nằm trên trục đường Alice, Brisbane City Botanic Gardens bảo tồn hàng nghìn loài thực vật quý hiếm, nổi bật với vẻ nguyên sơ. Khu vườn này là một trong những điểm đến lý tưởng cho người chuộng nét thanh bình giữa lòng đô thị. Tại đây, du khách có thể khám phá con đường dạo bộ ven sông, chiêm ngưỡng rặng thông Bunya được trồng từ năm 1858. Điểm đến tiếp theo là Bamboo Grove - con đường tre rợp mát, được ví như 'khu rừng xa xôi giữa thành phố hiện đại'. Vườn bách thảo tổ chức sự kiện quanh năm như biểu diễn Riverstage, lễ hội đa văn hóa, trưng bày nghệ thuật cùng hoạt động cộng đồng miễn phí. Trong đó, chợ Riverside Sunday Market hút hàng nghìn du khách nhờ gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden Tại Epicurious, du khách có thể khám phá ẩm thực bang Queensland đa dạng, nhất là rau, củ, quả, thảo mộc hữu cơ theo mùa. 14 chuyên viên tình nguyện chăm sóc khu vườn kỹ lưỡng, mong truyền cảm hứng cho người yêu nấu ăn và trồng trọt. 'Tới Epicurious, tôi và bạn bè được hướng dẫn cách chăm sóc rau củ, trái cây, thảo mộc và thưởng thức miễn phí', một du khách viết trên Facebook, nhận hàng trăm nghìn lượt thích. Mount Coot-tha Botanic Gardens Mở cửa đón khách từ năm 1976, Mount Coot-tha Botanic Gardens tọa lạc chân núi Coot-tha, là vườn thực vật nhiệt đới hàng đầu Brisbane, diện tích đến 56 ha. Dạo quanh khu vườn, du khách có thể chiêm ngưỡng hoa xuân, các loài cây nhiệt đới và khu thảo dược. Nơi đây là điểm đến quen thuộc của người yêu thiên nhiên, picnic, mê hoạt động thể chất, với đường chạy bộ thoáng đãng. Để khám phá thành thủ phủ bang Queensland, bạn có thể chọn đường bay thẳng từ TP HCM đến Brisbane của Vietjet, với 9 giờ trên máy bay thân rộng, thoải mái cùng loạt dịch vụ tiện ích, ưu đãi như: bảo hiểm Sky Care miễn phí, chương trình tích điểm SkyJoy, đổi quà từ hơn 250 thương hiệu lớn toàn cầu. Trước đó ngày14-15/9, Vietjet đồng hành lễ hội thả diều Vietjet Redcliffe KiteFest tại Redcliffe, Queensland. Hãng hàng không Việt còn áp dụng nhiều chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu. Đông Vệ</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Brisbane, thành phố lớn thứ ba của Australia với khí hậu ôn hòa quanh năm. Thành phố có nhiều công viên và vườn thực vật nổi tiếng như South Bank Parklands, Roma Street Parkland và Brisbane City Botanic Gardens bảo tồn hàng nghìn loài cây quý hiếm trên trục đường Alice. Hội chợ Riverside Sunday Market hút du khách với gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden giới thiệu ẩm thực Queensland đa dạng. Mount Coot-tha Botanic Gardens nằm trên núi Coot-tha, là vườn thực vật lớn của Brisbane. Vietjet cung cấp đường bay thẳng TP HCM - Brisbane với nhiều dịch vụ tiện ích và chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{
-  "id": 6,
-  "style": "news_brief",
-  "article": "Brisbane nằm phía đông nam bang Queensland, là thành phố lớn thứ ba tại Australia. Do gần đường xích đạo, khí hậu nơi đây ôn hòa, quanh năm nắng ấm. Trung tâm Brisbane không chỉ có những khối bê tông, khu mua sắm, mà còn bao phủ bởi mảng xanh, với 5 công viên và vườn thực vật nổi tiếng. Dưới đây là 5 điểm đến hút du khách ở Brisbane. South Bank Parklands Nằm bên bờ sông Brisbane, South Bank Parklands được ví như 'ốc đảo xanh' giữa lòng thành phố sôi động, nổi bật với rừng mưa nhiệt đới và loạt hoạt động giải trí cho mọi lứa tuổi. Ngay cửa ngõ công viên là thảm cỏ, hàng cây rợp bóng và vườn hoa. Nhiều người dân thường picnic, dã ngoại, vui chơi tại bãi biển nhân tạo Streets Beach, River Quay Green, Rainforest Green hay Liana Lounge. Ngoài ra, Wheel of Brisbane - vòng đu quay cao tới 60 m - là biểu tượng tại South Bank Parklands, dễ dàng ngắm toàn cảnh Brisbane từ trên cao. Roma Street Parkland Nằm cạnh ga xe lửa Roma Street, công viên cùng tên cũng được người dân lẫn du khách gọi là 'ốc đảo xanh mát' giữa Brisbane, ghi dấu với những khu vườn và bãi cỏ rộng lớn. Tại đây, du khách hòa mình vào khu vườn Spectacle - nơi trồng hàng nghìn gốc violets, cẩm chướng, delphiniums và foxgloves. Khí hậu ôn hòa thu hút chim kookaburras, gà lôi, vẹt. Bạn cũng có thể tổ chức tiệc BBQ ngoài trời, cho con khám phá công viên trẻ em. Brisbane City Botanic Gardens Nằm trên trục đường Alice, Brisbane City Botanic Gardens bảo tồn hàng nghìn loài thực vật quý hiếm, nổi bật với vẻ nguyên sơ. Khu vườn này là một trong những điểm đến lý tưởng cho người chuộng nét thanh bình giữa lòng đô thị. Tại đây, du khách có thể khám phá con đường dạo bộ ven sông, chiêm ngưỡng rặng thông Bunya được trồng từ năm 1858. Điểm đến tiếp theo là Bamboo Grove - con đường tre rợp mát, được ví như 'khu rừng xa xôi giữa thành phố hiện đại'. Vườn bách thảo tổ chức sự kiện quanh năm như biểu diễn Riverstage, lễ hội đa văn hóa, trưng bày nghệ thuật cùng hoạt động cộng đồng miễn phí. Trong đó, chợ Riverside Sunday Market hút hàng nghìn du khách nhờ gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden Tại Epicurious, du khách có thể khám phá ẩm thực bang Queensland đa dạng, nhất là rau, củ, quả, thảo mộc hữu cơ theo mùa. 14 chuyên viên tình nguyện chăm sóc khu vườn kỹ lưỡng, mong truyền cảm hứng cho người yêu nấu ăn và trồng trọt. 'Tới Epicurious, tôi và bạn bè được hướng dẫn cách chăm sóc rau củ, trái cây, thảo mộc và thưởng thức miễn phí', một du khách viết trên Facebook, nhận hàng trăm nghìn lượt thích. Mount Coot-tha Botanic Gardens Mở cửa đón khách từ năm 1976, Mount Coot-tha Botanic Gardens tọa lạc chân núi Coot-tha, là vườn thực vật nhiệt đới hàng đầu Brisbane, diện tích đến 56 ha. Dạo quanh khu vườn, du khách có thể chiêm ngưỡng hoa xuân, các loài cây nhiệt đới và khu thảo dược. Nơi đây là điểm đến quen thuộc của người yêu thiên nhiên, picnic, mê hoạt động thể chất, với đường chạy bộ thoáng đãng. Để khám phá thành thủ phủ bang Queensland, bạn có thể chọn đường bay thẳng từ TP HCM đến Brisbane của Vietjet, với 9 giờ trên máy bay thân rộng, thoải mái cùng loạt dịch vụ tiện ích, ưu đãi như: bảo hiểm Sky Care miễn phí, chương trình tích điểm SkyJoy, đổi quà từ hơn 250 thương hiệu lớn toàn cầu. Trước đó ngày14-15/9, Vietjet đồng hành lễ hội thả diều Vietjet Redcliffe KiteFest tại Redcliffe, Queensland. Hãng hàng không Việt còn áp dụng nhiều chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu. Đông Vệ",
-  "summary": "Brisbane, thành phố lớn thứ ba của Australia với khí hậu ôn hòa quanh năm. Thành phố có nhiều công viên và vườn thực vật nổi tiếng như South Bank Parklands, Roma Street Parkland và Brisbane City Botanic Gardens bảo tồn hàng nghìn loài cây quý hiếm trên trục đường Alice. Hội chợ Riverside Sunday Market hút du khách với gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden giới thiệu ẩm thực Queensland đa dạng. Mount Coot-tha Botanic Gardens nằm trên núi Coot-tha, là vườn thực vật lớn của Brisbane. Vietjet cung cấp đường bay thẳng TP HCM - Brisbane với nhiều dịch vụ tiện ích và chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu.",
-  "faithfulness_score": 0.8,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng có bỏ sót một số chi tiết quan trọng như mô tả cụ thể về các hoạt động giải trí tại South Bank Parklands và Roma Street Parkland",
-  "relevance_score": 0.9,
-  "relevance_reason": "Bản tóm tắt bao hàm đủ các ý chính quan trọng nhất về các điểm đến hút du khách ở Brisbane, tuy nhiên có thể thêm thông tin về các sự kiện và hoạt động tại các công viên",
-  "coherence_conciseness_score": 0.7,
-  "coherence_conciseness_reason": "Bản tóm tắt có logic và dễ đọc nhưng có thể cải thiện bằng cách loại bỏ các từ ngữ lặp từ và sắp xếp lại cấu trúc câu cho rõ ràng hơn"
-}</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -616,22 +563,7 @@
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{
-  "id": 7,
-  "style": "news_brief",
-  "article": "Công ty du lịch NhatbanAZ mở bán chùm tour Nhật Bản khởi hành dịp Tết Dương lịch và Âm lịch từ đầu tháng 10. Trong đó, các tour truyền thống đến Osaka, Kyoto và Tokyo được làm mới bằng những hoạt động phù hợp với mùa đông xuân như trượt tuyết tại Fujiten Resort, ngắm tuyết làng cổ Oshino Hakkai và tham gia lễ hội ánh sáng Nabana no sato. NhatbanAZ cũng mở rộng các cung đường mới cho du khách trải nghiệm trong dịp Tết 2025. Cụ thể, tour Hokkaido gồm Asahikawa, Monbetsu và Sapporo với giá 55,9 triệu đồng mỗi khách. Du khách sẽ tham gia câu cá trên băng, đi tàu phá băng và thưởng thức bia hơi tại Sapporo, cùng dịch vụ hàng không 5 sao và lưu trú khách sạn 4 sao quốc tế. Tour thứ hai là chuyến thăm làng cổ Shirakawago, núi Phú Sĩ và Tokyo trong 6 ngày 5 đêm với giá 31,9 triệu đồng mỗi khách. Du khách sẽ được chiêm ngưỡng tuyết trắng tại Shirakawago, một Di sản Văn hóa Thế giới của UNESCO từ năm 1995. Tour cũng gồm tham quan lâu đài Matsumoto - di tích bảo vật quốc gia của Nhật Bản và trải nghiệm trượt tuyết tại Fujiten Snow Resort - top 3 khu trượt tuyết nổi tiếng. Bà Hồ Như Thảo, Giám đốc Điều hành NhatbanAZ Văn phòng TP HCM cho biết sản phẩm mới này nhận được sự quan tâm lớn từ du khách, đặc biệt là những người từng đi Nhật và muốn trở lại với hành trình mới. Khu vực Hokkaido được biết đến với tuyết rơi dày đặc hơn Tokyo hay Osaka, nên lịch khởi hành tour Hokkaido dịp Tết Âm lịch nhận được nhiều đăng ký giữ chỗ. Trong dịp Tết Nguyên đán 2025, NhatbanAZ cung cấp các hành trình từ 5 đến 6 ngày với mức giá cơ bản đến cao cấp, khoảng 31,9 - 55,9 triệu đồng mỗi khách để đáp ứng nhu cầu đa dạng. Giá tour Tết có phần chênh lệch so với ngày thường và tăng so với cùng kỳ năm trước. Do đó, NhatbanAZ chủ động gặp gỡ và làm việc với các đối tác cung cấp dịch vụ, từ đó xây dựng chương trình, đưa ra chính sách ưu đãi tốt nhất cho khách hàng. Với kinh nghiệm hơn 15 năm trong ngành du lịch chuyên thị trường Nhật Bản, NhatbanAZ thuộc danh sách công ty chỉ định nộp visa bởi Đại sứ quán Nhật Bản đề xuất. Đồng thời là đối tác chiến lược của các hãng hàng không, khách sạn và đối tác land tour uy tín tại Nhật Bản. Công ty cũng là nhà tư vấn và tổ chức những chuyến Famtrip kết nối các công ty du lịch Việt Nam tới tham quan xúc tiến đầu tư, hợp tác tại Nhật Bản. Thanh Thư",
-  "summary": "",
-  "faithfulness_score": 1.0,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, sai số liệu, hay xuyên tạc ý nghĩa của văn bản gốc",
-  "relevance_score": 1.0,
-  "relevance_reason": "Bản tóm tắt bao hàm đủ các ý chính quan trọng nhất và không bỏ sót thông điệp cốt lõi nào",
-  "coherence_conciseness_score": 1.0,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic, dễ đọc và loại bỏ được các chi tiết rườm rà/lặp từ không"
-}</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -639,27 +571,8 @@
           <t>Theo bảng xếp hạng 20 quốc gia tốt nhất thế giới năm 2024 (The Best Countries in the World) do tạp chí du lịch Mỹ Condé Nast Traveler công bố vào tháng 10, Việt Nam ở vị trí 15 với 89 điểm. Một điểm đến khác thuộc Đông Nam Á có mặt trong danh sách này là Thái Lan, xếp thứ ba với 92,29 điểm. Đứng đầu top 20 là Nhật Bản với 95,32 điểm. Xếp hạng nằm trong giải thưởng thường niênReaders' Choice Awards của tạp chí Mỹ, dựa trên đánh giá của hơn 575.000 độc giả về các trải nghiệm du lịch ở mỗi quốc gia, xét theo các tiêu chí văn hóa, cảnh quan, dịch vụ du lịch và cơ sở hạ tầng. Độc giả của Condé Nast Traveler nhận xét Việt Nam thu hút du khách nhờ vẻ đẹp mộc mạc và quyến rũ. 'Với lượng khách nước ngoài đang trên đà tăng từ 2019 đến nay, Việt Nam không còn là điểm đến đáng chú ý mà thành điểm đến đáng ghé thăm', biên tập tờ Condé Nast Traveler viết. Theo số liệu từ Tổng cục Thống kê, trong 9 tháng đầu năm, Việt Nam đón hơn 12,7 triệu lượt khách quốc tế, vượt lượng khách cả năm 2023 là 12,6 triệu lượt. Lượng khách quốc tế đến Việt Nam tăng trưởng tích cực 9 tháng đầu năm 2024, với một số thị trường phục hồi hoàn toàn, tăng mạnh so với 2019, theo Cục Du lịch Quốc gia. Cục cũng dự đoán với đà tăng trường như hiện nay, Việt Nam sẽ hoàn thành mục tiêu đón 17-18 triệu lượt khách quốc tế năm 2024. Thái Lan được tạp chí Mỹ nhận xét là quốc gia đa dạng cảnh quan, giao thông thuận tiện với nhiều tàu thuyền, xe buýt đêm và chuyến bay nội địa giá rẻ. Ẩm thực cũng là điểm sáng của xứ chùa Vàng khi có nhiều khu chợ đêm nhộn nhịp, bày bán đặc sản địa phương. 8 tháng đầu năm 2024, Thái Lan đón hơn 20 triệu lượt khách quốc tế, tăng 34% so với cùng kỳ năm trước. Quốc gia này đặt mục tiêu đón ít nhất 36-37 triệu lượt khách nước ngoài trong cả năm nay, kỳ vọng thu về khoảng 3.500 tỷ baht (95,5 tỷ USD). Condé Nast Traveler là tạp chí du lịch nổi tiếng toàn cầu, ra mắt vào năm 1987. Các bảng xếp hạng của Condé Nast Traveler như Readers' Choice Awards được chuyên gia du lịch đánh giá là uy tín vì dựa trên ý kiến từ hàng triệu độc giả quốc tế. Bích Phương(TheoCNTraveller)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LỖI: 'NoneType' object is not iterable</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{
-  "id": 8,
-  "style": "news_brief",
-  "article": "Theo bảng xếp hạng 20 quốc gia tốt nhất thế giới năm 2024 (The Best Countries in the World) do tạp chí du lịch Mỹ Condé Nast Traveler công bố vào tháng 10, Việt Nam ở vị trí 15 với 89 điểm. Một điểm đến khác thuộc Đông Nam Á có mặt trong danh sách này là Thái Lan, xếp thứ ba với 92,29 điểm. Đứng đầu top 20 là Nhật Bản với 95,32 điểm. Xếp hạng nằm trong giải thưởng thường niênReaders' Choice Awards của tạp chí Mỹ, dựa trên đánh giá của hơn 575.000 độc giả về các trải nghiệm du lịch ở mỗi quốc gia, xét theo các tiêu chí văn hóa, cảnh quan, dịch vụ du lịch và cơ sở hạ tầng. Độc giả của Condé Nast Traveler nhận xét Việt Nam thu hút du khách nhờ vẻ đẹp mộc mạc và quyến rũ. 'Với lượng khách nước ngoài đang trên đà tăng từ 2019 đến nay, Việt Nam không còn là điểm đến đáng chú ý mà thành điểm đến đáng ghé thăm', biên tập tờ Condé Nast Traveler viết. Theo số liệu từ Tổng cục Thống kê, trong 9 tháng đầu năm, Việt Nam đón hơn 12,7 triệu lượt khách quốc tế, vượt lượng khách cả năm 2023 là 12,6 triệu lượt. Lượng khách quốc tế đến Việt Nam tăng trưởng tích cực 9 tháng đầu năm 2024, với một số thị trường phục hồi hoàn toàn, tăng mạnh so với 2019, theo Cục Du lịch Quốc gia. Cục cũng dự đoán với đà tăng trường như hiện nay, Việt Nam sẽ hoàn thành mục tiêu đón 17-18 triệu lượt khách quốc tế năm 2024. Thái Lan được tạp chí Mỹ nhận xét là quốc gia đa dạng cảnh quan, giao thông thuận tiện với nhiều tàu thuyền, xe buýt đêm và chuyến bay nội địa giá rẻ. Ẩm thực cũng là điểm sáng của xứ chùa Vàng khi có nhiều khu chợ đêm nhộn nhịp, bày bán đặc sản địa phương. 8 tháng đầu năm 2024, Thái Lan đón hơn 20 triệu lượt khách quốc tế, tăng 34% so với cùng kỳ năm trước. Quốc gia này đặt mục tiêu đón ít nhất 36-37 triệu lượt khách nước ngoài trong cả năm nay, kỳ vọng thu về khoảng 3.500 tỷ baht (95,5 tỷ USD). Condé Nast Traveler là tạp chí du lịch nổi tiếng toàn cầu, ra mắt vào năm 1987. Các bảng xếp hạng của Condé Nast Traveler như Readers' Choice Awards được chuyên gia du lịch đánh giá là uy tín vì dựa trên ý kiến từ hàng triệu độc giả quốc tế. Bích Phương(TheoCNTraveller)",
-  "summary": "LỖI: 'NoneType' object is not iterable",
-  "faithfulness_score": 0.0,
-  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin gì về văn bản gốc, không có nội dung để đánh giá tính trung thực.",
-  "relevance_score": 0.0,
-  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không thể đánh giá tính bao quát.",
-  "coherence_conciseness_score": 0.0,
-  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá tính mạch lạc và súc tích."
-}</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -667,27 +580,8 @@
           <t>Theo KTO Việt Nam, 8 tháng năm nay, Hàn Quốc đón 389.000 lượt khách Việt, tăng 27% so với cùng kỳ năm 2023. Số lượng khách Việt Nam đến Hàn Quốc dự kiến tăng mạnh hơn bởi đất nước này đang bước vào mùa lá vàng đẹp nhất năm. Đại diện KTO khẳng định, Việt Nam là thị trường quan trọng với ngành du lịch Hàn Quốc với nhiều sự kiện tổ chức thành công. Cụ thể, trong năm nay, KTO Việt Nam xúc tiến các chương trình quảng bá, phát triển sản phẩm du lịch Hàn Quốc phù hợp với nhu cầu du khách Việt. Kết quả, nhiều sản phẩm du lịch mới được ra mắt thị trường trong nước như: tour du lịch Hàn Quốc kết hợp giải chạy Marathon tại Gyeongju và Jeju, tour trải nghiệm Esports, tour lễ hội đèn lồng truyền thống Yeondeunghoe hay tour đạp xe đạp đường dài khám phá Hàn Quốc... Chương trình Năm du lịch Hàn Quốc 2023-2024 (Visit Korea Year 2023-2024) do Tổng cục du lịch Hàn Quốc (KTO) triển khai cũng mang đến những hoạt động mới mẻ, quảng bá du lịch Hàn Quốc đến cộng đồng quốc tế. Bên cạnh đó, nhằm mang đến những trải nghiệm chân thực và đậm chất bản địa, KTO tổ chức nhiều famtour. Nổi bật là famtour trải nghiệm Esports cùng các KOL hàng đầu làng thể thao điện tử như: SofM, reviewer Duy Thẩm, Hải Triều, streamer Hà Tiều Phu, BLV Esports nổi tiếng Văn Tùng, Hoàng Luân, kết hợp Box Esports. Làn sóng văn hóa Hallyu cũng được lồng ghép vào sản phẩm du lịch, khi hàng loạt tên tuổi lớn đến Việt Nam trong khuôn khổ sự kiện Korea Travel Festa, tổ chức tháng 5 vừa qua. Mới nhất, KTO Việt Nam có mặt tại Hội chợ Du lịch Quốc tế (ITE) TP HCM, mang theo không gian đặc trưng Hàn Quốc cùng nhiều trải nghiệm mới mẻ, độc đáo. Nắm bắt nhu cầu du lịch Hàn Quốc tăng cao trong mùa cuối năm của du khách Việt, KTO Việt Nam tiếp tục đẩy mạnh các chương trình ưu đãi đặc biệt. Cùng các đối tác, công ty du lịch hàng đầu Việt Nam, KTO góp phần phát triển nhiều tuyến điểm mới trong hành trình du lịch Hàn Quốc, mang đến đa dạng lựa chọn và nhiều trải nghiệm cho khách hàng. Hồi tháng 5, KTO Việt Nam ký kết thỏa thuận hợp tác cùng Tập đoàn Vingroup, nhằm thúc đẩy hơn nữa sự giao lưu, trao đổi du lịch giữa hai nước. Theo đó, KTO triển khai chiến dịch hỗ trợ dành riêng cho khách hàng thuộc hệ sinh thái Vingroup khi mua tour du lịch Hàn Quốc từ tháng 10 đến tháng 12 Cụ thể, chủ sở hữu xe Vinfast, cư dân Vinhomes, nhân viên Vingroup) và hội viên Vinclub (gọi chung là Vintizen) sẽ nhận được mức giá ưu đãi đặc biệt từ các công ty du lịch và KTO Việt Nam. Bên cạnh mức giá ưu đãi từ các công ty du lịch, Vintizen có cơ hội áp dụng đồng thời voucher trị giá một triệu đồng mỗi khách hàng, mua tối đa 5 tour du lịch Hàn Quốc để nhận voucher lên đến 5 triệu đồng từ KTO Việt Nam, trong thời gian 1-10/10. Ngoài thời gian trên, du khách mua tour tại các đối tác du lịch sẽ nhận được nhiều phần quà Hàn Quốc từ KTO Việt Nam. Thanh Thư</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Hàn Quốc đón 389.000 lượt khách Việt Nam tăng 27% nhờ mùa lá vàng đẹp nhất năm và chương trình quảng bá du lịch mới, trong đó Vintizen hưởng ưu đãi giảm giá tour từ tháng 10 đến tháng 12 với voucher trị giá một triệu đồng mỗi khách hàng.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{
-  "id": 9,
-  "style": "news_brief",
-  "article": "Theo KTO Việt Nam, 8 tháng năm nay, Hàn Quốc đón 389.000 lượt khách Việt, tăng 27% so với cùng kỳ năm 2023. Số lượng khách Việt Nam đến Hàn Quốc dự kiến tăng mạnh hơn bởi đất nước này đang bước vào mùa lá vàng đẹp nhất năm. Đại diện KTO khẳng định, Việt Nam là thị trường quan trọng với ngành du lịch Hàn Quốc với nhiều sự kiện tổ chức thành công. Cụ thể, trong năm nay, KTO Việt Nam xúc tiến các chương trình quảng bá, phát triển sản phẩm du lịch Hàn Quốc phù hợp với nhu cầu du khách Việt. Kết quả, nhiều sản phẩm du lịch mới được ra mắt thị trường trong nước như: tour du lịch Hàn Quốc kết hợp giải chạy Marathon tại Gyeongju và Jeju, tour trải nghiệm Esports, tour lễ hội đèn lồng truyền thống Yeondeunghoe hay tour đạp xe đạp đường dài khám phá Hàn Quốc... Chương trình Năm du lịch Hàn Quốc 2023-2024 (Visit Korea Year 2023-2024) do Tổng cục du lịch Hàn Quốc (KTO) triển khai cũng mang đến những hoạt động mới mẻ, quảng bá du lịch Hàn Quốc đến cộng đồng quốc tế. Bên cạnh đó, nhằm mang đến những trải nghiệm chân thực và đậm chất bản địa, KTO tổ chức nhiều famtour. Nổi bật là famtour trải nghiệm Esports cùng các KOL hàng đầu làng thể thao điện tử như: SofM, reviewer Duy Thẩm, Hải Triều, streamer Hà Tiều Phu, BLV Esports nổi tiếng Văn Tùng, Hoàng Luân, kết hợp Box Esports. Làn sóng văn hóa Hallyu cũng được lồng ghép vào sản phẩm du lịch, khi hàng loạt tên tuổi lớn đến Việt Nam trong khuôn khổ sự kiện Korea Travel Festa, tổ chức tháng 5 vừa qua. Mới nhất, KTO Việt Nam có mặt tại Hội chợ Du lịch Quốc tế (ITE) TP HCM, mang theo không gian đặc trưng Hàn Quốc cùng nhiều trải nghiệm mới mẻ, độc đáo. Nắm bắt nhu cầu du lịch Hàn Quốc tăng cao trong mùa cuối năm của du khách Việt, KTO Việt Nam tiếp tục đẩy mạnh các chương trình ưu đãi đặc biệt. Cùng các đối tác, công ty du lịch hàng đầu Việt Nam, KTO góp phần phát triển nhiều tuyến điểm mới trong hành trình du lịch Hàn Quốc, mang đến đa dạng lựa chọn và nhiều trải nghiệm cho khách hàng. Hồi tháng 5, KTO Việt Nam ký kết thỏa thuận hợp tác cùng Tập đoàn Vingroup, nhằm thúc đẩy hơn nữa sự giao lưu, trao đổi du lịch giữa hai nước. Theo đó, KTO triển khai chiến dịch hỗ trợ dành riêng cho khách hàng thuộc hệ sinh thái Vingroup khi mua tour du lịch Hàn Quốc từ tháng 10 đến tháng 12 Cụ thể, chủ sở hữu xe Vinfast, cư dân Vinhomes, nhân viên Vingroup) và hội viên Vinclub (gọi chung là Vintizen) sẽ nhận được mức giá ưu đãi đặc biệt từ các công ty du lịch và KTO Việt Nam. Bên cạnh mức giá ưu đãi từ các công ty du lịch, Vintizen có cơ hội áp dụng đồng thời voucher trị giá một triệu đồng mỗi khách hàng, mua tối đa 5 tour du lịch Hàn Quốc để nhận voucher lên đến 5 triệu đồng từ KTO Việt Nam, trong thời gian 1-10/10. Ngoài thời gian trên, du khách mua tour tại các đối tác du lịch sẽ nhận được nhiều phần quà Hàn Quốc từ KTO Việt Nam. Thanh Thư",
-  "summary": "Hàn Quốc đón 389.000 lượt khách Việt Nam tăng 27% nhờ mùa lá vàng đẹp nhất năm và chương trình quảng bá du lịch mới, trong đó Vintizen hưởng ưu đãi giảm giá tour từ tháng 10 đến tháng 12 với voucher trị giá một triệu đồng mỗi khách hàng.",
-  "faithfulness_score": 0.8,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng có thể thiếu chính xác khi không đề cập đầy đủ đến các chương trình quảng bá du lịch và sự kiện cụ thể",
-  "relevance_score": 0.7,
-  "relevance_reason": "Bản tóm tắt bao gồm một số ý chính nhưng bỏ sót thông tin quan trọng về các sản phẩm du lịch mới và chương trình Năm du lịch Hàn Quốc 2023-2024",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, tuy nhiên có thể rút gọn một số chi tiết để tăng tính súc tích"
-}</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -695,27 +589,8 @@
           <t>Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) là đơn vị phụ trách tổ chức. Với chủ đề 'Liên kết cùng phát triển - Kiên Giang 2024', diễn đàn hướng đến tăng cường hợp tác, liên kết giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với các Bộ, ngành Trung ương, các địa phương khác trên cả nước. Từ đó, các bên có thêm cơ sở đẩy mạnh, phát huy tiềm năng về sản phẩm OCOP của vùng. Đến nay, đã có trên 35 tỉnh, thành phố đăng ký tham gia diễn đàn cùng hơn 300 nhà đầu tư đến tìm hiểu cơ hội, xúc tiến hợp tác kinh doanh. Diễn đàn dự kiến thu hút khoảng 50.000-100.000 khách tham quan suốt thời gian diễn ra. Hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước sẽ cùng trưng bày, giới thiệu các sản phẩm OCOP tiêu biểu, công nghiệp nông thôn, đặc sản địa phương. Ngoài chương trình chính, sự kiện còn bao gồm chuỗi hoạt động khác như: triển lãm sản phẩm OCOP; hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024'; các hội nghị, hội thảo, ký kết biên bản hợp tác... Đặc biệt, khách tham dự còn được tìm hiểu quy trình sản xuất nước mắm truyền thống Phú Quốc, một trong những đặc sản nổi tiếng của Kiên Giang. Buổi tối, diễn dàn có các chương trình ca nhạc với sự góp mặt của các ca sĩ, nghệ sĩ nổi tiếng. Diễn đàn kết nối sản phẩm OCOP là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh, thành phố vùng Đồng bằng sông Cửu Long tổ chức quy mô cấp vùng. Đây vừa là nơi giao lưu, kết nối kinh doanh, vừa là cơ hội để các sản phẩm này vươn ra thế giới, góp phần phát triển kinh tế nông nghiệp, xây dựng nông thôn mới bền vững. Á Hiên</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp với Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) phụ trách việc tổ chức. Chủ đề của diễn đàn là 'Liên kết cùng phát triển - Kiên Giang 2024', hướng đến tăng cường hợp tác giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với Bộ ngành Trung ương và địa phương khác trên cả nước. Diễn đàn đã thu hút hơn 35 tỉnh/thành phố đăng ký tham gia cùng gần 300 nhà đầu tư tìm hiểu cơ hội xúc tiến hợp tác kinh doanh, dự kiến sẽ có khoảng 50-100 nghìn khách tham quan và trưng bày hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước. Ngoài chương trình chính như triển lãm sản phẩm OCOP, hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024', diễn đàn còn có chuỗi hoạt động khác gồm: ký kết biên bản hợp tác, ca nhạc với sự góp mặt của các nghệ sĩ nổi tiếng. Đây là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh/thành phố vùng Đồng bằng sông Cửu Long tổ chức, vừa giúp giao lưu kinh doanh vừa tạo cơ hội cho sản phẩm OCOP vươn ra thế giới.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{
-  "id": 10,
-  "style": "news_brief",
-  "article": "Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) là đơn vị phụ trách tổ chức. Với chủ đề 'Liên kết cùng phát triển - Kiên Giang 2024', diễn đàn hướng đến tăng cường hợp tác, liên kết giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với các Bộ, ngành Trung ương, các địa phương khác trên cả nước. Từ đó, các bên có thêm cơ sở đẩy mạnh, phát huy tiềm năng về sản phẩm OCOP của vùng. Đến nay, đã có trên 35 tỉnh, thành phố đăng ký tham gia diễn đàn cùng hơn 300 nhà đầu tư đến tìm hiểu cơ hội, xúc tiến hợp tác kinh doanh. Diễn đàn dự kiến thu hút khoảng 50.000-100.000 khách tham quan suốt thời gian diễn ra. Hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước sẽ cùng trưng bày, giới thiệu các sản phẩm OCOP tiêu biểu, công nghiệp nông thôn, đặc sản địa phương. Ngoài chương trình chính, sự kiện còn bao gồm chuỗi hoạt động khác như: triển lãm sản phẩm OCOP; hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024'; các hội nghị, hội thảo, ký kết biên bản hợp tác... Đặc biệt, khách tham dự còn được tìm hiểu quy trình sản xuất nước mắm truyền thống Phú Quốc, một trong những đặc sản nổi tiếng của Kiên Giang. Buổi tối, diễn dàn có các chương trình ca nhạc với sự góp mặt của các ca sĩ, nghệ sĩ nổi tiếng. Diễn đàn kết nối sản phẩm OCOP là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh, thành phố vùng Đồng bằng sông Cửu Long tổ chức quy mô cấp vùng. Đây vừa là nơi giao lưu, kết nối kinh doanh, vừa là cơ hội để các sản phẩm này vươn ra thế giới, góp phần phát triển kinh tế nông nghiệp, xây dựng nông thôn mới bền vững. Á Hiên",
-  "summary": "Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp với Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) phụ trách việc tổ chức. Chủ đề của diễn đàn là 'Liên kết cùng phát triển - Kiên Giang 2024', hướng đến tăng cường hợp tác giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với Bộ ngành Trung ương và địa phương khác trên cả nước. Diễn đàn đã thu hút hơn 35 tỉnh/thành phố đăng ký tham gia cùng gần 300 nhà đầu tư tìm hiểu cơ hội xúc tiến hợp tác kinh doanh, dự kiến sẽ có khoảng 50-100 nghìn khách tham quan và trưng bày hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước. Ngoài chương trình chính như triển lãm sản phẩm OCOP, hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024', diễn đàn còn có chuỗi hoạt động khác gồm: ký kết biên bản hợp tác, ca nhạc với sự góp mặt của các nghệ sĩ nổi tiếng. Đây là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh/thành phố vùng Đồng bằng sông Cửu Long tổ chức, vừa giúp giao lưu kinh doanh vừa tạo cơ hội cho sản phẩm OCOP vươn ra thế giới.",
-  "faithfulness_score": 0.9,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thêm thông tin, nhưng có một số chi tiết được tóm tắt không đầy đủ như việc khách tham dự có thể tìm hiểu quy trình sản xuất nước mắm truyền thống Phú Quốc",
-  "relevance_score": 0.8,
-  "relevance_reason": "Bản tóm tắt bao hàm đủ các ý chính quan trọng, nhưng có thể thêm thông tin về mục tiêu của diễn đàn và ý nghĩa của việc tăng cường hợp tác giữa các tỉnh, thành phố",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, nhưng có thể rút gọn một số câu để tăng tính súc tích"
-}</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -723,27 +598,8 @@
           <t>Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Hoàng Giang</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LỖI: 'NoneType' object is not iterable</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{
-  "id": 11,
-  "style": "news_brief",
-  "article": "Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Hoàng Giang",
-  "summary": "LỖI: 'NoneType' object is not iterable",
-  "faithfulness_score": 0.0,
-  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không phản ánh nội dung của văn bản.",
-  "relevance_score": 0.0,
-  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không đề cập đến các sự kiện, tình huống hoặc thông điệp chính.",
-  "coherence_conciseness_score": 0.0,
-  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá về tính mạch lạc và súc tích."
-}</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -751,27 +607,8 @@
           <t>Bếp trưởng Christian Le Squer nổi tiếng với 22 năm liên tiếp đạt 3 sao Michelin, hiện đảm nhiệm vai trò bếp trưởng tại La Maison 1888. Nhà hàng là điểm đến ẩm thực Pháp cao cấp, nằm ngay trong khuôn viên resort InterContinental Danang Sun Peninsula Resort. Tháng 7 vừa qua đánh dấu cột mốc quan trọng khi La Maison 1888 gia nhập 'bản đồ' Michelin Guide với ngôi sao đầu tiên. Với sự điều hành của bếp trưởng Christian Le Squer, thực khách sẽ được trải nghiệm ẩm thực Pháp cao cấp giao hòa giữa nghệ thuật và thẩm mỹ cao cấp, mang đậm dấu ấn cá nhân của ông. Ông Seif Hamdy, Tổng giám đốc khu nghỉ dưỡng cho biết sự góp mặt của bếp trưởng Christian tại InterContinental Danang là bước tiến quan trọng. Sự sáng tạo trong ẩm thực cùng khả năng của ông là điều đã được chứng minh bằng 22 năm liên tục được trao tặng ba sao Michelin. Christian Le Squer còn từng đạt danh hiệu 'Bếp trưởng của năm' do Gault &amp; Millau trao tặng năm 2023. 'Christian Le Squer sẽ mang đến làn gió mới cùng tầm nhìn sáng tạo, góp phần nâng tầm trải nghiệm ẩm thực cho thực khách tại La Maison 1888 với phong cách 'haute couture' đặc trưng do chính ông tạo ra', ông Seif Hamdy nói. Sinh ra và lớn lên bên bờ biển Brittany (Pháp), bếp trưởng Christian có nhiều trải nghiệm tuổi thơ gắn liền với ẩm thực. Những ký ức thuở nhỏ gieo cho ông đam mê ẩm thực sâu sắc và dẫn lối ông đến kinh đô ánh sáng và thời trang Paris. Đến năm 34 tuổi, ông được trao sao Michelin đầu tiên tại nhà hàng Café de la Paix. Thành công này đã thôi thúc ông tiếp tục hành trình chinh phục những đỉnh cao ẩm thực kế tiếp. Sau đó, ông gia nhập nhà hàng Pavillon Ledoyen năm 1999, giúp nơi này giành được ba sao Michelin không lâu sau đó. Thành tích này được ông Christian lặp lại tại Le Cinq, nhà hàng Pháp biểu tượng tại khách sạn Four Seasons Hotel George V ở Paris. Bếp trưởng Christian ví von phong cách ẩm thực độc đáo của mình như những tác phẩm thời trang nghệ thuật cao cấp 'haute couture' trên bàn ăn. Ông cho biết mỗi món đều mang dấu ấn riêng biệt, sở hữu hương vị và diện mạo thanh lịch như một bộ trang phục sang trọng hay một chai nước hoa độc bản được giới thiệu tại Tuần lễ Thời trang Paris. Sau nhiều chuyến ghé thăm Việt Nam, đặc biệt là Đà Nẵng, ông hiểu hơn về nhu cầu của thực khách nơi đây. Nhiều người ông gặp cho biết họ tìm kiếm sự kết hợp hài hòa giữa truyền thống và hiện đại trong ẩm thực Pháp. Việc khám phá các hương vị, nguyên liệu, văn hóa ẩm thực đặc sắc của Việt Nam đã trở thành nguồn cảm hứng để ông phác họa nên bức tranh ẩm thực riêng cho La Maison 1888. 'Tôi rất mong chờ được cùng làm việc với đội ngũ tài năng tại La Maison 1888, đặc biệt là Bếp trưởng Florian Stein', Christian nói. Nằm trong một dinh thự theo phong cách Đông Dương thanh lịch do Bill Bensley thiết kế, La Maison 1888 là một trong những điểm đến ẩm thực quốc tế đáng cân nhắc tại Đông Nam Á. Nhà hàng sở hữu hầm rượu vang với bộ sưu tập phong phú cùng tầm nhìn đẹp hướng biển. Nơi đây chinh phục thực khách bằng ẩm thực cao cấp với chất lượng được Michelin công nhận cùng không gian sang trọng đậm chất Pháp. Sắp tới, bếp trưởng Christian hứa hẹn mang đến nhiều bất ngờ thú vị, góp phần nâng tầm trải nghiệm ẩm thực của thực khách tại đây. Á Hiên</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LỖI: 'NoneType' object is not iterable</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{
-  "id": 12,
-  "style": "news_brief",
-  "article": "Bếp trưởng Christian Le Squer nổi tiếng với 22 năm liên tiếp đạt 3 sao Michelin, hiện đảm nhiệm vai trò bếp trưởng tại La Maison 1888. Nhà hàng là điểm đến ẩm thực Pháp cao cấp, nằm ngay trong khuôn viên resort InterContinental Danang Sun Peninsula Resort. Tháng 7 vừa qua đánh dấu cột mốc quan trọng khi La Maison 1888 gia nhập 'bản đồ' Michelin Guide với ngôi sao đầu tiên. Với sự điều hành của bếp trưởng Christian Le Squer, thực khách sẽ được trải nghiệm ẩm thực Pháp cao cấp giao hòa giữa nghệ thuật và thẩm mỹ cao cấp, mang đậm dấu ấn cá nhân của ông. Ông Seif Hamdy, Tổng giám đốc khu nghỉ dưỡng cho biết sự góp mặt của bếp trưởng Christian tại InterContinental Danang là bước tiến quan trọng. Sự sáng tạo trong ẩm thực cùng khả năng của ông là điều đã được chứng minh bằng 22 năm liên tục được trao tặng ba sao Michelin. Christian Le Squer còn từng đạt danh hiệu 'Bếp trưởng của năm' do Gault &amp; Millau trao tặng năm 2023. 'Christian Le Squer sẽ mang đến làn gió mới cùng tầm nhìn sáng tạo, góp phần nâng tầm trải nghiệm ẩm thực cho thực khách tại La Maison 1888 với phong cách 'haute couture' đặc trưng do chính ông tạo ra', ông Seif Hamdy nói. Sinh ra và lớn lên bên bờ biển Brittany (Pháp), bếp trưởng Christian có nhiều trải nghiệm tuổi thơ gắn liền với ẩm thực. Những ký ức thuở nhỏ gieo cho ông đam mê ẩm thực sâu sắc và dẫn lối ông đến kinh đô ánh sáng và thời trang Paris. Đến năm 34 tuổi, ông được trao sao Michelin đầu tiên tại nhà hàng Café de la Paix. Thành công này đã thôi thúc ông tiếp tục hành trình chinh phục những đỉnh cao ẩm thực kế tiếp. Sau đó, ông gia nhập nhà hàng Pavillon Ledoyen năm 1999, giúp nơi này giành được ba sao Michelin không lâu sau đó. Thành tích này được ông Christian lặp lại tại Le Cinq, nhà hàng Pháp biểu tượng tại khách sạn Four Seasons Hotel George V ở Paris. Bếp trưởng Christian ví von phong cách ẩm thực độc đáo của mình như những tác phẩm thời trang nghệ thuật cao cấp 'haute couture' trên bàn ăn. Ông cho biết mỗi món đều mang dấu ấn riêng biệt, sở hữu hương vị và diện mạo thanh lịch như một bộ trang phục sang trọng hay một chai nước hoa độc bản được giới thiệu tại Tuần lễ Thời trang Paris. Sau nhiều chuyến ghé thăm Việt Nam, đặc biệt là Đà Nẵng, ông hiểu hơn về nhu cầu của thực khách nơi đây. Nhiều người ông gặp cho biết họ tìm kiếm sự kết hợp hài hòa giữa truyền thống và hiện đại trong ẩm thực Pháp. Việc khám phá các hương vị, nguyên liệu, văn hóa ẩm thực đặc sắc của Việt Nam đã trở thành nguồn cảm hứng để ông phác họa nên bức tranh ẩm thực riêng cho La Maison 1888. 'Tôi rất mong chờ được cùng làm việc với đội ngũ tài năng tại La Maison 1888, đặc biệt là Bếp trưởng Florian Stein', Christian nói. Nằm trong một dinh thự theo phong cách Đông Dương thanh lịch do Bill Bensley thiết kế, La Maison 1888 là một trong những điểm đến ẩm thực quốc tế đáng cân nhắc tại Đông Nam Á. Nhà hàng sở hữu hầm rượu vang với bộ sưu tập phong phú cùng tầm nhìn đẹp hướng biển. Nơi đây chinh phục thực khách bằng ẩm thực cao cấp với chất lượng được Michelin công nhận cùng không gian sang trọng đậm chất Pháp. Sắp tới, bếp trưởng Christian hứa hẹn mang đến nhiều bất ngờ thú vị, góp phần nâng tầm trải nghiệm ẩm thực của thực khách tại đây. Á Hiên",
-  "summary": "LỖI: 'NoneType' object is not iterable",
-  "faithfulness_score": 0.0,
-  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không có nội dung để đánh giá tính trung thực.",
-  "relevance_score": 0.0,
-  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không có nội dung để đánh giá tính bao quát.",
-  "coherence_conciseness_score": 0.0,
-  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá tính mạch lạc và súc tích."
-}</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -779,27 +616,8 @@
           <t>Đại diện Sun World Sầm Sơn cho biết chương trình ưu đãi nhằm tri ân khách hàng đã ủng hộ suốt thời gian công viên nước ra mắt. Từ ngày 3/9, giá 100.000 đồng áp dụng chung cho mọi lứa tuổi. Trước đó, giá gốc 200.000 đồng (khách ngoại tỉnh) và 150.000 đồng (người Thanh Hóa). Riêng bé dưới 1 m được miễn phí vé. Khai trương đúng dịp cao điểm hè 30/6, Sun World Sầm Sơn - công viên nước quy mô nhất miền Bắc cùng tổ hợp trò chơi đạt kỷ lục châu Á - Thái Bình Dương - là 'cú hích' cho du lịch Sầm Sơn năm nay, hút hàng nghìn lượt khách mỗi ngày. Công viên nước thuộc phường Quảng Châu, Quảng Tiến, ngay đại lộ Nam sông Mã - cửa ngõ Sầm Sơn, cách trung tâm TP Thanh Hóa13 km và bãi biển Sầm Sơn 1,5 km. Thiết kế không gian lấy cảm hứng từ truyện dân gian Việt Nam, kết hợp hài hòa kiến trúc truyền thống và hiện đại. Các trò chơi cùng cảnh quan vừa gần gũi, vừa mới mẻ. Công viên nước chia ba phân khu riêng biệt dành cho mọi lứa tuổi: gia đình, trẻ em và khu cảm giác mạnh. Trong đó, trò 'Vịnh sóng thần' có diện tích 6.100 m2, chiều dài bờ biển nhân tạo đến 179 m. Cụ thể, phân khu cảm giác mạnh tập hợp những trò tốc độ, kích thích, góp phần giúp du khách giải tỏa áp lực công việc, cuộc sống. Điển hình là tổ hợp hàm cá mập, với các đường trượt uốn lượn, độ dốc cao chủ đề 'cá mập hung tàn' hay 'cá mập siêu bạo chúa'. Nhằm đáp ứng nhu cầu vui chơi của gia đình lẫn nhóm bạn trẻ, ban tổ chức kiến tạo mê cung quy mô lớn, nhấn vào các đường trượt đan chéo và vực lốc xoáy (tổ hợp ống trượt uốn lượn, xoắn ốc như các xoáy nước dành cho phao đôi đầu tiên tại châu Á - Thái Bình Dương). Du khách có thể khám phá đa dạng đường trượt gồm: 'cá đuối vượt sóng', 'cá trê vượt thác' hay 8 làn trượt thảm bạch tuộc. Chủ dự án cũng bố trí phân khu bến tuổi thơ cho trẻ, với 3 tổ hợp nhỏ mô hình sinh vật dưới nước quen thuộc. Bao quanh khu trò chơi là sông lười, gợi nhớ dòng Đơ tại Sầm Sơn. Tại đây, du khách có thể lênh đênh theo dòng nước, thư giãn và tận hưởng cảm giác sảng khoái như trẻ thơ. Nếu muốn khám phá trọn vẹn công viên nước, du khách nên đến từ 10h hoặc 15h bởi nắng không quá gắt, thích hợp với cả người già lẫn trẻ nhỏ. Vạn Phát</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Sun World Sầm Sơn giảm giá vé 100.000 đồng từ ngày 3/9, miễn phí cho trẻ dưới 1m. Công viên nước quy mô lớn nằm gần trung tâm TP Thanh Hóa, hấp dẫn du khách nhờ nhiều trò chơi kết hợp giữa truyền thống và hiện đại.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{
-  "id": 13,
-  "style": "news_brief",
-  "article": "Đại diện Sun World Sầm Sơn cho biết chương trình ưu đãi nhằm tri ân khách hàng đã ủng hộ suốt thời gian công viên nước ra mắt. Từ ngày 3/9, giá 100.000 đồng áp dụng chung cho mọi lứa tuổi. Trước đó, giá gốc 200.000 đồng (khách ngoại tỉnh) và 150.000 đồng (người Thanh Hóa). Riêng bé dưới 1 m được miễn phí vé. Khai trương đúng dịp cao điểm hè 30/6, Sun World Sầm Sơn - công viên nước quy mô nhất miền Bắc cùng tổ hợp trò chơi đạt kỷ lục châu Á - Thái Bình Dương - là 'cú hích' cho du lịch Sầm Sơn năm nay, hút hàng nghìn lượt khách mỗi ngày. Công viên nước thuộc phường Quảng Châu, Quảng Tiến, ngay đại lộ Nam sông Mã - cửa ngõ Sầm Sơn, cách trung tâm TP Thanh Hóa13 km và bãi biển Sầm Sơn 1,5 km. Thiết kế không gian lấy cảm hứng từ truyện dân gian Việt Nam, kết hợp hài hòa kiến trúc truyền thống và hiện đại. Các trò chơi cùng cảnh quan vừa gần gũi, vừa mới mẻ. Công viên nước chia ba phân khu riêng biệt dành cho mọi lứa tuổi: gia đình, trẻ em và khu cảm giác mạnh. Trong đó, trò 'Vịnh sóng thần' có diện tích 6.100 m2, chiều dài bờ biển nhân tạo đến 179 m. Cụ thể, phân khu cảm giác mạnh tập hợp những trò tốc độ, kích thích, góp phần giúp du khách giải tỏa áp lực công việc, cuộc sống. Điển hình là tổ hợp hàm cá mập, với các đường trượt uốn lượn, độ dốc cao chủ đề 'cá mập hung tàn' hay 'cá mập siêu bạo chúa'. Nhằm đáp ứng nhu cầu vui chơi của gia đình lẫn nhóm bạn trẻ, ban tổ chức kiến tạo mê cung quy mô lớn, nhấn vào các đường trượt đan chéo và vực lốc xoáy (tổ hợp ống trượt uốn lượn, xoắn ốc như các xoáy nước dành cho phao đôi đầu tiên tại châu Á - Thái Bình Dương). Du khách có thể khám phá đa dạng đường trượt gồm: 'cá đuối vượt sóng', 'cá trê vượt thác' hay 8 làn trượt thảm bạch tuộc. Chủ dự án cũng bố trí phân khu bến tuổi thơ cho trẻ, với 3 tổ hợp nhỏ mô hình sinh vật dưới nước quen thuộc. Bao quanh khu trò chơi là sông lười, gợi nhớ dòng Đơ tại Sầm Sơn. Tại đây, du khách có thể lênh đênh theo dòng nước, thư giãn và tận hưởng cảm giác sảng khoái như trẻ thơ. Nếu muốn khám phá trọn vẹn công viên nước, du khách nên đến từ 10h hoặc 15h bởi nắng không quá gắt, thích hợp với cả người già lẫn trẻ nhỏ. Vạn Phát",
-  "summary": "Sun World Sầm Sơn giảm giá vé 100.000 đồng từ ngày 3/9, miễn phí cho trẻ dưới 1m. Công viên nước quy mô lớn nằm gần trung tâm TP Thanh Hóa, hấp dẫn du khách nhờ nhiều trò chơi kết hợp giữa truyền thống và hiện đại.",
-  "faithfulness_score": 0.8,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng thiếu sót một số chi tiết quan trọng như thời gian khai trương, các phân khu trong công viên nước và một số trò chơi đặc biệt",
-  "relevance_score": 0.7,
-  "relevance_reason": "Bản tóm tắt chưa bao hàm đủ các ý chính quan trọng như mục đích của chương trình ưu đãi, vị trí và thiết kế của công viên nước",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt có logic, dễ đọc và súc tích, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng mà không làm cho bản tóm tắt trở nên rườm rà"
-}</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -807,27 +625,8 @@
           <t>Chiều 28/8, khách sạn Grand Mercure Hanoi đón hơn 200 vị khách thuộc đoàn 4.500 du khách từ Ấn Độ sang Việt Nam. Theo ông Remi Faubel, tổng quản lý khách sạn, đây là cơ hội lớn để quảng bá nét đẹp văn hóa, truyền thống tới khách quốc tế. 'Chúng tôi tự tin các yếu tố như lối kiến trúc Đông Dương, hệ thống cửa Bức Bàn, các chi tiết nội thất lấy cảm hứng từ hoa sen, trống đồng, hạt gạo, ruộng bậc thang,... sẽ góp phần để lại ấn tượng tốt đẹp trong lòng du khách', ông Faubel nói. Do nhu cầu của khách, Grand Mercure Hanoi vẫn phục vụ chủ yếu các món Ấn. Bếp trưởng - Nguyễn Minh Nguyện lý giải, du khách Ấn Độ luôn có nhu cầu thưởng thức ẩm thực đất nước họ để có cảm giác gần gũi và thoải mái khi đi du lịch. Đó cũng là cách họ gìn giữ văn hóa và chế độ ăn truyền thống. 'Khi lên kế hoạch, chúng tôi phải trao đổi với phía đại diện đoàn để nắm thông tin về chế độ ăn, suất ăn tôn giáo, yêu cầu đặc biệt, từ đó lựa chọn các loại gia vị đặc trưng của Ấn Độ để các món ăn giữ được hương vị', vị bếp trưởng nói. Tuy nhiên, khách sạn cũng chuẩn bị thêm một số món ăn đặc trưng của Việt Nam như gà, bánh cuốn, xôi, hoa quả nhiệt đới... để giới thiệu đến đoàn khách. Từ ngày 27/8 đến 3/9, Việt Nam đón 4.500 du khách thuộc tập đoàn dược phẩm lớn đến từ Ấn Độ. Dự kiến, họ sẽ chia thành các nhóm nhỏ tới Hà Nội - Ninh Bình - Hạ Long và sử dụng các dịch vụ lưu trú, ăn uống tại các khách sạn 5 sao trên địa bàn thủ đô. Ấn Độ là một trong 10 thị trường khách du lịch quốc tế lớn nhất Việt Nam. Theo số liệu từ Cục Du lịch Quốc gia, trong 6 tháng đầu năm, nước ta đã đón 231.000 lượt khách Ấn Độ, tăng 164% so với cùng kỳ năm 2023. Việt Nam có nhiều thế mạnh để thu hút và phát triển thị trường này. Các đường bay thẳng giữa hai nước được khai thác trong thời gian gần đây khiến thời gian di chuyển rút ngắn chỉ còn khoảng 4 - 5 tiếng. Theo Outlook Traveller, Việt Nam sở hữu những cảnh quan đẹp, nền văn hóa đa dạng và chiều sâu lịch sử. Giá thành dịch vụ cạnh tranh khiến nước ta trở thành điểm đến lý tưởng cho du khách Ấn Độ. Lan Anh</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Hàng nghìn du khách Ấn Độ đến Grand Mercure Hanoi, nơi lối kiến trúc Đông Dương và ẩm thực truyền thống tạo ấn tượng tốt. Việt Nam với cảnh quan đẹp đa dạng văn hóa lịch sử thu hút du khách do giá cả hợp lý.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{
-  "id": 14,
-  "style": "news_brief",
-  "article": "Chiều 28/8, khách sạn Grand Mercure Hanoi đón hơn 200 vị khách thuộc đoàn 4.500 du khách từ Ấn Độ sang Việt Nam. Theo ông Remi Faubel, tổng quản lý khách sạn, đây là cơ hội lớn để quảng bá nét đẹp văn hóa, truyền thống tới khách quốc tế. 'Chúng tôi tự tin các yếu tố như lối kiến trúc Đông Dương, hệ thống cửa Bức Bàn, các chi tiết nội thất lấy cảm hứng từ hoa sen, trống đồng, hạt gạo, ruộng bậc thang,... sẽ góp phần để lại ấn tượng tốt đẹp trong lòng du khách', ông Faubel nói. Do nhu cầu của khách, Grand Mercure Hanoi vẫn phục vụ chủ yếu các món Ấn. Bếp trưởng - Nguyễn Minh Nguyện lý giải, du khách Ấn Độ luôn có nhu cầu thưởng thức ẩm thực đất nước họ để có cảm giác gần gũi và thoải mái khi đi du lịch. Đó cũng là cách họ gìn giữ văn hóa và chế độ ăn truyền thống. 'Khi lên kế hoạch, chúng tôi phải trao đổi với phía đại diện đoàn để nắm thông tin về chế độ ăn, suất ăn tôn giáo, yêu cầu đặc biệt, từ đó lựa chọn các loại gia vị đặc trưng của Ấn Độ để các món ăn giữ được hương vị', vị bếp trưởng nói. Tuy nhiên, khách sạn cũng chuẩn bị thêm một số món ăn đặc trưng của Việt Nam như gà, bánh cuốn, xôi, hoa quả nhiệt đới... để giới thiệu đến đoàn khách. Từ ngày 27/8 đến 3/9, Việt Nam đón 4.500 du khách thuộc tập đoàn dược phẩm lớn đến từ Ấn Độ. Dự kiến, họ sẽ chia thành các nhóm nhỏ tới Hà Nội - Ninh Bình - Hạ Long và sử dụng các dịch vụ lưu trú, ăn uống tại các khách sạn 5 sao trên địa bàn thủ đô. Ấn Độ là một trong 10 thị trường khách du lịch quốc tế lớn nhất Việt Nam. Theo số liệu từ Cục Du lịch Quốc gia, trong 6 tháng đầu năm, nước ta đã đón 231.000 lượt khách Ấn Độ, tăng 164% so với cùng kỳ năm 2023. Việt Nam có nhiều thế mạnh để thu hút và phát triển thị trường này. Các đường bay thẳng giữa hai nước được khai thác trong thời gian gần đây khiến thời gian di chuyển rút ngắn chỉ còn khoảng 4 - 5 tiếng. Theo Outlook Traveller, Việt Nam sở hữu những cảnh quan đẹp, nền văn hóa đa dạng và chiều sâu lịch sử. Giá thành dịch vụ cạnh tranh khiến nước ta trở thành điểm đến lý tưởng cho du khách Ấn Độ. Lan Anh",
-  "summary": "Hàng nghìn du khách Ấn Độ đến Grand Mercure Hanoi, nơi lối kiến trúc Đông Dương và ẩm thực truyền thống tạo ấn tượng tốt. Việt Nam với cảnh quan đẹp đa dạng văn hóa lịch sử thu hút du khách do giá cả hợp lý.",
-  "faithfulness_score": 0.8,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng thiếu sót một số chi tiết quan trọng như số lượng du khách và các hoạt động cụ thể tại khách sạn",
-  "relevance_score": 0.7,
-  "relevance_reason": "Bản tóm tắt chưa bao hàm đủ các ý chính quan trọng như nhu cầu ẩm thực của du khách Ấn Độ và việc giới thiệu văn hóa Việt Nam",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, tuy nhiên có thể rút gọn một số từ ngữ để tăng tính súc tích"
-}</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -835,27 +634,8 @@
           <t>Theo Báo cáo Hạnh phúc Thế giới (World Happiness Report) 2024 của Liên Hợp Quốc công bố hồi tháng 3, Lithuania là quốc gia 'hạnh phúc nhất thế giới dành cho những người dưới 30 tuổi (gen Z)'. Hai nhà sáng tạo nội dung Ammar Kandil và Staffan Taylor đến từ Yes Theory, kênh truyền thông nổi tiếng của Canada, quyết định đến thủ đô Vilnius để tìm hiểu xem liệu báo cáo có nói đúng. Khi hạ cánh xuống Vilnius, Amma và Staffan bắt đầu nói chuyện với người dân địa phương. Hầu hết người trẻ đều đồng ý quốc gia họ đang sống là nơi tốt nhờ 'đồ ăn tuyệt vời, người dân thân thiện, nhiều cơ hội nghề nghiệp và nền kinh tế đang phát triển'. Nhiều người trong số đó cho rằng các khó khăn mà thế hệ trước chịu đựng đã dạy thế hệ trẻ ngày nay cách tận hưởng cuộc sống trong từng khoảnh khắc và 'tìm thấy vẻ đẹp trong những điều giản dị'. Để thu hút nhiều người trẻ đến nói chuyện hơn, Amma và Staffan đã tổ chức một buổi gặp gỡ. Tại sự kiện, những người tham dự lần lượt bày tỏ quan điểm. 'Sau một năm sống tại Mỹ, tôi đánh giá cao cuộc sống ở Lithuania vì tính kết nối với thiên nhiên', một thanh niên chia sẻ. Người này nói thêm du khách có thể dễ dàng tiếp cận một hồ nước hay khu rừng tại Lithuania và chiêm ngưỡng khung cảnh thiên nhiên tuyệt đẹp ở đó. 'Lithuania chưa bao giờ tốt như hiện nay', một phụ nữ trẻ khác thừa nhận. Khi nói về hạnh phúc, một người dân địa phương cho biết dù người trẻ sống ở đất nước này 'khá vui vẻ' nhưng không có nghĩa họ không phải đối mặt với nhiều vấn đề, áp lực cuộc sống. Sau buổi gặp gỡ, Ammar và Staffan dành phần còn lại của chuyến đi để giao lưu với người dân địa phương, ghé thăm các điểm du lịch như nhà tù cũ Lukiškės giờ là địa điểm văn hóa và tượng đài Hill of Crosses. 'Đây là một trong những trải nghiệm du lịch hạnh phúc nhất tôi từng có', Ammar, người từng đi khắp thế giới, chia sẻ với độc giả trên kênh Yes Theory khi đang tham gia một bữa tiệc tối. Steffan đồng tình khi nhận định Lithuania chắc chắn là một trong những quốc gia cởi mở, hào phóng, tử tế nhất mà anh từng đến. Video của hai du khách đến từ Canada đã thu hút gần một triệu lượt xem và bình luận chỉ sau vài ngày đăng tải. Một người từng đến Vilnius học theo diện trao đổi sinh viên chia sẻ thời gian ở Liathuania là quãng thời gian hạnh phúc nhất của mình. 'Cảm ơn Liathuania đã chào đón tôi', người này nói. 'Tình yêu, sự sáng tạo và lòng tốt có thể giúp chúng ta vượt qua quá khứ đen tối, biến tiêu cực thành ánh sáng và giúp đỡ người khác', một người dân địa phương bày tỏ sau khi xem video của Ammar và Steffan. Anh Minh(TheoYes Theory, DM)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Lithuania được đánh giá cao về sự cởi mở, hào phóng và đồ ăn ngon. Tuy nhiên, cuộc sống vẫn có áp lực từ thế hệ trước đã dạy trẻ tận hưởng từng khoảnh khắc và tìm thấy vẻ đẹp trong giản dị.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{
-  "id": 15,
-  "style": "news_brief",
-  "article": "Theo Báo cáo Hạnh phúc Thế giới (World Happiness Report) 2024 của Liên Hợp Quốc công bố hồi tháng 3, Lithuania là quốc gia 'hạnh phúc nhất thế giới dành cho những người dưới 30 tuổi (gen Z)'. Hai nhà sáng tạo nội dung Ammar Kandil và Staffan Taylor đến từ Yes Theory, kênh truyền thông nổi tiếng của Canada, quyết định đến thủ đô Vilnius để tìm hiểu xem liệu báo cáo có nói đúng. Khi hạ cánh xuống Vilnius, Amma và Staffan bắt đầu nói chuyện với người dân địa phương. Hầu hết người trẻ đều đồng ý quốc gia họ đang sống là nơi tốt nhờ 'đồ ăn tuyệt vời, người dân thân thiện, nhiều cơ hội nghề nghiệp và nền kinh tế đang phát triển'. Nhiều người trong số đó cho rằng các khó khăn mà thế hệ trước chịu đựng đã dạy thế hệ trẻ ngày nay cách tận hưởng cuộc sống trong từng khoảnh khắc và 'tìm thấy vẻ đẹp trong những điều giản dị'. Để thu hút nhiều người trẻ đến nói chuyện hơn, Amma và Staffan đã tổ chức một buổi gặp gỡ. Tại sự kiện, những người tham dự lần lượt bày tỏ quan điểm. 'Sau một năm sống tại Mỹ, tôi đánh giá cao cuộc sống ở Lithuania vì tính kết nối với thiên nhiên', một thanh niên chia sẻ. Người này nói thêm du khách có thể dễ dàng tiếp cận một hồ nước hay khu rừng tại Lithuania và chiêm ngưỡng khung cảnh thiên nhiên tuyệt đẹp ở đó. 'Lithuania chưa bao giờ tốt như hiện nay', một phụ nữ trẻ khác thừa nhận. Khi nói về hạnh phúc, một người dân địa phương cho biết dù người trẻ sống ở đất nước này 'khá vui vẻ' nhưng không có nghĩa họ không phải đối mặt với nhiều vấn đề, áp lực cuộc sống. Sau buổi gặp gỡ, Ammar và Staffan dành phần còn lại của chuyến đi để giao lưu với người dân địa phương, ghé thăm các điểm du lịch như nhà tù cũ Lukiškės giờ là địa điểm văn hóa và tượng đài Hill of Crosses. 'Đây là một trong những trải nghiệm du lịch hạnh phúc nhất tôi từng có', Ammar, người từng đi khắp thế giới, chia sẻ với độc giả trên kênh Yes Theory khi đang tham gia một bữa tiệc tối. Steffan đồng tình khi nhận định Lithuania chắc chắn là một trong những quốc gia cởi mở, hào phóng, tử tế nhất mà anh từng đến. Video của hai du khách đến từ Canada đã thu hút gần một triệu lượt xem và bình luận chỉ sau vài ngày đăng tải. Một người từng đến Vilnius học theo diện trao đổi sinh viên chia sẻ thời gian ở Liathuania là quãng thời gian hạnh phúc nhất của mình. 'Cảm ơn Liathuania đã chào đón tôi', người này nói. 'Tình yêu, sự sáng tạo và lòng tốt có thể giúp chúng ta vượt qua quá khứ đen tối, biến tiêu cực thành ánh sáng và giúp đỡ người khác', một người dân địa phương bày tỏ sau khi xem video của Ammar và Steffan. Anh Minh(TheoYes Theory, DM)",
-  "summary": "Lithuania được đánh giá cao về sự cởi mở, hào phóng và đồ ăn ngon. Tuy nhiên, cuộc sống vẫn có áp lực từ thế hệ trước đã dạy trẻ tận hưởng từng khoảnh khắc và tìm thấy vẻ đẹp trong giản dị.",
-  "faithfulness_score": 0.8,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng thiếu sót một số chi tiết quan trọng như việc Lithuania được đánh giá là quốc gia hạnh phúc nhất thế giới dành cho người dưới 30 tuổi và các hoạt động của Ammar và Staffan khi đến Vilnius",
-  "relevance_score": 0.7,
-  "relevance_reason": "Bản tóm tắt không bao hàm đủ các ý chính quan trọng như việc người dân Lithuania đánh giá cao cuộc sống ở đây vì đồ ăn tuyệt vời, người dân thân thiện, nhiều cơ hội nghề nghiệp và nền kinh tế đang phát triển",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, tuy nhiên có thể rút gọn một số chi tiết để tăng tính súc tích"
-}</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -863,27 +643,8 @@
           <t>Đi dạo trong khuôn viên lâu đài của mình ở Pháp vào một buổi tối mùa hè 2023, Philippa Girling cảm thấy nhẹ nhõm khi nghe thấy tiếng cười của những du khách nữ đang lưu trú tại đây. Tiếng cười là mục tiêu mà CEO Camp Château, nơi tổ chức trại hè dành riêng cho phụ nữ, mong muốn khi mở dịch vụ này. Tuy mới thành lập được hai năm, danh sách khách đăng ký đến nghỉ dưỡng tại lâu đài cổ nằm trên đỉnh đồi ở vùng Quercy, tây nam nước Pháp, năm nay đã kín chỗ. Lượng khách chờ cho mùa hè 2025 đã lên đến 11.000 người. Philippa rất vui khi được mọi người yêu thích dịch vụ cũng nhưng cảm thấy rất tiếc cho những người trong danh sách chờ khi nhiều du khách sẽ phải đợi 20 năm mới đến lượt. Cô đang xem xét để mở rộng trại hè, giúp nhiều du khách nữ có thể sử dụng dịch vụ hơn. Philippa nói mục đích tồn tại của Camp Château rất đơn giản: mang đến cho phụ nữ trải nghiệm vui vẻ. Philippa từng làm 30 năm trong ngành ngân hàng nên thấu hiểu áp lực mà phụ nữ ngày nay phải đối mặt. Do đó, cô cùng các đồng sáng lập tạo ra Camp Château để giúp các khách hàng nữ của mình thư giãn, mang lại cho họ sự chăm sóc sức khỏe tinh thần và thể chất, không gian yên tĩnh và thời gian để hồi phục trước khi quay về cuộc sống thường ngày. Kỳ nghỉ trong trại hè kéo dài sáu ngày năm đêm với nhiều hoạt động để hội viên tham gia như làm nến, nếm thử phô mai, cưỡi ngựa, yoga. Một số phụ nữ hào hứng tham gia mọi hoạt động, số khác thích dành phần lớn thời gian nằm bên hồ bơi. Mỗi đợt đón khách khoảng 50 người. Girling, người lớn lên ở miền nam nước Anh, thường đi nghỉ ở Quercy và hiện sống ở California, Mỹ, nhận thấy 'phụ nữ khi ở bên nhau thật tuyệt vời'. Những người phụ nữ đều rất hòa đồng. Họ nằm giường tầng trong các căn phòng tại lâu đài hoặc trong lều dành cho hai người. Tất cả cùng dùng chung bữa tối tại sảnh lớn và có khung giờ phục vụ đồ uống riêng. Trọng tâm của chương trình trại hè này là trao cho phụ nữ quyền tự quyết, làm mọi thứ họ muốn và chỉ cần đối xử tử tế với nhau. Toàn bộ thiết kế của Camp Château đều hướng tới mục đích giúp mọi người có thể gặp gỡ, trò chuyện nhiều hơn một cách tự nhiên nhất. Điều duy nhất khách cần quyết định tại Camp Château là muốn nghỉ ngơi hay vui chơi. Tất cả phụ nữ đều được chào đón tại trại hè. Từ tháng 7 trở về trước, phần lớn khách đến đây là người Mỹ. Nhưng từ đầu tháng 8, số lượng quốc tịch đa dạng hơn khi có thêm các khách đến từ Andorra, Canada, Ai Cập, Anh và Nigeria. Độ tuổi từ 19 đến ngoài 70 tuổi. Nhiều người đến một mình và không ít người gọi trại hè này là 'môi trường an toàn phục vụ niềm đam mê du lịch' của họ. Ngoài ra, trại hè cũng đón các nhóm khách nhỏ gồm mẹ và con gái. Giá một kỳ nghỉ là 2.178 euro, gồm mọi chi phí ăn ở, vui chơi và không tính đưa đón sân bay, dịch vụ massage. Philippa nói số tiền này không nhỏ nhưng cô và các cộng sự đã phải tính toán để đưa ra mức giá phải chăng nhất có thể. Càng ngày, lượng khách đăng ký càng đông. Nhưng Philippa nói sẽ không tăng giá vì muốn nhiều người có thể tiếp cận trải nghiệm này thay vì hướng tới tệp khách nhà giàu. Anh Minh(TheoEuro News)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Du khách nữ đến Camp Château, lâu đài cổ ở Quercy, Tây Nam Pháp với các hoạt động như làm nến, yoga hoặc thư giãn bên hồ bơi. Mục tiêu trại hè là mang lại trải nghiệm vui vẻ và chăm sóc sức khỏe tinh thần thể chất cho phụ nữ tự quyết định mọi thứ trong sự tôn trọng lẫn nhau. Camp Château đón khách đa dạng từ Mỹ đến Andorra với 11.000 người đăng ký mùa hè năm nay, nhưng nhiều du khách phải đợi hai thập kỷ mới được phục vụ. Philippa Girling tăng giá không vì muốn tiếp cận rộng rãi hơn mà nhằm tập trung vào tệp khách giàu có; tuy nhiên, cô cũng nhận ra rằng cần mở rộng dịch vụ để giúp phụ nữ sử dụng nó dễ dàng hơn. Camp Château tạo điều kiện cho các phụ nữ thư giãn và hồi phục sau khi quay về cuộc sống thường ngày, nhấn mạnh quyền tự quyết định của họ trong sự tôn trọng lẫn nhau.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{
-  "id": 16,
-  "style": "news_brief",
-  "article": "Đi dạo trong khuôn viên lâu đài của mình ở Pháp vào một buổi tối mùa hè 2023, Philippa Girling cảm thấy nhẹ nhõm khi nghe thấy tiếng cười của những du khách nữ đang lưu trú tại đây. Tiếng cười là mục tiêu mà CEO Camp Château, nơi tổ chức trại hè dành riêng cho phụ nữ, mong muốn khi mở dịch vụ này. Tuy mới thành lập được hai năm, danh sách khách đăng ký đến nghỉ dưỡng tại lâu đài cổ nằm trên đỉnh đồi ở vùng Quercy, tây nam nước Pháp, năm nay đã kín chỗ. Lượng khách chờ cho mùa hè 2025 đã lên đến 11.000 người. Philippa rất vui khi được mọi người yêu thích dịch vụ cũng nhưng cảm thấy rất tiếc cho những người trong danh sách chờ khi nhiều du khách sẽ phải đợi 20 năm mới đến lượt. Cô đang xem xét để mở rộng trại hè, giúp nhiều du khách nữ có thể sử dụng dịch vụ hơn. Philippa nói mục đích tồn tại của Camp Château rất đơn giản: mang đến cho phụ nữ trải nghiệm vui vẻ. Philippa từng làm 30 năm trong ngành ngân hàng nên thấu hiểu áp lực mà phụ nữ ngày nay phải đối mặt. Do đó, cô cùng các đồng sáng lập tạo ra Camp Château để giúp các khách hàng nữ của mình thư giãn, mang lại cho họ sự chăm sóc sức khỏe tinh thần và thể chất, không gian yên tĩnh và thời gian để hồi phục trước khi quay về cuộc sống thường ngày. Kỳ nghỉ trong trại hè kéo dài sáu ngày năm đêm với nhiều hoạt động để hội viên tham gia như làm nến, nếm thử phô mai, cưỡi ngựa, yoga. Một số phụ nữ hào hứng tham gia mọi hoạt động, số khác thích dành phần lớn thời gian nằm bên hồ bơi. Mỗi đợt đón khách khoảng 50 người. Girling, người lớn lên ở miền nam nước Anh, thường đi nghỉ ở Quercy và hiện sống ở California, Mỹ, nhận thấy 'phụ nữ khi ở bên nhau thật tuyệt vời'. Những người phụ nữ đều rất hòa đồng. Họ nằm giường tầng trong các căn phòng tại lâu đài hoặc trong lều dành cho hai người. Tất cả cùng dùng chung bữa tối tại sảnh lớn và có khung giờ phục vụ đồ uống riêng. Trọng tâm của chương trình trại hè này là trao cho phụ nữ quyền tự quyết, làm mọi thứ họ muốn và chỉ cần đối xử tử tế với nhau. Toàn bộ thiết kế của Camp Château đều hướng tới mục đích giúp mọi người có thể gặp gỡ, trò chuyện nhiều hơn một cách tự nhiên nhất. Điều duy nhất khách cần quyết định tại Camp Château là muốn nghỉ ngơi hay vui chơi. Tất cả phụ nữ đều được chào đón tại trại hè. Từ tháng 7 trở về trước, phần lớn khách đến đây là người Mỹ. Nhưng từ đầu tháng 8, số lượng quốc tịch đa dạng hơn khi có thêm các khách đến từ Andorra, Canada, Ai Cập, Anh và Nigeria. Độ tuổi từ 19 đến ngoài 70 tuổi. Nhiều người đến một mình và không ít người gọi trại hè này là 'môi trường an toàn phục vụ niềm đam mê du lịch' của họ. Ngoài ra, trại hè cũng đón các nhóm khách nhỏ gồm mẹ và con gái. Giá một kỳ nghỉ là 2.178 euro, gồm mọi chi phí ăn ở, vui chơi và không tính đưa đón sân bay, dịch vụ massage. Philippa nói số tiền này không nhỏ nhưng cô và các cộng sự đã phải tính toán để đưa ra mức giá phải chăng nhất có thể. Càng ngày, lượng khách đăng ký càng đông. Nhưng Philippa nói sẽ không tăng giá vì muốn nhiều người có thể tiếp cận trải nghiệm này thay vì hướng tới tệp khách nhà giàu. Anh Minh(TheoEuro News)",
-  "summary": "Du khách nữ đến Camp Château, lâu đài cổ ở Quercy, Tây Nam Pháp với các hoạt động như làm nến, yoga hoặc thư giãn bên hồ bơi. Mục tiêu trại hè là mang lại trải nghiệm vui vẻ và chăm sóc sức khỏe tinh thần thể chất cho phụ nữ tự quyết định mọi thứ trong sự tôn trọng lẫn nhau. Camp Château đón khách đa dạng từ Mỹ đến Andorra với 11.000 người đăng ký mùa hè năm nay, nhưng nhiều du khách phải đợi hai thập kỷ mới được phục vụ. Philippa Girling tăng giá không vì muốn tiếp cận rộng rãi hơn mà nhằm tập trung vào tệp khách giàu có; tuy nhiên, cô cũng nhận ra rằng cần mở rộng dịch vụ để giúp phụ nữ sử dụng nó dễ dàng hơn. Camp Château tạo điều kiện cho các phụ nữ thư giãn và hồi phục sau khi quay về cuộc sống thường ngày, nhấn mạnh quyền tự quyết định của họ trong sự tôn trọng lẫn nhau.",
-  "faithfulness_score": 0.8,
-  "faithfulness_reason": "Bản tóm tắt có một số điểm không chính xác như việc Philippa Girling tăng giá không phải để tập trung vào tệp khách giàu có mà là không tăng giá để giúp nhiều người có thể tiếp cận trải nghiệm này",
-  "relevance_score": 0.9,
-  "relevance_reason": "Bản tóm tắt bao gồm hầu hết các ý chính quan trọng như mục tiêu của Camp Château, các hoạt động và đối tượng khách hàng, tuy nhiên có thể thêm một số chi tiết về lý do thành lập và không gian của lâu đài",
-  "coherence_conciseness_score": 0.8,
-  "coherence_conciseness_reason": "Bản tóm tắt có logic và dễ đọc, tuy nhiên có một số câu dài và phức tạp, cần được tinh gọn hơn để tăng tính súc tích"
-}</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -891,27 +652,8 @@
           <t>Thời gian này tại Malaysia cũng có nhiều sự kiện để du khách trải nghiệm như: lễ hội trò chơi dân gian tại Kuala Lumpur (13-16/9), lễ hội văn hóa Putrajaya (27-29/9), lễ hội bãi biển Tanjung Aru 2024 tại Kota Kinabalu (1 và 22/9)... Điểm đến phổ biến nhất tại Malaysia là thủ đô Kuala Lumpur - đô thị sầm uất với những di sản kiến trúc cùng các cao ốc hiện đại. Công trình nổi tiếng nhất là tháp đôi Petronas cao 88 tầng. Tại đây có đài quan sát toàn cảnh thành phố, cầu treo trên không, trung tâm khám phá khoa học Petrosains, thủy cung Aquaria KLCC và trung tâm mua sắm Suria KLCC. Quận trung tâm thành phố Kuala Lumpur là Bukit Bintang, khu vực nhộn nhịp bậc nhất với các khu mua sắm, khách sạn và nhà hàng cao cấp cùng nhiều tụ điểm vui chơi, giải trí. Đảo Penang lại mang đến không khí bình yên, nhẹ nhàng. Đặc biệt, George Town - thủ phủ của bang Penang là di sản thế giới, phản ánh rõ nét dấu vết lịch sử qua từng công trình kiến trúc lẫn đời sống văn hóa của cư dân, từ những ngõ nhỏ với căn nhà hai tầng của người Hoa đến tòa hội đồng thành phố, tháp đồng hồ từ thời thuộc địa Anh. Du khách đừng quên ghé đồi Penang Hill hay đền Kek Lok Si. Langkawi là quần đảo với 99 đảo nhỏ ngoài khơi biển Andaman. Vùng đất này có nhiều bãi biển hoang sơ với khu nghỉ dưỡng cao cấp, phù hợp cho kỳ nghỉ thư giãn sau những ngày bận rộn. Ngoài ra, hòn đảo này còn là điểm đến lý tưởng cho các môn thể thao dưới nước như lặn biển, dù kéo, mô tô nước hoặc khám phá công viên địa chất hàng triệu năm tuổi. Cao nguyên Cameron là địa danh nằm ở bang Pahang, được bao phủ một màu xanh dài bất tận bởi những đồi chè và loại cây ôn đới. Khí hậu của cao nguyên này mang đến cho du khách sự mát mẻ, dễ chịu như đang ở châu Âu. Khi đến đây, du khách đừng quên ghé thăm nông trại chế biến trà, vườn hoa oải hương, thung lũng hoa hồng hay thử trekking leo núi Batu Brinchang. Malaysia có nhiều món ăn hấp dẫn du khách, nổi bật là món cơm 'quốc dân' Nasi Lemak. Món cơm này gồm cơm, nấu từ gạo với nước cốt dừa, trứng luộc, gà chiên, lạc, dưa chuột thái lát, cá khô... ăn kèm xốt sambal. Món ăn tuy đơn giản song đủ dinh dưỡng và được nhiều người ưa thích. Char Kway Teow, món hủ tiếu xào nổi tiếng của cộng đồng người Hoa tại Malaysia được chế biến từ hủ tiếu bản to xào cùng tôm, chả cá, lạp xưởng, trứng, giá đỗ và hẹ. Ngoài ra, Roti Canai là món ăn của cộng đồng người Ấn. Đây là loại bánh dẹt, thơm, giòn và xốp, thường dùng kèm các loại cà ri. Thanh Thư</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LỖI: 'NoneType' object is not iterable</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{
-  "id": 17,
-  "style": "news_brief",
-  "article": "Thời gian này tại Malaysia cũng có nhiều sự kiện để du khách trải nghiệm như: lễ hội trò chơi dân gian tại Kuala Lumpur (13-16/9), lễ hội văn hóa Putrajaya (27-29/9), lễ hội bãi biển Tanjung Aru 2024 tại Kota Kinabalu (1 và 22/9)... Điểm đến phổ biến nhất tại Malaysia là thủ đô Kuala Lumpur - đô thị sầm uất với những di sản kiến trúc cùng các cao ốc hiện đại. Công trình nổi tiếng nhất là tháp đôi Petronas cao 88 tầng. Tại đây có đài quan sát toàn cảnh thành phố, cầu treo trên không, trung tâm khám phá khoa học Petrosains, thủy cung Aquaria KLCC và trung tâm mua sắm Suria KLCC. Quận trung tâm thành phố Kuala Lumpur là Bukit Bintang, khu vực nhộn nhịp bậc nhất với các khu mua sắm, khách sạn và nhà hàng cao cấp cùng nhiều tụ điểm vui chơi, giải trí. Đảo Penang lại mang đến không khí bình yên, nhẹ nhàng. Đặc biệt, George Town - thủ phủ của bang Penang là di sản thế giới, phản ánh rõ nét dấu vết lịch sử qua từng công trình kiến trúc lẫn đời sống văn hóa của cư dân, từ những ngõ nhỏ với căn nhà hai tầng của người Hoa đến tòa hội đồng thành phố, tháp đồng hồ từ thời thuộc địa Anh. Du khách đừng quên ghé đồi Penang Hill hay đền Kek Lok Si. Langkawi là quần đảo với 99 đảo nhỏ ngoài khơi biển Andaman. Vùng đất này có nhiều bãi biển hoang sơ với khu nghỉ dưỡng cao cấp, phù hợp cho kỳ nghỉ thư giãn sau những ngày bận rộn. Ngoài ra, hòn đảo này còn là điểm đến lý tưởng cho các môn thể thao dưới nước như lặn biển, dù kéo, mô tô nước hoặc khám phá công viên địa chất hàng triệu năm tuổi. Cao nguyên Cameron là địa danh nằm ở bang Pahang, được bao phủ một màu xanh dài bất tận bởi những đồi chè và loại cây ôn đới. Khí hậu của cao nguyên này mang đến cho du khách sự mát mẻ, dễ chịu như đang ở châu Âu. Khi đến đây, du khách đừng quên ghé thăm nông trại chế biến trà, vườn hoa oải hương, thung lũng hoa hồng hay thử trekking leo núi Batu Brinchang. Malaysia có nhiều món ăn hấp dẫn du khách, nổi bật là món cơm 'quốc dân' Nasi Lemak. Món cơm này gồm cơm, nấu từ gạo với nước cốt dừa, trứng luộc, gà chiên, lạc, dưa chuột thái lát, cá khô... ăn kèm xốt sambal. Món ăn tuy đơn giản song đủ dinh dưỡng và được nhiều người ưa thích. Char Kway Teow, món hủ tiếu xào nổi tiếng của cộng đồng người Hoa tại Malaysia được chế biến từ hủ tiếu bản to xào cùng tôm, chả cá, lạp xưởng, trứng, giá đỗ và hẹ. Ngoài ra, Roti Canai là món ăn của cộng đồng người Ấn. Đây là loại bánh dẹt, thơm, giòn và xốp, thường dùng kèm các loại cà ri. Thanh Thư",
-  "summary": "LỖI: 'NoneType' object is not iterable",
-  "faithfulness_score": 0.0,
-  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin gì về văn bản gốc, không có nội dung để đánh giá tính trung thực.",
-  "relevance_score": 0.0,
-  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không phản ánh được nội dung chính.",
-  "coherence_conciseness_score": 0.0,
-  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá tính mạch lạc và súc tích."
-}</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -919,27 +661,8 @@
           <t>Lodo, 62 tuổi, hôm 6/8 đã có buổi sáng trải nghiệm đan võng cùng với nghệ nhân ở Cù Lao Chàm. Ông bất ngờ về độ bền chắc và sự khéo léo, kỳ công của nghệ nhân làm ra nó. Lodo đã mua một chiếc võng về làm kỷ niệm trong chuyến du lịch Việt Nam lần này. 'Tôi nghĩ đây là một vật liệu xanh giúp bảo vệ môi trường', du khách đến từ Pháp nói. Theo ông Lê Vĩnh Thuận, Phó giám đốc Ban quản lý khu bảo tồn biển Cù Lao Chàm, trong dịp Festival 'Cù Lao Chàm - mùa ngô đồng đỏ' năm 2024 diễn ra từ ngày 5 đến 11/8, lượng du khách đổ về Cù Lao Chàm tham gia lễ hội 'rất đông'. Đến đây, du khách được tìm hiểu về nguồn gốc và tham gia cùng với nghệ nhân đan loại võng truyền thống của đảo. Theo giới thiệu của Trung tâm Quản lý bảo tồn di sản Hội An, sợi võng được làm từ các mảng vỏ cây ngô đồng. Sau khi được tách ra từ thân cây, vỏ sẽ được gom lại thành từng bó rồi ngâm nước ở các khe, suối trên đảo như khe Ruộng Chùa, khe Ông Thơ, khe Xóm Mới. Sau một tháng, người thợ đem vỏ về tách chọn lớp bên trong có màu trắng đục, tước từng sợi nhỏ, phơi khô cho đến khi có màu trắng tinh mới có thể bắt tay vào đan võng. Công đoạn tước đòi hỏi sự tập trung cao của người thợ vì 'sợi càng mỏng đan võng càng chặt', nghệ nhân đan võng Ngô Thị Lê, 70 tuổi, cho biết. Vào khoảng tháng 7, người dân trên đảo đi chọn vỏ những cây ngô đồng làm nguyên liệu đan võng, khi cây ra hoa, rụng hết lá, vỏ đủ khô để thu hoạch. Cây ngô đồng dùng làm võng phải có dáng thẳng mới cho ra sợi suôn, mềm, dai và chịu lực tốt. Bà Lê cho biết khi đã chọn được cây, người dân khai thác bằng cách chỉ chặt ngang thân để cây còn nảy chồi, phát triển sinh sống trở lại. Bà Huỳnh Thị Út, 56 tuổi, cùng với bà Lê là hai trong số ít nghệ nhân ở Cù Lao Chàm duy trì nghề đan võng ngô đồng cho biết loại võng này được người xã đảo sáng tạo ra trong quá trình lao động sản xuất. 'Để làm ra chiếc võng đẹp, ngoài tước sợi mỏng còn yêu cầu thắt nút các mối mắt võng đều', bà Út nói. Lodo nói những nghệ nhân đan võng đã giúp ông phân biệt võng tư có bốn dây đan nối nhau và võng sáu có sáu dây dày hơn đan thành hình tứ giác. Võng ngô đồng dài 2,6 m, đan thủ công hơn một tháng, độ bền của võng có thể kéo dài từ 5 đến 10 năm, có giá từ 5 đến 10 triệu đồng. 'Mức giá này xứng đáng với công sức những người thợ bỏ ra', Lodo cho hay. Chị Hà Nhi, 45 tuổi, sống tại Hà Nội, cũng ấn tượng với loại võng không làm từ sợi công nghiệp mà hoàn toàn từ vỏ cây. 'Những sản phẩm thủ công truyền thống thẩm mỹ cao như thế này là điểm nhấn cho du khách khi du lịch trên đảo', chị Nhi nói. Ngô đồng gắn liền với đời sống hàng ngày của người dân Cù Lao Chàm từ hơn 300 năm trước, theo Ban quản lý khu bảo tồn biển Cù Lao Chàm. Trải qua nhiều đời gìn giữ và nỗ lực bảo tồn, phát huy giá trị văn hóa, nghề đan võng ngô đồng ở địa phương được Bộ Văn hóa Thể thao và Du lịch công nhận là Di sản văn hóa phi vật thể quốc gia hôm 6/8. Tuấn Anh</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LỖI: 'NoneType' object is not iterable</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{
-  "id": 18,
-  "style": "news_brief",
-  "article": "Lodo, 62 tuổi, hôm 6/8 đã có buổi sáng trải nghiệm đan võng cùng với nghệ nhân ở Cù Lao Chàm. Ông bất ngờ về độ bền chắc và sự khéo léo, kỳ công của nghệ nhân làm ra nó. Lodo đã mua một chiếc võng về làm kỷ niệm trong chuyến du lịch Việt Nam lần này. 'Tôi nghĩ đây là một vật liệu xanh giúp bảo vệ môi trường', du khách đến từ Pháp nói. Theo ông Lê Vĩnh Thuận, Phó giám đốc Ban quản lý khu bảo tồn biển Cù Lao Chàm, trong dịp Festival 'Cù Lao Chàm - mùa ngô đồng đỏ' năm 2024 diễn ra từ ngày 5 đến 11/8, lượng du khách đổ về Cù Lao Chàm tham gia lễ hội 'rất đông'. Đến đây, du khách được tìm hiểu về nguồn gốc và tham gia cùng với nghệ nhân đan loại võng truyền thống của đảo. Theo giới thiệu của Trung tâm Quản lý bảo tồn di sản Hội An, sợi võng được làm từ các mảng vỏ cây ngô đồng. Sau khi được tách ra từ thân cây, vỏ sẽ được gom lại thành từng bó rồi ngâm nước ở các khe, suối trên đảo như khe Ruộng Chùa, khe Ông Thơ, khe Xóm Mới. Sau một tháng, người thợ đem vỏ về tách chọn lớp bên trong có màu trắng đục, tước từng sợi nhỏ, phơi khô cho đến khi có màu trắng tinh mới có thể bắt tay vào đan võng. Công đoạn tước đòi hỏi sự tập trung cao của người thợ vì 'sợi càng mỏng đan võng càng chặt', nghệ nhân đan võng Ngô Thị Lê, 70 tuổi, cho biết. Vào khoảng tháng 7, người dân trên đảo đi chọn vỏ những cây ngô đồng làm nguyên liệu đan võng, khi cây ra hoa, rụng hết lá, vỏ đủ khô để thu hoạch. Cây ngô đồng dùng làm võng phải có dáng thẳng mới cho ra sợi suôn, mềm, dai và chịu lực tốt. Bà Lê cho biết khi đã chọn được cây, người dân khai thác bằng cách chỉ chặt ngang thân để cây còn nảy chồi, phát triển sinh sống trở lại. Bà Huỳnh Thị Út, 56 tuổi, cùng với bà Lê là hai trong số ít nghệ nhân ở Cù Lao Chàm duy trì nghề đan võng ngô đồng cho biết loại võng này được người xã đảo sáng tạo ra trong quá trình lao động sản xuất. 'Để làm ra chiếc võng đẹp, ngoài tước sợi mỏng còn yêu cầu thắt nút các mối mắt võng đều', bà Út nói. Lodo nói những nghệ nhân đan võng đã giúp ông phân biệt võng tư có bốn dây đan nối nhau và võng sáu có sáu dây dày hơn đan thành hình tứ giác. Võng ngô đồng dài 2,6 m, đan thủ công hơn một tháng, độ bền của võng có thể kéo dài từ 5 đến 10 năm, có giá từ 5 đến 10 triệu đồng. 'Mức giá này xứng đáng với công sức những người thợ bỏ ra', Lodo cho hay. Chị Hà Nhi, 45 tuổi, sống tại Hà Nội, cũng ấn tượng với loại võng không làm từ sợi công nghiệp mà hoàn toàn từ vỏ cây. 'Những sản phẩm thủ công truyền thống thẩm mỹ cao như thế này là điểm nhấn cho du khách khi du lịch trên đảo', chị Nhi nói. Ngô đồng gắn liền với đời sống hàng ngày của người dân Cù Lao Chàm từ hơn 300 năm trước, theo Ban quản lý khu bảo tồn biển Cù Lao Chàm. Trải qua nhiều đời gìn giữ và nỗ lực bảo tồn, phát huy giá trị văn hóa, nghề đan võng ngô đồng ở địa phương được Bộ Văn hóa Thể thao và Du lịch công nhận là Di sản văn hóa phi vật thể quốc gia hôm 6/8. Tuấn Anh",
-  "summary": "LỖI: 'NoneType' object is not iterable",
-  "faithfulness_score": 0.0,
-  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không phản ánh nội dung của bài viết.",
-  "relevance_score": 0.0,
-  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ ý chính quan trọng nào từ văn bản gốc, không đề cập đến chủ đề về nghề đan võng ngô đồng tại Cù Lao Chàm.",
-  "coherence_conciseness_score": 0.0,
-  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá về tính mạch lạc và súc tích."
-}</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -947,27 +670,8 @@
           <t>Với mục tiêu quảng bá du lịch mua sắm tại Singapore, Vietrantour cùng Tổng Cục du lịch Singapore giới thiệu những điểm đến mua sắm và check in hấp dẫn. Nếu du khách đang tìm kiếm những món đồ phiên bản giới hạn của các hãng thời trang cao cấp như Prada, Louis Vuitton, Hermes, ION Orchard và Scotts Square, nên tới trục đường Orchard Road. Đặc biệt, một số thời điểm, các cửa hàng thời trang tại khu vực này khuyến mại tới 70%. Ngoài ra, một số địa điểm mua sắm người dân địa phương hay tới là Tampines 1, Jem và Westgate với nhiều cửa hàng bán lẻ, thời trang phục vụ nhu cầu đời sống. Nếu đang trong chuyến đi cùng gia đình, du khách hãy ghé qua trung tâm thương mại Tanglin Mall hoặc House of Anli với hàng nghìn mặt hàng gia dụng, sản phẩm dành cho mẹ và bé. Trong khi đó, trung tâm mua sắm Mustafa - tụ điểm mua sắm đêm khuya quen thuộc của người dân địa phương cũng là nơi nổi tiếng với những món đồ công nghệ hàng đầu, đến các sản phẩm tiêu dùng với giá cả phải chăng. Khi mua sắm tại Singapore, khách hàng còn được hoàn thuế tới 7%. Là quốc gia phát triển mạnh về dịch vụ du lịch, Singapore chú trọng nhiều đến trải nghiệm khách hàng. Đất nước này cũng được đánh giá là trạm trung gian lý tưởng để bảo hành các sản phẩm đồ hiệu, 'thiên đường' mua hàng miễn thuế với nhiều thương hiệu quốc tế và các nhãn hàng địa phương như mỹ phẩm, nước hoa, bia rượu, đồng hồ, thực phẩm... Tại Singapore, một trong những trải nghiệm thú vị là du khách có thể tự tay hoàn thiện các sản phẩm thủ công truyền thống. Các cửa hàng sẽ có thợ thủ công lành nghề hướng dẫn du khách chưng cất rượu gin tại Brass Lion Distillery, làm đồ da tại Atelier Lodge hoặc học kỹ thuật thêu tranh hạt cườm truyền thống tại Rumah Bebe. Bạn cũng có thể dạo qua khu phố di sản Kampong Gelam, nơi sở hữu những cửa hàng bày bán đồ truyền thống như đồ gốm, đồ da thủ công,.. Trải nghiệm này sẽ giúp du khách hiểu rõ hơn về nét đẹp văn hóa Singapore, đồng thời thể hiện phong cách cá nhân trong từng sản phẩm. Du khách nêndạo các nhà sách như Books Actually và Huggs-Epigram Coffee Bookshop để khám phá văn học kinh điển từ một số nhà thơ, tiểu thuyết gia của Singapore. Thanh Thư</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LỖI: 'NoneType' object is not iterable</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{
-  "id": 19,
-  "style": "news_brief",
-  "article": "Với mục tiêu quảng bá du lịch mua sắm tại Singapore, Vietrantour cùng Tổng Cục du lịch Singapore giới thiệu những điểm đến mua sắm và check in hấp dẫn. Nếu du khách đang tìm kiếm những món đồ phiên bản giới hạn của các hãng thời trang cao cấp như Prada, Louis Vuitton, Hermes, ION Orchard và Scotts Square, nên tới trục đường Orchard Road. Đặc biệt, một số thời điểm, các cửa hàng thời trang tại khu vực này khuyến mại tới 70%. Ngoài ra, một số địa điểm mua sắm người dân địa phương hay tới là Tampines 1, Jem và Westgate với nhiều cửa hàng bán lẻ, thời trang phục vụ nhu cầu đời sống. Nếu đang trong chuyến đi cùng gia đình, du khách hãy ghé qua trung tâm thương mại Tanglin Mall hoặc House of Anli với hàng nghìn mặt hàng gia dụng, sản phẩm dành cho mẹ và bé. Trong khi đó, trung tâm mua sắm Mustafa - tụ điểm mua sắm đêm khuya quen thuộc của người dân địa phương cũng là nơi nổi tiếng với những món đồ công nghệ hàng đầu, đến các sản phẩm tiêu dùng với giá cả phải chăng. Khi mua sắm tại Singapore, khách hàng còn được hoàn thuế tới 7%. Là quốc gia phát triển mạnh về dịch vụ du lịch, Singapore chú trọng nhiều đến trải nghiệm khách hàng. Đất nước này cũng được đánh giá là trạm trung gian lý tưởng để bảo hành các sản phẩm đồ hiệu, 'thiên đường' mua hàng miễn thuế với nhiều thương hiệu quốc tế và các nhãn hàng địa phương như mỹ phẩm, nước hoa, bia rượu, đồng hồ, thực phẩm... Tại Singapore, một trong những trải nghiệm thú vị là du khách có thể tự tay hoàn thiện các sản phẩm thủ công truyền thống. Các cửa hàng sẽ có thợ thủ công lành nghề hướng dẫn du khách chưng cất rượu gin tại Brass Lion Distillery, làm đồ da tại Atelier Lodge hoặc học kỹ thuật thêu tranh hạt cườm truyền thống tại Rumah Bebe. Bạn cũng có thể dạo qua khu phố di sản Kampong Gelam, nơi sở hữu những cửa hàng bày bán đồ truyền thống như đồ gốm, đồ da thủ công,.. Trải nghiệm này sẽ giúp du khách hiểu rõ hơn về nét đẹp văn hóa Singapore, đồng thời thể hiện phong cách cá nhân trong từng sản phẩm. Du khách nêndạo các nhà sách như Books Actually và Huggs-Epigram Coffee Bookshop để khám phá văn học kinh điển từ một số nhà thơ, tiểu thuyết gia của Singapore. Thanh Thư",
-  "summary": "LỖI: 'NoneType' object is not iterable",
-  "faithfulness_score": 0.0,
-  "faithfulness_reason": "Bản tóm tắt không cung cấp thông tin nào về văn bản gốc, không có nội dung để đánh giá tính trung thực.",
-  "relevance_score": 0.0,
-  "relevance_reason": "Bản tóm tắt không bao gồm bất kỳ thông tin quan trọng nào từ văn bản gốc, không thể đánh giá tính bao quát.",
-  "coherence_conciseness_score": 0.0,
-  "coherence_conciseness_reason": "Bản tóm tắt không có nội dung, không thể đánh giá tính mạch lạc và súc tích."
-}</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -975,27 +679,8 @@
           <t>Chương trình lần này có sự đồng hành của diễn viên Ninh Dương Lan Ngọc. Thông qua Epic Sale, diễn viên mong muốn lan tỏa tinh thần du lịch thông minh, tiện lợi và tối ưu chi phí. Ông Iko Putera, Giám đốc Vận chuyển Traveloka, cho biết việc hợp tác cùng Lan Ngọc đánh dấu cột mốc quan trọng trên hành trình mang đến trải nghiệm du lịch tiện nghi tối ưu cho khách hàng. Tầm ảnh hưởng và đam mê du lịch của cô phù hợp với sứ mệnh nền tảng theo đuổi. Đôi bên đều muốn truyền cảm hứng khám phá thế giới qua những chuyến đi. Với Epic Sale lần này, Traveloka áp dụng ưu đãi đến 50% cho các sản phẩm du lịch, dịch vụ trên toàn thế giới. 'Đây là lời tri ân chúng tôi muốn gửi đến khách hàng đã luôn ủng hộ, gắn bó trên hành trình kiến tạo những chuyến đi đáng nhớ cùng Traveloka', ông Iko Putera cho biết. Từ khi trở thành đại sứ thương hiệu tại Việt Nam, diễn viên Ninh Dương Lan Ngọc đã có nhiều trải nghiệm du lịch chất lượng với nền tảng. Với loạt khuyến mại, ưu đãi, quà tặng trong Epic Sale 2024, cô nói sẽ tranh thủ săn vé, đặt phòng, chuẩn bị cho những chuyến đi sắp tới. Theo Lan Ngọc, chương trình mang lại cho du khách cơ hội du lịch tiện nghi với chi phí tiết kiệm, giúp khơi dậy mong muốn đi đây đi đó, khám phá thế giới. Cô đánh giá cao sự tiện lợi và các dịch vụ toàn diện của nền tảng, giúp việc lên kế hoạch cho các chuyến đi thêm dễ dàng, thú vị. Traveloka đã hợp tác cùng hàng nghìn đối tác để mang đến những deal giá ưu đãi sâu. Người dùng có thể truy cập nền tảng, theo dõi các ưu đãi hàng ngày trong các mục Vé máy bay, Khách sạn, Xperience và nhiều sản phẩm du lịch khác. 'Siêu ưu đãi Epic' (Super Epic Deal) sẽ được áp dụng cho các sản phẩm nhất định trong khung giờ giới hạn. Cụ thể, giờ vàng Epic Hour Deal ưu đãi vé máy bay mỗi thứ Bảy từ 14h-17h; đặt khách sạn giờ vàng EPIC Hotel Hour Deal diễn ra hàng ngày từ 18h-19h. Du khách có thể săn vé máy bay quốc nội và quốc tế với giá ưu đãi. Trong đó, vé nội địa Vietravel giá chỉ từ 781.925 đồng; vé China Southern Airlines đi Thâm Quyến từ 2,819 đồng; vé T'way Air đến Hàn Quốc và Nhật Bản lần lượt chỉ từ 2,667 triệu đồng và 2,682 triệu đồng. Khách hàng còn có cơ hội nghỉ dưỡng tại khách sạn 5 sao trong nước với giá từ 794.000 đồng. Hàng loạt khách sạn Hàn Quốc giá từ 1,858 triệu đồng, Nhật Bản từ 1,146 triệu đồng. Với dịch vụ giải trí, nền tảng áp dụng ưu đãi 'mua 1 tặng 1' vé tham quan Sun World, công viên nước The Amazing Bay, thủy cung Sea Life Bangkok Ocean World (Thái Lan). Để du khách có trải nghiệm du lịch trọn vẹn, Traveloka giới thiệu thêm nhiều tính năng khác như: hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt... Xem thêm thông tin chi tiết về chương trình Epic Sale trên ứng dụng, website và các tài khoản mạng xã hội của Traveloka. Á Hiên</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>781.925 đồng vé Vietravel, 2.819 triệu Thâm Quyến; 2.667 và 2.682 triệu Hàn Quốc-Nhật Bản. Khách sạn từ 794.000-1.858 triệu. Áp dụng 'mua 1 tặng 1' Sun World, The Amazing Bay, Sea Life Bangkok Ocean World. Hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt trên Traveloka. Epic Sale của Ninh Dương Lan Ngọc mong muốn lan tỏa tinh thần du lịch thông minh và áp dụng ưu đãi đến 50% cho các sản phẩm toàn thế giới nhằm tri ân khách hàng và khích lệ khám phá thế giới qua những chuyến đi tiện nghi với chi phí tiết kiệm.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{
-  "id": 20,
-  "style": "news_brief",
-  "article": "Chương trình lần này có sự đồng hành của diễn viên Ninh Dương Lan Ngọc. Thông qua Epic Sale, diễn viên mong muốn lan tỏa tinh thần du lịch thông minh, tiện lợi và tối ưu chi phí. Ông Iko Putera, Giám đốc Vận chuyển Traveloka, cho biết việc hợp tác cùng Lan Ngọc đánh dấu cột mốc quan trọng trên hành trình mang đến trải nghiệm du lịch tiện nghi tối ưu cho khách hàng. Tầm ảnh hưởng và đam mê du lịch của cô phù hợp với sứ mệnh nền tảng theo đuổi. Đôi bên đều muốn truyền cảm hứng khám phá thế giới qua những chuyến đi. Với Epic Sale lần này, Traveloka áp dụng ưu đãi đến 50% cho các sản phẩm du lịch, dịch vụ trên toàn thế giới. 'Đây là lời tri ân chúng tôi muốn gửi đến khách hàng đã luôn ủng hộ, gắn bó trên hành trình kiến tạo những chuyến đi đáng nhớ cùng Traveloka', ông Iko Putera cho biết. Từ khi trở thành đại sứ thương hiệu tại Việt Nam, diễn viên Ninh Dương Lan Ngọc đã có nhiều trải nghiệm du lịch chất lượng với nền tảng. Với loạt khuyến mại, ưu đãi, quà tặng trong Epic Sale 2024, cô nói sẽ tranh thủ săn vé, đặt phòng, chuẩn bị cho những chuyến đi sắp tới. Theo Lan Ngọc, chương trình mang lại cho du khách cơ hội du lịch tiện nghi với chi phí tiết kiệm, giúp khơi dậy mong muốn đi đây đi đó, khám phá thế giới. Cô đánh giá cao sự tiện lợi và các dịch vụ toàn diện của nền tảng, giúp việc lên kế hoạch cho các chuyến đi thêm dễ dàng, thú vị. Traveloka đã hợp tác cùng hàng nghìn đối tác để mang đến những deal giá ưu đãi sâu. Người dùng có thể truy cập nền tảng, theo dõi các ưu đãi hàng ngày trong các mục Vé máy bay, Khách sạn, Xperience và nhiều sản phẩm du lịch khác. 'Siêu ưu đãi Epic' (Super Epic Deal) sẽ được áp dụng cho các sản phẩm nhất định trong khung giờ giới hạn. Cụ thể, giờ vàng Epic Hour Deal ưu đãi vé máy bay mỗi thứ Bảy từ 14h-17h; đặt khách sạn giờ vàng EPIC Hotel Hour Deal diễn ra hàng ngày từ 18h-19h. Du khách có thể săn vé máy bay quốc nội và quốc tế với giá ưu đãi. Trong đó, vé nội địa Vietravel giá chỉ từ 781.925 đồng; vé China Southern Airlines đi Thâm Quyến từ 2,819 đồng; vé T'way Air đến Hàn Quốc và Nhật Bản lần lượt chỉ từ 2,667 triệu đồng và 2,682 triệu đồng. Khách hàng còn có cơ hội nghỉ dưỡng tại khách sạn 5 sao trong nước với giá từ 794.000 đồng. Hàng loạt khách sạn Hàn Quốc giá từ 1,858 triệu đồng, Nhật Bản từ 1,146 triệu đồng. Với dịch vụ giải trí, nền tảng áp dụng ưu đãi 'mua 1 tặng 1' vé tham quan Sun World, công viên nước The Amazing Bay, thủy cung Sea Life Bangkok Ocean World (Thái Lan). Để du khách có trải nghiệm du lịch trọn vẹn, Traveloka giới thiệu thêm nhiều tính năng khác như: hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt... Xem thêm thông tin chi tiết về chương trình Epic Sale trên ứng dụng, website và các tài khoản mạng xã hội của Traveloka. Á Hiên",
-  "summary": "781.925 đồng vé Vietravel, 2.819 triệu Thâm Quyến; 2.667 và 2.682 triệu Hàn Quốc-Nhật Bản. Khách sạn từ 794.000-1.858 triệu. Áp dụng 'mua 1 tặng 1' Sun World, The Amazing Bay, Sea Life Bangkok Ocean World. Hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt trên Traveloka. Epic Sale của Ninh Dương Lan Ngọc mong muốn lan tỏa tinh thần du lịch thông minh và áp dụng ưu đãi đến 50% cho các sản phẩm toàn thế giới nhằm tri ân khách hàng và khích lệ khám phá thế giới qua những chuyến đi tiện nghi với chi phí tiết kiệm.",
-  "faithfulness_score": 0.8,
-  "faithfulness_reason": "Bản tóm tắt không bịa đặt thông tin nhưng có thể thiếu một số chi tiết quan trọng như việc hợp tác giữa Traveloka và Ninh Dương Lan Ngọc, cũng như một số thông tin về các dịch vụ và ưu đãi cụ thể.",
-  "relevance_score": 0.7,
-  "relevance_reason": "Bản tóm tắt bao gồm một số ý chính như giá vé máy bay, khách sạn và các ưu đãi, nhưng có thể bỏ sót một số thông điệp cốt lõi như sứ mệnh của Traveloka và tầm ảnh hưởng của Ninh Dương Lan Ngọc.",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Bản tóm tắt trôi chảy, logic và dễ đọc, tuy nhiên có thể có một số từ ngữ lặp lại hoặc không cần thiết, nhưng tổng thể vẫn rõ ràng và súc tích."
-}</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Thư mục KQ/VB sau tóm tắt/test_results.xlsx
+++ b/Thư mục KQ/VB sau tóm tắt/test_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Regent Hotels &amp; Resorts tổ chức Taste Studio với chủ đề 'Dáng hình của biển', quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, giới hạn 20 khách mời mỗi tối.</t>
+          <t>Regent Hotels &amp; Resorts tổ chức Taste Studio với chủ đề 'Dáng hình của biển', quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, chỉ có 20 khách mời mỗi tối.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -462,13 +462,13 @@
   "id": 1,
   "style": "news_brief",
   "article": "Taste Studio do thương hiệu Regent Hotels &amp; Resorts tổ chức nhằm mang đến trải nghiệm đa giác quan qua ẩm thực và nghệ thuật. Sự kiện này quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, từ nhà thiết kế thời trang đến nhạc sĩ, kết hợp cùng các thương hiệu hàng đầu như Vietnam Airlines. Sự kiện hướng đến phân khúc khách hàng sang trọng. Mùa một và hai diễn ra lần được vào tháng 4, tháng 11 năm ngoái. Taste Studio năm nay với chủ đề 'Dáng hình của biển', giới hạn 20 khách mời mỗi tối. Các khách mời được tham gia vào chuỗi khám phá gồm 7 chương đặc sắc về vẻ đẹp của biển, qua lăng kính nghệ sĩ tài hoa Mr. Dripping - nghệ sĩ vẽ tranh bằng phương pháp nhỏ giọt (drip art). Không gian nhà hàng, nơi diễn ra sự kiện với nội thất dùng tre, mây và tầm vông do kiến trúc sư Nguyễn Trung Nghĩa thiết kế. Ngoài hai nghệ sĩ này, Taste Studio còn có sự tham gia của bếp trưởng Francesco đến từ Milan, với 20 năm kinh nghiệm làm việc tại các khách sạn danh tiếng thế giới, đang bắt đầu hành trình mới tại Việt Nam. Ông đảm nhận vai trò cố vấn ẩm thực tại Regent Phú Quốc, mang đến trải nghiệm độc đáo cho thực khách. Bên cạnh đó, phó bếp trưởng điều hành Huân Trần tại chương trình mong muốn chinh phục các hương vị vùng miền khác nhau. Được nếm nhiều nguyên liệu địa phương và các loại gia vị đặc biệt, vị đầu bếp để lại điểm nhấn riêng trong cách giữ gìn, nâng tầm phong vị của quê hương tại Regent Phú Quốc. Chương trình có sự góp mặt của bếp trưởng nhà hàng Oku - Andy Huỳnh. Trước khi gia nhập Regent Phú Quốc, anh phát triển kỹ thuật nấu ăn Nhật Bản tại Nobu, San Diego và Nassau. Các món ăn của Andy luôn mang ý nghĩa hướng về cội nguồn. Bếp trưởng nhà hàng Ocean Club Daniel và bếp trưởng Duyến Nguyễn của khu nghỉ dưỡng này cũng tham gia, sáng tạo một số hương vị độc đáo từ nguyên liệu địa phương. Đại diện Regent Phú Quốc cho biết, thông qua Taste Studio, đơn vị mong muốn tiếp tục kiến tạo trải nghiệm đưa nét bản địa đặc sắc của Việt Nam lên bản đồ thế giới, từ đó chinh phục khách hàng hạng sang và giới chuyên gia. Thanh Thư",
-  "summary": "Regent Hotels &amp; Resorts tổ chức Taste Studio với chủ đề 'Dáng hình của biển', quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, giới hạn 20 khách mời mỗi tối.",
+  "summary": "Regent Hotels &amp; Resorts tổ chức Taste Studio với chủ đề 'Dáng hình của biển', quy tụ nhiều đầu bếp và nghệ sĩ nổi tiếng, chỉ có 20 khách mời mỗi tối.",
   "faithfulness_score": 0.8,
   "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như sự tham gia của các thương hiệu hàng đầu và nghệ sĩ tài năng",
   "relevance_score": 0.6,
-  "relevance_reason": "Tóm tắt chỉ đề cập đến chủ đề của sự kiện và giới hạn khách mời, nhưng bỏ qua các thông tin quan trọng về mục tiêu của chương trình và sự tham gia của các đầu bếp nổi tiếng",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và không có thông tin trùng lặp, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng để làm cho tóm tắt trở nên đầy đủ hơn"
+  "relevance_reason": "Tóm tắt chỉ đề cập đến chủ đề và số lượng khách mời mà không bao gồm các thông tin quan trọng về sự kiện như mục tiêu và ý nghĩa của chương trình",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và không có từ ngữ lặp lại, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng"
 }</t>
         </is>
       </c>
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amiana Resort Nha Trang tiếp tục nhận hai giải thưởng 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới', sau 4 năm liên tiếp. Phong cách hòa hợp giữa truyền thống và hiện đại tạo không gian thư giãn gần gũi thiên nhiên, biệt thự có cửa sổ lớn và ban công rộng, hồ bơi riêng tư và vườn nhiệt đới xanh mát. Resort chú trọng bảo vệ môi trường bằng giải pháp bền vững.</t>
+          <t>Khu nghỉ dưỡng Amiana Nha Trang tiếp tục nhận hai giải thưởng 'Thiết kế kiến trúc tốt nhất thế giới' và 'Hướng biển sang trọng lãng mạn', sau 4 năm liên tiếp. Phong cách truyền thống hiện đại tạo không gian gần gũi thiên nhiên, biệt thự có cửa sổ lớn ban công rộng, hồ bơi riêng tư vườn nhiệt đới xanh mát. Resort bảo vệ môi trường bền vững.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,13 +490,13 @@
   "id": 2,
   "style": "news_brief",
   "article": "Hai giải thưởng gồm 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới'. Đây cũng là năm thứ tư liên tiếp đơn vị đạt giải thưởng này, sau quá trình thẩm định từ hội đồng chuyên môn toàn cầu và bình chọn bởi hàng nghìn du khách, khách sạn quốc tế khác. 'Giải thưởng góp phần khẳng định Amiana Resort Nha Trang là điểm đến lý tưởng cho du khách tìm kiếm không gian riêng tư, gần gũi thiên nhiên với kiến trúc cao cấp, mang lại trải nghiệm sang trọng, độc đáo', đại diện resort chia sẻ. Amiana có kiến trúc hòa hợp thiên nhiên, kết hợp yếu tố truyền thống và hiện đại, tạo nên không gian thư giãn, sang trọng nhưng vẫn giữ được cảm giác gần gũi, yên bình. Bãi biển riêng tư với hàng dừa rợp bóng xanh mát là nơi du khách có thể thư giãn, nghỉ ngơi thoải mái. Resort còn tận dụng địa hình tự nhiên để bố trí các công trình công cộng như hồ bơi, nhà hàng, phòng hội nghị, spa... Các yếu tố đậm chất nhiệt đới như dừa xanh, sóng biển, đá và gỗ được lồng ghép khéo léo trong từng chi tiết thiết kế nội ngoại thất. Biệt thự, phòng nghỉ, nhà hàng đều có sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại. Mỗi căn biệt thự đều mang kiến trúc mở, sử dụng nội thất chủ yếu từ gỗ, đá tự nhiên. Tất cả phòng đều có cửa sổ lớn và ban công rộng, tối ưu tầm nhìn hướng biển với cảnh quan thiên nhiên vây quanh. Biệt thự còn có hồ bơi riêng, không gian vườn với các loại cây nhiệt đới, đảm bảo yếu tố riêng tư cho khách hàng. Resort không chỉ chú trọng xây dựng công trình tiện ích, mà còn đặc biệt lưu ý việc bảo vệ môi trường, sử dụng các giải pháp bền vững. Những không gian xanh, vườn cây, hồ nước đều được bố trí hợp lý, tạo nên hệ sinh thái tự nhiên trong lòng khu nghỉ dưỡng. Theo đại diện Amiana Resort Nha Trang, những chi tiết kiến trúc thông minh cùng không gian mở, vật liệu tự nhiên, sự khéo léo trong thiết kế tại đây góp phần tạo nên khu nghỉ dưỡng lý tưởng cho những ai tìm kiếm sự an yên, lãng mạn và xa hoa. Á Hiên",
-  "summary": "Amiana Resort Nha Trang tiếp tục nhận hai giải thưởng 'Khu nghỉ dưỡng có thiết kế kiến trúc tốt nhất thế giới' và 'Khu nghỉ dưỡng hướng biển lãng mạn sang trọng nhất thế giới', sau 4 năm liên tiếp. Phong cách hòa hợp giữa truyền thống và hiện đại tạo không gian thư giãn gần gũi thiên nhiên, biệt thự có cửa sổ lớn và ban công rộng, hồ bơi riêng tư và vườn nhiệt đới xanh mát. Resort chú trọng bảo vệ môi trường bằng giải pháp bền vững.",
-  "faithfulness_score": 0.9,
-  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể làm rõ hơn về quá trình thẩm định và bình chọn của hội đồng chuyên môn toàn cầu",
-  "relevance_score": 0.8,
-  "relevance_reason": "Tóm tắt đã bao gồm các điểm chính về giải thưởng và thiết kế của khu nghỉ dưỡng, nhưng bỏ qua một số chi tiết quan trọng như hệ sinh thái tự nhiên và sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể rút gọn một số câu để tăng độ súc tích"
+  "summary": "Khu nghỉ dưỡng Amiana Nha Trang tiếp tục nhận hai giải thưởng 'Thiết kế kiến trúc tốt nhất thế giới' và 'Hướng biển sang trọng lãng mạn', sau 4 năm liên tiếp. Phong cách truyền thống hiện đại tạo không gian gần gũi thiên nhiên, biệt thự có cửa sổ lớn ban công rộng, hồ bơi riêng tư vườn nhiệt đới xanh mát. Resort bảo vệ môi trường bền vững.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể làm rõ hơn một số chi tiết như quá trình thẩm định và bình chọn của hội đồng chuyên môn toàn cầu",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt đã bao gồm các điểm chính về giải thưởng và đặc điểm của khu nghỉ dưỡng, nhưng bỏ qua một số chi tiết quan trọng như hệ sinh thái tự nhiên và sự kết hợp giữa vật liệu tự nhiên và công nghệ hiện đại",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể rút gọn một số câu để tăng sự cô đọng"
 }</t>
         </is>
       </c>
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ. Nơi đây là điểm đến ngắm dòng Tiền Giang và đón gió mát dịu. Du khách còn được tham quan khu du lịch sinh thái với bộ sưu tập gỗ lũa độc đáo. Gỗ lũa lấy từ đáy sông, sau khi bị bào mòn chỉ còn phần lõi bền chắc. Khu du lịch này có tiểu cảnh và nhà nghỉ làm bằng vật liệu chính là những thân cây khủng này. Một bức tranh điêu khắc dài hơn 24m nặng 20 tấn được thực hiện trên khúc gỗ trầm thủy, tùy từng đoạn chiều cao từ 1,5 - 1,8 m. Cạnh đó còn có bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ và tiểu cảnh làm từ gỗ lũa. Du khách cũng ngắm hoàng hôn trên sông tại đây. Giá vé vào cổng là 80.000 đồng.</t>
+          <t>Gỗ lũa từ sông Tiền tạo nên khu du lịch Cồn Én, với tiểu cảnh và bức tranh điêu khắc dài 24 m. Chị Phúc Điền sưu tập hàng nghìn thân gỗ lũa thành điểm tham quan yên bình ở miền Tây; giá vé 80.000 đồng cho khách từ TP HCM tới qua quốc lộ 30 hoặc phà Tấn Long.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,13 +518,13 @@
   "id": 3,
   "style": "news_brief",
   "article": "Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ, rộng hơn 300 ha. Nơi đây ngoài là điểm đến ngắm dòng Tiền Giang, đón gió sông mát dịu, còn là địa chỉ thu hút khách với bộ sưu tập gỗ lũa nội thất độc đáo của khu du lịch trên cồn. Gỗ lũa tức những thân cây khủng, vớt từ đáy sông, bên ngoài bị dòng nước bào mòn, chỉ còn phần lõi bền chắc. Hàng nghìn thân gỗ lũa được người chủ tuyển chọn làm vật liệu chính xây Khu du lịch sinh thái Cồn Én từ tiểu cảnh, nhà đến đài quan sát. Hơn 20 năm trước, ông Nguyễn Văn Nghỉ ở huyện Chợ Mới đã sưu tập rất nhiều gỗ lũa. Ban đầu ông trục vớt chúng để khơi thông dòng chảy, hạn chế tình trạng lưới đánh cá mắc vào thân cây. Lâu dần, ông yêu mến và muốn lưu giữ những thân gỗ trầm thủy này. Ba năm trước, ông Nghỉ dùng số gỗ lũa để xây khu du lịch ven sông Tiền rộng 6 ha. Đặc sắc trong các vật liệu từ gỗ lũa là bức tranh điêu khắc về phong cảnh làng quê Việt Nam xưa dài hơn 24 m, nặng 20 tấn. Bức tranh do nghệ nhân ở Huế thực hiện trong 7 năm, trên khúc gỗ trầm thủy khủng, tùy từng đoạn có chiều cao từ 1,5 - 1,8 m. Cạnh bức tranh là bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ như tứ quý, sảnh tiến tới của nhiều dòng xe nổi tiếng. Dọc các lối đi là những tiểu cảnh làm từ gỗ lũa. Một số được điêu khắc thành các con vật, chim muông. Những cây gỗ lũa kích thước lớn được tận dụng làm đài quan sát cao 26 m, hoặc móng trụ để xây nhà nghỉ, cầu vượt. Khuôn viên cũng được phủ bởi nhiều cây kiểng, dừa cùng dãy nhà sàn ven sông. Tại đây du khách được ngắm hoàng hôn trên sông, tắm sông và thưởng thức ẩm thực miền Tây. Chị Phúc Điền, du khách ở TP HCM, cho biết khá thích với khung cảnh miền Tây yên bình ở Cồn Én. Chị cũng bất ngờ với sự kỳ công của người đã sưu tập hàng nghìn thân gỗ lũa và biến chúng thành điểm tham quan độc đáo. Cồn Én, nằm cách TP HCM 170 km, du khách có thể đến đây từ hướng quốc lộ 30 của tỉnh Đồng Tháp hoặc lên phà Tấn Long vượt sông Tiền từ phía huyện Chợ Mới. Giá vé vào cổng là 80.000 đồng. Ngọc Tài",
-  "summary": "Cồn Én nằm giữa sông Tiền, thuộc xã Tấn Mỹ. Nơi đây là điểm đến ngắm dòng Tiền Giang và đón gió mát dịu. Du khách còn được tham quan khu du lịch sinh thái với bộ sưu tập gỗ lũa độc đáo. Gỗ lũa lấy từ đáy sông, sau khi bị bào mòn chỉ còn phần lõi bền chắc. Khu du lịch này có tiểu cảnh và nhà nghỉ làm bằng vật liệu chính là những thân cây khủng này. Một bức tranh điêu khắc dài hơn 24m nặng 20 tấn được thực hiện trên khúc gỗ trầm thủy, tùy từng đoạn chiều cao từ 1,5 - 1,8 m. Cạnh đó còn có bộ sưu tập hàng trăm chiếc xe máy biển số độc lạ và tiểu cảnh làm từ gỗ lũa. Du khách cũng ngắm hoàng hôn trên sông tại đây. Giá vé vào cổng là 80.000 đồng.",
-  "faithfulness_score": 0.9,
-  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng thiếu một số chi tiết quan trọng như diện tích của khu du lịch và quá trình sưu tập gỗ lũa của ông Nguyễn Văn Nghỉ",
-  "relevance_score": 0.8,
-  "relevance_reason": "Tóm tắt bao gồm các điểm chính như vị trí, đặc điểm của gỗ lũa và hoạt động du lịch, nhưng bỏ qua một số thông tin quan trọng như vị trí của Cồn Én so với TP HCM và cách di chuyển đến đó",
-  "coherence_conciseness_score": 0.9,
-  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể rút gọn một số câu để tăng độ súc tích"
+  "summary": "Gỗ lũa từ sông Tiền tạo nên khu du lịch Cồn Én, với tiểu cảnh và bức tranh điêu khắc dài 24 m. Chị Phúc Điền sưu tập hàng nghìn thân gỗ lũa thành điểm tham quan yên bình ở miền Tây; giá vé 80.000 đồng cho khách từ TP HCM tới qua quốc lộ 30 hoặc phà Tấn Long.",
+  "faithfulness_score": 0.2,
+  "faithfulness_reason": "Tóm tắt chứa thông tin không chính xác, ví dụ như việc gán cho chị Phúc Điền là người sưu tập hàng nghìn thân gỗ lũa, trong khi thực tế là ông Nguyễn Văn Nghỉ",
+  "relevance_score": 0.6,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số điểm nổi bật của Cồn Én, nhưng bỏ qua nhiều thông tin quan trọng như lịch sử hình thành, các điểm tham quan khác",
+  "coherence_conciseness_score": 0.4,
+  "coherence_conciseness_reason": "Tóm tắt không rõ ràng, có nhiều thông tin bị lẫn lộn và không có sự liên kết logic giữa các ý"
 }</t>
         </is>
       </c>
@@ -535,8 +535,27 @@
           <t>Văn phòng mới của MayTrip tại địa chỉ 833 Lê Hồng Phong, quận 10, nhằm mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Văn phòng mới được kỳ vọng là điểm đến thuận tiện cho khách hàng trong việc tìm hiểu và sử dụng dịch vụ của công ty. Trong ngày khai trương, MayTrip trao tặng nhiều quà tặng và ưu đãi cho khách tham dự. Các voucher gồm: 2 triệu đồng cho khách đăng ký tour Bắc Á trong ba ngày khai trương, 1 triệu đồng cho tour Đông Nam Á trong ba tháng từ ngày khai trương, 500.000 đồng cho dịch vụ tour nội địa trong một năm, 200.000 đồng dịch vụ đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và 100.000 đồng với dịch vụ vé máy bay trong 6 tháng. Buổi lễ khai trương văn phòng tại Sài Gòn còn giới thiệu các chương trìnhtour Nhật Bảndịp Tết Âm lịch như cung đường vàng trải nghiệm trượt tuyết, Hokkaido - miền tuyết trắng. Những chuyến đi này được MayTrip thiết kế kỹ lưỡng, phù hợp với không khí đón xuân cho gia đình và cặp đôi Việt trong dịp Tết Nguyên đán. Năm nay, MayTrip xác định tour Hokkaido là sản phẩm 'đinh' trong dịp Tết Nguyên đán. Hokkaido nằm ở miền Bắc Nhật Bản, nổi tiếng với những đợt tuyết dày và phong cảnh mùa đông đặc trưng. Tour Hokkaido dịp Tết là hành trình lý tưởng để du khách tận hưởng kỳ nghỉ theo cách mới mẻ và ấn tượng trong tuyết trắng. Bên cạnh đó, tour Hokkaido của MayTrip cũng mang đến trải nghiệm suối nước nóng onsen giữa băng tuyết, giúp du khách thư giãn sau những hoạt động trong ngày. Bên cạnh đó, MayTrip cũng cung cấp các tour du lịch khác với lịch khởi hành linh hoạt kéo dài đến hết năm 2025, gồm hành trình ngắm hoa anh đào, hoa mơ, mận và nghỉ lễ 30/4 và 1/5. Các hành trình này dựa trên xu hướng và sở thích của du khách Việt Nam. Theo đại diện công ty, sự kiện khai trương văn phòng mới tại TP HCM đánh dấu bước phát triển mới của MayTrip. Với mục tiêu ưu tiên trải nghiệm khách hàng, đơn vị hy vọng nhận được sự ủng hộ từ khách hàng để trở thành công ty lữ hành hàng đầu, hướng mục tiêu thương hiệu toàn cầu vào năm 2030. Ngoài TP HCM, MayTrip còn có văn phòng tại Hải Phòng và TP Vinh. Các văn phòng này giúp MayTrip dễ dàng tiếp cận và đáp ứng nhu cầu đa dạng của khách hàng. Công ty cam kết đảm bảo chất lượng dịch vụ để mang lại chuyến đi an toàn, trọn vẹn cho khách hàng. Thanh Thư</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MayTrip khai trương văn phòng mới tại 833 Lê Hồng Phong, mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Công ty trao tặng quà cho khách tham dự với ưu đãi tour Bắc Á trong ba ngày đầu; tour Đông Nam Á trong ba tháng từ ngày khai trương; tour nội địa trong một năm; đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và vé máy bay trong 6 tháng. MayTrip giới thiệu các chương trình tour Hokkaido dịp Tết Nguyên đán, cung cấp trải nghiệm suối nước nóng trên tuyết trắng cho năm 2030.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{
+  "id": 4,
+  "style": "news_brief",
+  "article": "Văn phòng mới của MayTrip tại địa chỉ 833 Lê Hồng Phong, quận 10, nhằm mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Văn phòng mới được kỳ vọng là điểm đến thuận tiện cho khách hàng trong việc tìm hiểu và sử dụng dịch vụ của công ty. Trong ngày khai trương, MayTrip trao tặng nhiều quà tặng và ưu đãi cho khách tham dự. Các voucher gồm: 2 triệu đồng cho khách đăng ký tour Bắc Á trong ba ngày khai trương, 1 triệu đồng cho tour Đông Nam Á trong ba tháng từ ngày khai trương, 500.000 đồng cho dịch vụ tour nội địa trong một năm, 200.000 đồng dịch vụ đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và 100.000 đồng với dịch vụ vé máy bay trong 6 tháng. Buổi lễ khai trương văn phòng tại Sài Gòn còn giới thiệu các chương trìnhtour Nhật Bảndịp Tết Âm lịch như cung đường vàng trải nghiệm trượt tuyết, Hokkaido - miền tuyết trắng. Những chuyến đi này được MayTrip thiết kế kỹ lưỡng, phù hợp với không khí đón xuân cho gia đình và cặp đôi Việt trong dịp Tết Nguyên đán. Năm nay, MayTrip xác định tour Hokkaido là sản phẩm 'đinh' trong dịp Tết Nguyên đán. Hokkaido nằm ở miền Bắc Nhật Bản, nổi tiếng với những đợt tuyết dày và phong cảnh mùa đông đặc trưng. Tour Hokkaido dịp Tết là hành trình lý tưởng để du khách tận hưởng kỳ nghỉ theo cách mới mẻ và ấn tượng trong tuyết trắng. Bên cạnh đó, tour Hokkaido của MayTrip cũng mang đến trải nghiệm suối nước nóng onsen giữa băng tuyết, giúp du khách thư giãn sau những hoạt động trong ngày. Bên cạnh đó, MayTrip cũng cung cấp các tour du lịch khác với lịch khởi hành linh hoạt kéo dài đến hết năm 2025, gồm hành trình ngắm hoa anh đào, hoa mơ, mận và nghỉ lễ 30/4 và 1/5. Các hành trình này dựa trên xu hướng và sở thích của du khách Việt Nam. Theo đại diện công ty, sự kiện khai trương văn phòng mới tại TP HCM đánh dấu bước phát triển mới của MayTrip. Với mục tiêu ưu tiên trải nghiệm khách hàng, đơn vị hy vọng nhận được sự ủng hộ từ khách hàng để trở thành công ty lữ hành hàng đầu, hướng mục tiêu thương hiệu toàn cầu vào năm 2030. Ngoài TP HCM, MayTrip còn có văn phòng tại Hải Phòng và TP Vinh. Các văn phòng này giúp MayTrip dễ dàng tiếp cận và đáp ứng nhu cầu đa dạng của khách hàng. Công ty cam kết đảm bảo chất lượng dịch vụ để mang lại chuyến đi an toàn, trọn vẹn cho khách hàng. Thanh Thư",
+  "summary": "MayTrip khai trương văn phòng mới tại 833 Lê Hồng Phong, mở rộng dịch vụ và nâng cao trải nghiệm khách hàng khu vực phía Nam. Công ty trao tặng quà cho khách tham dự với ưu đãi tour Bắc Á trong ba ngày đầu; tour Đông Nam Á trong ba tháng từ ngày khai trương; tour nội địa trong một năm; đặt phòng khách sạn hoặc xe du lịch trong 6 tháng và vé máy bay trong 6 tháng. MayTrip giới thiệu các chương trình tour Hokkaido dịp Tết Nguyên đán, cung cấp trải nghiệm suối nước nóng trên tuyết trắng cho năm 2030.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có một số điểm không chính xác như không đề cập đến việc MayTrip có văn phòng tại Hải Phòng và TP Vinh, cũng như không nhắc đến mục tiêu của công ty là trở thành công ty lữ hành hàng đầu vào năm 2030. Ngoài ra, tóm tắt cũng không rõ ràng về thời gian áp dụng các chương trình ưu đãi.",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt đã đề cập đến việc MayTrip khai trương văn phòng mới và một số chương trình tour du lịch, nhưng lại bỏ qua một số điểm quan trọng như mục tiêu của công ty và các văn phòng khác của MayTrip. Điều này làm cho tóm tắt không đầy đủ và thiếu thông tin quan trọng.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng và dễ hiểu, không có từ ngữ lặp lại hoặc thông tin thừa. Tuy nhiên, có một số điểm như việc nhắc đến năm 2030 không rõ ràng về mục đích và có thể gây nhầm lẫn cho người đọc."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -545,7 +564,22 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{
+  "id": 5,
+  "style": "news_brief",
+  "article": "Ngày 29/10, tại Khu du lịch Sun World Fansipan Legend, Hiệp hội Du lịch tỉnh Lào Cai công bố chương trình kích cầu du lịch lớn nhất năm với chủ đề 'Chạm Sa Pa - Chạm những tầng mây', diễn ra từ 2/11 đến 30/12. Trong thời gian này, 130 doanh nghiệp tại Sa Pa sẽ cung cấp nhiều ưu đãi lên đến 50% và cam kết đảm bảo chất lượng dịch vụ. Theo đó, Công ty Cáp treo Fansipan Sa Pa (Khu du lịch Sun World Fansipan Legend) áp dụng đồng giá vé cáp treo hai chiều Fansipan chỉ còn 550.000 đồng cho du khách Việt Nam. Mức giá này giảm 30% so với giá gốc. Du khách có thể khám phá đỉnh Fansipan, chiêm ngưỡng kiến trúc tâm linh và tham gia các hoạt động văn hóa của 7 dân tộc thiểu số Tây Bắc tại Bản Mây. Nhiều điểm du lịch khác tại Sa Pa cũng miễn phí vé tham quan và cung cấp ưu đãi hấp dẫn. Trong đó, vườn đá Tả Phìn và vườn hồng Mộng Mơ miễn phí vé, Khu du lịch Cát Cát miễn phí trải nghiệm ẩm thực Tây Bắc cùng các hoạt động vẽ sáp ong, xe lanh, dệt vải... với bà con dân bản. Các khách sạn như Chaulong Sapa, Amazing Sapa, Vườn Sa Pa, Arista Sa Pa và Le Bordeaux Sapa áp dụng giảm giá phòng trực tiếp tới 50%. Hotel de la Coupole và Lady Hill Sapa Resort có nhiều ưu đãi về dịch vụ ăn uống, spa. Một số nhà xe như Inter Bus Lines và Eco Sa Pa cũng giảm giá vé xe khứ hồi đến 30%, cung cấp đa dạng hình thức di chuyển từ xe limousine đến xe lớn. Ông Phạm Cao Vỹ, đại diện Hiệp hội Du lịch tỉnh Lào Cai nhấn mạnh sự cần thiết của việc kích cầu du lịch để phục hồi ngành sau ảnh hưởng nặng nề của bão lũ. Ông kêu gọi tất cả doanh nghiệp du lịch trên địa bàn tham gia nhằm tạo sức bật cho du lịch Sa Pa phát triển mạnh mẽ vào giai đoạn cuối năm 2024. Ông Nguyễn Xuân Chiến, Phó chủ tịch Sun Group Vùng Miền Bắc, cho biết trước đây chương trình kích cầu 'Đến Sa Pa - Bay giữa mùa hoa' thành công ngoài mong đợi. 'Lần này, thông qua chính sách ưu đãi sâu, chúng tôi hy vọng thu hút đông đảo du khách đến Sa Pa để khám phá vẻ đẹp độc đáo của mùa mây', ông Chiến nói. Ngoài chính sách ưu đãi sâu, tỉnh Lào Cai và thị xã Sa Pa tổ chức nhiều sự kiện văn hóa đặc sắc nhằm mang đến trải nghiệm độc đáo cho du khách. Các hoạt động bao gồm lễ hội truyền thống, triển lãm nghệ thuật, thể thao và giải trí. Đặc biệt là sự kiện ánh sáng 3D Mapping và lễ hội hoa sen đá lần đầu tiên được tổ chức tại Sun World Fansipan Legend. Sa Pa đang trong mùa mây - thời điểm lý tưởng để vui chơi ngoài trời. Ban tổ chức kỳ vọng chương trình kích cầu sẽ tăng sức hút của Sa Pa và củng cố vị thế là điểm đến hàng đầu miền Bắc. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 1.0,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, không chứa số liệu không chính xác và giữ nguyên ý nghĩa của văn bản gốc",
+  "relevance_score": 1.0,
+  "relevance_reason": "Tóm tắt bao gồm tất cả các điểm chính quan trọng, không bỏ sót thông điệp cốt lõi nào của văn bản gốc",
+  "coherence_conciseness_score": 1.0,
+  "coherence_conciseness_reason": "Tóm tắt viết một cách trôi chảy, logic, dễ đọc và đã loại bỏ thành công các chi tiết thừa hoặc từ ngữ lặp đi lặp lại"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -553,8 +587,27 @@
           <t>Brisbane nằm phía đông nam bang Queensland, là thành phố lớn thứ ba tại Australia. Do gần đường xích đạo, khí hậu nơi đây ôn hòa, quanh năm nắng ấm. Trung tâm Brisbane không chỉ có những khối bê tông, khu mua sắm, mà còn bao phủ bởi mảng xanh, với 5 công viên và vườn thực vật nổi tiếng. Dưới đây là 5 điểm đến hút du khách ở Brisbane. South Bank Parklands Nằm bên bờ sông Brisbane, South Bank Parklands được ví như 'ốc đảo xanh' giữa lòng thành phố sôi động, nổi bật với rừng mưa nhiệt đới và loạt hoạt động giải trí cho mọi lứa tuổi. Ngay cửa ngõ công viên là thảm cỏ, hàng cây rợp bóng và vườn hoa. Nhiều người dân thường picnic, dã ngoại, vui chơi tại bãi biển nhân tạo Streets Beach, River Quay Green, Rainforest Green hay Liana Lounge. Ngoài ra, Wheel of Brisbane - vòng đu quay cao tới 60 m - là biểu tượng tại South Bank Parklands, dễ dàng ngắm toàn cảnh Brisbane từ trên cao. Roma Street Parkland Nằm cạnh ga xe lửa Roma Street, công viên cùng tên cũng được người dân lẫn du khách gọi là 'ốc đảo xanh mát' giữa Brisbane, ghi dấu với những khu vườn và bãi cỏ rộng lớn. Tại đây, du khách hòa mình vào khu vườn Spectacle - nơi trồng hàng nghìn gốc violets, cẩm chướng, delphiniums và foxgloves. Khí hậu ôn hòa thu hút chim kookaburras, gà lôi, vẹt. Bạn cũng có thể tổ chức tiệc BBQ ngoài trời, cho con khám phá công viên trẻ em. Brisbane City Botanic Gardens Nằm trên trục đường Alice, Brisbane City Botanic Gardens bảo tồn hàng nghìn loài thực vật quý hiếm, nổi bật với vẻ nguyên sơ. Khu vườn này là một trong những điểm đến lý tưởng cho người chuộng nét thanh bình giữa lòng đô thị. Tại đây, du khách có thể khám phá con đường dạo bộ ven sông, chiêm ngưỡng rặng thông Bunya được trồng từ năm 1858. Điểm đến tiếp theo là Bamboo Grove - con đường tre rợp mát, được ví như 'khu rừng xa xôi giữa thành phố hiện đại'. Vườn bách thảo tổ chức sự kiện quanh năm như biểu diễn Riverstage, lễ hội đa văn hóa, trưng bày nghệ thuật cùng hoạt động cộng đồng miễn phí. Trong đó, chợ Riverside Sunday Market hút hàng nghìn du khách nhờ gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden Tại Epicurious, du khách có thể khám phá ẩm thực bang Queensland đa dạng, nhất là rau, củ, quả, thảo mộc hữu cơ theo mùa. 14 chuyên viên tình nguyện chăm sóc khu vườn kỹ lưỡng, mong truyền cảm hứng cho người yêu nấu ăn và trồng trọt. 'Tới Epicurious, tôi và bạn bè được hướng dẫn cách chăm sóc rau củ, trái cây, thảo mộc và thưởng thức miễn phí', một du khách viết trên Facebook, nhận hàng trăm nghìn lượt thích. Mount Coot-tha Botanic Gardens Mở cửa đón khách từ năm 1976, Mount Coot-tha Botanic Gardens tọa lạc chân núi Coot-tha, là vườn thực vật nhiệt đới hàng đầu Brisbane, diện tích đến 56 ha. Dạo quanh khu vườn, du khách có thể chiêm ngưỡng hoa xuân, các loài cây nhiệt đới và khu thảo dược. Nơi đây là điểm đến quen thuộc của người yêu thiên nhiên, picnic, mê hoạt động thể chất, với đường chạy bộ thoáng đãng. Để khám phá thành thủ phủ bang Queensland, bạn có thể chọn đường bay thẳng từ TP HCM đến Brisbane của Vietjet, với 9 giờ trên máy bay thân rộng, thoải mái cùng loạt dịch vụ tiện ích, ưu đãi như: bảo hiểm Sky Care miễn phí, chương trình tích điểm SkyJoy, đổi quà từ hơn 250 thương hiệu lớn toàn cầu. Trước đó ngày14-15/9, Vietjet đồng hành lễ hội thả diều Vietjet Redcliffe KiteFest tại Redcliffe, Queensland. Hãng hàng không Việt còn áp dụng nhiều chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu. Đông Vệ</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brisbane, thành phố lớn thứ ba của Australia với khí hậu ôn hòa quanh năm. Nhiều công viên và vườn thực vật nổi tiếng như South Bank Parklands, Roma Street Parkland và Brisbane City Botanic Gardens bảo tồn hàng nghìn loài cây quý hiếm trên trục đường Alice. Hội chợ Riverside Sunday Market hút du khách với gian hàng thủ công, trái cây tươi và ẩm thực độc đáo từ Epicurious Garden đến Mount Coot-tha Botanic Gardens nổi tiếng thiên nhiên. Vietjet cung cấp đường bay thẳng TP HCM-Brisbane trong 9 giờ cùng loạt dịch vụ tiện ích và chương trình ưu đãi đặc biệt nhân dịp đón hành khách thứ 200 triệu.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{
+  "id": 6,
+  "style": "news_brief",
+  "article": "Brisbane nằm phía đông nam bang Queensland, là thành phố lớn thứ ba tại Australia. Do gần đường xích đạo, khí hậu nơi đây ôn hòa, quanh năm nắng ấm. Trung tâm Brisbane không chỉ có những khối bê tông, khu mua sắm, mà còn bao phủ bởi mảng xanh, với 5 công viên và vườn thực vật nổi tiếng. Dưới đây là 5 điểm đến hút du khách ở Brisbane. South Bank Parklands Nằm bên bờ sông Brisbane, South Bank Parklands được ví như 'ốc đảo xanh' giữa lòng thành phố sôi động, nổi bật với rừng mưa nhiệt đới và loạt hoạt động giải trí cho mọi lứa tuổi. Ngay cửa ngõ công viên là thảm cỏ, hàng cây rợp bóng và vườn hoa. Nhiều người dân thường picnic, dã ngoại, vui chơi tại bãi biển nhân tạo Streets Beach, River Quay Green, Rainforest Green hay Liana Lounge. Ngoài ra, Wheel of Brisbane - vòng đu quay cao tới 60 m - là biểu tượng tại South Bank Parklands, dễ dàng ngắm toàn cảnh Brisbane từ trên cao. Roma Street Parkland Nằm cạnh ga xe lửa Roma Street, công viên cùng tên cũng được người dân lẫn du khách gọi là 'ốc đảo xanh mát' giữa Brisbane, ghi dấu với những khu vườn và bãi cỏ rộng lớn. Tại đây, du khách hòa mình vào khu vườn Spectacle - nơi trồng hàng nghìn gốc violets, cẩm chướng, delphiniums và foxgloves. Khí hậu ôn hòa thu hút chim kookaburras, gà lôi, vẹt. Bạn cũng có thể tổ chức tiệc BBQ ngoài trời, cho con khám phá công viên trẻ em. Brisbane City Botanic Gardens Nằm trên trục đường Alice, Brisbane City Botanic Gardens bảo tồn hàng nghìn loài thực vật quý hiếm, nổi bật với vẻ nguyên sơ. Khu vườn này là một trong những điểm đến lý tưởng cho người chuộng nét thanh bình giữa lòng đô thị. Tại đây, du khách có thể khám phá con đường dạo bộ ven sông, chiêm ngưỡng rặng thông Bunya được trồng từ năm 1858. Điểm đến tiếp theo là Bamboo Grove - con đường tre rợp mát, được ví như 'khu rừng xa xôi giữa thành phố hiện đại'. Vườn bách thảo tổ chức sự kiện quanh năm như biểu diễn Riverstage, lễ hội đa văn hóa, trưng bày nghệ thuật cùng hoạt động cộng đồng miễn phí. Trong đó, chợ Riverside Sunday Market hút hàng nghìn du khách nhờ gian hàng thủ công, trái cây tươi và ẩm thực độc đáo. Epicurious Garden Tại Epicurious, du khách có thể khám phá ẩm thực bang Queensland đa dạng, nhất là rau, củ, quả, thảo mộc hữu cơ theo mùa. 14 chuyên viên tình nguyện chăm sóc khu vườn kỹ lưỡng, mong truyền cảm hứng cho người yêu nấu ăn và trồng trọt. 'Tới Epicurious, tôi và bạn bè được hướng dẫn cách chăm sóc rau củ, trái cây, thảo mộc và thưởng thức miễn phí', một du khách viết trên Facebook, nhận hàng trăm nghìn lượt thích. Mount Coot-tha Botanic Gardens Mở cửa đón khách từ năm 1976, Mount Coot-tha Botanic Gardens tọa lạc chân núi Coot-tha, là vườn thực vật nhiệt đới hàng đầu Brisbane, diện tích đến 56 ha. Dạo quanh khu vườn, du khách có thể chiêm ngưỡng hoa xuân, các loài cây nhiệt đới và khu thảo dược. Nơi đây là điểm đến quen thuộc của người yêu thiên nhiên, picnic, mê hoạt động thể chất, với đường chạy bộ thoáng đãng. Để khám phá thành thủ phủ bang Queensland, bạn có thể chọn đường bay thẳng từ TP HCM đến Brisbane của Vietjet, với 9 giờ trên máy bay thân rộng, thoải mái cùng loạt dịch vụ tiện ích, ưu đãi như: bảo hiểm Sky Care miễn phí, chương trình tích điểm SkyJoy, đổi quà từ hơn 250 thương hiệu lớn toàn cầu. Trước đó ngày14-15/9, Vietjet đồng hành lễ hội thả diều Vietjet Redcliffe KiteFest tại Redcliffe, Queensland. Hãng hàng không Việt còn áp dụng nhiều chương trình ưu đãi nhân dịp đón hành khách thứ 200 triệu. Đông Vệ",
+  "summary": "Brisbane, thành phố lớn thứ ba của Australia với khí hậu ôn hòa quanh năm. Nhiều công viên và vườn thực vật nổi tiếng như South Bank Parklands, Roma Street Parkland và Brisbane City Botanic Gardens bảo tồn hàng nghìn loài cây quý hiếm trên trục đường Alice. Hội chợ Riverside Sunday Market hút du khách với gian hàng thủ công, trái cây tươi và ẩm thực độc đáo từ Epicurious Garden đến Mount Coot-tha Botanic Gardens nổi tiếng thiên nhiên. Vietjet cung cấp đường bay thẳng TP HCM-Brisbane trong 9 giờ cùng loạt dịch vụ tiện ích và chương trình ưu đãi đặc biệt nhân dịp đón hành khách thứ 200 triệu.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể làm mất một số chi tiết quan trọng như mô tả cụ thể về các công viên và vườn thực vật, cũng như bỏ qua một số hoạt động và sự kiện tại các địa điểm này.",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt bao gồm một số điểm đến chính nhưng có thể bỏ qua một số thông tin quan trọng như vị trí và đặc điểm của từng công viên, cũng như không đề cập đến một số hoạt động giải trí và sự kiện tại Brisbane.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, dễ đọc và không có thông tin trùng lặp, tuy nhiên có thể cải thiện bằng cách thêm một số từ khóa hoặc cụm từ để tăng tính liên kết giữa các ý tưởng."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -562,8 +615,27 @@
           <t>Công ty du lịch NhatbanAZ mở bán chùm tour Nhật Bản khởi hành dịp Tết Dương lịch và Âm lịch từ đầu tháng 10. Trong đó, các tour truyền thống đến Osaka, Kyoto và Tokyo được làm mới bằng những hoạt động phù hợp với mùa đông xuân như trượt tuyết tại Fujiten Resort, ngắm tuyết làng cổ Oshino Hakkai và tham gia lễ hội ánh sáng Nabana no sato. NhatbanAZ cũng mở rộng các cung đường mới cho du khách trải nghiệm trong dịp Tết 2025. Cụ thể, tour Hokkaido gồm Asahikawa, Monbetsu và Sapporo với giá 55,9 triệu đồng mỗi khách. Du khách sẽ tham gia câu cá trên băng, đi tàu phá băng và thưởng thức bia hơi tại Sapporo, cùng dịch vụ hàng không 5 sao và lưu trú khách sạn 4 sao quốc tế. Tour thứ hai là chuyến thăm làng cổ Shirakawago, núi Phú Sĩ và Tokyo trong 6 ngày 5 đêm với giá 31,9 triệu đồng mỗi khách. Du khách sẽ được chiêm ngưỡng tuyết trắng tại Shirakawago, một Di sản Văn hóa Thế giới của UNESCO từ năm 1995. Tour cũng gồm tham quan lâu đài Matsumoto - di tích bảo vật quốc gia của Nhật Bản và trải nghiệm trượt tuyết tại Fujiten Snow Resort - top 3 khu trượt tuyết nổi tiếng. Bà Hồ Như Thảo, Giám đốc Điều hành NhatbanAZ Văn phòng TP HCM cho biết sản phẩm mới này nhận được sự quan tâm lớn từ du khách, đặc biệt là những người từng đi Nhật và muốn trở lại với hành trình mới. Khu vực Hokkaido được biết đến với tuyết rơi dày đặc hơn Tokyo hay Osaka, nên lịch khởi hành tour Hokkaido dịp Tết Âm lịch nhận được nhiều đăng ký giữ chỗ. Trong dịp Tết Nguyên đán 2025, NhatbanAZ cung cấp các hành trình từ 5 đến 6 ngày với mức giá cơ bản đến cao cấp, khoảng 31,9 - 55,9 triệu đồng mỗi khách để đáp ứng nhu cầu đa dạng. Giá tour Tết có phần chênh lệch so với ngày thường và tăng so với cùng kỳ năm trước. Do đó, NhatbanAZ chủ động gặp gỡ và làm việc với các đối tác cung cấp dịch vụ, từ đó xây dựng chương trình, đưa ra chính sách ưu đãi tốt nhất cho khách hàng. Với kinh nghiệm hơn 15 năm trong ngành du lịch chuyên thị trường Nhật Bản, NhatbanAZ thuộc danh sách công ty chỉ định nộp visa bởi Đại sứ quán Nhật Bản đề xuất. Đồng thời là đối tác chiến lược của các hãng hàng không, khách sạn và đối tác land tour uy tín tại Nhật Bản. Công ty cũng là nhà tư vấn và tổ chức những chuyến Famtrip kết nối các công ty du lịch Việt Nam tới tham quan xúc tiến đầu tư, hợp tác tại Nhật Bản. Thanh Thư</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Osaka, Kyoto và Tokyo được làm mới trong tour Nhật Bản dịp Tết Dương lịch của NhatbanAZ với giá 55,9 triệu đồng mỗi khách; Shirakawago, núi Phú Sĩ và Tokyo trong 6 ngày 5 đêm có giá 31,9 triệu đồng. Công ty đã nhận sự quan tâm từ du khách muốn trải nghiệm Hokkaido tuyết dày đặc; NhatbanAZ chủ động gặp đối tác để xây dựng chương trình và chính sách ưu đãi tốt nhất cho khách hàng; thuộc danh sách công ty chỉ định nộp visa bởi Đại sứ quán Nhật Bản, là đối tác chiến lược của hãng hàng không, khách sạn và land tour uy tín tại Nhật Bản cùng nhà tư vấn Famtrip.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{
+  "id": 7,
+  "style": "news_brief",
+  "article": "Công ty du lịch NhatbanAZ mở bán chùm tour Nhật Bản khởi hành dịp Tết Dương lịch và Âm lịch từ đầu tháng 10. Trong đó, các tour truyền thống đến Osaka, Kyoto và Tokyo được làm mới bằng những hoạt động phù hợp với mùa đông xuân như trượt tuyết tại Fujiten Resort, ngắm tuyết làng cổ Oshino Hakkai và tham gia lễ hội ánh sáng Nabana no sato. NhatbanAZ cũng mở rộng các cung đường mới cho du khách trải nghiệm trong dịp Tết 2025. Cụ thể, tour Hokkaido gồm Asahikawa, Monbetsu và Sapporo với giá 55,9 triệu đồng mỗi khách. Du khách sẽ tham gia câu cá trên băng, đi tàu phá băng và thưởng thức bia hơi tại Sapporo, cùng dịch vụ hàng không 5 sao và lưu trú khách sạn 4 sao quốc tế. Tour thứ hai là chuyến thăm làng cổ Shirakawago, núi Phú Sĩ và Tokyo trong 6 ngày 5 đêm với giá 31,9 triệu đồng mỗi khách. Du khách sẽ được chiêm ngưỡng tuyết trắng tại Shirakawago, một Di sản Văn hóa Thế giới của UNESCO từ năm 1995. Tour cũng gồm tham quan lâu đài Matsumoto - di tích bảo vật quốc gia của Nhật Bản và trải nghiệm trượt tuyết tại Fujiten Snow Resort - top 3 khu trượt tuyết nổi tiếng. Bà Hồ Như Thảo, Giám đốc Điều hành NhatbanAZ Văn phòng TP HCM cho biết sản phẩm mới này nhận được sự quan tâm lớn từ du khách, đặc biệt là những người từng đi Nhật và muốn trở lại với hành trình mới. Khu vực Hokkaido được biết đến với tuyết rơi dày đặc hơn Tokyo hay Osaka, nên lịch khởi hành tour Hokkaido dịp Tết Âm lịch nhận được nhiều đăng ký giữ chỗ. Trong dịp Tết Nguyên đán 2025, NhatbanAZ cung cấp các hành trình từ 5 đến 6 ngày với mức giá cơ bản đến cao cấp, khoảng 31,9 - 55,9 triệu đồng mỗi khách để đáp ứng nhu cầu đa dạng. Giá tour Tết có phần chênh lệch so với ngày thường và tăng so với cùng kỳ năm trước. Do đó, NhatbanAZ chủ động gặp gỡ và làm việc với các đối tác cung cấp dịch vụ, từ đó xây dựng chương trình, đưa ra chính sách ưu đãi tốt nhất cho khách hàng. Với kinh nghiệm hơn 15 năm trong ngành du lịch chuyên thị trường Nhật Bản, NhatbanAZ thuộc danh sách công ty chỉ định nộp visa bởi Đại sứ quán Nhật Bản đề xuất. Đồng thời là đối tác chiến lược của các hãng hàng không, khách sạn và đối tác land tour uy tín tại Nhật Bản. Công ty cũng là nhà tư vấn và tổ chức những chuyến Famtrip kết nối các công ty du lịch Việt Nam tới tham quan xúc tiến đầu tư, hợp tác tại Nhật Bản. Thanh Thư",
+  "summary": "Osaka, Kyoto và Tokyo được làm mới trong tour Nhật Bản dịp Tết Dương lịch của NhatbanAZ với giá 55,9 triệu đồng mỗi khách; Shirakawago, núi Phú Sĩ và Tokyo trong 6 ngày 5 đêm có giá 31,9 triệu đồng. Công ty đã nhận sự quan tâm từ du khách muốn trải nghiệm Hokkaido tuyết dày đặc; NhatbanAZ chủ động gặp đối tác để xây dựng chương trình và chính sách ưu đãi tốt nhất cho khách hàng; thuộc danh sách công ty chỉ định nộp visa bởi Đại sứ quán Nhật Bản, là đối tác chiến lược của hãng hàng không, khách sạn và land tour uy tín tại Nhật Bản cùng nhà tư vấn Famtrip.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể làm mất một số chi tiết quan trọng như các hoạt động cụ thể trong tour và dịch vụ 5 sao, tuy nhiên vẫn giữ được thông tin chính về giá và điểm đến.",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt đã bao gồm các điểm đến chính và giá cả, nhưng lại bỏ qua một số thông tin quan trọng như thời gian khởi hành và các dịch vụ đi kèm, điều này làm cho tóm tắt không đầy đủ.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, thông tin được trình bày một cách cô đọng và không lặp lại, giúp người đọc dễ dàng hiểu được nội dung chính."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -572,7 +644,22 @@
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{
+  "id": 8,
+  "style": "news_brief",
+  "article": "Theo bảng xếp hạng 20 quốc gia tốt nhất thế giới năm 2024 (The Best Countries in the World) do tạp chí du lịch Mỹ Condé Nast Traveler công bố vào tháng 10, Việt Nam ở vị trí 15 với 89 điểm. Một điểm đến khác thuộc Đông Nam Á có mặt trong danh sách này là Thái Lan, xếp thứ ba với 92,29 điểm. Đứng đầu top 20 là Nhật Bản với 95,32 điểm. Xếp hạng nằm trong giải thưởng thường niênReaders' Choice Awards của tạp chí Mỹ, dựa trên đánh giá của hơn 575.000 độc giả về các trải nghiệm du lịch ở mỗi quốc gia, xét theo các tiêu chí văn hóa, cảnh quan, dịch vụ du lịch và cơ sở hạ tầng. Độc giả của Condé Nast Traveler nhận xét Việt Nam thu hút du khách nhờ vẻ đẹp mộc mạc và quyến rũ. 'Với lượng khách nước ngoài đang trên đà tăng từ 2019 đến nay, Việt Nam không còn là điểm đến đáng chú ý mà thành điểm đến đáng ghé thăm', biên tập tờ Condé Nast Traveler viết. Theo số liệu từ Tổng cục Thống kê, trong 9 tháng đầu năm, Việt Nam đón hơn 12,7 triệu lượt khách quốc tế, vượt lượng khách cả năm 2023 là 12,6 triệu lượt. Lượng khách quốc tế đến Việt Nam tăng trưởng tích cực 9 tháng đầu năm 2024, với một số thị trường phục hồi hoàn toàn, tăng mạnh so với 2019, theo Cục Du lịch Quốc gia. Cục cũng dự đoán với đà tăng trường như hiện nay, Việt Nam sẽ hoàn thành mục tiêu đón 17-18 triệu lượt khách quốc tế năm 2024. Thái Lan được tạp chí Mỹ nhận xét là quốc gia đa dạng cảnh quan, giao thông thuận tiện với nhiều tàu thuyền, xe buýt đêm và chuyến bay nội địa giá rẻ. Ẩm thực cũng là điểm sáng của xứ chùa Vàng khi có nhiều khu chợ đêm nhộn nhịp, bày bán đặc sản địa phương. 8 tháng đầu năm 2024, Thái Lan đón hơn 20 triệu lượt khách quốc tế, tăng 34% so với cùng kỳ năm trước. Quốc gia này đặt mục tiêu đón ít nhất 36-37 triệu lượt khách nước ngoài trong cả năm nay, kỳ vọng thu về khoảng 3.500 tỷ baht (95,5 tỷ USD). Condé Nast Traveler là tạp chí du lịch nổi tiếng toàn cầu, ra mắt vào năm 1987. Các bảng xếp hạng của Condé Nast Traveler như Readers' Choice Awards được chuyên gia du lịch đánh giá là uy tín vì dựa trên ý kiến từ hàng triệu độc giả quốc tế. Bích Phương(TheoCNTraveller)",
+  "summary": "",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể bỏ qua một số chi tiết nhỏ như số lượng độc giả của tạp chí Condé Nast Traveler",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính như vị trí của Việt Nam và Thái Lan trong bảng xếp hạng, nhưng có thể bỏ qua một số thông tin quan trọng như mục tiêu đón khách quốc tế của hai quốc gia",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt còn một số từ ngữ lặp lại và có thể được viết một cách ngắn gọn hơn, nhưng vẫn dễ đọc và hiểu"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -580,8 +667,27 @@
           <t>Theo KTO Việt Nam, 8 tháng năm nay, Hàn Quốc đón 389.000 lượt khách Việt, tăng 27% so với cùng kỳ năm 2023. Số lượng khách Việt Nam đến Hàn Quốc dự kiến tăng mạnh hơn bởi đất nước này đang bước vào mùa lá vàng đẹp nhất năm. Đại diện KTO khẳng định, Việt Nam là thị trường quan trọng với ngành du lịch Hàn Quốc với nhiều sự kiện tổ chức thành công. Cụ thể, trong năm nay, KTO Việt Nam xúc tiến các chương trình quảng bá, phát triển sản phẩm du lịch Hàn Quốc phù hợp với nhu cầu du khách Việt. Kết quả, nhiều sản phẩm du lịch mới được ra mắt thị trường trong nước như: tour du lịch Hàn Quốc kết hợp giải chạy Marathon tại Gyeongju và Jeju, tour trải nghiệm Esports, tour lễ hội đèn lồng truyền thống Yeondeunghoe hay tour đạp xe đạp đường dài khám phá Hàn Quốc... Chương trình Năm du lịch Hàn Quốc 2023-2024 (Visit Korea Year 2023-2024) do Tổng cục du lịch Hàn Quốc (KTO) triển khai cũng mang đến những hoạt động mới mẻ, quảng bá du lịch Hàn Quốc đến cộng đồng quốc tế. Bên cạnh đó, nhằm mang đến những trải nghiệm chân thực và đậm chất bản địa, KTO tổ chức nhiều famtour. Nổi bật là famtour trải nghiệm Esports cùng các KOL hàng đầu làng thể thao điện tử như: SofM, reviewer Duy Thẩm, Hải Triều, streamer Hà Tiều Phu, BLV Esports nổi tiếng Văn Tùng, Hoàng Luân, kết hợp Box Esports. Làn sóng văn hóa Hallyu cũng được lồng ghép vào sản phẩm du lịch, khi hàng loạt tên tuổi lớn đến Việt Nam trong khuôn khổ sự kiện Korea Travel Festa, tổ chức tháng 5 vừa qua. Mới nhất, KTO Việt Nam có mặt tại Hội chợ Du lịch Quốc tế (ITE) TP HCM, mang theo không gian đặc trưng Hàn Quốc cùng nhiều trải nghiệm mới mẻ, độc đáo. Nắm bắt nhu cầu du lịch Hàn Quốc tăng cao trong mùa cuối năm của du khách Việt, KTO Việt Nam tiếp tục đẩy mạnh các chương trình ưu đãi đặc biệt. Cùng các đối tác, công ty du lịch hàng đầu Việt Nam, KTO góp phần phát triển nhiều tuyến điểm mới trong hành trình du lịch Hàn Quốc, mang đến đa dạng lựa chọn và nhiều trải nghiệm cho khách hàng. Hồi tháng 5, KTO Việt Nam ký kết thỏa thuận hợp tác cùng Tập đoàn Vingroup, nhằm thúc đẩy hơn nữa sự giao lưu, trao đổi du lịch giữa hai nước. Theo đó, KTO triển khai chiến dịch hỗ trợ dành riêng cho khách hàng thuộc hệ sinh thái Vingroup khi mua tour du lịch Hàn Quốc từ tháng 10 đến tháng 12 Cụ thể, chủ sở hữu xe Vinfast, cư dân Vinhomes, nhân viên Vingroup) và hội viên Vinclub (gọi chung là Vintizen) sẽ nhận được mức giá ưu đãi đặc biệt từ các công ty du lịch và KTO Việt Nam. Bên cạnh mức giá ưu đãi từ các công ty du lịch, Vintizen có cơ hội áp dụng đồng thời voucher trị giá một triệu đồng mỗi khách hàng, mua tối đa 5 tour du lịch Hàn Quốc để nhận voucher lên đến 5 triệu đồng từ KTO Việt Nam, trong thời gian 1-10/10. Ngoài thời gian trên, du khách mua tour tại các đối tác du lịch sẽ nhận được nhiều phần quà Hàn Quốc từ KTO Việt Nam. Thanh Thư</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hàn Quốc đón 389.000 lượt khách Việt Nam tăng 27% do mùa lá vàng đẹp và chương trình ưu đãi từ KTO Việt Nam, giảm giá tour tháng 10-12, voucher một triệu đồng mỗi khách hàng.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{
+  "id": 9,
+  "style": "news_brief",
+  "article": "Theo KTO Việt Nam, 8 tháng năm nay, Hàn Quốc đón 389.000 lượt khách Việt, tăng 27% so với cùng kỳ năm 2023. Số lượng khách Việt Nam đến Hàn Quốc dự kiến tăng mạnh hơn bởi đất nước này đang bước vào mùa lá vàng đẹp nhất năm. Đại diện KTO khẳng định, Việt Nam là thị trường quan trọng với ngành du lịch Hàn Quốc với nhiều sự kiện tổ chức thành công. Cụ thể, trong năm nay, KTO Việt Nam xúc tiến các chương trình quảng bá, phát triển sản phẩm du lịch Hàn Quốc phù hợp với nhu cầu du khách Việt. Kết quả, nhiều sản phẩm du lịch mới được ra mắt thị trường trong nước như: tour du lịch Hàn Quốc kết hợp giải chạy Marathon tại Gyeongju và Jeju, tour trải nghiệm Esports, tour lễ hội đèn lồng truyền thống Yeondeunghoe hay tour đạp xe đạp đường dài khám phá Hàn Quốc... Chương trình Năm du lịch Hàn Quốc 2023-2024 (Visit Korea Year 2023-2024) do Tổng cục du lịch Hàn Quốc (KTO) triển khai cũng mang đến những hoạt động mới mẻ, quảng bá du lịch Hàn Quốc đến cộng đồng quốc tế. Bên cạnh đó, nhằm mang đến những trải nghiệm chân thực và đậm chất bản địa, KTO tổ chức nhiều famtour. Nổi bật là famtour trải nghiệm Esports cùng các KOL hàng đầu làng thể thao điện tử như: SofM, reviewer Duy Thẩm, Hải Triều, streamer Hà Tiều Phu, BLV Esports nổi tiếng Văn Tùng, Hoàng Luân, kết hợp Box Esports. Làn sóng văn hóa Hallyu cũng được lồng ghép vào sản phẩm du lịch, khi hàng loạt tên tuổi lớn đến Việt Nam trong khuôn khổ sự kiện Korea Travel Festa, tổ chức tháng 5 vừa qua. Mới nhất, KTO Việt Nam có mặt tại Hội chợ Du lịch Quốc tế (ITE) TP HCM, mang theo không gian đặc trưng Hàn Quốc cùng nhiều trải nghiệm mới mẻ, độc đáo. Nắm bắt nhu cầu du lịch Hàn Quốc tăng cao trong mùa cuối năm của du khách Việt, KTO Việt Nam tiếp tục đẩy mạnh các chương trình ưu đãi đặc biệt. Cùng các đối tác, công ty du lịch hàng đầu Việt Nam, KTO góp phần phát triển nhiều tuyến điểm mới trong hành trình du lịch Hàn Quốc, mang đến đa dạng lựa chọn và nhiều trải nghiệm cho khách hàng. Hồi tháng 5, KTO Việt Nam ký kết thỏa thuận hợp tác cùng Tập đoàn Vingroup, nhằm thúc đẩy hơn nữa sự giao lưu, trao đổi du lịch giữa hai nước. Theo đó, KTO triển khai chiến dịch hỗ trợ dành riêng cho khách hàng thuộc hệ sinh thái Vingroup khi mua tour du lịch Hàn Quốc từ tháng 10 đến tháng 12 Cụ thể, chủ sở hữu xe Vinfast, cư dân Vinhomes, nhân viên Vingroup) và hội viên Vinclub (gọi chung là Vintizen) sẽ nhận được mức giá ưu đãi đặc biệt từ các công ty du lịch và KTO Việt Nam. Bên cạnh mức giá ưu đãi từ các công ty du lịch, Vintizen có cơ hội áp dụng đồng thời voucher trị giá một triệu đồng mỗi khách hàng, mua tối đa 5 tour du lịch Hàn Quốc để nhận voucher lên đến 5 triệu đồng từ KTO Việt Nam, trong thời gian 1-10/10. Ngoài thời gian trên, du khách mua tour tại các đối tác du lịch sẽ nhận được nhiều phần quà Hàn Quốc từ KTO Việt Nam. Thanh Thư",
+  "summary": "Hàn Quốc đón 389.000 lượt khách Việt Nam tăng 27% do mùa lá vàng đẹp và chương trình ưu đãi từ KTO Việt Nam, giảm giá tour tháng 10-12, voucher một triệu đồng mỗi khách hàng.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như các sự kiện và chương trình quảng bá du lịch Hàn Quốc",
+  "relevance_score": 0.6,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số điểm chính như số lượng khách du lịch và chương trình ưu đãi, nhưng bỏ qua các thông tin quan trọng khác như các sản phẩm du lịch mới và làn sóng văn hóa Hallyu",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt dễ đọc và logic, nhưng có thể được cải thiện bằng cách thêm một số chi tiết quan trọng và tránh sự trùng lặp thông tin"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -590,7 +696,22 @@
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{
+  "id": 10,
+  "style": "news_brief",
+  "article": "Diễn đàn năm nay là sự kiện trọng điểm do UBND tỉnh Kiên Giang phối hợp Bộ Nông nghiệp và Phát triển nông thôn tổ chức. Công ty Cổ phần Truyền Thông Vương Hậu (TP HCM) là đơn vị phụ trách tổ chức. Với chủ đề 'Liên kết cùng phát triển - Kiên Giang 2024', diễn đàn hướng đến tăng cường hợp tác, liên kết giữa các tỉnh, thành phố trong vùng Đồng bằng sông Cửu Long với các Bộ, ngành Trung ương, các địa phương khác trên cả nước. Từ đó, các bên có thêm cơ sở đẩy mạnh, phát huy tiềm năng về sản phẩm OCOP của vùng. Đến nay, đã có trên 35 tỉnh, thành phố đăng ký tham gia diễn đàn cùng hơn 300 nhà đầu tư đến tìm hiểu cơ hội, xúc tiến hợp tác kinh doanh. Diễn đàn dự kiến thu hút khoảng 50.000-100.000 khách tham quan suốt thời gian diễn ra. Hơn 320 gian hàng từ các tỉnh ĐBSCL và cả nước sẽ cùng trưng bày, giới thiệu các sản phẩm OCOP tiêu biểu, công nghiệp nông thôn, đặc sản địa phương. Ngoài chương trình chính, sự kiện còn bao gồm chuỗi hoạt động khác như: triển lãm sản phẩm OCOP; hội thi 'Sản phẩm OCOP tiêu biểu ĐBSCL 2024'; các hội nghị, hội thảo, ký kết biên bản hợp tác... Đặc biệt, khách tham dự còn được tìm hiểu quy trình sản xuất nước mắm truyền thống Phú Quốc, một trong những đặc sản nổi tiếng của Kiên Giang. Buổi tối, diễn dàn có các chương trình ca nhạc với sự góp mặt của các ca sĩ, nghệ sĩ nổi tiếng. Diễn đàn kết nối sản phẩm OCOP là sự kiện thường niên do Bộ Nông nghiệp và Phát triển nông thôn phối hợp UBND các tỉnh, thành phố vùng Đồng bằng sông Cửu Long tổ chức quy mô cấp vùng. Đây vừa là nơi giao lưu, kết nối kinh doanh, vừa là cơ hội để các sản phẩm này vươn ra thế giới, góp phần phát triển kinh tế nông nghiệp, xây dựng nông thôn mới bền vững. Á Hiên",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết quan trọng như số lượng gian hàng và khách tham quan dự kiến",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính như chủ đề diễn đàn, mục đích và các hoạt động chính, tuy nhiên có thể cần thêm thông tin về ý nghĩa của sự kiện",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt còn dài và có thể bị lặp lại một số thông tin, cần tinh gọn và sắp xếp lại để dễ đọc hơn"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -598,8 +719,27 @@
           <t>Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Hoàng Giang</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Các mặt hàng gốm Chiêm Mai vẫn còn bùn đất, người dân phơi nắng. Bảo tàng Bát Tràng mở cửa sau 2018 với kinh phí 150 tỷ đồng và thiết kế độc đáo nhiều tầng chuyên về lịch sử làng nghề Việt. Đình Bát Tràng 300 tuổi lưu giữ đạo sắc phong hơn 50 đạo, được cấp bằng Di tích năm 2005 sau lụt.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{
+  "id": 11,
+  "style": "news_brief",
+  "article": "Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Bên lề đường khu vực Chiêm Mai, nơi có nhiều xưởng làm gốm, các mặt hàng bị ngâm nước vẫn còn bùn đất bám lại. Những sản phẩm còn sử dụng được người dân mang ra phơi nắng. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Trong chợ gốm, nhiều cửa hàng quây bạt, chưa mở cửa lại. 'Nhiều chủ hàng chưa mở lại do phải dọn dẹp nhà cửa bị ngập trước đó, chưa có thời gian dọn cửa hàng', chị Tuyết, chủ một cửa hàng, nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Chị Lan, chủ một cửa hàng trong chợ, cho biết nhà chị không bị thiệt hại nặng nên dọn hàng ra sớm để đón khách. 'Ngày thường ít khách lui tới nhưng đông vào dịp cuối tuần', chị Lan nói. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Cửa hàng nặn gốm của chị Lan đã sẵn sàng đón khách hàng đến trải nghiệm. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Các gian hàng mở lại với lác đác du khách tới tham quan, mua sắm - trái với khung cảnh tấp nập mỗi dịp lễ, Tết khi mặt hàng gốm sứ được nhiều người tìm mua. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bảo tàng gốm Bát Tràng nằm gần ngoài đê, trước khi vào làng gốm, cũng đã mở cửa sẵn sàng đón khách. Bảo tàng được xây dựng từ năm 2018 với kinh phí 150 tỷ đồng, là 'trung tâm tinh hoa làng nghề Việt'. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Bên trong bảo tàng có thiết kế độc đáo, nhiều tầng với các chuyên đề khác nhau về lịch sử hình thành, phát triển cũng như các loại hình gốm tại Bát Tràng. 'Đến làng gốm để có trải nghiệm thú vị, thay đổi không khí và tìm hiểu về gốm truyền thống', Phạm Hoàng Hiệu, Thanh Xuân, Hà Nội, cho biết khi đến đây sau những ngày phải ở nhà vì mưa lụt. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Đình làng Bát Tràng hơn 300 tuổi không bị ảnh hưởng sau trận lụt. Đình được coi là 'báu vật đi cùng năm tháng' ở làng, hiện lưu giữ hơn 50 đạo sắc phong. Đình Bát Tràng được Bộ Văn hóa Thể thao và Du lịch cấp bằng Di tích văn hóa kiến trúc nghệ thuật năm 2005. Hoàng Giang",
+  "summary": "Các mặt hàng gốm Chiêm Mai vẫn còn bùn đất, người dân phơi nắng. Bảo tàng Bát Tràng mở cửa sau 2018 với kinh phí 150 tỷ đồng và thiết kế độc đáo nhiều tầng chuyên về lịch sử làng nghề Việt. Đình Bát Tràng 300 tuổi lưu giữ đạo sắc phong hơn 50 đạo, được cấp bằng Di tích năm 2005 sau lụt.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như tình trạng của các cửa hàng và phản ứng của người dân sau lụt",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số điểm chính như tình trạng gốm và bảo tàng nhưng bỏ qua thông tin về cuộc sống của người dân và hoạt động của các cửa hàng sau lụt",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và không có thông tin trùng lặp, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -607,8 +747,27 @@
           <t>Bếp trưởng Christian Le Squer nổi tiếng với 22 năm liên tiếp đạt 3 sao Michelin, hiện đảm nhiệm vai trò bếp trưởng tại La Maison 1888. Nhà hàng là điểm đến ẩm thực Pháp cao cấp, nằm ngay trong khuôn viên resort InterContinental Danang Sun Peninsula Resort. Tháng 7 vừa qua đánh dấu cột mốc quan trọng khi La Maison 1888 gia nhập 'bản đồ' Michelin Guide với ngôi sao đầu tiên. Với sự điều hành của bếp trưởng Christian Le Squer, thực khách sẽ được trải nghiệm ẩm thực Pháp cao cấp giao hòa giữa nghệ thuật và thẩm mỹ cao cấp, mang đậm dấu ấn cá nhân của ông. Ông Seif Hamdy, Tổng giám đốc khu nghỉ dưỡng cho biết sự góp mặt của bếp trưởng Christian tại InterContinental Danang là bước tiến quan trọng. Sự sáng tạo trong ẩm thực cùng khả năng của ông là điều đã được chứng minh bằng 22 năm liên tục được trao tặng ba sao Michelin. Christian Le Squer còn từng đạt danh hiệu 'Bếp trưởng của năm' do Gault &amp; Millau trao tặng năm 2023. 'Christian Le Squer sẽ mang đến làn gió mới cùng tầm nhìn sáng tạo, góp phần nâng tầm trải nghiệm ẩm thực cho thực khách tại La Maison 1888 với phong cách 'haute couture' đặc trưng do chính ông tạo ra', ông Seif Hamdy nói. Sinh ra và lớn lên bên bờ biển Brittany (Pháp), bếp trưởng Christian có nhiều trải nghiệm tuổi thơ gắn liền với ẩm thực. Những ký ức thuở nhỏ gieo cho ông đam mê ẩm thực sâu sắc và dẫn lối ông đến kinh đô ánh sáng và thời trang Paris. Đến năm 34 tuổi, ông được trao sao Michelin đầu tiên tại nhà hàng Café de la Paix. Thành công này đã thôi thúc ông tiếp tục hành trình chinh phục những đỉnh cao ẩm thực kế tiếp. Sau đó, ông gia nhập nhà hàng Pavillon Ledoyen năm 1999, giúp nơi này giành được ba sao Michelin không lâu sau đó. Thành tích này được ông Christian lặp lại tại Le Cinq, nhà hàng Pháp biểu tượng tại khách sạn Four Seasons Hotel George V ở Paris. Bếp trưởng Christian ví von phong cách ẩm thực độc đáo của mình như những tác phẩm thời trang nghệ thuật cao cấp 'haute couture' trên bàn ăn. Ông cho biết mỗi món đều mang dấu ấn riêng biệt, sở hữu hương vị và diện mạo thanh lịch như một bộ trang phục sang trọng hay một chai nước hoa độc bản được giới thiệu tại Tuần lễ Thời trang Paris. Sau nhiều chuyến ghé thăm Việt Nam, đặc biệt là Đà Nẵng, ông hiểu hơn về nhu cầu của thực khách nơi đây. Nhiều người ông gặp cho biết họ tìm kiếm sự kết hợp hài hòa giữa truyền thống và hiện đại trong ẩm thực Pháp. Việc khám phá các hương vị, nguyên liệu, văn hóa ẩm thực đặc sắc của Việt Nam đã trở thành nguồn cảm hứng để ông phác họa nên bức tranh ẩm thực riêng cho La Maison 1888. 'Tôi rất mong chờ được cùng làm việc với đội ngũ tài năng tại La Maison 1888, đặc biệt là Bếp trưởng Florian Stein', Christian nói. Nằm trong một dinh thự theo phong cách Đông Dương thanh lịch do Bill Bensley thiết kế, La Maison 1888 là một trong những điểm đến ẩm thực quốc tế đáng cân nhắc tại Đông Nam Á. Nhà hàng sở hữu hầm rượu vang với bộ sưu tập phong phú cùng tầm nhìn đẹp hướng biển. Nơi đây chinh phục thực khách bằng ẩm thực cao cấp với chất lượng được Michelin công nhận cùng không gian sang trọng đậm chất Pháp. Sắp tới, bếp trưởng Christian hứa hẹn mang đến nhiều bất ngờ thú vị, góp phần nâng tầm trải nghiệm ẩm thực của thực khách tại đây. Á Hiên</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Christian Le Squer, bếp trưởng Michelin 3 sao và 'Bếp trưởng của năm' trong 22 năm liên tiếp đạt danh hiệu này, hiện là quản lý nhà hàng La Maison 1888 tại InterContinental Danang Sun Peninsula Resort. Ông nổi tiếng với nghệ thuật nấu ăn sáng tạo mang đến trải nghiệm haute couture độc đáo cho thực khách. Trước đó, ông đã chinh phục Michelin đầu tiên khi còn trẻ ở Pavillon Ledoyen và Le Cinq trước khi gia nhập La Maison 1888 với tầm nhìn mới. Nhà hàng nằm trong dinh thự Đông Dương do Bill Bensley thiết kế, sở hữu hầm rượu vang phong phú hướng biển, phục vụ ẩm thực cao cấp Michelin-certified. Christian Stein cam kết mang đến nhiều trải nghiệm thú vị sắp tới tại đây.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{
+  "id": 12,
+  "style": "news_brief",
+  "article": "Bếp trưởng Christian Le Squer nổi tiếng với 22 năm liên tiếp đạt 3 sao Michelin, hiện đảm nhiệm vai trò bếp trưởng tại La Maison 1888. Nhà hàng là điểm đến ẩm thực Pháp cao cấp, nằm ngay trong khuôn viên resort InterContinental Danang Sun Peninsula Resort. Tháng 7 vừa qua đánh dấu cột mốc quan trọng khi La Maison 1888 gia nhập 'bản đồ' Michelin Guide với ngôi sao đầu tiên. Với sự điều hành của bếp trưởng Christian Le Squer, thực khách sẽ được trải nghiệm ẩm thực Pháp cao cấp giao hòa giữa nghệ thuật và thẩm mỹ cao cấp, mang đậm dấu ấn cá nhân của ông. Ông Seif Hamdy, Tổng giám đốc khu nghỉ dưỡng cho biết sự góp mặt của bếp trưởng Christian tại InterContinental Danang là bước tiến quan trọng. Sự sáng tạo trong ẩm thực cùng khả năng của ông là điều đã được chứng minh bằng 22 năm liên tục được trao tặng ba sao Michelin. Christian Le Squer còn từng đạt danh hiệu 'Bếp trưởng của năm' do Gault &amp; Millau trao tặng năm 2023. 'Christian Le Squer sẽ mang đến làn gió mới cùng tầm nhìn sáng tạo, góp phần nâng tầm trải nghiệm ẩm thực cho thực khách tại La Maison 1888 với phong cách 'haute couture' đặc trưng do chính ông tạo ra', ông Seif Hamdy nói. Sinh ra và lớn lên bên bờ biển Brittany (Pháp), bếp trưởng Christian có nhiều trải nghiệm tuổi thơ gắn liền với ẩm thực. Những ký ức thuở nhỏ gieo cho ông đam mê ẩm thực sâu sắc và dẫn lối ông đến kinh đô ánh sáng và thời trang Paris. Đến năm 34 tuổi, ông được trao sao Michelin đầu tiên tại nhà hàng Café de la Paix. Thành công này đã thôi thúc ông tiếp tục hành trình chinh phục những đỉnh cao ẩm thực kế tiếp. Sau đó, ông gia nhập nhà hàng Pavillon Ledoyen năm 1999, giúp nơi này giành được ba sao Michelin không lâu sau đó. Thành tích này được ông Christian lặp lại tại Le Cinq, nhà hàng Pháp biểu tượng tại khách sạn Four Seasons Hotel George V ở Paris. Bếp trưởng Christian ví von phong cách ẩm thực độc đáo của mình như những tác phẩm thời trang nghệ thuật cao cấp 'haute couture' trên bàn ăn. Ông cho biết mỗi món đều mang dấu ấn riêng biệt, sở hữu hương vị và diện mạo thanh lịch như một bộ trang phục sang trọng hay một chai nước hoa độc bản được giới thiệu tại Tuần lễ Thời trang Paris. Sau nhiều chuyến ghé thăm Việt Nam, đặc biệt là Đà Nẵng, ông hiểu hơn về nhu cầu của thực khách nơi đây. Nhiều người ông gặp cho biết họ tìm kiếm sự kết hợp hài hòa giữa truyền thống và hiện đại trong ẩm thực Pháp. Việc khám phá các hương vị, nguyên liệu, văn hóa ẩm thực đặc sắc của Việt Nam đã trở thành nguồn cảm hứng để ông phác họa nên bức tranh ẩm thực riêng cho La Maison 1888. 'Tôi rất mong chờ được cùng làm việc với đội ngũ tài năng tại La Maison 1888, đặc biệt là Bếp trưởng Florian Stein', Christian nói. Nằm trong một dinh thự theo phong cách Đông Dương thanh lịch do Bill Bensley thiết kế, La Maison 1888 là một trong những điểm đến ẩm thực quốc tế đáng cân nhắc tại Đông Nam Á. Nhà hàng sở hữu hầm rượu vang với bộ sưu tập phong phú cùng tầm nhìn đẹp hướng biển. Nơi đây chinh phục thực khách bằng ẩm thực cao cấp với chất lượng được Michelin công nhận cùng không gian sang trọng đậm chất Pháp. Sắp tới, bếp trưởng Christian hứa hẹn mang đến nhiều bất ngờ thú vị, góp phần nâng tầm trải nghiệm ẩm thực của thực khách tại đây. Á Hiên",
+  "summary": "Christian Le Squer, bếp trưởng Michelin 3 sao và 'Bếp trưởng của năm' trong 22 năm liên tiếp đạt danh hiệu này, hiện là quản lý nhà hàng La Maison 1888 tại InterContinental Danang Sun Peninsula Resort. Ông nổi tiếng với nghệ thuật nấu ăn sáng tạo mang đến trải nghiệm haute couture độc đáo cho thực khách. Trước đó, ông đã chinh phục Michelin đầu tiên khi còn trẻ ở Pavillon Ledoyen và Le Cinq trước khi gia nhập La Maison 1888 với tầm nhìn mới. Nhà hàng nằm trong dinh thự Đông Dương do Bill Bensley thiết kế, sở hữu hầm rượu vang phong phú hướng biển, phục vụ ẩm thực cao cấp Michelin-certified. Christian Stein cam kết mang đến nhiều trải nghiệm thú vị sắp tới tại đây.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có một số điểm không chính xác như việc gọi Christian Le Squer là 'Bếp trưởng của năm' trong 22 năm liên tiếp, trong khi văn bản gốc chỉ đề cập đến việc ông đạt danh hiệu 'Bếp trưởng của năm' do Gault &amp; Millau trao tặng năm 2023. Ngoài ra, tóm tắt cũng không đề cập rõ ràng đến việc Christian Le Squer đã trải qua nhiều năm kinh nghiệm và đạt được nhiều thành tựu trước khi gia nhập La Maison 1888.",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt đã đề cập đến một số điểm quan trọng như việc Christian Le Squer là bếp trưởng Michelin 3 sao, nhà hàng La Maison 1888 và phong cách ẩm thực haute couture của ông. Tuy nhiên, tóm tắt lại bỏ qua một số chi tiết quan trọng như việc Christian Le Squer đã có nhiều năm kinh nghiệm, đạt được nhiều thành tựu và hiểu biết về nhu cầu của thực khách tại Việt Nam.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc. Các ý tưởng được trình bày một cách mạch lạc và không có thông tin trùng lặp. Tuy nhiên, có một số điểm như việc sử dụng từ 'trước đó' có thể được thay thế bằng từ khác để tăng tính mạch lạc cho tóm tắt."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -617,7 +776,22 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{
+  "id": 13,
+  "style": "news_brief",
+  "article": "Đại diện Sun World Sầm Sơn cho biết chương trình ưu đãi nhằm tri ân khách hàng đã ủng hộ suốt thời gian công viên nước ra mắt. Từ ngày 3/9, giá 100.000 đồng áp dụng chung cho mọi lứa tuổi. Trước đó, giá gốc 200.000 đồng (khách ngoại tỉnh) và 150.000 đồng (người Thanh Hóa). Riêng bé dưới 1 m được miễn phí vé. Khai trương đúng dịp cao điểm hè 30/6, Sun World Sầm Sơn - công viên nước quy mô nhất miền Bắc cùng tổ hợp trò chơi đạt kỷ lục châu Á - Thái Bình Dương - là 'cú hích' cho du lịch Sầm Sơn năm nay, hút hàng nghìn lượt khách mỗi ngày. Công viên nước thuộc phường Quảng Châu, Quảng Tiến, ngay đại lộ Nam sông Mã - cửa ngõ Sầm Sơn, cách trung tâm TP Thanh Hóa13 km và bãi biển Sầm Sơn 1,5 km. Thiết kế không gian lấy cảm hứng từ truyện dân gian Việt Nam, kết hợp hài hòa kiến trúc truyền thống và hiện đại. Các trò chơi cùng cảnh quan vừa gần gũi, vừa mới mẻ. Công viên nước chia ba phân khu riêng biệt dành cho mọi lứa tuổi: gia đình, trẻ em và khu cảm giác mạnh. Trong đó, trò 'Vịnh sóng thần' có diện tích 6.100 m2, chiều dài bờ biển nhân tạo đến 179 m. Cụ thể, phân khu cảm giác mạnh tập hợp những trò tốc độ, kích thích, góp phần giúp du khách giải tỏa áp lực công việc, cuộc sống. Điển hình là tổ hợp hàm cá mập, với các đường trượt uốn lượn, độ dốc cao chủ đề 'cá mập hung tàn' hay 'cá mập siêu bạo chúa'. Nhằm đáp ứng nhu cầu vui chơi của gia đình lẫn nhóm bạn trẻ, ban tổ chức kiến tạo mê cung quy mô lớn, nhấn vào các đường trượt đan chéo và vực lốc xoáy (tổ hợp ống trượt uốn lượn, xoắn ốc như các xoáy nước dành cho phao đôi đầu tiên tại châu Á - Thái Bình Dương). Du khách có thể khám phá đa dạng đường trượt gồm: 'cá đuối vượt sóng', 'cá trê vượt thác' hay 8 làn trượt thảm bạch tuộc. Chủ dự án cũng bố trí phân khu bến tuổi thơ cho trẻ, với 3 tổ hợp nhỏ mô hình sinh vật dưới nước quen thuộc. Bao quanh khu trò chơi là sông lười, gợi nhớ dòng Đơ tại Sầm Sơn. Tại đây, du khách có thể lênh đênh theo dòng nước, thư giãn và tận hưởng cảm giác sảng khoái như trẻ thơ. Nếu muốn khám phá trọn vẹn công viên nước, du khách nên đến từ 10h hoặc 15h bởi nắng không quá gắt, thích hợp với cả người già lẫn trẻ nhỏ. Vạn Phát",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết nhỏ như diện tích của 'Vịnh sóng thần' và chiều dài bờ biển nhân tạo",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính như chương trình ưu đãi, giá vé, thiết kế công viên nước và các trò chơi, tuy nhiên có thể chưa đề cập đủ đến tầm quan trọng của công viên nước đối với du lịch Sầm Sơn",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt còn dài và có thể bị lặp lại một số thông tin, cần tinh gọn và sắp xếp lại để dễ đọc hơn"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -625,8 +799,27 @@
           <t>Chiều 28/8, khách sạn Grand Mercure Hanoi đón hơn 200 vị khách thuộc đoàn 4.500 du khách từ Ấn Độ sang Việt Nam. Theo ông Remi Faubel, tổng quản lý khách sạn, đây là cơ hội lớn để quảng bá nét đẹp văn hóa, truyền thống tới khách quốc tế. 'Chúng tôi tự tin các yếu tố như lối kiến trúc Đông Dương, hệ thống cửa Bức Bàn, các chi tiết nội thất lấy cảm hứng từ hoa sen, trống đồng, hạt gạo, ruộng bậc thang,... sẽ góp phần để lại ấn tượng tốt đẹp trong lòng du khách', ông Faubel nói. Do nhu cầu của khách, Grand Mercure Hanoi vẫn phục vụ chủ yếu các món Ấn. Bếp trưởng - Nguyễn Minh Nguyện lý giải, du khách Ấn Độ luôn có nhu cầu thưởng thức ẩm thực đất nước họ để có cảm giác gần gũi và thoải mái khi đi du lịch. Đó cũng là cách họ gìn giữ văn hóa và chế độ ăn truyền thống. 'Khi lên kế hoạch, chúng tôi phải trao đổi với phía đại diện đoàn để nắm thông tin về chế độ ăn, suất ăn tôn giáo, yêu cầu đặc biệt, từ đó lựa chọn các loại gia vị đặc trưng của Ấn Độ để các món ăn giữ được hương vị', vị bếp trưởng nói. Tuy nhiên, khách sạn cũng chuẩn bị thêm một số món ăn đặc trưng của Việt Nam như gà, bánh cuốn, xôi, hoa quả nhiệt đới... để giới thiệu đến đoàn khách. Từ ngày 27/8 đến 3/9, Việt Nam đón 4.500 du khách thuộc tập đoàn dược phẩm lớn đến từ Ấn Độ. Dự kiến, họ sẽ chia thành các nhóm nhỏ tới Hà Nội - Ninh Bình - Hạ Long và sử dụng các dịch vụ lưu trú, ăn uống tại các khách sạn 5 sao trên địa bàn thủ đô. Ấn Độ là một trong 10 thị trường khách du lịch quốc tế lớn nhất Việt Nam. Theo số liệu từ Cục Du lịch Quốc gia, trong 6 tháng đầu năm, nước ta đã đón 231.000 lượt khách Ấn Độ, tăng 164% so với cùng kỳ năm 2023. Việt Nam có nhiều thế mạnh để thu hút và phát triển thị trường này. Các đường bay thẳng giữa hai nước được khai thác trong thời gian gần đây khiến thời gian di chuyển rút ngắn chỉ còn khoảng 4 - 5 tiếng. Theo Outlook Traveller, Việt Nam sở hữu những cảnh quan đẹp, nền văn hóa đa dạng và chiều sâu lịch sử. Giá thành dịch vụ cạnh tranh khiến nước ta trở thành điểm đến lý tưởng cho du khách Ấn Độ. Lan Anh</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Đông Dương lối kiến trúc và món ăn truyền thống tạo ấn tượng tốt cho 4.500 du khách Ấn Độ đến Grand Mercure Hanoi ngày 28/8, thu hút bởi cảnh quan đẹp, văn hóa đa dạng và lịch sử sâu lắng của Việt Nam.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{
+  "id": 14,
+  "style": "news_brief",
+  "article": "Chiều 28/8, khách sạn Grand Mercure Hanoi đón hơn 200 vị khách thuộc đoàn 4.500 du khách từ Ấn Độ sang Việt Nam. Theo ông Remi Faubel, tổng quản lý khách sạn, đây là cơ hội lớn để quảng bá nét đẹp văn hóa, truyền thống tới khách quốc tế. 'Chúng tôi tự tin các yếu tố như lối kiến trúc Đông Dương, hệ thống cửa Bức Bàn, các chi tiết nội thất lấy cảm hứng từ hoa sen, trống đồng, hạt gạo, ruộng bậc thang,... sẽ góp phần để lại ấn tượng tốt đẹp trong lòng du khách', ông Faubel nói. Do nhu cầu của khách, Grand Mercure Hanoi vẫn phục vụ chủ yếu các món Ấn. Bếp trưởng - Nguyễn Minh Nguyện lý giải, du khách Ấn Độ luôn có nhu cầu thưởng thức ẩm thực đất nước họ để có cảm giác gần gũi và thoải mái khi đi du lịch. Đó cũng là cách họ gìn giữ văn hóa và chế độ ăn truyền thống. 'Khi lên kế hoạch, chúng tôi phải trao đổi với phía đại diện đoàn để nắm thông tin về chế độ ăn, suất ăn tôn giáo, yêu cầu đặc biệt, từ đó lựa chọn các loại gia vị đặc trưng của Ấn Độ để các món ăn giữ được hương vị', vị bếp trưởng nói. Tuy nhiên, khách sạn cũng chuẩn bị thêm một số món ăn đặc trưng của Việt Nam như gà, bánh cuốn, xôi, hoa quả nhiệt đới... để giới thiệu đến đoàn khách. Từ ngày 27/8 đến 3/9, Việt Nam đón 4.500 du khách thuộc tập đoàn dược phẩm lớn đến từ Ấn Độ. Dự kiến, họ sẽ chia thành các nhóm nhỏ tới Hà Nội - Ninh Bình - Hạ Long và sử dụng các dịch vụ lưu trú, ăn uống tại các khách sạn 5 sao trên địa bàn thủ đô. Ấn Độ là một trong 10 thị trường khách du lịch quốc tế lớn nhất Việt Nam. Theo số liệu từ Cục Du lịch Quốc gia, trong 6 tháng đầu năm, nước ta đã đón 231.000 lượt khách Ấn Độ, tăng 164% so với cùng kỳ năm 2023. Việt Nam có nhiều thế mạnh để thu hút và phát triển thị trường này. Các đường bay thẳng giữa hai nước được khai thác trong thời gian gần đây khiến thời gian di chuyển rút ngắn chỉ còn khoảng 4 - 5 tiếng. Theo Outlook Traveller, Việt Nam sở hữu những cảnh quan đẹp, nền văn hóa đa dạng và chiều sâu lịch sử. Giá thành dịch vụ cạnh tranh khiến nước ta trở thành điểm đến lý tưởng cho du khách Ấn Độ. Lan Anh",
+  "summary": "Đông Dương lối kiến trúc và món ăn truyền thống tạo ấn tượng tốt cho 4.500 du khách Ấn Độ đến Grand Mercure Hanoi ngày 28/8, thu hút bởi cảnh quan đẹp, văn hóa đa dạng và lịch sử sâu lắng của Việt Nam.",
+  "faithfulness_score": 0.6,
+  "faithfulness_reason": "Tóm tắt có một số thông tin không chính xác, như không đề cập đến việc khách sạn phục vụ món ăn Ấn Độ cho du khách, và cũng không nhắc đến việc du khách sẽ chia thành các nhóm nhỏ để thăm Hà Nội - Ninh Bình - Hạ Long",
+  "relevance_score": 0.4,
+  "relevance_reason": "Tóm tắt không đề cập đến một số điểm quan trọng như nhu cầu của du khách Ấn Độ về ẩm thực, việc khách sạn chuẩn bị món ăn đặc trưng của Việt Nam, và sự tăng trưởng của lượng du khách Ấn Độ đến Việt Nam",
+  "coherence_conciseness_score": 0.8,
+  "coherence_conciseness_reason": "Tóm tắt có thể dễ dàng hiểu được, tuy nhiên có một số từ ngữ không rõ ràng và có thể được viết một cách ngắn gọn hơn để tăng độ súc tích"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -635,7 +828,22 @@
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{
+  "id": 15,
+  "style": "news_brief",
+  "article": "Theo Báo cáo Hạnh phúc Thế giới (World Happiness Report) 2024 của Liên Hợp Quốc công bố hồi tháng 3, Lithuania là quốc gia 'hạnh phúc nhất thế giới dành cho những người dưới 30 tuổi (gen Z)'. Hai nhà sáng tạo nội dung Ammar Kandil và Staffan Taylor đến từ Yes Theory, kênh truyền thông nổi tiếng của Canada, quyết định đến thủ đô Vilnius để tìm hiểu xem liệu báo cáo có nói đúng. Khi hạ cánh xuống Vilnius, Amma và Staffan bắt đầu nói chuyện với người dân địa phương. Hầu hết người trẻ đều đồng ý quốc gia họ đang sống là nơi tốt nhờ 'đồ ăn tuyệt vời, người dân thân thiện, nhiều cơ hội nghề nghiệp và nền kinh tế đang phát triển'. Nhiều người trong số đó cho rằng các khó khăn mà thế hệ trước chịu đựng đã dạy thế hệ trẻ ngày nay cách tận hưởng cuộc sống trong từng khoảnh khắc và 'tìm thấy vẻ đẹp trong những điều giản dị'. Để thu hút nhiều người trẻ đến nói chuyện hơn, Amma và Staffan đã tổ chức một buổi gặp gỡ. Tại sự kiện, những người tham dự lần lượt bày tỏ quan điểm. 'Sau một năm sống tại Mỹ, tôi đánh giá cao cuộc sống ở Lithuania vì tính kết nối với thiên nhiên', một thanh niên chia sẻ. Người này nói thêm du khách có thể dễ dàng tiếp cận một hồ nước hay khu rừng tại Lithuania và chiêm ngưỡng khung cảnh thiên nhiên tuyệt đẹp ở đó. 'Lithuania chưa bao giờ tốt như hiện nay', một phụ nữ trẻ khác thừa nhận. Khi nói về hạnh phúc, một người dân địa phương cho biết dù người trẻ sống ở đất nước này 'khá vui vẻ' nhưng không có nghĩa họ không phải đối mặt với nhiều vấn đề, áp lực cuộc sống. Sau buổi gặp gỡ, Ammar và Staffan dành phần còn lại của chuyến đi để giao lưu với người dân địa phương, ghé thăm các điểm du lịch như nhà tù cũ Lukiškės giờ là địa điểm văn hóa và tượng đài Hill of Crosses. 'Đây là một trong những trải nghiệm du lịch hạnh phúc nhất tôi từng có', Ammar, người từng đi khắp thế giới, chia sẻ với độc giả trên kênh Yes Theory khi đang tham gia một bữa tiệc tối. Steffan đồng tình khi nhận định Lithuania chắc chắn là một trong những quốc gia cởi mở, hào phóng, tử tế nhất mà anh từng đến. Video của hai du khách đến từ Canada đã thu hút gần một triệu lượt xem và bình luận chỉ sau vài ngày đăng tải. Một người từng đến Vilnius học theo diện trao đổi sinh viên chia sẻ thời gian ở Liathuania là quãng thời gian hạnh phúc nhất của mình. 'Cảm ơn Liathuania đã chào đón tôi', người này nói. 'Tình yêu, sự sáng tạo và lòng tốt có thể giúp chúng ta vượt qua quá khứ đen tối, biến tiêu cực thành ánh sáng và giúp đỡ người khác', một người dân địa phương bày tỏ sau khi xem video của Ammar và Steffan. Anh Minh(TheoYes Theory, DM)",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết quan trọng như ý kiến của người dân về khó khăn mà thế hệ trước đã trải qua",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính như lý do Lithuania được coi là quốc gia hạnh phúc nhất cho thế hệ gen Z và ý kiến của người dân về cuộc sống tại đây",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt có thể còn một số phần lặp lại hoặc không rõ ràng, nhưng tổng thể vẫn dễ đọc và logic"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -643,8 +851,27 @@
           <t>Đi dạo trong khuôn viên lâu đài của mình ở Pháp vào một buổi tối mùa hè 2023, Philippa Girling cảm thấy nhẹ nhõm khi nghe thấy tiếng cười của những du khách nữ đang lưu trú tại đây. Tiếng cười là mục tiêu mà CEO Camp Château, nơi tổ chức trại hè dành riêng cho phụ nữ, mong muốn khi mở dịch vụ này. Tuy mới thành lập được hai năm, danh sách khách đăng ký đến nghỉ dưỡng tại lâu đài cổ nằm trên đỉnh đồi ở vùng Quercy, tây nam nước Pháp, năm nay đã kín chỗ. Lượng khách chờ cho mùa hè 2025 đã lên đến 11.000 người. Philippa rất vui khi được mọi người yêu thích dịch vụ cũng nhưng cảm thấy rất tiếc cho những người trong danh sách chờ khi nhiều du khách sẽ phải đợi 20 năm mới đến lượt. Cô đang xem xét để mở rộng trại hè, giúp nhiều du khách nữ có thể sử dụng dịch vụ hơn. Philippa nói mục đích tồn tại của Camp Château rất đơn giản: mang đến cho phụ nữ trải nghiệm vui vẻ. Philippa từng làm 30 năm trong ngành ngân hàng nên thấu hiểu áp lực mà phụ nữ ngày nay phải đối mặt. Do đó, cô cùng các đồng sáng lập tạo ra Camp Château để giúp các khách hàng nữ của mình thư giãn, mang lại cho họ sự chăm sóc sức khỏe tinh thần và thể chất, không gian yên tĩnh và thời gian để hồi phục trước khi quay về cuộc sống thường ngày. Kỳ nghỉ trong trại hè kéo dài sáu ngày năm đêm với nhiều hoạt động để hội viên tham gia như làm nến, nếm thử phô mai, cưỡi ngựa, yoga. Một số phụ nữ hào hứng tham gia mọi hoạt động, số khác thích dành phần lớn thời gian nằm bên hồ bơi. Mỗi đợt đón khách khoảng 50 người. Girling, người lớn lên ở miền nam nước Anh, thường đi nghỉ ở Quercy và hiện sống ở California, Mỹ, nhận thấy 'phụ nữ khi ở bên nhau thật tuyệt vời'. Những người phụ nữ đều rất hòa đồng. Họ nằm giường tầng trong các căn phòng tại lâu đài hoặc trong lều dành cho hai người. Tất cả cùng dùng chung bữa tối tại sảnh lớn và có khung giờ phục vụ đồ uống riêng. Trọng tâm của chương trình trại hè này là trao cho phụ nữ quyền tự quyết, làm mọi thứ họ muốn và chỉ cần đối xử tử tế với nhau. Toàn bộ thiết kế của Camp Château đều hướng tới mục đích giúp mọi người có thể gặp gỡ, trò chuyện nhiều hơn một cách tự nhiên nhất. Điều duy nhất khách cần quyết định tại Camp Château là muốn nghỉ ngơi hay vui chơi. Tất cả phụ nữ đều được chào đón tại trại hè. Từ tháng 7 trở về trước, phần lớn khách đến đây là người Mỹ. Nhưng từ đầu tháng 8, số lượng quốc tịch đa dạng hơn khi có thêm các khách đến từ Andorra, Canada, Ai Cập, Anh và Nigeria. Độ tuổi từ 19 đến ngoài 70 tuổi. Nhiều người đến một mình và không ít người gọi trại hè này là 'môi trường an toàn phục vụ niềm đam mê du lịch' của họ. Ngoài ra, trại hè cũng đón các nhóm khách nhỏ gồm mẹ và con gái. Giá một kỳ nghỉ là 2.178 euro, gồm mọi chi phí ăn ở, vui chơi và không tính đưa đón sân bay, dịch vụ massage. Philippa nói số tiền này không nhỏ nhưng cô và các cộng sự đã phải tính toán để đưa ra mức giá phải chăng nhất có thể. Càng ngày, lượng khách đăng ký càng đông. Nhưng Philippa nói sẽ không tăng giá vì muốn nhiều người có thể tiếp cận trải nghiệm này thay vì hướng tới tệp khách nhà giàu. Anh Minh(TheoEuro News)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Phụ nữ đã kín chỗ tại Camp Château, lâu đài Quercy ở tây nam Pháp với 11.000 người đăng ký cho mùa hè 2025. CEO Philippa Girling mong muốn mở rộng trại hè để giúp phụ nữ có cơ hội thư giãn và hồi phục sức khỏe tinh thần, thể chất hơn. Camp Château tổ chức các hoạt động như làm nến, yoga và nằm bên hồ bơi, thu hút sự tham gia của hầu hết khách hàng. Girling nhận thấy 'phụ nữ khi ở bên nhau thật tuyệt vời'. Lượng khách tăng nhưng giá 2.178 euro cho kỳ nghỉ không tính đưa đón sân bay hay dịch vụ massage vẫn giữ ổn định để nhiều người có thể tham gia.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{
+  "id": 16,
+  "style": "news_brief",
+  "article": "Đi dạo trong khuôn viên lâu đài của mình ở Pháp vào một buổi tối mùa hè 2023, Philippa Girling cảm thấy nhẹ nhõm khi nghe thấy tiếng cười của những du khách nữ đang lưu trú tại đây. Tiếng cười là mục tiêu mà CEO Camp Château, nơi tổ chức trại hè dành riêng cho phụ nữ, mong muốn khi mở dịch vụ này. Tuy mới thành lập được hai năm, danh sách khách đăng ký đến nghỉ dưỡng tại lâu đài cổ nằm trên đỉnh đồi ở vùng Quercy, tây nam nước Pháp, năm nay đã kín chỗ. Lượng khách chờ cho mùa hè 2025 đã lên đến 11.000 người. Philippa rất vui khi được mọi người yêu thích dịch vụ cũng nhưng cảm thấy rất tiếc cho những người trong danh sách chờ khi nhiều du khách sẽ phải đợi 20 năm mới đến lượt. Cô đang xem xét để mở rộng trại hè, giúp nhiều du khách nữ có thể sử dụng dịch vụ hơn. Philippa nói mục đích tồn tại của Camp Château rất đơn giản: mang đến cho phụ nữ trải nghiệm vui vẻ. Philippa từng làm 30 năm trong ngành ngân hàng nên thấu hiểu áp lực mà phụ nữ ngày nay phải đối mặt. Do đó, cô cùng các đồng sáng lập tạo ra Camp Château để giúp các khách hàng nữ của mình thư giãn, mang lại cho họ sự chăm sóc sức khỏe tinh thần và thể chất, không gian yên tĩnh và thời gian để hồi phục trước khi quay về cuộc sống thường ngày. Kỳ nghỉ trong trại hè kéo dài sáu ngày năm đêm với nhiều hoạt động để hội viên tham gia như làm nến, nếm thử phô mai, cưỡi ngựa, yoga. Một số phụ nữ hào hứng tham gia mọi hoạt động, số khác thích dành phần lớn thời gian nằm bên hồ bơi. Mỗi đợt đón khách khoảng 50 người. Girling, người lớn lên ở miền nam nước Anh, thường đi nghỉ ở Quercy và hiện sống ở California, Mỹ, nhận thấy 'phụ nữ khi ở bên nhau thật tuyệt vời'. Những người phụ nữ đều rất hòa đồng. Họ nằm giường tầng trong các căn phòng tại lâu đài hoặc trong lều dành cho hai người. Tất cả cùng dùng chung bữa tối tại sảnh lớn và có khung giờ phục vụ đồ uống riêng. Trọng tâm của chương trình trại hè này là trao cho phụ nữ quyền tự quyết, làm mọi thứ họ muốn và chỉ cần đối xử tử tế với nhau. Toàn bộ thiết kế của Camp Château đều hướng tới mục đích giúp mọi người có thể gặp gỡ, trò chuyện nhiều hơn một cách tự nhiên nhất. Điều duy nhất khách cần quyết định tại Camp Château là muốn nghỉ ngơi hay vui chơi. Tất cả phụ nữ đều được chào đón tại trại hè. Từ tháng 7 trở về trước, phần lớn khách đến đây là người Mỹ. Nhưng từ đầu tháng 8, số lượng quốc tịch đa dạng hơn khi có thêm các khách đến từ Andorra, Canada, Ai Cập, Anh và Nigeria. Độ tuổi từ 19 đến ngoài 70 tuổi. Nhiều người đến một mình và không ít người gọi trại hè này là 'môi trường an toàn phục vụ niềm đam mê du lịch' của họ. Ngoài ra, trại hè cũng đón các nhóm khách nhỏ gồm mẹ và con gái. Giá một kỳ nghỉ là 2.178 euro, gồm mọi chi phí ăn ở, vui chơi và không tính đưa đón sân bay, dịch vụ massage. Philippa nói số tiền này không nhỏ nhưng cô và các cộng sự đã phải tính toán để đưa ra mức giá phải chăng nhất có thể. Càng ngày, lượng khách đăng ký càng đông. Nhưng Philippa nói sẽ không tăng giá vì muốn nhiều người có thể tiếp cận trải nghiệm này thay vì hướng tới tệp khách nhà giàu. Anh Minh(TheoEuro News)",
+  "summary": "Phụ nữ đã kín chỗ tại Camp Château, lâu đài Quercy ở tây nam Pháp với 11.000 người đăng ký cho mùa hè 2025. CEO Philippa Girling mong muốn mở rộng trại hè để giúp phụ nữ có cơ hội thư giãn và hồi phục sức khỏe tinh thần, thể chất hơn. Camp Château tổ chức các hoạt động như làm nến, yoga và nằm bên hồ bơi, thu hút sự tham gia của hầu hết khách hàng. Girling nhận thấy 'phụ nữ khi ở bên nhau thật tuyệt vời'. Lượng khách tăng nhưng giá 2.178 euro cho kỳ nghỉ không tính đưa đón sân bay hay dịch vụ massage vẫn giữ ổn định để nhiều người có thể tham gia.",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như độ tuổi và quốc tịch của khách hàng, cũng như mục đích của Camp Château là mang lại trải nghiệm vui vẻ cho phụ nữ",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính như số lượng khách hàng, giá cả và hoạt động, nhưng bỏ qua một số thông tin quan trọng như lý do Philippa Girling thành lập Camp Château và không gian yên tĩnh cho khách hàng",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng và tránh lặp lại thông tin"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -653,7 +880,22 @@
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>{
+  "id": 17,
+  "style": "news_brief",
+  "article": "Thời gian này tại Malaysia cũng có nhiều sự kiện để du khách trải nghiệm như: lễ hội trò chơi dân gian tại Kuala Lumpur (13-16/9), lễ hội văn hóa Putrajaya (27-29/9), lễ hội bãi biển Tanjung Aru 2024 tại Kota Kinabalu (1 và 22/9)... Điểm đến phổ biến nhất tại Malaysia là thủ đô Kuala Lumpur - đô thị sầm uất với những di sản kiến trúc cùng các cao ốc hiện đại. Công trình nổi tiếng nhất là tháp đôi Petronas cao 88 tầng. Tại đây có đài quan sát toàn cảnh thành phố, cầu treo trên không, trung tâm khám phá khoa học Petrosains, thủy cung Aquaria KLCC và trung tâm mua sắm Suria KLCC. Quận trung tâm thành phố Kuala Lumpur là Bukit Bintang, khu vực nhộn nhịp bậc nhất với các khu mua sắm, khách sạn và nhà hàng cao cấp cùng nhiều tụ điểm vui chơi, giải trí. Đảo Penang lại mang đến không khí bình yên, nhẹ nhàng. Đặc biệt, George Town - thủ phủ của bang Penang là di sản thế giới, phản ánh rõ nét dấu vết lịch sử qua từng công trình kiến trúc lẫn đời sống văn hóa của cư dân, từ những ngõ nhỏ với căn nhà hai tầng của người Hoa đến tòa hội đồng thành phố, tháp đồng hồ từ thời thuộc địa Anh. Du khách đừng quên ghé đồi Penang Hill hay đền Kek Lok Si. Langkawi là quần đảo với 99 đảo nhỏ ngoài khơi biển Andaman. Vùng đất này có nhiều bãi biển hoang sơ với khu nghỉ dưỡng cao cấp, phù hợp cho kỳ nghỉ thư giãn sau những ngày bận rộn. Ngoài ra, hòn đảo này còn là điểm đến lý tưởng cho các môn thể thao dưới nước như lặn biển, dù kéo, mô tô nước hoặc khám phá công viên địa chất hàng triệu năm tuổi. Cao nguyên Cameron là địa danh nằm ở bang Pahang, được bao phủ một màu xanh dài bất tận bởi những đồi chè và loại cây ôn đới. Khí hậu của cao nguyên này mang đến cho du khách sự mát mẻ, dễ chịu như đang ở châu Âu. Khi đến đây, du khách đừng quên ghé thăm nông trại chế biến trà, vườn hoa oải hương, thung lũng hoa hồng hay thử trekking leo núi Batu Brinchang. Malaysia có nhiều món ăn hấp dẫn du khách, nổi bật là món cơm 'quốc dân' Nasi Lemak. Món cơm này gồm cơm, nấu từ gạo với nước cốt dừa, trứng luộc, gà chiên, lạc, dưa chuột thái lát, cá khô... ăn kèm xốt sambal. Món ăn tuy đơn giản song đủ dinh dưỡng và được nhiều người ưa thích. Char Kway Teow, món hủ tiếu xào nổi tiếng của cộng đồng người Hoa tại Malaysia được chế biến từ hủ tiếu bản to xào cùng tôm, chả cá, lạp xưởng, trứng, giá đỗ và hẹ. Ngoài ra, Roti Canai là món ăn của cộng đồng người Ấn. Đây là loại bánh dẹt, thơm, giòn và xốp, thường dùng kèm các loại cà ri. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 1.0,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, không chứa số liệu không chính xác và giữ nguyên ý nghĩa của văn bản gốc.",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính quan trọng nhưng có thể bỏ qua một số chi tiết thú vị về các địa điểm du lịch tại Malaysia.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt dễ đọc, logic và loại bỏ được các chi tiết thừa, tuy nhiên có thể cải thiện hơn về mặt trình bày và sắp xếp thông tin."
+}</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -662,7 +904,22 @@
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{
+  "id": 18,
+  "style": "news_brief",
+  "article": "Lodo, 62 tuổi, hôm 6/8 đã có buổi sáng trải nghiệm đan võng cùng với nghệ nhân ở Cù Lao Chàm. Ông bất ngờ về độ bền chắc và sự khéo léo, kỳ công của nghệ nhân làm ra nó. Lodo đã mua một chiếc võng về làm kỷ niệm trong chuyến du lịch Việt Nam lần này. 'Tôi nghĩ đây là một vật liệu xanh giúp bảo vệ môi trường', du khách đến từ Pháp nói. Theo ông Lê Vĩnh Thuận, Phó giám đốc Ban quản lý khu bảo tồn biển Cù Lao Chàm, trong dịp Festival 'Cù Lao Chàm - mùa ngô đồng đỏ' năm 2024 diễn ra từ ngày 5 đến 11/8, lượng du khách đổ về Cù Lao Chàm tham gia lễ hội 'rất đông'. Đến đây, du khách được tìm hiểu về nguồn gốc và tham gia cùng với nghệ nhân đan loại võng truyền thống của đảo. Theo giới thiệu của Trung tâm Quản lý bảo tồn di sản Hội An, sợi võng được làm từ các mảng vỏ cây ngô đồng. Sau khi được tách ra từ thân cây, vỏ sẽ được gom lại thành từng bó rồi ngâm nước ở các khe, suối trên đảo như khe Ruộng Chùa, khe Ông Thơ, khe Xóm Mới. Sau một tháng, người thợ đem vỏ về tách chọn lớp bên trong có màu trắng đục, tước từng sợi nhỏ, phơi khô cho đến khi có màu trắng tinh mới có thể bắt tay vào đan võng. Công đoạn tước đòi hỏi sự tập trung cao của người thợ vì 'sợi càng mỏng đan võng càng chặt', nghệ nhân đan võng Ngô Thị Lê, 70 tuổi, cho biết. Vào khoảng tháng 7, người dân trên đảo đi chọn vỏ những cây ngô đồng làm nguyên liệu đan võng, khi cây ra hoa, rụng hết lá, vỏ đủ khô để thu hoạch. Cây ngô đồng dùng làm võng phải có dáng thẳng mới cho ra sợi suôn, mềm, dai và chịu lực tốt. Bà Lê cho biết khi đã chọn được cây, người dân khai thác bằng cách chỉ chặt ngang thân để cây còn nảy chồi, phát triển sinh sống trở lại. Bà Huỳnh Thị Út, 56 tuổi, cùng với bà Lê là hai trong số ít nghệ nhân ở Cù Lao Chàm duy trì nghề đan võng ngô đồng cho biết loại võng này được người xã đảo sáng tạo ra trong quá trình lao động sản xuất. 'Để làm ra chiếc võng đẹp, ngoài tước sợi mỏng còn yêu cầu thắt nút các mối mắt võng đều', bà Út nói. Lodo nói những nghệ nhân đan võng đã giúp ông phân biệt võng tư có bốn dây đan nối nhau và võng sáu có sáu dây dày hơn đan thành hình tứ giác. Võng ngô đồng dài 2,6 m, đan thủ công hơn một tháng, độ bền của võng có thể kéo dài từ 5 đến 10 năm, có giá từ 5 đến 10 triệu đồng. 'Mức giá này xứng đáng với công sức những người thợ bỏ ra', Lodo cho hay. Chị Hà Nhi, 45 tuổi, sống tại Hà Nội, cũng ấn tượng với loại võng không làm từ sợi công nghiệp mà hoàn toàn từ vỏ cây. 'Những sản phẩm thủ công truyền thống thẩm mỹ cao như thế này là điểm nhấn cho du khách khi du lịch trên đảo', chị Nhi nói. Ngô đồng gắn liền với đời sống hàng ngày của người dân Cù Lao Chàm từ hơn 300 năm trước, theo Ban quản lý khu bảo tồn biển Cù Lao Chàm. Trải qua nhiều đời gìn giữ và nỗ lực bảo tồn, phát huy giá trị văn hóa, nghề đan võng ngô đồng ở địa phương được Bộ Văn hóa Thể thao và Du lịch công nhận là Di sản văn hóa phi vật thể quốc gia hôm 6/8. Tuấn Anh",
+  "summary": "",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể thiếu một số chi tiết nhỏ về quá trình sản xuất võng ngô đồng, tuy nhiên tổng thể vẫn giữ được ý nghĩa và nội dung chính của văn bản gốc",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt đã bao gồm các điểm chính về nghề đan võng ngô đồng, nhưng có thể bỏ qua một số thông tin phụ như việc khai thác vỏ cây ngô đồng và quá trình phát triển của nghề này",
+  "coherence_conciseness_score": 0.85,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách logic và dễ đọc, tuy nhiên có thể có một số câu dài và phức tạp, cần được tinh gọn hơn để tăng độ rõ ràng và dễ hiểu"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -671,7 +928,22 @@
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{
+  "id": 19,
+  "style": "news_brief",
+  "article": "Với mục tiêu quảng bá du lịch mua sắm tại Singapore, Vietrantour cùng Tổng Cục du lịch Singapore giới thiệu những điểm đến mua sắm và check in hấp dẫn. Nếu du khách đang tìm kiếm những món đồ phiên bản giới hạn của các hãng thời trang cao cấp như Prada, Louis Vuitton, Hermes, ION Orchard và Scotts Square, nên tới trục đường Orchard Road. Đặc biệt, một số thời điểm, các cửa hàng thời trang tại khu vực này khuyến mại tới 70%. Ngoài ra, một số địa điểm mua sắm người dân địa phương hay tới là Tampines 1, Jem và Westgate với nhiều cửa hàng bán lẻ, thời trang phục vụ nhu cầu đời sống. Nếu đang trong chuyến đi cùng gia đình, du khách hãy ghé qua trung tâm thương mại Tanglin Mall hoặc House of Anli với hàng nghìn mặt hàng gia dụng, sản phẩm dành cho mẹ và bé. Trong khi đó, trung tâm mua sắm Mustafa - tụ điểm mua sắm đêm khuya quen thuộc của người dân địa phương cũng là nơi nổi tiếng với những món đồ công nghệ hàng đầu, đến các sản phẩm tiêu dùng với giá cả phải chăng. Khi mua sắm tại Singapore, khách hàng còn được hoàn thuế tới 7%. Là quốc gia phát triển mạnh về dịch vụ du lịch, Singapore chú trọng nhiều đến trải nghiệm khách hàng. Đất nước này cũng được đánh giá là trạm trung gian lý tưởng để bảo hành các sản phẩm đồ hiệu, 'thiên đường' mua hàng miễn thuế với nhiều thương hiệu quốc tế và các nhãn hàng địa phương như mỹ phẩm, nước hoa, bia rượu, đồng hồ, thực phẩm... Tại Singapore, một trong những trải nghiệm thú vị là du khách có thể tự tay hoàn thiện các sản phẩm thủ công truyền thống. Các cửa hàng sẽ có thợ thủ công lành nghề hướng dẫn du khách chưng cất rượu gin tại Brass Lion Distillery, làm đồ da tại Atelier Lodge hoặc học kỹ thuật thêu tranh hạt cườm truyền thống tại Rumah Bebe. Bạn cũng có thể dạo qua khu phố di sản Kampong Gelam, nơi sở hữu những cửa hàng bày bán đồ truyền thống như đồ gốm, đồ da thủ công,.. Trải nghiệm này sẽ giúp du khách hiểu rõ hơn về nét đẹp văn hóa Singapore, đồng thời thể hiện phong cách cá nhân trong từng sản phẩm. Du khách nêndạo các nhà sách như Books Actually và Huggs-Epigram Coffee Bookshop để khám phá văn học kinh điển từ một số nhà thơ, tiểu thuyết gia của Singapore. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết quan trọng như việc hoàn thuế tới 7% khi mua sắm tại Singapore",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm mua sắm và trải nghiệm quan trọng, tuy nhiên có thể cần thêm thông tin về các hoạt động văn hóa và nghệ thuật tại Singapore",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt còn một số đoạn văn không liên kết chặt chẽ và có thể rút gọn để tăng độ súc tích và dễ đọc"
+}</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -679,8 +951,783 @@
           <t>Chương trình lần này có sự đồng hành của diễn viên Ninh Dương Lan Ngọc. Thông qua Epic Sale, diễn viên mong muốn lan tỏa tinh thần du lịch thông minh, tiện lợi và tối ưu chi phí. Ông Iko Putera, Giám đốc Vận chuyển Traveloka, cho biết việc hợp tác cùng Lan Ngọc đánh dấu cột mốc quan trọng trên hành trình mang đến trải nghiệm du lịch tiện nghi tối ưu cho khách hàng. Tầm ảnh hưởng và đam mê du lịch của cô phù hợp với sứ mệnh nền tảng theo đuổi. Đôi bên đều muốn truyền cảm hứng khám phá thế giới qua những chuyến đi. Với Epic Sale lần này, Traveloka áp dụng ưu đãi đến 50% cho các sản phẩm du lịch, dịch vụ trên toàn thế giới. 'Đây là lời tri ân chúng tôi muốn gửi đến khách hàng đã luôn ủng hộ, gắn bó trên hành trình kiến tạo những chuyến đi đáng nhớ cùng Traveloka', ông Iko Putera cho biết. Từ khi trở thành đại sứ thương hiệu tại Việt Nam, diễn viên Ninh Dương Lan Ngọc đã có nhiều trải nghiệm du lịch chất lượng với nền tảng. Với loạt khuyến mại, ưu đãi, quà tặng trong Epic Sale 2024, cô nói sẽ tranh thủ săn vé, đặt phòng, chuẩn bị cho những chuyến đi sắp tới. Theo Lan Ngọc, chương trình mang lại cho du khách cơ hội du lịch tiện nghi với chi phí tiết kiệm, giúp khơi dậy mong muốn đi đây đi đó, khám phá thế giới. Cô đánh giá cao sự tiện lợi và các dịch vụ toàn diện của nền tảng, giúp việc lên kế hoạch cho các chuyến đi thêm dễ dàng, thú vị. Traveloka đã hợp tác cùng hàng nghìn đối tác để mang đến những deal giá ưu đãi sâu. Người dùng có thể truy cập nền tảng, theo dõi các ưu đãi hàng ngày trong các mục Vé máy bay, Khách sạn, Xperience và nhiều sản phẩm du lịch khác. 'Siêu ưu đãi Epic' (Super Epic Deal) sẽ được áp dụng cho các sản phẩm nhất định trong khung giờ giới hạn. Cụ thể, giờ vàng Epic Hour Deal ưu đãi vé máy bay mỗi thứ Bảy từ 14h-17h; đặt khách sạn giờ vàng EPIC Hotel Hour Deal diễn ra hàng ngày từ 18h-19h. Du khách có thể săn vé máy bay quốc nội và quốc tế với giá ưu đãi. Trong đó, vé nội địa Vietravel giá chỉ từ 781.925 đồng; vé China Southern Airlines đi Thâm Quyến từ 2,819 đồng; vé T'way Air đến Hàn Quốc và Nhật Bản lần lượt chỉ từ 2,667 triệu đồng và 2,682 triệu đồng. Khách hàng còn có cơ hội nghỉ dưỡng tại khách sạn 5 sao trong nước với giá từ 794.000 đồng. Hàng loạt khách sạn Hàn Quốc giá từ 1,858 triệu đồng, Nhật Bản từ 1,146 triệu đồng. Với dịch vụ giải trí, nền tảng áp dụng ưu đãi 'mua 1 tặng 1' vé tham quan Sun World, công viên nước The Amazing Bay, thủy cung Sea Life Bangkok Ocean World (Thái Lan). Để du khách có trải nghiệm du lịch trọn vẹn, Traveloka giới thiệu thêm nhiều tính năng khác như: hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt... Xem thêm thông tin chi tiết về chương trình Epic Sale trên ứng dụng, website và các tài khoản mạng xã hội của Traveloka. Á Hiên</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>794.000 đồng khách sạn 5 sao trong nước; 1.858 triệu đồng Hàn Quốc, 1.146 triệu đồng Nhật Bản; vé China Southern Airlines Thâm Quyến 2.819 triệu đồng, Vietravel từ 2.667-2.682 triệu đồng; T'way Air và Sea Life Bangkok Ocean World có ưu đãi 'mua 1 tặng 1'; Traveloka hoàn tiền 100%, linh hoạt thanh toán...</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{
+  "id": 20,
+  "style": "news_brief",
+  "article": "Chương trình lần này có sự đồng hành của diễn viên Ninh Dương Lan Ngọc. Thông qua Epic Sale, diễn viên mong muốn lan tỏa tinh thần du lịch thông minh, tiện lợi và tối ưu chi phí. Ông Iko Putera, Giám đốc Vận chuyển Traveloka, cho biết việc hợp tác cùng Lan Ngọc đánh dấu cột mốc quan trọng trên hành trình mang đến trải nghiệm du lịch tiện nghi tối ưu cho khách hàng. Tầm ảnh hưởng và đam mê du lịch của cô phù hợp với sứ mệnh nền tảng theo đuổi. Đôi bên đều muốn truyền cảm hứng khám phá thế giới qua những chuyến đi. Với Epic Sale lần này, Traveloka áp dụng ưu đãi đến 50% cho các sản phẩm du lịch, dịch vụ trên toàn thế giới. 'Đây là lời tri ân chúng tôi muốn gửi đến khách hàng đã luôn ủng hộ, gắn bó trên hành trình kiến tạo những chuyến đi đáng nhớ cùng Traveloka', ông Iko Putera cho biết. Từ khi trở thành đại sứ thương hiệu tại Việt Nam, diễn viên Ninh Dương Lan Ngọc đã có nhiều trải nghiệm du lịch chất lượng với nền tảng. Với loạt khuyến mại, ưu đãi, quà tặng trong Epic Sale 2024, cô nói sẽ tranh thủ săn vé, đặt phòng, chuẩn bị cho những chuyến đi sắp tới. Theo Lan Ngọc, chương trình mang lại cho du khách cơ hội du lịch tiện nghi với chi phí tiết kiệm, giúp khơi dậy mong muốn đi đây đi đó, khám phá thế giới. Cô đánh giá cao sự tiện lợi và các dịch vụ toàn diện của nền tảng, giúp việc lên kế hoạch cho các chuyến đi thêm dễ dàng, thú vị. Traveloka đã hợp tác cùng hàng nghìn đối tác để mang đến những deal giá ưu đãi sâu. Người dùng có thể truy cập nền tảng, theo dõi các ưu đãi hàng ngày trong các mục Vé máy bay, Khách sạn, Xperience và nhiều sản phẩm du lịch khác. 'Siêu ưu đãi Epic' (Super Epic Deal) sẽ được áp dụng cho các sản phẩm nhất định trong khung giờ giới hạn. Cụ thể, giờ vàng Epic Hour Deal ưu đãi vé máy bay mỗi thứ Bảy từ 14h-17h; đặt khách sạn giờ vàng EPIC Hotel Hour Deal diễn ra hàng ngày từ 18h-19h. Du khách có thể săn vé máy bay quốc nội và quốc tế với giá ưu đãi. Trong đó, vé nội địa Vietravel giá chỉ từ 781.925 đồng; vé China Southern Airlines đi Thâm Quyến từ 2,819 đồng; vé T'way Air đến Hàn Quốc và Nhật Bản lần lượt chỉ từ 2,667 triệu đồng và 2,682 triệu đồng. Khách hàng còn có cơ hội nghỉ dưỡng tại khách sạn 5 sao trong nước với giá từ 794.000 đồng. Hàng loạt khách sạn Hàn Quốc giá từ 1,858 triệu đồng, Nhật Bản từ 1,146 triệu đồng. Với dịch vụ giải trí, nền tảng áp dụng ưu đãi 'mua 1 tặng 1' vé tham quan Sun World, công viên nước The Amazing Bay, thủy cung Sea Life Bangkok Ocean World (Thái Lan). Để du khách có trải nghiệm du lịch trọn vẹn, Traveloka giới thiệu thêm nhiều tính năng khác như: hoàn tiền 100%, thay đổi lịch trình, thanh toán linh hoạt... Xem thêm thông tin chi tiết về chương trình Epic Sale trên ứng dụng, website và các tài khoản mạng xã hội của Traveloka. Á Hiên",
+  "summary": "794.000 đồng khách sạn 5 sao trong nước; 1.858 triệu đồng Hàn Quốc, 1.146 triệu đồng Nhật Bản; vé China Southern Airlines Thâm Quyến 2.819 triệu đồng, Vietravel từ 2.667-2.682 triệu đồng; T'way Air và Sea Life Bangkok Ocean World có ưu đãi 'mua 1 tặng 1'; Traveloka hoàn tiền 100%, linh hoạt thanh toán...",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng lại bỏ qua một số chi tiết quan trọng như mục đích của chương trình Epic Sale và vai trò của diễn viên Ninh Dương Lan Ngọc, dẫn đến mất đi một phần ý nghĩa và thông điệp của văn bản gốc.",
+  "relevance_score": 0.6,
+  "relevance_reason": "Tóm tắt chỉ tập trung vào việc liệt kê các ưu đãi và giá cả mà bỏ qua các điểm chính như sự hợp tác giữa Traveloka và Ninh Dương Lan Ngọc, cũng như không đề cập đến mục tiêu của chương trình là mang lại trải nghiệm du lịch thông minh và tiết kiệm cho khách hàng.",
+  "coherence_conciseness_score": 0.4,
+  "coherence_conciseness_reason": "Tóm tắt thiếu sự mạch lạc và rõ ràng, chỉ là một danh sách các ưu đãi và giá cả mà không có sự liên kết logic giữa các thông tin, khiến cho người đọc khó hiểu và không có cái nhìn tổng quan về chương trình Epic Sale."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Với chủ đề 'Trải nghiệm địa phương - Khám phá đa dạng', ngoài những điểm đến đã trở nên phổ biến, Cơ quan Xúc tiến Du lịch Nhật Bản (JNTO) tập trung vào tính địa phương và sự đa dạng, chưa nhiều người biết tại Nhật Bản cho khách quốc tế, trong đó có Việt Nam. Công viên giải trí nhập vai Immersive Fort Immersive Fort Tokyo là công viên giải trí chủ đề nhập vai đầu tiên trên thế giới, nằm tại khu vực Odaiba của thủ đô Tokyo. Tại đây, bạn sẽ được khám phá những điểm tham quan độc đáo và sống động, biến những câu chuyện và tưởng tượng phi thường thành hiện thực. Không chỉ đơn thuần là người quan sát, khách du lịch còn có cơ hội tham gia vào các hoạt động hấp dẫn tại công viên. Thế giới kỳ diệu và sự tương tác chân thực với các nhân vật trong từng câu chuyện sẽ đưa du khách ra khỏi thế giới thực tại, hóa thành nhân vật chính trong những câu chuyện lôi cuốn. Immersive Fort Tokyo có chủ đề và bối cảnh đa dạng, dành cho mọi lứa tuổi, tái hiện lại những câu chuyện như Sherlock Holmes, Jack the Ripper và anime Oshi no Ko. Thủy cung Kobe Suma Thủy cung Kobe Suma nằm ở thành phố Kobe thuộc tỉnh Hyogo. Trải dọc theo vịnh Osaka, công viên bờ biển Suma nổi tiếng với phong cảnh đẹp và mang đến cơ hội ngắm nhìn, tìm hiểu về sự sống ở đại dương. Thủy cung hướng đến thể hiện sự kết nối với đại dương thông qua triển lãm và các hoạt động giải trí kết hợp cung cấp thông tin, trải nghiệm vui chơi cho cả gia đình. Một điểm đặc biệt tại công viên chính là hồ cá heo (Dolphin Lagoon) đầu tiên tại Nhật Bản do khách sạn Kobe Suma Sea World quản lý. Khách lưu trú tại khách sạn có thể trải nghiệm bơi cùng cá heo (có tính phí). Khách sạn có tổng cộng 80 phòng, mỗi phòng đều có tầm nhìn ra biển. Ngắm núi Phú Sĩ tại tỉnh Shizuoka Núi Phú Sĩ là biểu tượng của Nhật Bản với vẻ đẹp hùng vĩ. Ngoài các cung leo núi thường mở cửa vào đầu tháng 7 hàng năm, còn có rất nhiều cách để chiêm ngưỡng vẻ đẹp của ngọn núi này. Tỉnh Shizuoka, nằm ở miền Trung, là nơi có tầm nhìn đẹp để ngắm trọn ngọn núi. Sự thay đổi thiên nhiên theo mùa tạo nên khung cảnh đỉnh núi phủ vào những tháng lạnh hoặc sườn núi đá vào những tháng có thời tiết ấm áp. Shizuoka là nơi bạn có thể chiêm ngưỡng dáng vẻ hùng vĩ của núi Phú Sĩ và những kỳ quan ở các khu vực xung quanh. Nghỉ dưỡng tại một ryokan truyền thống của Nhật Bản, giải trí cùng văn hóa geisha địa phương, trải nghiệm du lịch nông nghiệp tại làng Wasabi hoặc đắm mình trong khung cảnh hoàng hôn của ngọn núi lửa nổi tiếng thế giới tại khu cắm trại nghỉ dưỡng là các trải nghiệm tại Shizuoka. Tâm Anh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Thủ đô Tokyo tái hiện Sherlock Holmes và Jack the Ripper trong Công viên Immersive Fort Tokyo. Kobe, Hyogo: Thủy cung Suma có hồ cá heo đầu tiên tại Nhật Bản. Shizuoka: Ngắm núi Phú Sĩ với tầm nhìn đẹp; trải nghiệm ryokan truyền thống, geisha địa phương hoặc du lịch nông nghiệp Wasabi.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{
+  "id": 21,
+  "style": "news_brief",
+  "article": "Với chủ đề 'Trải nghiệm địa phương - Khám phá đa dạng', ngoài những điểm đến đã trở nên phổ biến, Cơ quan Xúc tiến Du lịch Nhật Bản (JNTO) tập trung vào tính địa phương và sự đa dạng, chưa nhiều người biết tại Nhật Bản cho khách quốc tế, trong đó có Việt Nam. Công viên giải trí nhập vai Immersive Fort Immersive Fort Tokyo là công viên giải trí chủ đề nhập vai đầu tiên trên thế giới, nằm tại khu vực Odaiba của thủ đô Tokyo. Tại đây, bạn sẽ được khám phá những điểm tham quan độc đáo và sống động, biến những câu chuyện và tưởng tượng phi thường thành hiện thực. Không chỉ đơn thuần là người quan sát, khách du lịch còn có cơ hội tham gia vào các hoạt động hấp dẫn tại công viên. Thế giới kỳ diệu và sự tương tác chân thực với các nhân vật trong từng câu chuyện sẽ đưa du khách ra khỏi thế giới thực tại, hóa thành nhân vật chính trong những câu chuyện lôi cuốn. Immersive Fort Tokyo có chủ đề và bối cảnh đa dạng, dành cho mọi lứa tuổi, tái hiện lại những câu chuyện như Sherlock Holmes, Jack the Ripper và anime Oshi no Ko. Thủy cung Kobe Suma Thủy cung Kobe Suma nằm ở thành phố Kobe thuộc tỉnh Hyogo. Trải dọc theo vịnh Osaka, công viên bờ biển Suma nổi tiếng với phong cảnh đẹp và mang đến cơ hội ngắm nhìn, tìm hiểu về sự sống ở đại dương. Thủy cung hướng đến thể hiện sự kết nối với đại dương thông qua triển lãm và các hoạt động giải trí kết hợp cung cấp thông tin, trải nghiệm vui chơi cho cả gia đình. Một điểm đặc biệt tại công viên chính là hồ cá heo (Dolphin Lagoon) đầu tiên tại Nhật Bản do khách sạn Kobe Suma Sea World quản lý. Khách lưu trú tại khách sạn có thể trải nghiệm bơi cùng cá heo (có tính phí). Khách sạn có tổng cộng 80 phòng, mỗi phòng đều có tầm nhìn ra biển. Ngắm núi Phú Sĩ tại tỉnh Shizuoka Núi Phú Sĩ là biểu tượng của Nhật Bản với vẻ đẹp hùng vĩ. Ngoài các cung leo núi thường mở cửa vào đầu tháng 7 hàng năm, còn có rất nhiều cách để chiêm ngưỡng vẻ đẹp của ngọn núi này. Tỉnh Shizuoka, nằm ở miền Trung, là nơi có tầm nhìn đẹp để ngắm trọn ngọn núi. Sự thay đổi thiên nhiên theo mùa tạo nên khung cảnh đỉnh núi phủ vào những tháng lạnh hoặc sườn núi đá vào những tháng có thời tiết ấm áp. Shizuoka là nơi bạn có thể chiêm ngưỡng dáng vẻ hùng vĩ của núi Phú Sĩ và những kỳ quan ở các khu vực xung quanh. Nghỉ dưỡng tại một ryokan truyền thống của Nhật Bản, giải trí cùng văn hóa geisha địa phương, trải nghiệm du lịch nông nghiệp tại làng Wasabi hoặc đắm mình trong khung cảnh hoàng hôn của ngọn núi lửa nổi tiếng thế giới tại khu cắm trại nghỉ dưỡng là các trải nghiệm tại Shizuoka. Tâm Anh",
+  "summary": "Thủ đô Tokyo tái hiện Sherlock Holmes và Jack the Ripper trong Công viên Immersive Fort Tokyo. Kobe, Hyogo: Thủy cung Suma có hồ cá heo đầu tiên tại Nhật Bản. Shizuoka: Ngắm núi Phú Sĩ với tầm nhìn đẹp; trải nghiệm ryokan truyền thống, geisha địa phương hoặc du lịch nông nghiệp Wasabi.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như sự đa dạng và tính địa phương của các điểm đến, cũng như trải nghiệm tại công viên Immersive Fort Tokyo",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số điểm đến quan trọng nhưng bỏ qua các hoạt động và trải nghiệm cụ thể tại từng địa điểm, như thế giới kỳ diệu tại Immersive Fort Tokyo và các hoạt động tại thủy cung Kobe Suma",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và logic, tuy nhiên có thể cải thiện bằng cách thêm một số từ khóa hoặc cụm từ để kết nối các ý tưởng và làm cho tóm tắt trở nên mượt mà hơn"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ngày lễ còn có tên Hari Merdeka, nhằm đánh dấu mốc Malaysia được giải phóng khỏi thực dân Anh năm 1957. Sự kiện này được người dân cả nước mong chờ hàng năm và thu hút rất đông du khách tham gia. Lễ kỷ niệm Quốc khánh Malaysia năm nay mang chủ đề 'Malaysia Madani: Jiwa Merdeka', thể hiện tinh thần quyết tâm phát triển đất nước và đoàn kết nhân dân, được tổ chức tại Putrajaya. Nếu đến Malaysia đúng dịp lễ hội này, bạn có thể tham gia rất nhiều hoạt động sôi nổi và ý nghĩa. Diễu hành Merdeka Lễ kỷ niệm Quốc khánh Malaysia bắt đầu từ buổi sáng với sự hiện diện của Quốc vương và Hoàng hậu, Thủ tướng, nội các, phái đoàn ngoại giao tại Malaysia. Một trong những hoạt động chính của buổi lễ là diễu hành Merdeka. Màn diễu hành có quy mô lớn với hàng nghìn người tham gia, nhằm nêu cao lòng tự hào dân tộc, tình yêu nước cùng sự đoàn kết cho mỗi người dân. Nổi bật nhất là các hoạt động biểu dương lực lượng của Cảnh sát Hoàng gia Malaysia, Quân đội Malaysia. Bên cạnh đó, hàng nghìn người sẽ mặc trang phục truyền thống hoặc quần áo đại diện cho các tầng lớp, nghề nghiệp trong xã hội, cầm lá quốc kỳ Malaysia (Jalur Gemilang) diễu hành trên đường tạo nên không khí rộn ràng, sôi động. Điểm nhấn của màn diễu hành là những xe hoa rực rỡ đi qua khán đài. Với người dân Malaysia, đây là lúc để tưởng nhớ và tri ân những anh hùng nằm xuống trong quá khứ để giành được độc lập, mang lại cuộc sống hòa bình như ngày nay. Màn diễu hành này diễn ra ở khắp nơi, từ thành thị tới nông thôn. Chương trình văn hóa, nghệ thuật Xuyên suốt lễ hội là những chương trình văn hóa, nghệ thuật đặc sắc. Các địa phương đều tổ chức các chương trình ca múa, biểu diễn âm nhạc nhằm tạo ra không khí rộn ràng trong ngày lễ đặc biệt. Nhiều chương trình biểu diễn mang đậm phong cách truyền thống cũng được tổ chức, nhằm hun đúc tình yêu cho thế hệ trẻ, tiếp tục bảo tồn, giữ gìn nét văn hóa này. Bên cạnh đó cũng có các chương trình có âm nhạc sôi động thu hút người dân đến xem. Ngoài ra, nhiều tác phẩm nghệ thuật cũng được giới họa sĩ giới thiệu trong những chương trình triển lãm được tổ chức nhiều nơi. Lễ hội văn hóa và ẩm thực Nếu đến Malaysia trong dịp này, du khách sẽ thấy hàng loạt hội chợ ẩm thực, món ăn đường phố đa dạng, các buổi hòa nhạc, triển lãm... Không khí lễ hội dâng cao với nhiều chương trình, ưu đãi hấp dẫn. Trong đó, du khách có thể khám phá nét đa dạng trong ẩm thực Malaysia tại tiệc buffet theo chủ đề tại khách sạn đang lưu trú. Hoạt động thể thao Người dân Malaysia thường rất hào hứng với các hoạt động thể thao, thưởng thức biểu diễn võ truyền thống. Ngoài ra, các địa phương còn tổ chức chương trình kéo co để các làng thi đấu với nhau. Trẻ em cũng hòa vào sự sôi động với những cuộc thi thể thao quy mô nhỏ phù hợp lứa tuổi như tô màu. Bắn pháo hoa Ban ngày, nếu người dân Malaysia mong chờ diễu hành Merdeka, buổi tối họ lại háo hức theo dõi màn bắn pháo hoa hoành tráng. Nhiều người dân và du khách sẽ chọn các địa điểm đẹp để chiêm ngưỡng pháo hoa, trước khi diễn ra hàng giờ đồng hồ. Thậm chí, đêm trước khi lễ hội Merdeka diễn ra, những màn pháo hoa đẹp mắt đã được các địa phương bắn, mang tới sự hứng khởi, niềm tự hào cho mỗi người dân Malaysia. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{
+  "id": 22,
+  "style": "news_brief",
+  "article": "Ngày lễ còn có tên Hari Merdeka, nhằm đánh dấu mốc Malaysia được giải phóng khỏi thực dân Anh năm 1957. Sự kiện này được người dân cả nước mong chờ hàng năm và thu hút rất đông du khách tham gia. Lễ kỷ niệm Quốc khánh Malaysia năm nay mang chủ đề 'Malaysia Madani: Jiwa Merdeka', thể hiện tinh thần quyết tâm phát triển đất nước và đoàn kết nhân dân, được tổ chức tại Putrajaya. Nếu đến Malaysia đúng dịp lễ hội này, bạn có thể tham gia rất nhiều hoạt động sôi nổi và ý nghĩa. Diễu hành Merdeka Lễ kỷ niệm Quốc khánh Malaysia bắt đầu từ buổi sáng với sự hiện diện của Quốc vương và Hoàng hậu, Thủ tướng, nội các, phái đoàn ngoại giao tại Malaysia. Một trong những hoạt động chính của buổi lễ là diễu hành Merdeka. Màn diễu hành có quy mô lớn với hàng nghìn người tham gia, nhằm nêu cao lòng tự hào dân tộc, tình yêu nước cùng sự đoàn kết cho mỗi người dân. Nổi bật nhất là các hoạt động biểu dương lực lượng của Cảnh sát Hoàng gia Malaysia, Quân đội Malaysia. Bên cạnh đó, hàng nghìn người sẽ mặc trang phục truyền thống hoặc quần áo đại diện cho các tầng lớp, nghề nghiệp trong xã hội, cầm lá quốc kỳ Malaysia (Jalur Gemilang) diễu hành trên đường tạo nên không khí rộn ràng, sôi động. Điểm nhấn của màn diễu hành là những xe hoa rực rỡ đi qua khán đài. Với người dân Malaysia, đây là lúc để tưởng nhớ và tri ân những anh hùng nằm xuống trong quá khứ để giành được độc lập, mang lại cuộc sống hòa bình như ngày nay. Màn diễu hành này diễn ra ở khắp nơi, từ thành thị tới nông thôn. Chương trình văn hóa, nghệ thuật Xuyên suốt lễ hội là những chương trình văn hóa, nghệ thuật đặc sắc. Các địa phương đều tổ chức các chương trình ca múa, biểu diễn âm nhạc nhằm tạo ra không khí rộn ràng trong ngày lễ đặc biệt. Nhiều chương trình biểu diễn mang đậm phong cách truyền thống cũng được tổ chức, nhằm hun đúc tình yêu cho thế hệ trẻ, tiếp tục bảo tồn, giữ gìn nét văn hóa này. Bên cạnh đó cũng có các chương trình có âm nhạc sôi động thu hút người dân đến xem. Ngoài ra, nhiều tác phẩm nghệ thuật cũng được giới họa sĩ giới thiệu trong những chương trình triển lãm được tổ chức nhiều nơi. Lễ hội văn hóa và ẩm thực Nếu đến Malaysia trong dịp này, du khách sẽ thấy hàng loạt hội chợ ẩm thực, món ăn đường phố đa dạng, các buổi hòa nhạc, triển lãm... Không khí lễ hội dâng cao với nhiều chương trình, ưu đãi hấp dẫn. Trong đó, du khách có thể khám phá nét đa dạng trong ẩm thực Malaysia tại tiệc buffet theo chủ đề tại khách sạn đang lưu trú. Hoạt động thể thao Người dân Malaysia thường rất hào hứng với các hoạt động thể thao, thưởng thức biểu diễn võ truyền thống. Ngoài ra, các địa phương còn tổ chức chương trình kéo co để các làng thi đấu với nhau. Trẻ em cũng hòa vào sự sôi động với những cuộc thi thể thao quy mô nhỏ phù hợp lứa tuổi như tô màu. Bắn pháo hoa Ban ngày, nếu người dân Malaysia mong chờ diễu hành Merdeka, buổi tối họ lại háo hức theo dõi màn bắn pháo hoa hoành tráng. Nhiều người dân và du khách sẽ chọn các địa điểm đẹp để chiêm ngưỡng pháo hoa, trước khi diễn ra hàng giờ đồng hồ. Thậm chí, đêm trước khi lễ hội Merdeka diễn ra, những màn pháo hoa đẹp mắt đã được các địa phương bắn, mang tới sự hứng khởi, niềm tự hào cho mỗi người dân Malaysia. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 0.0,
+  "faithfulness_reason": "Không có bản tóm tắt nào được cung cấp để đánh giá tính trung thực.",
+  "relevance_score": 0.0,
+  "relevance_reason": "Không có bản tóm tắt nào được cung cấp để đánh giá tính liên quan.",
+  "coherence_conciseness_score": 0.0,
+  "coherence_conciseness_reason": "Không có bản tóm tắt nào được cung cấp để đánh giá tính mạch lạc và conciseness."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Hiện Việt Nam có nhiều chuyển bay thẳng đến Kuala Lumpur từ sân bay Nội Bài, Tân Sơn Nhất, Đà Nẵng, Phú Quốc của các hãng hàng không Vietnam Airlines, Malaysia Airlines, AirAsia, Batik Air và Vietjet. Nếu xuất phát từ TP HCM, thời gian bay sang Malaysia sẽ khoảng 1 giờ 40 phút. Các chuyến bay thẳng từ Hà Nội sẽ dài khoảng 3 giờ 20 phút và từ Đà Nẵng là 2 giờ 50 phút. Khi sang tới Malaysia, bạn có thể lựa chọn nhiều phương tiện như xe buýt, tàu điện ngầm, tàu điện, taxi, taxi công nghệ. Malaysia là quốc gia nhiệt đới với khí hậu và thời tiết ấm áp. Nhiệt độ trung bình năm tại đây khoảng 27-33 độ C và thấp nhất khoảng 17 độ C. Lãnh thổ Malaysia có hai phần: bán đảo Malaysia ở phía Tây và một phần trên đảo Borneo ở phía Đông. Điều này mang đến lợi thế du lịch quanh năm thuận lợi cho quốc gia giàu tài nguyên biển đảo này. Các điểm vui chơi tại Malaysia cũng phong phú, trải dài khắp đất nước. Trong đó, Kuala Lumpur là thủ đô luôn sầm uất, náo nhiệt, với biểu tượng mới là công trình Merdeka 118, tòa nhà cao thứ nhì thế giới với độ cao 678,9 m. Được mệnh danh là 'Hòn ngọc phương Đông', Penang là tiểu bang có bề dày lịch sử và văn hóa, thủ phủ George Town là di sản thế giới được UNESCO công nhận. Nơi đây còn có khung cảnh thiên nhiên nguyên sơ, hòn đảo Penang ẩn mình trong nét văn hóa độc đáo của địa phương. Thành phố Melaka cũng được UNESCO công nhận là một trong những di sản thế giới vào năm 2008. Những căn nhà tại đây sở hữu kiến trúc cổ xưa, mang màu sắc độc đáo, cùng nền ẩm thực phong phú. Đặc biệt, Melaka có nhiều điểm tham quan mang giá trị lịch sử như pháo đài A’Famosa, Hội đồng thành phố Stadhuys, nhà thờ St Paul... Sát bên đảo Penang là 'viên ngọc quý vùng Kedah', đảo Langkawi. Đây là hòn đảo du lịch thu hút du khách với vẻ đẹp tự nhiên hoang sơ như hồ nước ngọt trên núi, công viên địa chất toàn cầu UNESCO, rừng ngập mặn và những chú chim đại bàng nâu hoang dã. Bên cạnh đó, Johor Bahru là thiên đường du lịch cho các gia đình khi đến Malaysia. Ngoài việc lên danh sách điểm đến, trong mỗi một chuyến du lịch, việc đặt phòng khách sạn cũng là điều quan trọng. Du khách có thể tham khảo khu Bukit Bintang và KLCC, Chinatown KL, KL Sentral, Bangsar, Mid Valley... Malaysia là một quốc gia đa chủng tộc cùng sinh sống, do đó ẩm thực cũng là sự kết hợp hương vị Mã Lai, Hoa, và Ấn. Bạn có thể tìm đến các khu ẩm thực như Jalan Alor (Kuala Lumpur), Gurney Drive (Penang) hoặc trong các trung tâm mua sắm để thưởng thức các món ăn đa dạng của Malaysia. Du khách có thể thưởng thức các món ăn mang đặc trưng tại quốc gia này như: thịt xiên nướng Satay, bún Laksa, bánh nướng với cà ri Roti Canai, hủ tiếu xào Char Kway Teow, cơm Nasi Lemak , chè Cendol, , rau quả trộn Rojak... Đến Malaysia, du khách cần lưu ý mang ô (dù) du lịch cho những cơn mưa bất chợt, ổ cắm chuyển đổi cho các thiết bị điện tử, SIM điện thoại và tải các ứng dụng đặt xe công nghệ để chuyến đi thuận tiện hơn. Ngoài ra, từ ngày 1/1 năm nay, du khách quốc tế cần phải khai phiếu nhập cảnh điện tử Malaysia Digital Arrival Card ba ngày trước khi đến Malaysia. Tờ khaitại đây. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{
+  "id": 23,
+  "style": "news_brief",
+  "article": "Hiện Việt Nam có nhiều chuyển bay thẳng đến Kuala Lumpur từ sân bay Nội Bài, Tân Sơn Nhất, Đà Nẵng, Phú Quốc của các hãng hàng không Vietnam Airlines, Malaysia Airlines, AirAsia, Batik Air và Vietjet. Nếu xuất phát từ TP HCM, thời gian bay sang Malaysia sẽ khoảng 1 giờ 40 phút. Các chuyến bay thẳng từ Hà Nội sẽ dài khoảng 3 giờ 20 phút và từ Đà Nẵng là 2 giờ 50 phút. Khi sang tới Malaysia, bạn có thể lựa chọn nhiều phương tiện như xe buýt, tàu điện ngầm, tàu điện, taxi, taxi công nghệ. Malaysia là quốc gia nhiệt đới với khí hậu và thời tiết ấm áp. Nhiệt độ trung bình năm tại đây khoảng 27-33 độ C và thấp nhất khoảng 17 độ C. Lãnh thổ Malaysia có hai phần: bán đảo Malaysia ở phía Tây và một phần trên đảo Borneo ở phía Đông. Điều này mang đến lợi thế du lịch quanh năm thuận lợi cho quốc gia giàu tài nguyên biển đảo này. Các điểm vui chơi tại Malaysia cũng phong phú, trải dài khắp đất nước. Trong đó, Kuala Lumpur là thủ đô luôn sầm uất, náo nhiệt, với biểu tượng mới là công trình Merdeka 118, tòa nhà cao thứ nhì thế giới với độ cao 678,9 m. Được mệnh danh là 'Hòn ngọc phương Đông', Penang là tiểu bang có bề dày lịch sử và văn hóa, thủ phủ George Town là di sản thế giới được UNESCO công nhận. Nơi đây còn có khung cảnh thiên nhiên nguyên sơ, hòn đảo Penang ẩn mình trong nét văn hóa độc đáo của địa phương. Thành phố Melaka cũng được UNESCO công nhận là một trong những di sản thế giới vào năm 2008. Những căn nhà tại đây sở hữu kiến trúc cổ xưa, mang màu sắc độc đáo, cùng nền ẩm thực phong phú. Đặc biệt, Melaka có nhiều điểm tham quan mang giá trị lịch sử như pháo đài A’Famosa, Hội đồng thành phố Stadhuys, nhà thờ St Paul... Sát bên đảo Penang là 'viên ngọc quý vùng Kedah', đảo Langkawi. Đây là hòn đảo du lịch thu hút du khách với vẻ đẹp tự nhiên hoang sơ như hồ nước ngọt trên núi, công viên địa chất toàn cầu UNESCO, rừng ngập mặn và những chú chim đại bàng nâu hoang dã. Bên cạnh đó, Johor Bahru là thiên đường du lịch cho các gia đình khi đến Malaysia. Ngoài việc lên danh sách điểm đến, trong mỗi một chuyến du lịch, việc đặt phòng khách sạn cũng là điều quan trọng. Du khách có thể tham khảo khu Bukit Bintang và KLCC, Chinatown KL, KL Sentral, Bangsar, Mid Valley... Malaysia là một quốc gia đa chủng tộc cùng sinh sống, do đó ẩm thực cũng là sự kết hợp hương vị Mã Lai, Hoa, và Ấn. Bạn có thể tìm đến các khu ẩm thực như Jalan Alor (Kuala Lumpur), Gurney Drive (Penang) hoặc trong các trung tâm mua sắm để thưởng thức các món ăn đa dạng của Malaysia. Du khách có thể thưởng thức các món ăn mang đặc trưng tại quốc gia này như: thịt xiên nướng Satay, bún Laksa, bánh nướng với cà ri Roti Canai, hủ tiếu xào Char Kway Teow, cơm Nasi Lemak , chè Cendol, , rau quả trộn Rojak... Đến Malaysia, du khách cần lưu ý mang ô (dù) du lịch cho những cơn mưa bất chợt, ổ cắm chuyển đổi cho các thiết bị điện tử, SIM điện thoại và tải các ứng dụng đặt xe công nghệ để chuyến đi thuận tiện hơn. Ngoài ra, từ ngày 1/1 năm nay, du khách quốc tế cần phải khai phiếu nhập cảnh điện tử Malaysia Digital Arrival Card ba ngày trước khi đến Malaysia. Tờ khaitại đây. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết nhỏ, tuy nhiên vẫn giữ được ý nghĩa chính của văn bản gốc",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính như thời gian bay, phương tiện đi lại, khí hậu, các điểm du lịch nổi tiếng và ẩm thực đặc trưng của Malaysia",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt còn một số đoạn văn không liên kết chặt chẽ và có thể rút gọn để tăng độ súc tích và dễ đọc"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ban ngày, Quảng Bình chào đón du khách khám phá thiên nhiên hùng vĩ, thơ mộng với điểm đến đầu tiên là vườn quốc gia Phong Nha - Kẻ Bàng. Nơi đây có 400 hang động, trong đó hang Sơn Đoòng lớn nhất thế giới, hang Én lớn thứ ba thế giới với hàng triệu con chim én trú ngụ. Tại đây, du khách sẽ leo núi, cắm trại, tham quan thác nước trong động. Nằm trong hệ thống vườn quốc gia Phong Nha - Kẻ Bàng, suối nước Moọc có thiên nhiên ngập tràn sắc xanh. Du khách có thể tham quan rừng nguyên sinh, trải nghiệm các hoạt động thể thao như đua bơi, chèo thuyền Kayak, câu cá, đu dây... Tiếp đến là bãi biển Nhật Lệ và Bảo Ninh, thường xuyên tổ chức hoạt động thể thao biển, ẩm thực với nhiều món hải sản. Bãi biển cũng là nơi nghỉ dưỡng thích hợp cho những người muốn có không khí trong lành, lắng nghe tiếng sóng vỗ... Du khách muốn tham gia trải nghiệm mới, có thể lựa chọn trượt cát ở cồn cát Quang Phú. Địa điểm nằm giữa thành phố Đồng Hới và huyện Bố Trạch, vẫn giữ được nét hoang sơ vốn có. Những ngọn đồi cát trắng mịn, cao hơn 100m giúp du khách cảm nhận như đang lạc vào sa mạc thu nhỏ. Một điểm nhấn du lịch khác ở Quảng Bình trong mùa hè, là đô thịRegal Legendtại trung tâm thành phố Đồng Hới. Đô thị sở hữu dịch vụ lưu trú, nghỉ dưỡng 5 sao, tuyến phố đêm gói gọn hàng trăm tiện ích, giúp du khách không cần di chuyển xa trong điều kiện thời tiết nóng nực. Tại các tuyến phố về đêm sẽ diễn ra nhiều sự kiện nghệ thuật, giải trí quy mô lớn, cùng với nhiều thương hiệu thời trang, ẩm thực, mua sắm, vui chơi, giải trí... Ngoài ra, vào đầu tháng 7, du khách có thể được tham gia lễ hội mùa hè Legend Summer Festival, tổ chức 9 ngày 9 đêm do Regal Group tổ chức. Mỗi đêm ban tổ chức sẽ đưa khán giả đến với những chủ đề âm nhạc khác nhau như Pop Ballad, Rap &amp; Hip Hop, Flamenco, EDM, Rock... Tối 12/7, sự kiện khởi động kinh doanh tòa tháp Regal Residence Luxury với Đại nhạc hội EDM quốc tế và trình diễn pháo hoa quốc tế sẽ diễn ra, đón chào du khách tham gia. Sự kiện có sự tham gia của nhiều tên tuổi như Lou Hoàng, ICD, Muộii, DJ PIA &amp; TUMIE, DJ FWIN. Cuối cùng là lễ hội ẩm thực tổ chức vào 6-14/7, với gần 300 gian hàng về du lịch, ẩm thực ba miền, vui chơi giải trí tại tuyến phố đi bộ. Loạt nghệ nhân ẩm thực nổi tiếng sẽ tham gia, như: Nguyễn Hồ Tiếu Anh với tác phẩm 'Hoa tình thương', nghệ nhân Hồ Đắc Thiếu Anh với '50 món kẹo mứt miền Trung', nghệ nhân ưu tú Phan Tôn Gia Hiền với 'Nem công chả phượng'; nghệ nhân Hồ Nhất Phương với 'Gà tần sâm bố chính hoàng gia'; nghệ nhân Lê Văn Khánh có 'Kình ngư hóa long'... Văn Hà</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Regal Legend tại Đồng Hới đón du khách với lễ hội mùa hè 6-14/7, bao gồm khám phá vườn quốc gia Phong Nha - Kẻ Bàng và Moọc Suối. Đại nhạc hội EDM quốc tế diễn ra tối 12/7 do Regal Residence Luxury tổ chức.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{
+  "id": 24,
+  "style": "news_brief",
+  "article": "Ban ngày, Quảng Bình chào đón du khách khám phá thiên nhiên hùng vĩ, thơ mộng với điểm đến đầu tiên là vườn quốc gia Phong Nha - Kẻ Bàng. Nơi đây có 400 hang động, trong đó hang Sơn Đoòng lớn nhất thế giới, hang Én lớn thứ ba thế giới với hàng triệu con chim én trú ngụ. Tại đây, du khách sẽ leo núi, cắm trại, tham quan thác nước trong động. Nằm trong hệ thống vườn quốc gia Phong Nha - Kẻ Bàng, suối nước Moọc có thiên nhiên ngập tràn sắc xanh. Du khách có thể tham quan rừng nguyên sinh, trải nghiệm các hoạt động thể thao như đua bơi, chèo thuyền Kayak, câu cá, đu dây... Tiếp đến là bãi biển Nhật Lệ và Bảo Ninh, thường xuyên tổ chức hoạt động thể thao biển, ẩm thực với nhiều món hải sản. Bãi biển cũng là nơi nghỉ dưỡng thích hợp cho những người muốn có không khí trong lành, lắng nghe tiếng sóng vỗ... Du khách muốn tham gia trải nghiệm mới, có thể lựa chọn trượt cát ở cồn cát Quang Phú. Địa điểm nằm giữa thành phố Đồng Hới và huyện Bố Trạch, vẫn giữ được nét hoang sơ vốn có. Những ngọn đồi cát trắng mịn, cao hơn 100m giúp du khách cảm nhận như đang lạc vào sa mạc thu nhỏ. Một điểm nhấn du lịch khác ở Quảng Bình trong mùa hè, là đô thịRegal Legendtại trung tâm thành phố Đồng Hới. Đô thị sở hữu dịch vụ lưu trú, nghỉ dưỡng 5 sao, tuyến phố đêm gói gọn hàng trăm tiện ích, giúp du khách không cần di chuyển xa trong điều kiện thời tiết nóng nực. Tại các tuyến phố về đêm sẽ diễn ra nhiều sự kiện nghệ thuật, giải trí quy mô lớn, cùng với nhiều thương hiệu thời trang, ẩm thực, mua sắm, vui chơi, giải trí... Ngoài ra, vào đầu tháng 7, du khách có thể được tham gia lễ hội mùa hè Legend Summer Festival, tổ chức 9 ngày 9 đêm do Regal Group tổ chức. Mỗi đêm ban tổ chức sẽ đưa khán giả đến với những chủ đề âm nhạc khác nhau như Pop Ballad, Rap &amp; Hip Hop, Flamenco, EDM, Rock... Tối 12/7, sự kiện khởi động kinh doanh tòa tháp Regal Residence Luxury với Đại nhạc hội EDM quốc tế và trình diễn pháo hoa quốc tế sẽ diễn ra, đón chào du khách tham gia. Sự kiện có sự tham gia của nhiều tên tuổi như Lou Hoàng, ICD, Muộii, DJ PIA &amp; TUMIE, DJ FWIN. Cuối cùng là lễ hội ẩm thực tổ chức vào 6-14/7, với gần 300 gian hàng về du lịch, ẩm thực ba miền, vui chơi giải trí tại tuyến phố đi bộ. Loạt nghệ nhân ẩm thực nổi tiếng sẽ tham gia, như: Nguyễn Hồ Tiếu Anh với tác phẩm 'Hoa tình thương', nghệ nhân Hồ Đắc Thiếu Anh với '50 món kẹo mứt miền Trung', nghệ nhân ưu tú Phan Tôn Gia Hiền với 'Nem công chả phượng'; nghệ nhân Hồ Nhất Phương với 'Gà tần sâm bố chính hoàng gia'; nghệ nhân Lê Văn Khánh có 'Kình ngư hóa long'... Văn Hà",
+  "summary": "Regal Legend tại Đồng Hới đón du khách với lễ hội mùa hè 6-14/7, bao gồm khám phá vườn quốc gia Phong Nha - Kẻ Bàng và Moọc Suối. Đại nhạc hội EDM quốc tế diễn ra tối 12/7 do Regal Residence Luxury tổ chức.",
+  "faithfulness_score": 0.6,
+  "faithfulness_reason": "Tóm tắt không cung cấp thông tin đầy đủ và chính xác về các điểm du lịch tại Quảng Bình, đồng thời không đề cập đến một số hoạt động và sự kiện quan trọng như trượt cát ở cồn cát Quang Phú, lễ hội ẩm thực và các nghệ nhân ẩm thực tham gia",
+  "relevance_score": 0.4,
+  "relevance_reason": "Tóm tắt chỉ tập trung vào một số điểm du lịch và sự kiện tại Regal Legend mà bỏ qua nhiều thông tin quan trọng khác về Quảng Bình, khiến cho tóm tắt không phản ánh đầy đủ nội dung của văn bản gốc",
+  "coherence_conciseness_score": 0.8,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng và dễ hiểu, tuy nhiên vẫn còn một số thông tin không cần thiết và có thể được trình bày một cách cô đọng hơn để tăng tính mạch lạc và thu hút người đọc"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Các tín đồ mua sắm có thể tìm những món hàng hiệu thiết kế hàng đầu đến những sản vật địa phương, thiết bị công nghệ tiên tiến, quà lưu niệm tại Bukit Bintang.Nơi đây gồm dãy các trung tâm mua sắm liền kề nhau khắp khu vực Bukit Bintang, giúp du khách dễ dàng lựa chọn những món đồ theo nhu cầu cá nhân. Pavilion Kuala Lumpur Pavilion Kuala Lumpur là điểm đến cho du khách thích sự sang trọng. Loạt thương hiệu nổi tiếng toàn cầu đều tập trung tại đây như Chanel, Dior, Gucci, Prada, Louis Vuitton, Hermes... Suria KLCC Suria KLCC nằm giữa lòng thủ đô Kuala Lumpur, với hàng loạt điểm đến thú vị để khám phá. Khung cảnh mua sắm tại đây nhộn nhịp với các cửa hàng thời trang thiết kế cao cấp, khu ẩm thực... giúp du khách trải nghiệm trọn vẹn. Trung tâm thương mại Lot 10 Trung tâm thương mại Lot 10 sở hữu loạt cửa hàng đáp ứng mọi nhu cầu của khách hàng. Bạn có thể tìm thấy những sản phẩm độc lạ tại cửa hàng Nhật Bản Isetan, The Marathon Shop, Butik Le’ Shene, Etincelle Couture... Trung tâm thương mại Low Yat Những ai đam mê thiết bị điện tử không nên bỏ qua Trung tâm thương mại Low Yat với dãy cửa hàng bày bán các linh kiện, phụ kiện, sửa chữa đồ công nghệ tại chỗ như Switch, C-Zone, TMT HP Concept Store, Asus Concept Store... Central Market Dành cho những ai yêu thích thủ công truyền thống, quà lưu niệm và ẩm thực Malaysia, Central Market là không gian trưng bày những món đồ Mã Lai. Tại đây, du khách có thể tìm mua những sản phẩm đặc biệt độc đáo và tinh tế như vải batik, vải songket và chế tác điêu khắc gỗ. Ngoài ra, Central Market cũng mang đến tinh hoa thủ công mỹ nghệ Trung Hoa gồm thư pháp, gốm sứ và ngọc bích. Du khách nên trải nghiệm sản phẩm may mặc và trang sức Ấn Độ phong phú tại đây. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Các trung tâm mua sắm Bukit Bintang, Pavilion Kuala Lumpur, Suria KLCC, Lot 10 và Central Market cung cấp hàng hiệu cao cấp đến sản phẩm thủ công độc đáo.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{
+  "id": 25,
+  "style": "news_brief",
+  "article": "Các tín đồ mua sắm có thể tìm những món hàng hiệu thiết kế hàng đầu đến những sản vật địa phương, thiết bị công nghệ tiên tiến, quà lưu niệm tại Bukit Bintang.Nơi đây gồm dãy các trung tâm mua sắm liền kề nhau khắp khu vực Bukit Bintang, giúp du khách dễ dàng lựa chọn những món đồ theo nhu cầu cá nhân. Pavilion Kuala Lumpur Pavilion Kuala Lumpur là điểm đến cho du khách thích sự sang trọng. Loạt thương hiệu nổi tiếng toàn cầu đều tập trung tại đây như Chanel, Dior, Gucci, Prada, Louis Vuitton, Hermes... Suria KLCC Suria KLCC nằm giữa lòng thủ đô Kuala Lumpur, với hàng loạt điểm đến thú vị để khám phá. Khung cảnh mua sắm tại đây nhộn nhịp với các cửa hàng thời trang thiết kế cao cấp, khu ẩm thực... giúp du khách trải nghiệm trọn vẹn. Trung tâm thương mại Lot 10 Trung tâm thương mại Lot 10 sở hữu loạt cửa hàng đáp ứng mọi nhu cầu của khách hàng. Bạn có thể tìm thấy những sản phẩm độc lạ tại cửa hàng Nhật Bản Isetan, The Marathon Shop, Butik Le’ Shene, Etincelle Couture... Trung tâm thương mại Low Yat Những ai đam mê thiết bị điện tử không nên bỏ qua Trung tâm thương mại Low Yat với dãy cửa hàng bày bán các linh kiện, phụ kiện, sửa chữa đồ công nghệ tại chỗ như Switch, C-Zone, TMT HP Concept Store, Asus Concept Store... Central Market Dành cho những ai yêu thích thủ công truyền thống, quà lưu niệm và ẩm thực Malaysia, Central Market là không gian trưng bày những món đồ Mã Lai. Tại đây, du khách có thể tìm mua những sản phẩm đặc biệt độc đáo và tinh tế như vải batik, vải songket và chế tác điêu khắc gỗ. Ngoài ra, Central Market cũng mang đến tinh hoa thủ công mỹ nghệ Trung Hoa gồm thư pháp, gốm sứ và ngọc bích. Du khách nên trải nghiệm sản phẩm may mặc và trang sức Ấn Độ phong phú tại đây. Thanh Thư",
+  "summary": "Các trung tâm mua sắm Bukit Bintang, Pavilion Kuala Lumpur, Suria KLCC, Lot 10 và Central Market cung cấp hàng hiệu cao cấp đến sản phẩm thủ công độc đáo.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như sự hiện diện của các thương hiệu nổi tiếng tại Pavilion Kuala Lumpur và các sản phẩm độc đáo tại Central Market",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số trung tâm mua sắm và không bao gồm tất cả các điểm nổi bật quan trọng như Suria KLCC và Lot 10",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và không có từ ngữ thừa, tuy nhiên có thể cải thiện bằng cách thêm một số từ khóa quan trọng để tăng độ rõ ràng"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Quy Nhơn, Bình Định nổi tiếng với vẻ đẹp hoang sơ, bờ biển dài trong xanh cùng đa dạng di sản văn hóa, ẩm thực. Nhiều gia đình chọn thành phố biển miền Trung làm điểm nghỉ dưỡng dịp hè vì mang lại cảm giác bình yên, ít xô bồ. Tọa lạc ngay tuyến đường trung tâm, gần trục đường biển Xuân Diệu, Fleur de Lys Hotel Quy Nhon là một trong những điểm đến lý tưởng cho cả gia đình. Ngoài chất lượng phòng ốc, dịch vụ chuẩn 4 sao, khách sạn còn mang đến đa dạng dịch vụ giải trí, thư giãn, ẩm thực, đáp ứng nhu cầu nghỉ dưỡng trọn vẹn cho gia đình đa thế hệ. Là một trong những khách sạn chuẩn 4 sao quốc tế tại Quy Nhơn, Fleur de Lys Hotel có kiến trúc hiện đại, tối gian nhưng vẫn đảm bảo yếu tố sang trọng. Khách sạn có đa dạng các loại phòng nghỉ với 100% hạng phòng hướng biển. Về dịch vụ tiện ích, La Pensée Spa được khách sạn ví như 'ốc đảo yên bình' thu nhỏ. Những du khách lớn tuổi như ông bà trong gia đình có thể thư giãn, tận hưởng những liệu pháp massage, hỗ trợ chăm sóc và hồi phục sức khỏe. Tầng 18 của khách sạn là SOL Skybar &amp; Lounge. Nơi lý tưởng để bố mẹ cùng nhau thưởng thức những ly cocktail màu sắc, ngắm toàn cảnh thành phố về đêm trong tiếng nhạc sôi động. Bể bơi ngoài trời rộng rãi với khu vực riêng cho trẻ em là nơi các bé có thể thỏa sức vui đùa, đắm mình trong dòng nước mát lạnh và làm quen với những người bạn mới. Sau một ngày khám phá vùng đất xứ Nẫu, cả gia đình có thể quây quần bên nhau tại nhà hàng Hoa FengHuang hay SOL Lounge của khách sạn. Ngoài những món ăn đặc sản địa phương, nhà hàng còn phục vụ loạt món ngon phương Đông lẫn Âu - Mỹ, các đầu bếp dày dặn kinh nghiệm trực tiếp chế biến. Về vị trí, Fleur de Lys Hotel Quy Nhon nằm ngay trung tâm, giúp du khách dễ dàng di chuyển đến các điểm tham quan nổi tiếng như Tháp Đôi, Eo Gió, Kỳ Co... Ngoài ra, khách sạn còn tổ chức các chuyến tham quan danh lam thắng cảnh, tham gia các hoạt động văn hóa đặc sắc tại địa phương... giúp bạn có thêm những trải nghiệm thú vị, hiểu hơn về vùng đất này. 'Với đội ngũ nhân viên chuyên nghiệp, nhiệt tình, Fleur de Lys Hotel Quy Nhon cam kết mang đến trải nghiệm nghỉ dưỡng chất lượng, hứa hẹn sẽ là nơi cả gia đình tận hưởng kỳ nghỉ trọn vẹn, tìm thấy niềm vui, thư giãn trí óc', đại diện khách sạn nói. Á Hiên</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fleur de Lys Hotel, 4 sao tại Quy Nhon, Bình Định, có phòng rộng với nhiều tiện ích; tuyển dụng nhân viên chất lượng.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{
+  "id": 26,
+  "style": "news_brief",
+  "article": "Quy Nhơn, Bình Định nổi tiếng với vẻ đẹp hoang sơ, bờ biển dài trong xanh cùng đa dạng di sản văn hóa, ẩm thực. Nhiều gia đình chọn thành phố biển miền Trung làm điểm nghỉ dưỡng dịp hè vì mang lại cảm giác bình yên, ít xô bồ. Tọa lạc ngay tuyến đường trung tâm, gần trục đường biển Xuân Diệu, Fleur de Lys Hotel Quy Nhon là một trong những điểm đến lý tưởng cho cả gia đình. Ngoài chất lượng phòng ốc, dịch vụ chuẩn 4 sao, khách sạn còn mang đến đa dạng dịch vụ giải trí, thư giãn, ẩm thực, đáp ứng nhu cầu nghỉ dưỡng trọn vẹn cho gia đình đa thế hệ. Là một trong những khách sạn chuẩn 4 sao quốc tế tại Quy Nhơn, Fleur de Lys Hotel có kiến trúc hiện đại, tối gian nhưng vẫn đảm bảo yếu tố sang trọng. Khách sạn có đa dạng các loại phòng nghỉ với 100% hạng phòng hướng biển. Về dịch vụ tiện ích, La Pensée Spa được khách sạn ví như 'ốc đảo yên bình' thu nhỏ. Những du khách lớn tuổi như ông bà trong gia đình có thể thư giãn, tận hưởng những liệu pháp massage, hỗ trợ chăm sóc và hồi phục sức khỏe. Tầng 18 của khách sạn là SOL Skybar &amp; Lounge. Nơi lý tưởng để bố mẹ cùng nhau thưởng thức những ly cocktail màu sắc, ngắm toàn cảnh thành phố về đêm trong tiếng nhạc sôi động. Bể bơi ngoài trời rộng rãi với khu vực riêng cho trẻ em là nơi các bé có thể thỏa sức vui đùa, đắm mình trong dòng nước mát lạnh và làm quen với những người bạn mới. Sau một ngày khám phá vùng đất xứ Nẫu, cả gia đình có thể quây quần bên nhau tại nhà hàng Hoa FengHuang hay SOL Lounge của khách sạn. Ngoài những món ăn đặc sản địa phương, nhà hàng còn phục vụ loạt món ngon phương Đông lẫn Âu - Mỹ, các đầu bếp dày dặn kinh nghiệm trực tiếp chế biến. Về vị trí, Fleur de Lys Hotel Quy Nhon nằm ngay trung tâm, giúp du khách dễ dàng di chuyển đến các điểm tham quan nổi tiếng như Tháp Đôi, Eo Gió, Kỳ Co... Ngoài ra, khách sạn còn tổ chức các chuyến tham quan danh lam thắng cảnh, tham gia các hoạt động văn hóa đặc sắc tại địa phương... giúp bạn có thêm những trải nghiệm thú vị, hiểu hơn về vùng đất này. 'Với đội ngũ nhân viên chuyên nghiệp, nhiệt tình, Fleur de Lys Hotel Quy Nhon cam kết mang đến trải nghiệm nghỉ dưỡng chất lượng, hứa hẹn sẽ là nơi cả gia đình tận hưởng kỳ nghỉ trọn vẹn, tìm thấy niềm vui, thư giãn trí óc', đại diện khách sạn nói. Á Hiên",
+  "summary": "Fleur de Lys Hotel, 4 sao tại Quy Nhon, Bình Định, có phòng rộng với nhiều tiện ích; tuyển dụng nhân viên chất lượng.",
+  "faithfulness_score": 0.2,
+  "faithfulness_reason": "Tóm tắt không chính xác khi đề cập rằng khách sạn 'tuyển dụng nhân viên chất lượng', điều này không được đề cập trong văn bản gốc. Ngoài ra, tóm tắt còn bỏ qua nhiều thông tin quan trọng về khách sạn như vị trí, dịch vụ giải trí, thư giãn, ẩm thực",
+  "relevance_score": 0.3,
+  "relevance_reason": "Tóm tắt không bao gồm các điểm chính của khách sạn như kiến trúc hiện đại, dịch vụ tiện ích, La Pensée Spa, SOL Skybar &amp; Lounge, bể bơi ngoài trời, nhà hàng Hoa FengHuang, vị trí trung tâm và các hoạt động văn hóa đặc sắc tại địa phương",
+  "coherence_conciseness_score": 0.1,
+  "coherence_conciseness_reason": "Tóm tắt không rõ ràng, thiếu logic và không thể hiện được sự liên kết giữa các thông tin, ngoài ra còn quá ngắn và không đủ để mô tả khách sạn một cách đầy đủ"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>National Geographickhen ngợi khung cảnh hùng vĩ của núi non Sapa, nơi khu nghỉ dưỡng này tọa lạc. Cam kết hỗ trợ cộng đồng địa phương của khu nghỉ dưỡng nhằm mang đến cho du khách trải nghiệm đích thực ở trung tâm Vườn quốc gia Hoàng Liên Sơn, Sa Pa, cũng được tổ chức đánh giá cao. Topas Ecolodge tọa lạc trên đỉnh đồi có vị thế và tầm nhìn bao quát, chinh phục du khách bởi vẻ đẹp thiên nhiên hoang sơ. Ẩn mình giữa những dãy núi trùng điệp, mỗi bungalow tại đây được thiết kế tỉ mỉ từ vật liệu truyền thống với phong cách Bắc Âu và tầm nhìn toàn cảnh núi rừng. Tổ chức này còn đề cập đến những nỗ lực phát triển du lịch bền vững của Topas Ecolodge. Theo họ, khu nghỉ dưỡng giúp giảm tác động đến môi trường thông qua các hệ thống làm nóng nước bể bơi thân thiện với môi trường. Hệ thống xử lý nước thải sinh hoạt cũng được thiết kế để giảm tiêu thụ các loại nhựa sử dụng một lần... Khu nghỉ dưỡng chú trọng hỗ trợ cộng đồng địa phương và tuyển dụng người dân bản địa. Người chưa có kinh nghiệm sẽ được đào tạo các kỹ năng trong ngành nhà hàng, khách sạn, giúp họ mở rộng cơ hội nghề nghiệp. Trong phần giới thiệu về Topas Ecolodge,National Geographicnhắc đến trải nghiệm ẩm thực độc đáo tại Tây Bắc Việt Nam. Du khách có thể thưởng thức ẩm thực được chế biến chuyên nghiệp bởi đội ngũ đầu bếp hàng đầu tại Việt Nam và Đan Mạch. Những món ăn kết hợp hài hòa giữa hương vị địa phương và quốc tế. Bạn có thể chọn giữa nhà hàng 360 với tầm nhìn toàn cảnh núi rừng hoặc nhà hàng Stilt House ấm cúng ngay trung tâm khu nghỉ dưỡng. Ngoài ẩm thực và cơ sở vật chất, Topas Ecolodge còn có những hoạt động trải nghiệm đa dạng: trekking qua thung lũng ruộng bậc thang, thăm những ngôi làng ẩn sâu trong núi, tìm hiểu văn hóa truyền thống của đồng bào dân tộc thiểu số hay thăm chợ phiên bản địa... Ngoài ra, giải chạy địa hình lâu đời nhất Việt Nam - Vietnam Mountain Marathon diễn ra hàng năm sắp tới cũng là cơ hội lý tưởng để du khách vừa thử thách bản thân, vừa thư giãn, ngắm cảnh. Topas Ecolodge là khu vực về đích của giải chạy năm nay, dự kiến thu hút hơn 5.000 vận động viên chạy địa hình vào tháng 9. Với sự kết hợp giữa cảnh quan đẹp mắt của Sa Pa, các hoạt động khám phá, nghỉ dưỡng đa dạng và ẩm thực phong phú, Topas Ecolodge hứa hẹn mang đến trải nghiệm đáng nhớ. Trước đó, khu nghỉ dưỡng nhiều lần được tổ chức này giới thiệu trong các danh sách khác như: 21 địa điểm phải trải nghiệm nếu quan tâm đến hành tinh năm 2017 và Những khu nghỉ dưỡng độc đáo nhất trên thế giới năm 2018. Á Hiên</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{
+  "id": 27,
+  "style": "news_brief",
+  "article": "National Geographickhen ngợi khung cảnh hùng vĩ của núi non Sapa, nơi khu nghỉ dưỡng này tọa lạc. Cam kết hỗ trợ cộng đồng địa phương của khu nghỉ dưỡng nhằm mang đến cho du khách trải nghiệm đích thực ở trung tâm Vườn quốc gia Hoàng Liên Sơn, Sa Pa, cũng được tổ chức đánh giá cao. Topas Ecolodge tọa lạc trên đỉnh đồi có vị thế và tầm nhìn bao quát, chinh phục du khách bởi vẻ đẹp thiên nhiên hoang sơ. Ẩn mình giữa những dãy núi trùng điệp, mỗi bungalow tại đây được thiết kế tỉ mỉ từ vật liệu truyền thống với phong cách Bắc Âu và tầm nhìn toàn cảnh núi rừng. Tổ chức này còn đề cập đến những nỗ lực phát triển du lịch bền vững của Topas Ecolodge. Theo họ, khu nghỉ dưỡng giúp giảm tác động đến môi trường thông qua các hệ thống làm nóng nước bể bơi thân thiện với môi trường. Hệ thống xử lý nước thải sinh hoạt cũng được thiết kế để giảm tiêu thụ các loại nhựa sử dụng một lần... Khu nghỉ dưỡng chú trọng hỗ trợ cộng đồng địa phương và tuyển dụng người dân bản địa. Người chưa có kinh nghiệm sẽ được đào tạo các kỹ năng trong ngành nhà hàng, khách sạn, giúp họ mở rộng cơ hội nghề nghiệp. Trong phần giới thiệu về Topas Ecolodge,National Geographicnhắc đến trải nghiệm ẩm thực độc đáo tại Tây Bắc Việt Nam. Du khách có thể thưởng thức ẩm thực được chế biến chuyên nghiệp bởi đội ngũ đầu bếp hàng đầu tại Việt Nam và Đan Mạch. Những món ăn kết hợp hài hòa giữa hương vị địa phương và quốc tế. Bạn có thể chọn giữa nhà hàng 360 với tầm nhìn toàn cảnh núi rừng hoặc nhà hàng Stilt House ấm cúng ngay trung tâm khu nghỉ dưỡng. Ngoài ẩm thực và cơ sở vật chất, Topas Ecolodge còn có những hoạt động trải nghiệm đa dạng: trekking qua thung lũng ruộng bậc thang, thăm những ngôi làng ẩn sâu trong núi, tìm hiểu văn hóa truyền thống của đồng bào dân tộc thiểu số hay thăm chợ phiên bản địa... Ngoài ra, giải chạy địa hình lâu đời nhất Việt Nam - Vietnam Mountain Marathon diễn ra hàng năm sắp tới cũng là cơ hội lý tưởng để du khách vừa thử thách bản thân, vừa thư giãn, ngắm cảnh. Topas Ecolodge là khu vực về đích của giải chạy năm nay, dự kiến thu hút hơn 5.000 vận động viên chạy địa hình vào tháng 9. Với sự kết hợp giữa cảnh quan đẹp mắt của Sa Pa, các hoạt động khám phá, nghỉ dưỡng đa dạng và ẩm thực phong phú, Topas Ecolodge hứa hẹn mang đến trải nghiệm đáng nhớ. Trước đó, khu nghỉ dưỡng nhiều lần được tổ chức này giới thiệu trong các danh sách khác như: 21 địa điểm phải trải nghiệm nếu quan tâm đến hành tinh năm 2017 và Những khu nghỉ dưỡng độc đáo nhất trên thế giới năm 2018. Á Hiên",
+  "summary": "",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể đã bỏ qua một số chi tiết nhỏ như hệ thống xử lý nước thải sinh hoạt của khu nghỉ dưỡng",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt đã bao gồm các điểm chính như vị trí, kiến trúc, ẩm thực và hoạt động, nhưng có thể đã bỏ qua một số điểm quan trọng như cam kết hỗ trợ cộng đồng địa phương của khu nghỉ dưỡng",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt có thể dễ đọc và hiểu, nhưng có một số câu dài và phức tạp, cần được tinh gọn và rõ ràng hơn để tăng độ mạch lạc"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fairy Blossomdiễn ra vào 11h hàng ngày tại quảng trường Noel Plaza, Sun World Ba Na Hills, sau các show diễn mùa hè từng ghi dấu ấn các năm trước nhưVũ hội Ánh DươnghayTrận chiến ở Vương quốc Mặt Trăng.Theo đơn vị sản xuất, đây sẽ là show diễn đầu tiên tại Việt Nam quy tụ nhiều loại hình nghệ thuật nhất, như xiếc, ảo thuật, đu bay, uốn dẻo, sway pole, diabolo, giữ thăng bằng trên dây, múa lụa trên không, parkour, tung hứng, vũ đạo... Show diễn có sự tham gia của Domitil Aillot - nam nghệ sĩ xiếc cột hàng đầu thế giới; cặp sao song sinh nổi tiếng của đoàn Cirque du Soleil - Crystal Ladies với đôi chân 'ma thuật'; cặp đôi nghệ sĩ hàng đầu nước Nga Oleg Izossimov, 'nàng tiên cá' múa lụa trên không Olga Moreva... Lấy cảm hứng từ vẻ đẹp của muôn loài hoa tại Bà Nà, với kết cấu chương hồi gồm 6 màn,Fairy Blossomkể về một xứ sở cổ tích với những loài sinh vật diệu kỳ sinh sôi nảy nở. Cốt truyện của show diễn lấy cảm hứng từ thần thoại Hy Lạp, khi Đất mẹ Gaia xuất hiện và ban phát sự sống, tạo ra một vườn địa đàng lộng lẫy, nơi các bông hoa khổng lồ và những loài vật vui vẻ cùng nhau chung sống. Show diễnđược tạo ra bởi trí tưởng tượng phong phú của 'phù thủy' xiếc Việt Tuấn Lê - nguyên thành viên của đoàn xiếc Cirque du Soleil.VớiFairy Blossom, khán giả sẽ được tận mắt thưởng thức chuỗi tiết mục kinh điển, những kỷ lục làm nên tên tuổi của các nghệ sĩ top 1 thế giới trong lĩnh vực xiếc và tạp kỹ. Đạo diễn Tuấn Lê chia sẻ, Fairy Blossom là sàn diễn đặc biệt, nơi nghệ thuật trình diễn được tôn vinh và thể hiện trọn vẹn những góc độ tinh tế cùng sự cuốn hút, dẫn dắt khán giả qua mọi cung bậc cảm xúc. 'Tại đây, tôi và Sun World Ba Na Hills đều có chung một giấc mơ: dùng nghệ thuật để tôn vinh văn hóa và ngược lại, dùng văn hóa làm chất dẫn để nghệ thuật thăng hoa', đạo diễn nói. Với show diễn độc đáo này, cặp song sinh Crystal Ladies nhận định sân khấu được thiết kế quy mô, rực rỡ. 'Fairy Blossomđộc đáo bởi được diễn ra tại sân khấu trình diễn trên độ cao gần 1.500 m, trong một không gian đầy sắc màu cổ tích và diệu kỳ', cặp đôi chia sẻ. Xem show, khán giả sẽ liên tục bất ngờ khi chứng kiến những màn nhào lộn từ độ cao hàng chục mét của các nghệ sĩ xiếc Việt và các màn trình diễn xiếc đẳng cấp thế giới của các ngôi sao quốc tế. Ngoài ra, tạo hình yêu kiều của những nàng tiên hoa cùng những điệu nhảy, màn đánh trống malambo... cũng khiến khán giả phấn khích. Tài nghệ của đạo diễn Tuấn Lê còn được ghi dấu ấn qua loạt tiểu tiết công phu, tạo nhiều trải nghiệm mới mẻ cho khán giả. Điểm nhấn của show diễn cũng nằm ở phần âm nhạc tươi vui, giàu sức biểu cảm, được tuyển chọn từ những bản giao hưởng nổi tiếng thế giới. 'Show có những phân cảnh xiếc quá nghẹt thở khiến tôi không thể tin vào mắt mình và chỉ biết hò reo, vỗ tay thán phục liên tục. Vũ đạo của show diễn cũng đẹp mắt, trong những trang phục rực rỡ sắc màu khiến tôi không thể rời mắt', chị Nguyễn Thùy Duyên (Hà Nội) bày tỏ cảm xúc sau khi xem show. Fairy Blossomđược kỳ vọng góp phần làm nên một mùa hè đáng nhớ cho du khách khi đến Sun World Ba Na Hills. Bên cạnh show Fairy Blossom, khu giải trí còn có chuỗi sân khấu Soloist tôn vinh các nghệ sĩ tài năng hay show Diễu hành Enchanment với sự tham gia của đoàn 40 nghệ sĩ nước ngoài. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{
+  "id": 28,
+  "style": "news_brief",
+  "article": "Fairy Blossomdiễn ra vào 11h hàng ngày tại quảng trường Noel Plaza, Sun World Ba Na Hills, sau các show diễn mùa hè từng ghi dấu ấn các năm trước nhưVũ hội Ánh DươnghayTrận chiến ở Vương quốc Mặt Trăng.Theo đơn vị sản xuất, đây sẽ là show diễn đầu tiên tại Việt Nam quy tụ nhiều loại hình nghệ thuật nhất, như xiếc, ảo thuật, đu bay, uốn dẻo, sway pole, diabolo, giữ thăng bằng trên dây, múa lụa trên không, parkour, tung hứng, vũ đạo... Show diễn có sự tham gia của Domitil Aillot - nam nghệ sĩ xiếc cột hàng đầu thế giới; cặp sao song sinh nổi tiếng của đoàn Cirque du Soleil - Crystal Ladies với đôi chân 'ma thuật'; cặp đôi nghệ sĩ hàng đầu nước Nga Oleg Izossimov, 'nàng tiên cá' múa lụa trên không Olga Moreva... Lấy cảm hứng từ vẻ đẹp của muôn loài hoa tại Bà Nà, với kết cấu chương hồi gồm 6 màn,Fairy Blossomkể về một xứ sở cổ tích với những loài sinh vật diệu kỳ sinh sôi nảy nở. Cốt truyện của show diễn lấy cảm hứng từ thần thoại Hy Lạp, khi Đất mẹ Gaia xuất hiện và ban phát sự sống, tạo ra một vườn địa đàng lộng lẫy, nơi các bông hoa khổng lồ và những loài vật vui vẻ cùng nhau chung sống. Show diễnđược tạo ra bởi trí tưởng tượng phong phú của 'phù thủy' xiếc Việt Tuấn Lê - nguyên thành viên của đoàn xiếc Cirque du Soleil.VớiFairy Blossom, khán giả sẽ được tận mắt thưởng thức chuỗi tiết mục kinh điển, những kỷ lục làm nên tên tuổi của các nghệ sĩ top 1 thế giới trong lĩnh vực xiếc và tạp kỹ. Đạo diễn Tuấn Lê chia sẻ, Fairy Blossom là sàn diễn đặc biệt, nơi nghệ thuật trình diễn được tôn vinh và thể hiện trọn vẹn những góc độ tinh tế cùng sự cuốn hút, dẫn dắt khán giả qua mọi cung bậc cảm xúc. 'Tại đây, tôi và Sun World Ba Na Hills đều có chung một giấc mơ: dùng nghệ thuật để tôn vinh văn hóa và ngược lại, dùng văn hóa làm chất dẫn để nghệ thuật thăng hoa', đạo diễn nói. Với show diễn độc đáo này, cặp song sinh Crystal Ladies nhận định sân khấu được thiết kế quy mô, rực rỡ. 'Fairy Blossomđộc đáo bởi được diễn ra tại sân khấu trình diễn trên độ cao gần 1.500 m, trong một không gian đầy sắc màu cổ tích và diệu kỳ', cặp đôi chia sẻ. Xem show, khán giả sẽ liên tục bất ngờ khi chứng kiến những màn nhào lộn từ độ cao hàng chục mét của các nghệ sĩ xiếc Việt và các màn trình diễn xiếc đẳng cấp thế giới của các ngôi sao quốc tế. Ngoài ra, tạo hình yêu kiều của những nàng tiên hoa cùng những điệu nhảy, màn đánh trống malambo... cũng khiến khán giả phấn khích. Tài nghệ của đạo diễn Tuấn Lê còn được ghi dấu ấn qua loạt tiểu tiết công phu, tạo nhiều trải nghiệm mới mẻ cho khán giả. Điểm nhấn của show diễn cũng nằm ở phần âm nhạc tươi vui, giàu sức biểu cảm, được tuyển chọn từ những bản giao hưởng nổi tiếng thế giới. 'Show có những phân cảnh xiếc quá nghẹt thở khiến tôi không thể tin vào mắt mình và chỉ biết hò reo, vỗ tay thán phục liên tục. Vũ đạo của show diễn cũng đẹp mắt, trong những trang phục rực rỡ sắc màu khiến tôi không thể rời mắt', chị Nguyễn Thùy Duyên (Hà Nội) bày tỏ cảm xúc sau khi xem show. Fairy Blossomđược kỳ vọng góp phần làm nên một mùa hè đáng nhớ cho du khách khi đến Sun World Ba Na Hills. Bên cạnh show Fairy Blossom, khu giải trí còn có chuỗi sân khấu Soloist tôn vinh các nghệ sĩ tài năng hay show Diễu hành Enchanment với sự tham gia của đoàn 40 nghệ sĩ nước ngoài. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết nhỏ như tên của đạo diễn show diễn",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính của show diễn nhưng có thể chưa đề cập đầy đủ đến các nghệ sĩ tham gia và các tiết mục cụ thể",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt dễ đọc và logic nhưng có thể còn một số từ ngữ và câu dài có thể được tinh gọn hơn"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SOL Skybar &amp; Lounge là một trong những điểm giải trí với tầm nhìn đẹp nhất thành phố Quy Nhơn. Ngoài vị trí trung tâm thuận lợi di chuyển, quán còn mang đến một không gian giải trí thú vị, tích hợp công nghệ trình chiếu, ánh sáng hiện đại cùng đa dạng trải nghiệm. Bước vào SOL Skybar &amp; Lounge, du khách sẽ được hòa vào không gian thiết kế hiện đại. Ánh đèn LED đa sắc màu kết hợp với âm nhạc sôi động tạo nên không khí náo nhiệt, giúp giải tỏa căng thẳng. Từ những bản nhạc EDM đến giai điệu pop ballad nhẹ nhàng, bất kể gu âm nhạc của bạn là gì, SOL Skybar &amp; Lounge đều có thể đáp ứng. Không gian rộng rãi cùng trang trí hiện đại cũng thích hợp tổ chức các sự kiện âm nhạc, giải trí, tiệc tùng hoặc họp mặt bạn bè, đồng nghiệp... Ngoài âm nhạc, không gian, SOL còn đầu tư thực đơn với các món ăn Âu - Á phong phú. Tất cả đều được chế biến bởi đội ngũ đầu bếp dày dặn kinh nghiệm. Kèm theo đó là bộ sưu tập rượu vang và cocktail, giúp gia tăng hương vị. SOL Skybar &amp; Lounge còn cung cấp trọn gói dịch vụ cho các sự kiện, tiệc lớn như đám cưới, tất niên công ty... Đội ngũ nhân viên chuyên nghiệp được đào tạo bài bản, đảm bảo chất lượng phục vụ. Vị trí thuận lợi nằm trên trục đường trung tâm Nguyễn Huệ, thuận tiện di chuyển. 'SOL Skybar &amp; Lounge là điểm đến lý tưởng cho ai tìm kiếm không gian giải trí cao cấp, hiện đại. Với sự kết hợp giữa âm nhạc, ẩm thực và tầm nhìn panorama, du khách sẽ có những khoảnh khắc thư giãn, tiệc tùng đáng nhớ', đại diện SOL chia sẻ. Á Hiên</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Đây là quán giải trí hiện đại SOL Skybar &amp; Lounge tại Nguyễn Huệ, Quy Nhơn với ánh đèn LED đa sắc màu và âm nhạc sôi động. Đội ngũ đầu bếp dày dặn kinh nghiệm cung cấp thực đơn Âu - Á phong phú cùng bộ sưu tập rượu vang và cocktail.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{
+  "id": 29,
+  "style": "news_brief",
+  "article": "SOL Skybar &amp; Lounge là một trong những điểm giải trí với tầm nhìn đẹp nhất thành phố Quy Nhơn. Ngoài vị trí trung tâm thuận lợi di chuyển, quán còn mang đến một không gian giải trí thú vị, tích hợp công nghệ trình chiếu, ánh sáng hiện đại cùng đa dạng trải nghiệm. Bước vào SOL Skybar &amp; Lounge, du khách sẽ được hòa vào không gian thiết kế hiện đại. Ánh đèn LED đa sắc màu kết hợp với âm nhạc sôi động tạo nên không khí náo nhiệt, giúp giải tỏa căng thẳng. Từ những bản nhạc EDM đến giai điệu pop ballad nhẹ nhàng, bất kể gu âm nhạc của bạn là gì, SOL Skybar &amp; Lounge đều có thể đáp ứng. Không gian rộng rãi cùng trang trí hiện đại cũng thích hợp tổ chức các sự kiện âm nhạc, giải trí, tiệc tùng hoặc họp mặt bạn bè, đồng nghiệp... Ngoài âm nhạc, không gian, SOL còn đầu tư thực đơn với các món ăn Âu - Á phong phú. Tất cả đều được chế biến bởi đội ngũ đầu bếp dày dặn kinh nghiệm. Kèm theo đó là bộ sưu tập rượu vang và cocktail, giúp gia tăng hương vị. SOL Skybar &amp; Lounge còn cung cấp trọn gói dịch vụ cho các sự kiện, tiệc lớn như đám cưới, tất niên công ty... Đội ngũ nhân viên chuyên nghiệp được đào tạo bài bản, đảm bảo chất lượng phục vụ. Vị trí thuận lợi nằm trên trục đường trung tâm Nguyễn Huệ, thuận tiện di chuyển. 'SOL Skybar &amp; Lounge là điểm đến lý tưởng cho ai tìm kiếm không gian giải trí cao cấp, hiện đại. Với sự kết hợp giữa âm nhạc, ẩm thực và tầm nhìn panorama, du khách sẽ có những khoảnh khắc thư giãn, tiệc tùng đáng nhớ', đại diện SOL chia sẻ. Á Hiên",
+  "summary": "Đây là quán giải trí hiện đại SOL Skybar &amp; Lounge tại Nguyễn Huệ, Quy Nhơn với ánh đèn LED đa sắc màu và âm nhạc sôi động. Đội ngũ đầu bếp dày dặn kinh nghiệm cung cấp thực đơn Âu - Á phong phú cùng bộ sưu tập rượu vang và cocktail.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như vị trí trung tâm thuận lợi di chuyển, không gian rộng rãi thích hợp tổ chức sự kiện và dịch vụ trọn gói cho các sự kiện lớn",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số điểm nổi bật như ánh đèn LED và âm nhạc sôi động, thực đơn phong phú nhưng bỏ qua các khía cạnh quan trọng khác như tầm nhìn đẹp, không gian thiết kế hiện đại và dịch vụ chuyên nghiệp",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và logic, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng và tránh bỏ qua các điểm nổi bật của SOL Skybar &amp; Lounge"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ngày 7/6, ông Khairul Firdaus Akbar Khan, Thứ trưởng Bộ Du lịch, Nghệ thuật và Văn hóa Malaysia cùng ông Manoharan Periasamy, Tổng giám đốc Cục Xúc tiến Du lịch Malaysia công bố khởi động chiến dịch, tại trung tâm thương mại Pavilion, Kuala Lumpur. Chương trình với sự tham gia của các trung tâm mua sắm và nhà bán lẻ hàng đầu Malaysia, mang đến chương trình giảm giá đến 85%. Sáng kiến này được thiết kế để thu hút du khách nội địa lẫn quốc tế, tăng giá trị kèm theo khi du lịch Malaysia. Đến Malaysia Mega Sale 2024, du khách được tận hưởng trải nghiệm mua sắm trọn vẹn và xứng đáng, phù hợp với thông điệp của chiến dịch mua sắm quốc gia 'MY Priceless Experience'(tạm dịch: Trải nghiệm mua sắm vô giá tại Malaysia). Chương trình này được kỳ vọng góp phần đáng kể vào doanh thu du lịch gần 553.000 tỷ trong năm nay. Chiến dịch mua sắm quốc gia Malaysia năm nay được tổ chức hai kỳ: Malaysia Mega Sale (15/6 – 31/7) và Year-End Sale (15/11 – 31/12). Trong năm 2025 và 2026, chiến dịch sẽ được tổ chức ba lần mỗi năm: Malaysia Super Sale (1–31/3), Malaysia Mega Sale (15/6 – 31/7), Year-End Sale (15/11 – 31/12). Bà Nor Hayati Zainuddin, Giám đốc Cục Xúc tiến Du lịch Malaysia tại Việt Nam mong muốn bổ sung tác động tích cực được Mega Sale mang đến. 'Mua sắm là một phần không thể thiếu trong trải nghiệm của du khách. Với các chương trình khuyến mãi độc nhất và hấp dẫn, Malaysia chắc chắn có thể nâng cao hình ảnh của một điểm đến mua sắm hàng đầu', bà Nor khẳng định. Với mục tiêu thu hút 470.000 du khách Việt Nam đến Malaysia trong năm 2024, Cục Xúc tiến Du lịch Malaysia tại Việt Nam kỳ vọng chiến dịch sẽ thu hút khách Việt đến mua sắm và khám phá nét văn hóa, hướng đến Năm Du lịch Malaysia 2026. Thanh Thư Trong khuôn khổ quảng bá chiến dịch Malaysia Mega Sale 2024 tại Việt Nam, Cục Xúc tiến Du lịch Malaysia hợp tác cùng hãng hàng không quốc gia Malaysia Airlines và ba đối tác Trip.com, Agoda.com, Traveloka.com, mang đến ưu đãi giảm giá khách sạn, vé máy bay từ Việt Nam đến các thành phố của Malaysia đến 30%.Thời gian đặt vé: 15/6 – 31/7Thời gian du lịch:15/6 – 31/3/2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{
+  "id": 30,
+  "style": "news_brief",
+  "article": "Ngày 7/6, ông Khairul Firdaus Akbar Khan, Thứ trưởng Bộ Du lịch, Nghệ thuật và Văn hóa Malaysia cùng ông Manoharan Periasamy, Tổng giám đốc Cục Xúc tiến Du lịch Malaysia công bố khởi động chiến dịch, tại trung tâm thương mại Pavilion, Kuala Lumpur. Chương trình với sự tham gia của các trung tâm mua sắm và nhà bán lẻ hàng đầu Malaysia, mang đến chương trình giảm giá đến 85%. Sáng kiến này được thiết kế để thu hút du khách nội địa lẫn quốc tế, tăng giá trị kèm theo khi du lịch Malaysia. Đến Malaysia Mega Sale 2024, du khách được tận hưởng trải nghiệm mua sắm trọn vẹn và xứng đáng, phù hợp với thông điệp của chiến dịch mua sắm quốc gia 'MY Priceless Experience'(tạm dịch: Trải nghiệm mua sắm vô giá tại Malaysia). Chương trình này được kỳ vọng góp phần đáng kể vào doanh thu du lịch gần 553.000 tỷ trong năm nay. Chiến dịch mua sắm quốc gia Malaysia năm nay được tổ chức hai kỳ: Malaysia Mega Sale (15/6 – 31/7) và Year-End Sale (15/11 – 31/12). Trong năm 2025 và 2026, chiến dịch sẽ được tổ chức ba lần mỗi năm: Malaysia Super Sale (1–31/3), Malaysia Mega Sale (15/6 – 31/7), Year-End Sale (15/11 – 31/12). Bà Nor Hayati Zainuddin, Giám đốc Cục Xúc tiến Du lịch Malaysia tại Việt Nam mong muốn bổ sung tác động tích cực được Mega Sale mang đến. 'Mua sắm là một phần không thể thiếu trong trải nghiệm của du khách. Với các chương trình khuyến mãi độc nhất và hấp dẫn, Malaysia chắc chắn có thể nâng cao hình ảnh của một điểm đến mua sắm hàng đầu', bà Nor khẳng định. Với mục tiêu thu hút 470.000 du khách Việt Nam đến Malaysia trong năm 2024, Cục Xúc tiến Du lịch Malaysia tại Việt Nam kỳ vọng chiến dịch sẽ thu hút khách Việt đến mua sắm và khám phá nét văn hóa, hướng đến Năm Du lịch Malaysia 2026. Thanh Thư Trong khuôn khổ quảng bá chiến dịch Malaysia Mega Sale 2024 tại Việt Nam, Cục Xúc tiến Du lịch Malaysia hợp tác cùng hãng hàng không quốc gia Malaysia Airlines và ba đối tác Trip.com, Agoda.com, Traveloka.com, mang đến ưu đãi giảm giá khách sạn, vé máy bay từ Việt Nam đến các thành phố của Malaysia đến 30%.Thời gian đặt vé: 15/6 – 31/7Thời gian du lịch:15/6 – 31/3/2025",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết quan trọng như thời gian diễn ra chiến dịch và mức giảm giá cụ thể",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính như mục tiêu thu hút du khách, chương trình giảm giá và thời gian diễn ra chiến dịch, tuy nhiên có thể cần thêm thông tin về tác động của chiến dịch đến nền kinh tế địa phương",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt còn một số từ ngữ và câu dài, cần cải thiện về mặt mạch lạc và dễ đọc để người đọc dễ dàng hiểu được nội dung chính"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ngày 31/5, tay vợt huyền thoại người Thụy Sĩ Roger Federer đăng tải trên trang Instagram hình ảnh chuyến du lịch qua các nước châu Á từ đầu năm, trong đó có chuyến nghỉ dưỡng tại Việt Nam cuối tháng 4. Anh viết trên trang cá nhân 'châu Á thật ngoạn mục' và mong chờ những chuyến đi sắp tới. Trong bộ ảnh đăng tải, Roger khoe hình bơi ở một bãi biển nhiệt đới, check in cảng Victoria ở Hong Kong, chụp hình cầu Vàng ở Đà Nẵng và sông Thu Bồn ở Hội An về đêm. Khi đến Đà Nẵng hồi cuối tháng 4, huyền thoại quần vợt sinh năm 1981 đã nghỉ ở một resort ở thị xã Điện Bàn, cách trung tâm phố cổ Hội An khoảng 6 km. Anh được nhiều người hâm mộ bắt gặp và chụp ảnh giao lưu cùng. Một doanh nhân ở Hà Nội, người tặng Federer một bức tranh, cho biết tay vợt lịch sự và thân thiện. Trên trang cá nhân, nhiều người hâm mộ bày tỏ sự ngưỡng mộ với cuộc sống tận hưởng tự do của Federer sau khi giải nghệ và mong chờ những chuyến đi kế tiếp của anh. Roger Federer là một trong những tay vợt vĩ đại nhất lịch sử làng quần vợt khi giành tổng cộng 20 danh hiệu Grand Slam trong sự nghiệp trước khi giải nghệ vào tháng 9/2022. Trước tay vợt, Hội An và Đà Nẵng cũng đón một số người nổi tiếng đến du lịch. Tháng 3, tỷ phúBill Gatesvà bạn gái đến Đà Nẵng nghỉ dưỡng 4 ngày tại một khu nghỉ cao cấp trên bán đảo Sơn Trà. Tháng 4, nam diễn viên Hàn,Jung Il Woo, có chuyến du lịch hơn 10 ngày đến nhiều địa phương Việt Nam. Tại Hội An, anh check in ngồi thuyền thúng và khoe mua đặc sản tại Cù Lao Chàm. Bích Phương</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Roger Federer khoe bãi biển Hong Kong, cầu Vàng Đà Nẵng và Hội An về đêm sau chuyến châu Á từ đầu năm; người hâm mộ ngưỡng mộ cuộc sống tự do của anh sau khi giải nghệ.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{
+  "id": 31,
+  "style": "news_brief",
+  "article": "Ngày 31/5, tay vợt huyền thoại người Thụy Sĩ Roger Federer đăng tải trên trang Instagram hình ảnh chuyến du lịch qua các nước châu Á từ đầu năm, trong đó có chuyến nghỉ dưỡng tại Việt Nam cuối tháng 4. Anh viết trên trang cá nhân 'châu Á thật ngoạn mục' và mong chờ những chuyến đi sắp tới. Trong bộ ảnh đăng tải, Roger khoe hình bơi ở một bãi biển nhiệt đới, check in cảng Victoria ở Hong Kong, chụp hình cầu Vàng ở Đà Nẵng và sông Thu Bồn ở Hội An về đêm. Khi đến Đà Nẵng hồi cuối tháng 4, huyền thoại quần vợt sinh năm 1981 đã nghỉ ở một resort ở thị xã Điện Bàn, cách trung tâm phố cổ Hội An khoảng 6 km. Anh được nhiều người hâm mộ bắt gặp và chụp ảnh giao lưu cùng. Một doanh nhân ở Hà Nội, người tặng Federer một bức tranh, cho biết tay vợt lịch sự và thân thiện. Trên trang cá nhân, nhiều người hâm mộ bày tỏ sự ngưỡng mộ với cuộc sống tận hưởng tự do của Federer sau khi giải nghệ và mong chờ những chuyến đi kế tiếp của anh. Roger Federer là một trong những tay vợt vĩ đại nhất lịch sử làng quần vợt khi giành tổng cộng 20 danh hiệu Grand Slam trong sự nghiệp trước khi giải nghệ vào tháng 9/2022. Trước tay vợt, Hội An và Đà Nẵng cũng đón một số người nổi tiếng đến du lịch. Tháng 3, tỷ phúBill Gatesvà bạn gái đến Đà Nẵng nghỉ dưỡng 4 ngày tại một khu nghỉ cao cấp trên bán đảo Sơn Trà. Tháng 4, nam diễn viên Hàn,Jung Il Woo, có chuyến du lịch hơn 10 ngày đến nhiều địa phương Việt Nam. Tại Hội An, anh check in ngồi thuyền thúng và khoe mua đặc sản tại Cù Lao Chàm. Bích Phương",
+  "summary": "Roger Federer khoe bãi biển Hong Kong, cầu Vàng Đà Nẵng và Hội An về đêm sau chuyến châu Á từ đầu năm; người hâm mộ ngưỡng mộ cuộc sống tự do của anh sau khi giải nghệ.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng lại bỏ qua một số chi tiết quan trọng như việc Roger Federer nghỉ dưỡng tại một resort ở thị xã Điện Bàn và được người hâm mộ bắt gặp, cũng như không nhắc đến việc anh là một trong những tay vợt vĩ đại nhất lịch sử",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số điểm nổi bật của chuyến du lịch châu Á của Roger Federer nhưng bỏ qua một số thông tin quan trọng khác như việc anh nghỉ dưỡng tại Việt Nam và tương tác với người hâm mộ",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách ngắn gọn, súc tích và dễ đọc, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng để làm cho tóm tắt trở nên đầy đủ hơn"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Năm nay, lễ vía Bà Linh Sơn Thánh Mẫu được tổ chức tại hệ thống các chùa núi Bà với các nghi lễ truyền thống, cùng chương trình cải lương tuồng cổ đặc sắc vào ngày 10/6. Đặc biệt, trên đỉnh núi Bà Đen, đại lễ dâng đăng với kỷ lục 55.000 ngọn đăng mừng lễ sẽ được tổ chức tại quảng trường dưới chân tượng Phật Bà Tây Bổ Đà Sơn và khu vực tôn tượng Bồ Tát Di Lặc vào tối 8/6 (tức 3/5 Âm lịch). 55.000 ngọn đèn hoa đăng này do các nhân viên của khu du lịch Sun World Ba Den Mountain chế tạo. Du khách, phật tử có thể tự tay viết lời nguyện ước lên hoa đăng, được thắp sáng bên các đĩa nước dưới chân tượng Phật Bà Tây Bổ Đà Sơn, tạo nên không gian huyền ảo trên đỉnh núi. Trong văn hóa Phật giáo, hoa đăng tượng trưng cho ánh sáng trí tuệ của Đức Phật. Thả đèn hoa đăng là mong muốn của nhân dân tìm kiếm an lạc trước ánh sáng trí tuệ. Do đó, đại lễ dâng đăng mừng ngày lễ vía Bà là hàng vạn lời nguyện ước bình an, hạnh phúc của nhân dân dâng lên chư Phật và Linh Sơn Thánh Mẫu Bồ Tát - đại diện của lòng từ bi, cứu độ chúng sinh. Được công nhận là Di sản Văn hóa Phi vật thể Quốc gia, lễ vía Bà Linh Sơn Thánh Mẫu hàng năm thu hút hàng nghìn người ở khắp nơi đến núi Bà Đen. Tại đây gồm các nghi lễ truyền thống như tụng kinh niệm Phật, cúng ngọ, lễ cáo yết Bà Đen, múa bóng rỗi, lễ dâng 10 loại lễ vật: hoa, đèn, nhang, trà, quả, thực, bỉnh, thủy xoàn, châu báu... Các nghi lễ chính được tổ chức tại Linh Sơn Tiên Thạch Tự và Điện Bà nằm ở lưng chừng núi Bà Đen. Nghi lễ đặc trưng và thiêng liêng nhất là lễ tắm Bà diễn ra vào đêm mùng 4/5 (Âm lịch), khi cửa cung cấm đóng kín và chỉ có những người phụ nữ được phân công từ trước thực hiện nghi lễ. Sau lễ tắm Bà, hàng nghìn người dân đến trước Điện Bà để xin lộc là những chiếc khăn đã dùng lau tượng Bà, nước đã dùng nhúng khăn lau tượng hay hoa quả trong lễ tắm. Trong đời sống tín ngưỡng dân gian của người Nam Bộ, Linh Sơn Thánh Mẫu được xem là vị thần bảo hộ cho cả một vùng đất, được thờ trong các chùa ở Tây Ninh với vai trò một vị hộ trì Tam bảo. Với người dân phía Nam, lễ vía Bà năm nay không chỉ là dịp tỏ lòng tôn kính với Linh Sơn Thánh Mẫu, còn là cơ hội để hành hương, chiêm bái ngọn núi linh thiêng. Trong đó, có các công trình tâm linh trên đỉnh núi như tượng Phật Bà Tây Bổ Đà Sơn cao nhất châu Á, tôn tượng Bồ Tát Di Lặc bằng đá sa thạch, trung tâm triển lãm Phật giáo lưu trữ các cổ vật và phiên bản mô phỏng nhiều tác phẩm văn hóa Phật giáo kinh điển của Việt Nam cũng như thế giới. Kéo dài trong suốt những ngày đầu tháng 5 Âm lịch, lễ vía Bà Linh Sơn Thánh Mẫu dự kiến đón hàng nghìn Phật tử và du khách đến chiêm bái, đảnh lễ. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>{
+  "id": 32,
+  "style": "news_brief",
+  "article": "Năm nay, lễ vía Bà Linh Sơn Thánh Mẫu được tổ chức tại hệ thống các chùa núi Bà với các nghi lễ truyền thống, cùng chương trình cải lương tuồng cổ đặc sắc vào ngày 10/6. Đặc biệt, trên đỉnh núi Bà Đen, đại lễ dâng đăng với kỷ lục 55.000 ngọn đăng mừng lễ sẽ được tổ chức tại quảng trường dưới chân tượng Phật Bà Tây Bổ Đà Sơn và khu vực tôn tượng Bồ Tát Di Lặc vào tối 8/6 (tức 3/5 Âm lịch). 55.000 ngọn đèn hoa đăng này do các nhân viên của khu du lịch Sun World Ba Den Mountain chế tạo. Du khách, phật tử có thể tự tay viết lời nguyện ước lên hoa đăng, được thắp sáng bên các đĩa nước dưới chân tượng Phật Bà Tây Bổ Đà Sơn, tạo nên không gian huyền ảo trên đỉnh núi. Trong văn hóa Phật giáo, hoa đăng tượng trưng cho ánh sáng trí tuệ của Đức Phật. Thả đèn hoa đăng là mong muốn của nhân dân tìm kiếm an lạc trước ánh sáng trí tuệ. Do đó, đại lễ dâng đăng mừng ngày lễ vía Bà là hàng vạn lời nguyện ước bình an, hạnh phúc của nhân dân dâng lên chư Phật và Linh Sơn Thánh Mẫu Bồ Tát - đại diện của lòng từ bi, cứu độ chúng sinh. Được công nhận là Di sản Văn hóa Phi vật thể Quốc gia, lễ vía Bà Linh Sơn Thánh Mẫu hàng năm thu hút hàng nghìn người ở khắp nơi đến núi Bà Đen. Tại đây gồm các nghi lễ truyền thống như tụng kinh niệm Phật, cúng ngọ, lễ cáo yết Bà Đen, múa bóng rỗi, lễ dâng 10 loại lễ vật: hoa, đèn, nhang, trà, quả, thực, bỉnh, thủy xoàn, châu báu... Các nghi lễ chính được tổ chức tại Linh Sơn Tiên Thạch Tự và Điện Bà nằm ở lưng chừng núi Bà Đen. Nghi lễ đặc trưng và thiêng liêng nhất là lễ tắm Bà diễn ra vào đêm mùng 4/5 (Âm lịch), khi cửa cung cấm đóng kín và chỉ có những người phụ nữ được phân công từ trước thực hiện nghi lễ. Sau lễ tắm Bà, hàng nghìn người dân đến trước Điện Bà để xin lộc là những chiếc khăn đã dùng lau tượng Bà, nước đã dùng nhúng khăn lau tượng hay hoa quả trong lễ tắm. Trong đời sống tín ngưỡng dân gian của người Nam Bộ, Linh Sơn Thánh Mẫu được xem là vị thần bảo hộ cho cả một vùng đất, được thờ trong các chùa ở Tây Ninh với vai trò một vị hộ trì Tam bảo. Với người dân phía Nam, lễ vía Bà năm nay không chỉ là dịp tỏ lòng tôn kính với Linh Sơn Thánh Mẫu, còn là cơ hội để hành hương, chiêm bái ngọn núi linh thiêng. Trong đó, có các công trình tâm linh trên đỉnh núi như tượng Phật Bà Tây Bổ Đà Sơn cao nhất châu Á, tôn tượng Bồ Tát Di Lặc bằng đá sa thạch, trung tâm triển lãm Phật giáo lưu trữ các cổ vật và phiên bản mô phỏng nhiều tác phẩm văn hóa Phật giáo kinh điển của Việt Nam cũng như thế giới. Kéo dài trong suốt những ngày đầu tháng 5 Âm lịch, lễ vía Bà Linh Sơn Thánh Mẫu dự kiến đón hàng nghìn Phật tử và du khách đến chiêm bái, đảnh lễ. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết nhỏ, tuy nhiên vẫn giữ được ý nghĩa và nội dung chính của văn bản gốc.",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính của văn bản gốc, bao gồm cả lễ vía Bà Linh Sơn Thánh Mẫu, đại lễ dâng đăng và các nghi lễ truyền thống, tuy nhiên có thể thiếu một số chi tiết phụ.",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt có thể còn một số đoạn văn không liên kết chặt chẽ, và có thể có một số từ ngữ hoặc cụm từ không cần thiết, làm giảm sự rõ ràng và mạch lạc của văn bản."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Pan-American là cao tốc dài nhất hành tinh (thích hợp cho xe cơ giới sử dụng) với hơn 24.000 km, xuyên qua 14 quốc gia, theo kỷ lục Guinness. Đường bắt đầu từ Alaska, Mỹ đến Santiago, Chile rồi đi về phía đông đến Buenos Aires, Argentina và kết thúc ở Brasilia, Brazil. 14 quốc gia tuyến đường này chạy qua gồm Mỹ, Canada, Mexico, Guatemala, El Salvador, Honduras, Nicaragua, Costa Rica, Panama, Colombia, Ecuador, Peru, Chile và Argentina. Tuy nhiên Pan-America có một đoạn bị ngắt quãng từ Panama đến Colombia do đi qua rừng nhiệt đới Darien Gap dài 100 km với địa hình hiểm trở, toàn núi và đầm lầy. Hầu hết mọi người đều vượt qua đoạn đường này bằng cách lên phà từ Panama đến Colombia hoặc Ecuador. Có rất ít người được công nhận đã đi bộ xuyên Pan-America, gồm đi qua cả Darién Gap. Người đầu tiên hoàn thành chuyến đi là cựu thủy thủ người Anh, George Meegan, khởi hành từ năm 1977 và mất hơn 2.400 ngày để hoàn thành hành trình này. Gần 40 năm sau, cựu lính Mỹ Holly Harrison đã thực hiện chuyến đi tương tự, hoàn thành lộ trình ngắn hơn, khoảng 23.000 km trong 530 ngày. Emmanuel Gentinetta, 18 tuổi người Mỹ, đã được kỷ lục Guinness công nhận là 'Người trẻ nhất đi xe đạp xuyên Pan-America'. Genitnetta bắt đầu từ vịnh Prudhoe, bang Alaska, Mỹ ngày 23/6/1999 và kết thúc tại Hahia Lapataia, quần đảo Tierra del Fuego, Argentina ngày 9/3/2000. Hành trình kéo dài 261 ngày với quãng đường dài hơn 24.500 km. Tuy nhiên, không nhiều người đồng tình với ý tưởng đi xuyên Darién Gap vì mức độ nguy hiểm của nó. Nếu dùng phà để di chuyển lại không phù hợp với tên gọi cao tốc xuyên Mỹ (chỉ đi trên mặt đất, không di chuyển bằng đường thủy). Do đó, một người dùng trên diễn đàn Reddit nổi tiếng của Mỹ đã tìm ra con đường khác thay thế Pan-America và an toàn hơn. Con đường bắt đầu từ Cape Town, Nam Phi và kết thúc ở Magadan, Nga với tổng chiều dài hơn 22.000 km, mất gần 4.500 giờ di chuyển, tương đương 187 ngày đi bộ không ngừng nghỉ hoặc 561 ngày nếu mỗi ngày di chuyển 8 tiếng. Bạn sẽ đi qua 17 quốc gia, 6 múi giờ và các mùa trong năm khi hoàn thành cung đường này. Còn nếu muốn đi bộ thẳng một đường, hãy suy nghĩ đến con đường do hai kỹ sư Rohan Chabukswar và Kushal Mukherjee người Ấn Độ đã nghiên cứu và tìm ra năm 2018. Đây là con đường thẳng (đường chim bay) dài nhất thế giới với điểm bắt đầu ở Trung Quốc và kết thúc ở Bồ Đào Nha. Con đường thẳng này sẽ xuyên qua các ngọn núi, mọi địa hình, dài 11.240 km, không băng qua bất kỳ vùng nước nào. Hành trình gồm Trung Quốc, Mông Cổ, Kazakhstan, Nga, Belarus, Ukraine, Ba Lan, Cộng hòa Czech, Đức, Áo, Liechtenstein, Thụy Sĩ, Pháp và Tây Ban Nha trước khi kết thúc ở Sagres, Bồ Đào Nha. Tuy nhiên, tuyến đường này được đánh giá 'bất khả thi' vì quá nguy hiểm. Anh Minh(TheoGuinness World Records, NZ Hearald)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>{
+  "id": 33,
+  "style": "news_brief",
+  "article": "Pan-American là cao tốc dài nhất hành tinh (thích hợp cho xe cơ giới sử dụng) với hơn 24.000 km, xuyên qua 14 quốc gia, theo kỷ lục Guinness. Đường bắt đầu từ Alaska, Mỹ đến Santiago, Chile rồi đi về phía đông đến Buenos Aires, Argentina và kết thúc ở Brasilia, Brazil. 14 quốc gia tuyến đường này chạy qua gồm Mỹ, Canada, Mexico, Guatemala, El Salvador, Honduras, Nicaragua, Costa Rica, Panama, Colombia, Ecuador, Peru, Chile và Argentina. Tuy nhiên Pan-America có một đoạn bị ngắt quãng từ Panama đến Colombia do đi qua rừng nhiệt đới Darien Gap dài 100 km với địa hình hiểm trở, toàn núi và đầm lầy. Hầu hết mọi người đều vượt qua đoạn đường này bằng cách lên phà từ Panama đến Colombia hoặc Ecuador. Có rất ít người được công nhận đã đi bộ xuyên Pan-America, gồm đi qua cả Darién Gap. Người đầu tiên hoàn thành chuyến đi là cựu thủy thủ người Anh, George Meegan, khởi hành từ năm 1977 và mất hơn 2.400 ngày để hoàn thành hành trình này. Gần 40 năm sau, cựu lính Mỹ Holly Harrison đã thực hiện chuyến đi tương tự, hoàn thành lộ trình ngắn hơn, khoảng 23.000 km trong 530 ngày. Emmanuel Gentinetta, 18 tuổi người Mỹ, đã được kỷ lục Guinness công nhận là 'Người trẻ nhất đi xe đạp xuyên Pan-America'. Genitnetta bắt đầu từ vịnh Prudhoe, bang Alaska, Mỹ ngày 23/6/1999 và kết thúc tại Hahia Lapataia, quần đảo Tierra del Fuego, Argentina ngày 9/3/2000. Hành trình kéo dài 261 ngày với quãng đường dài hơn 24.500 km. Tuy nhiên, không nhiều người đồng tình với ý tưởng đi xuyên Darién Gap vì mức độ nguy hiểm của nó. Nếu dùng phà để di chuyển lại không phù hợp với tên gọi cao tốc xuyên Mỹ (chỉ đi trên mặt đất, không di chuyển bằng đường thủy). Do đó, một người dùng trên diễn đàn Reddit nổi tiếng của Mỹ đã tìm ra con đường khác thay thế Pan-America và an toàn hơn. Con đường bắt đầu từ Cape Town, Nam Phi và kết thúc ở Magadan, Nga với tổng chiều dài hơn 22.000 km, mất gần 4.500 giờ di chuyển, tương đương 187 ngày đi bộ không ngừng nghỉ hoặc 561 ngày nếu mỗi ngày di chuyển 8 tiếng. Bạn sẽ đi qua 17 quốc gia, 6 múi giờ và các mùa trong năm khi hoàn thành cung đường này. Còn nếu muốn đi bộ thẳng một đường, hãy suy nghĩ đến con đường do hai kỹ sư Rohan Chabukswar và Kushal Mukherjee người Ấn Độ đã nghiên cứu và tìm ra năm 2018. Đây là con đường thẳng (đường chim bay) dài nhất thế giới với điểm bắt đầu ở Trung Quốc và kết thúc ở Bồ Đào Nha. Con đường thẳng này sẽ xuyên qua các ngọn núi, mọi địa hình, dài 11.240 km, không băng qua bất kỳ vùng nước nào. Hành trình gồm Trung Quốc, Mông Cổ, Kazakhstan, Nga, Belarus, Ukraine, Ba Lan, Cộng hòa Czech, Đức, Áo, Liechtenstein, Thụy Sĩ, Pháp và Tây Ban Nha trước khi kết thúc ở Sagres, Bồ Đào Nha. Tuy nhiên, tuyến đường này được đánh giá 'bất khả thi' vì quá nguy hiểm. Anh Minh(TheoGuinness World Records, NZ Hearald)",
+  "summary": "",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết nhỏ như số ngày cụ thể để hoàn thành hành trình của một số cá nhân, tuy nhiên điều này không làm thay đổi ý nghĩa tổng thể của văn bản gốc",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính như chiều dài của Pan-American, các quốc gia nó đi qua, và những người đã hoàn thành hành trình này, nhưng có thể bỏ qua một số chi tiết về các tuyến đường thay thế",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt có thể hơi dài dòng và không nhất quán trong việc trình bày thông tin, một số đoạn có thể được rút ngắn hoặc trình bày một cách rõ ràng hơn để tăng tính mạch lạc và dễ đọc"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Theo thỏa thuận hợp tác ký ngày 25/5, hai bên sẽ tổ chức nhiều hoạt động nhằm góp phần lan tỏa về văn hóa, du lịch. Cụ thể, Tổng cục Du lịch Hàn Quốc hỗ trợ giới thiệu thương hiệu Vinhomes, VinFast, Vinpearl, Vincom... đến cộng đồng người Hàn tại Việt Nam và người dân tại Hàn Quốc trong tương lai. Ngược lại, Vingroup cùng Tổng cục Du lịch Hàn Quốc thúc đẩy, phát triển mảng khách du lịch khen thưởng tham quan du lịch tại nước này. Trong đó, lễ hội Korea Travel Festa và sự kiện Summer K-Day diễn ra ngày 25-26/5 tại K-Town, công viên VinWonders Wave Park, khu đô thị Vinhomes Ocean Park 2. Đây là sự kiện khởi đầu chuỗi hoạt động hợp tác giữa hai bên trong năm 2024. Korea Travel Festa tập trung vào biểu diễn nghệ thuật Kpop và Vpop, quảng bá sản phẩm dịch vụ - du lịch dành cho cộng đồng Hàn Quốc, người hâm mộ làn sóng Hallyu. Còn Summer K-Day sẽ đưa ra các hoạt động vui chơi trải nghiệm chuẩn Hàn. Chuỗi hoạt động văn hóa sẽ tiếp tục được Tổng cục Du lịch Hàn Quốc và Vingroup phối hợp nhân rộng trên toàn quốc thời gian tới. Phát biểu tại sự kiện, ông Lee Hak Ju, Phó tổng cục trưởng Tổng cục Du lịch Hàn Quốc, cho biết hai quốc gia đã thiết lập quan hệ ngoại giao vào năm 1992, đạt được thành quả hợp tác trên nhiều lĩnh vực. Giao lưu nhân dân diễn ra rất sôi động, số lượng du khách giữa hai nước vượt mức bốn triệu lượt chỉ riêng trong năm 2023. Thông qua thỏa thuận hợp tác với Vingroup, hai bên có mục tiêu chung về mở rộng giao lưu và thúc đẩy hơn nữa hợp tác du lịch, trao đổi văn hóa. Ông Nguyễn Việt Quang, Phó Chủ tịch Hội đồng Quản trị kiêm Tổng giám đốc Tập đoàn Vingroup cho biết sẽ triển khai đồng loạt sự kiện văn hóa, hoạt động trải nghiệm và loạt dịch vụ, hướng tới khách hàng, cư dân Hàn Quốc đồng thời kiện toàn sản phẩm, phục vụ tốt hơn cho cộng đồng. Theo đại diện Vinhomes, dấu ấn Hàn Quốc đã tồn tại, thể hiện khá rõ nét tại một số khu đô thị Vinhomes từ khi đi vào hoạt động. Những địa điểm này thường xuyên thu hút người Hàn tại Việt Nam hoặc người Việt yêu thích văn hóa Hàn Quốc. Ví dụ 'phố Hàn' K-Town tại Vinhomes Ocean Park 2, công viên văn hóa K-Park tại Vinhomes Royal Island, trường học quốc tế KGS tại Vinhomes Ocean Park 1, Vinhomes Grand Park... Vingroup và các thương hiệu cùng hệ sinh thái thường xuyên tổ chức nhiều hoạt động giải trí, nghệ thuật, ẩm thực mang đậm phong vị 'xứ sở kim chi', thu hút hàng chục nghìn khách tham dự như như lễ hội K-Day in K-Town, K-Food Fair, K-Festival in Grand Park... Văn Hà</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hàn Quốc hỗ trợ giới thiệu thương hiệu Vinhomes, VinFast... đến người Hàn tại Việt Nam và ngược lại thông qua lễ hội Korea Travel Festa và Summer K-Day. Vingroup tổ chức nhiều hoạt động giải trí, nghệ thuật, ẩm thực thu hút hàng chục nghìn khách tham dự tại các địa điểm như Grand Park và K-Town.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>{
+  "id": 34,
+  "style": "news_brief",
+  "article": "Theo thỏa thuận hợp tác ký ngày 25/5, hai bên sẽ tổ chức nhiều hoạt động nhằm góp phần lan tỏa về văn hóa, du lịch. Cụ thể, Tổng cục Du lịch Hàn Quốc hỗ trợ giới thiệu thương hiệu Vinhomes, VinFast, Vinpearl, Vincom... đến cộng đồng người Hàn tại Việt Nam và người dân tại Hàn Quốc trong tương lai. Ngược lại, Vingroup cùng Tổng cục Du lịch Hàn Quốc thúc đẩy, phát triển mảng khách du lịch khen thưởng tham quan du lịch tại nước này. Trong đó, lễ hội Korea Travel Festa và sự kiện Summer K-Day diễn ra ngày 25-26/5 tại K-Town, công viên VinWonders Wave Park, khu đô thị Vinhomes Ocean Park 2. Đây là sự kiện khởi đầu chuỗi hoạt động hợp tác giữa hai bên trong năm 2024. Korea Travel Festa tập trung vào biểu diễn nghệ thuật Kpop và Vpop, quảng bá sản phẩm dịch vụ - du lịch dành cho cộng đồng Hàn Quốc, người hâm mộ làn sóng Hallyu. Còn Summer K-Day sẽ đưa ra các hoạt động vui chơi trải nghiệm chuẩn Hàn. Chuỗi hoạt động văn hóa sẽ tiếp tục được Tổng cục Du lịch Hàn Quốc và Vingroup phối hợp nhân rộng trên toàn quốc thời gian tới. Phát biểu tại sự kiện, ông Lee Hak Ju, Phó tổng cục trưởng Tổng cục Du lịch Hàn Quốc, cho biết hai quốc gia đã thiết lập quan hệ ngoại giao vào năm 1992, đạt được thành quả hợp tác trên nhiều lĩnh vực. Giao lưu nhân dân diễn ra rất sôi động, số lượng du khách giữa hai nước vượt mức bốn triệu lượt chỉ riêng trong năm 2023. Thông qua thỏa thuận hợp tác với Vingroup, hai bên có mục tiêu chung về mở rộng giao lưu và thúc đẩy hơn nữa hợp tác du lịch, trao đổi văn hóa. Ông Nguyễn Việt Quang, Phó Chủ tịch Hội đồng Quản trị kiêm Tổng giám đốc Tập đoàn Vingroup cho biết sẽ triển khai đồng loạt sự kiện văn hóa, hoạt động trải nghiệm và loạt dịch vụ, hướng tới khách hàng, cư dân Hàn Quốc đồng thời kiện toàn sản phẩm, phục vụ tốt hơn cho cộng đồng. Theo đại diện Vinhomes, dấu ấn Hàn Quốc đã tồn tại, thể hiện khá rõ nét tại một số khu đô thị Vinhomes từ khi đi vào hoạt động. Những địa điểm này thường xuyên thu hút người Hàn tại Việt Nam hoặc người Việt yêu thích văn hóa Hàn Quốc. Ví dụ 'phố Hàn' K-Town tại Vinhomes Ocean Park 2, công viên văn hóa K-Park tại Vinhomes Royal Island, trường học quốc tế KGS tại Vinhomes Ocean Park 1, Vinhomes Grand Park... Vingroup và các thương hiệu cùng hệ sinh thái thường xuyên tổ chức nhiều hoạt động giải trí, nghệ thuật, ẩm thực mang đậm phong vị 'xứ sở kim chi', thu hút hàng chục nghìn khách tham dự như như lễ hội K-Day in K-Town, K-Food Fair, K-Festival in Grand Park... Văn Hà",
+  "summary": "Hàn Quốc hỗ trợ giới thiệu thương hiệu Vinhomes, VinFast... đến người Hàn tại Việt Nam và ngược lại thông qua lễ hội Korea Travel Festa và Summer K-Day. Vingroup tổ chức nhiều hoạt động giải trí, nghệ thuật, ẩm thực thu hút hàng chục nghìn khách tham dự tại các địa điểm như Grand Park và K-Town.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như mục tiêu hợp tác giữa hai bên và ý nghĩa của các sự kiện Korea Travel Festa và Summer K-Day.",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số hoạt động và sự kiện cụ thể mà không bao quát được toàn bộ nội dung của văn bản gốc, đặc biệt là về quan hệ hợp tác giữa Vingroup và Tổng cục Du lịch Hàn Quốc.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể cô đọng hơn bằng cách loại bỏ một số từ ngữ không cần thiết và tập trung vào thông tin chính."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tiếp nối thành công của chương 1 được triển khai cuối tháng 4 vừa qua, chương 2 của chuỗi sự kiện 'Pause + Savour' đưa thực khách về hành trình khởi nguồn nguyên bản, lấy cảm hứng từ: đất, nước, lửa và khí. Tại đây, bếp trưởng Phi Công sẽ mời bếp trưởng Sĩ Toàn trở lại, kết hợp cùng anh cho một trải nghiệm mới. Theo đó, hai người sẽ sáng tạo thực đơn sáu món: bánh tart cá ngừ đất sét Cao Lanh (đất), hàu xốt ớt xanh nitơ lỏng (nước), bồ câu xông khói gỗ cherry và bánh mỳ bơ tôm hùm (khí), tôm hùm xốt ớt (lửa), bò Wagyu (lửa), bánh mousse trà bá tước (đất). 'Việt Nam sở hữu khí hậu nhiệt đới cùng thổ nhưỡng giàu dưỡng chất, ẩm thực luôn có giá trị đa tầng về dinh dưỡng, đa dạng về hương vị, cùng những cảm giác tươi ngon đặc biệt. Do đó, tôi dễ dàng tìm kiếm và nghiên cứu được những nguyên liệu mới mẻ, hương vị khác nhau của mỗi vùng miền', bếp trưởng Phi Công chia sẻ. Bên cạnh việc lấy cảm hứng từ nguyên liệu địa phương, tôn vinh tài năng Việt, chuỗi sự kiện 'Pause + Savour' còn hướng đến tạo ra những kỷ niệm vui và khoảnh khắc tận hưởng cuộc sống trọn vẹn. Song hành cùng bếp trưởng Sĩ Toàn và bếp trưởng Phi Công là Head Sommelier Huyền Hà - người giám tuyển thực đơn rượu vang kết hợp từng nguyên liệu món ăn, nhằm nâng tầm vị giác của thực khách. Giá Wine Pairing là 800.000 đồng mỗi thực khách. Ngoài ra, Barson còn có Cocktails Pairing cũng 800.000 đồng hoặc Mocktails Pairing (không cồn) với giá 450.000 đồng. Số lượng chỗ ngồi được giới hạn tại Barson trong ba đêm tiệc, từ 23 đến 25/5. Thực khách có thể đặt bàn ngay để hưởng ưu đãi Early Bird của chương trình lên đến 15%, hoặc nhận các ưu đãi khi là thành viên của Marriott Bonvoy (10%) hay chủ thẻ VPBank (lên đến 20%). Chuỗi sự kiện ẩm thực bàn tiệc của bếp trưởng 'Pause + Savour' được Le Méridien Saigon khởi động từ cuối tháng 4, với bếp trưởng khách mời đầu tiên đến từ khách sạn Le Méridien Myeongdong Seoul (Hàn Quốc). Bếp trưởng người Hàn này mang đến nhiều hoạt động ấn tượng cho thực khách, khi tạo ra hành trình ẩm thực kết nối văn hóa và hương vị đa quốc gia, đánh thức các giác quan với những nguyên liệu và kỹ thuật chế biến độc đáo. Thanh Thư Le Méridien SaigonĐịa chỉ: 3C Tôn Đức Thắng, quận 1, TP HCMEmail: Lemeridien.Saigon@lemeridien.comĐiện thoại: 028 6263 6688Website:www.lemeridiensaigon.comFanpage:www.facebook.com/LeMeridienSaigonFanpage Barson:www.facebook.com/Barson.sgn</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>{
+  "id": 35,
+  "style": "news_brief",
+  "article": "Tiếp nối thành công của chương 1 được triển khai cuối tháng 4 vừa qua, chương 2 của chuỗi sự kiện 'Pause + Savour' đưa thực khách về hành trình khởi nguồn nguyên bản, lấy cảm hứng từ: đất, nước, lửa và khí. Tại đây, bếp trưởng Phi Công sẽ mời bếp trưởng Sĩ Toàn trở lại, kết hợp cùng anh cho một trải nghiệm mới. Theo đó, hai người sẽ sáng tạo thực đơn sáu món: bánh tart cá ngừ đất sét Cao Lanh (đất), hàu xốt ớt xanh nitơ lỏng (nước), bồ câu xông khói gỗ cherry và bánh mỳ bơ tôm hùm (khí), tôm hùm xốt ớt (lửa), bò Wagyu (lửa), bánh mousse trà bá tước (đất). 'Việt Nam sở hữu khí hậu nhiệt đới cùng thổ nhưỡng giàu dưỡng chất, ẩm thực luôn có giá trị đa tầng về dinh dưỡng, đa dạng về hương vị, cùng những cảm giác tươi ngon đặc biệt. Do đó, tôi dễ dàng tìm kiếm và nghiên cứu được những nguyên liệu mới mẻ, hương vị khác nhau của mỗi vùng miền', bếp trưởng Phi Công chia sẻ. Bên cạnh việc lấy cảm hứng từ nguyên liệu địa phương, tôn vinh tài năng Việt, chuỗi sự kiện 'Pause + Savour' còn hướng đến tạo ra những kỷ niệm vui và khoảnh khắc tận hưởng cuộc sống trọn vẹn. Song hành cùng bếp trưởng Sĩ Toàn và bếp trưởng Phi Công là Head Sommelier Huyền Hà - người giám tuyển thực đơn rượu vang kết hợp từng nguyên liệu món ăn, nhằm nâng tầm vị giác của thực khách. Giá Wine Pairing là 800.000 đồng mỗi thực khách. Ngoài ra, Barson còn có Cocktails Pairing cũng 800.000 đồng hoặc Mocktails Pairing (không cồn) với giá 450.000 đồng. Số lượng chỗ ngồi được giới hạn tại Barson trong ba đêm tiệc, từ 23 đến 25/5. Thực khách có thể đặt bàn ngay để hưởng ưu đãi Early Bird của chương trình lên đến 15%, hoặc nhận các ưu đãi khi là thành viên của Marriott Bonvoy (10%) hay chủ thẻ VPBank (lên đến 20%). Chuỗi sự kiện ẩm thực bàn tiệc của bếp trưởng 'Pause + Savour' được Le Méridien Saigon khởi động từ cuối tháng 4, với bếp trưởng khách mời đầu tiên đến từ khách sạn Le Méridien Myeongdong Seoul (Hàn Quốc). Bếp trưởng người Hàn này mang đến nhiều hoạt động ấn tượng cho thực khách, khi tạo ra hành trình ẩm thực kết nối văn hóa và hương vị đa quốc gia, đánh thức các giác quan với những nguyên liệu và kỹ thuật chế biến độc đáo. Thanh Thư Le Méridien SaigonĐịa chỉ: 3C Tôn Đức Thắng, quận 1, TP HCMEmail: Lemeridien.Saigon@lemeridien.comĐiện thoại: 028 6263 6688Website:www.lemeridiensaigon.comFanpage:www.facebook.com/LeMeridienSaigonFanpage Barson:www.facebook.com/Barson.sgn",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết nhỏ như giá trị dinh dưỡng của ẩm thực Việt Nam, tuy nhiên vẫn giữ được ý chính của văn bản gốc.",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính như chuỗi sự kiện 'Pause + Savour', sự kết hợp của các bếp trưởng, thực đơn và giá cả, chỉ bỏ qua một số chi tiết phụ như địa chỉ và thông tin liên lạc.",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt còn dài và có thể được rút gọn hơn, một số câu còn dài và phức tạp, tuy nhiên vẫn dễ đọc và hiểu được."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Đây là một trong những hội chợ thương mại hàng đầu thế giới trong lĩnh vực công nghiệp hội nghị, sự kiện. Hội chợ cũng là nơi quy tụ nhiều công ty chuyên về du lịch sự kiện trên khắp thế giới đến giao lưu và tìm kiếm cơ hội thúc đẩy. Theo đại diện Vidotour, Imex Frankfurt 2024 đón 2.900 đơn vị triển lãm từ 150 quốc gia và vùng lãnh thổ, thu hút hơn 3.000 người mua đến từ 84 quốc gia và gần 12.000 khách tham quan. Trong đó, gian hàng của Sở Du lịch TP HCM diễn ra nhiều hoạt động thúc đẩy hình ảnh điểm đến TP HCM như: chương trình khuyến mại, gói du lịch kích cầu, bốc thăm trúng thưởng cho các khách hàng ghé thăm, hoạt động dân gian nặn tò he, trang trí nón lá... Gian hàng cũng giới thiệu thông tin hỗ trợ visa 15 ngày cho du khách châu Âu, nhằm kích cầu du lịch, nhất là thị trường Đức tiềm năng. Vidotour tham gia cùng Sở Du Lịch TP HCM lần này cũng mang đến các chương trình, sản phẩm du lịch chuyên về hội nghị: gói du lịch hội nghị bao gồm phòng ở và phòng họp, chương trình du lịch sức khỏe (wellness), du lịch kết hợp thể thao (giải golf và VnExpress Marathon...). Với kinh nghiệm hơn 34 năm hoạt động, Vidotour mang đến cho khách hàng châu Âu các dịch vụ chất lượng ở Việt Nam, Campuchia, Lào. Doanh nghiệp còn cam kết chuyển đổi xanh, đồng hành cùng du lich TP HCM mang đến các sản phẩm xanh và bền vững, phù hợp với mong muốn của mọi khách hàng. Đây là lần thứ 2 Vidotour đồng hành cùng Sở Du Lịch TP HCM tham dự hội chợ du lịch về MICE, IMEX. Lần đầu hai bên hợp tác là IMEX Mỹ, diễn ra tháng 10/2023 tại Las Vegas, Mỹ. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Vidotour tham dự Imex Frankfurt 2024 với hơn 1.500 gian hàng, thu hút gần 3.000 người mua và 12.000 khách tham quan. Gian hàng TP HCM tổ chức khuyến mại, gói du lịch kích cầu, trang trí nón lá và visa châu Âu. Vidotour cung cấp dịch vụ hội nghị và wellness với kinh nghiệm hơn 34 năm chuyển đổi xanh và sản phẩm bền vững.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>{
+  "id": 36,
+  "style": "news_brief",
+  "article": "Đây là một trong những hội chợ thương mại hàng đầu thế giới trong lĩnh vực công nghiệp hội nghị, sự kiện. Hội chợ cũng là nơi quy tụ nhiều công ty chuyên về du lịch sự kiện trên khắp thế giới đến giao lưu và tìm kiếm cơ hội thúc đẩy. Theo đại diện Vidotour, Imex Frankfurt 2024 đón 2.900 đơn vị triển lãm từ 150 quốc gia và vùng lãnh thổ, thu hút hơn 3.000 người mua đến từ 84 quốc gia và gần 12.000 khách tham quan. Trong đó, gian hàng của Sở Du lịch TP HCM diễn ra nhiều hoạt động thúc đẩy hình ảnh điểm đến TP HCM như: chương trình khuyến mại, gói du lịch kích cầu, bốc thăm trúng thưởng cho các khách hàng ghé thăm, hoạt động dân gian nặn tò he, trang trí nón lá... Gian hàng cũng giới thiệu thông tin hỗ trợ visa 15 ngày cho du khách châu Âu, nhằm kích cầu du lịch, nhất là thị trường Đức tiềm năng. Vidotour tham gia cùng Sở Du Lịch TP HCM lần này cũng mang đến các chương trình, sản phẩm du lịch chuyên về hội nghị: gói du lịch hội nghị bao gồm phòng ở và phòng họp, chương trình du lịch sức khỏe (wellness), du lịch kết hợp thể thao (giải golf và VnExpress Marathon...). Với kinh nghiệm hơn 34 năm hoạt động, Vidotour mang đến cho khách hàng châu Âu các dịch vụ chất lượng ở Việt Nam, Campuchia, Lào. Doanh nghiệp còn cam kết chuyển đổi xanh, đồng hành cùng du lich TP HCM mang đến các sản phẩm xanh và bền vững, phù hợp với mong muốn của mọi khách hàng. Đây là lần thứ 2 Vidotour đồng hành cùng Sở Du Lịch TP HCM tham dự hội chợ du lịch về MICE, IMEX. Lần đầu hai bên hợp tác là IMEX Mỹ, diễn ra tháng 10/2023 tại Las Vegas, Mỹ. Thanh Thư",
+  "summary": "Vidotour tham dự Imex Frankfurt 2024 với hơn 1.500 gian hàng, thu hút gần 3.000 người mua và 12.000 khách tham quan. Gian hàng TP HCM tổ chức khuyến mại, gói du lịch kích cầu, trang trí nón lá và visa châu Âu. Vidotour cung cấp dịch vụ hội nghị và wellness với kinh nghiệm hơn 34 năm chuyển đổi xanh và sản phẩm bền vững.",
+  "faithfulness_score": 0.6,
+  "faithfulness_reason": "Tóm tắt không chính xác về số lượng gian hàng, ban đầu là 2.900 đơn vị triển lãm từ 150 quốc gia và vùng lãnh thổ nhưng tóm tắt lại ghi là hơn 1.500 gian hàng, điều này làm sai lệch thông tin gốc",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt đã bao gồm các điểm chính như sự kiện Imex Frankfurt 2024, gian hàng của TP HCM và các hoạt động tại đó, cũng như dịch vụ của Vidotour, tuy nhiên thiếu thông tin về việc Vidotour đồng hành cùng Sở Du Lịch TP HCM lần thứ 2",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể cải thiện bằng cách thêm thông tin quan trọng và giảm bớt các chi tiết không cần thiết"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Nhiều gia đình hiểu rõ những chuyến du lịch dài ngày, đa thế hệ là trải nghiệm vô giá, nhưng vẫn luôn là kế hoạch xa vời. Với khác biệt tuổi tác và sở thích, các gia đình cảm thấy bối rối mỗi lần có ý định thiết kế chuyến đi. Hiểu được nỗi trăn trở này, Luxury Vacation Club thiết kế gói hội viên 10 năm cho khách du lịch gia đình. Khi tham gia, khách hàng được trải nghiệm những chuyến đi chất lượng, tại hệ thống nghỉ dưỡng 5 sao liên kết với thời gian lưu trú 8 ngày 7 đêm mỗi năm. Khách hàng có thể sử dụng quyền nghỉ linh hoạt cả về thời gian và điểm đến. Đặc biệt, du khách được tư vấn, hỗ trợ lên lịch trình cho các chuyến đi và nhận quà tặng như các dịch vụ đi kèm: du thuyền, lặn san hô, công viên nước, ưu đãi nhà hàng... tuỳ theo nhu cầu. Nghiên cứu của Đại học Massachusetts Amherst năm 2016 chỉ ra hai lợi ích chủ yếu của du lịch gia đình: tạo sự kết nối gia đình mạnh mẽ hơn và những kỷ niệm trọn đời; duy trì cải thiện chất lượng các mối quan hệ, củng cố hôn nhân và tăng chất lượng cuộc sống. Bên cạnh đó, việc đến những vùng đất lạ, tiếp xúc người bản địa, những món ăn đặc trưng, văn hóa, kiến trúc mới sẽ là những bài học không trường lớp, sách báo hay kênh tivi nào dạy con. Đây là lý do các gia đình châu Âu xem du lịch gia đình như một 'học kỳ' thứ ba của trẻ nhỏ. Với trẻ em, du lịch gia tăng khả năng thích ứng xã hội, trải nghiệm văn hóa, tăng tư duy cởi mở. Du lịch cùng gia đình cũng thúc đẩy sự độc lập, tự tin và kỹ năng giao tiếp cho trẻ. Các nghiên cứu về du lịch thế giới mỗi năm đều dự báo nhiều xu hướng trải nghiệm nổi bật, nhưng nhìn chung đều khẳng định sức nóng của du lịch gia đình. Khảo sát của Booking.com với 24.000 khách du lịch khắp thế giới năm 2022 cho thấy 54% trong số họ muốn lên kế hoạch đi nghỉ với gia đình. Khảo sát ngành Du lịch năm 2023 của Travel Weekly cũng chỉ ra 63% số người được hỏi chọn du lịch cùng gia đình là ưu tiên hàng đầu trong nhu cầu nghỉ dưỡng hàng năm. Còn Klook đưa ra nhận định hồi đầu năm nay, người dân châu Á- Thái Bình Dương có xu hướng ưu tiên trải nghiệm hơn chi phí, sẵn sàng tăng ngân sách để tận hưởng tối đa các chuyến du lịch. 17% khách Việt sẵn sàng chi hơn một nửa ngân sách du lịch của họ cho các hoạt động trải nghiệm. Đây là một trong những con số cao nhất tại khu vực. Người Việt cũng đứng đầu khu vực về nhu cầu du lịch cùng gia đình. 6 trong 10 du khách ưu tiên gắn kết với người thân trong các chuyến đi. Về lâu dài, các nhà nghiên cứu toàn cầu đánh giá, du khách đang đi du lịch chậm hơn và lâu hơn, chú trọng vào những trải nghiệm phong phú, cao cấp và toàn diện. Đặc biệt, với những gia đình có tiềm lực kinh tế, ngày càng có xu hướng không ngại chi tiền cho những trải nghiệm cá nhân hóa chuyên biệt, độc đáo. Luxury Vacation Club là doanh nghiệp có kinh nghiệm 3 năm tổ chức các chuyến du lịch cao cấp, mang tính cá nhân hóa cao cho khách quốc tế. Hiện công ty phát triển dịch vụ tại các thành phố biển tại Việt Nam như Đà Nẵng, Nha Trang, Cam Ranh... Với đội ngũ 200 nhân sự có trình độ cao và mạng lưới liên kết với hơn 100 khách sạn, resort lớn, uy tín như Intercontinental, Hilton, Amanoi, Movenpick, Melía &amp; Melía Vinpearl, Fusion, Pullman... Luxury Vacation Club giúp khách hàng tận hưởng trọn vẹn những trải nghiệm bên người thân. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Luxury Vacation Club thiết kế gói hội viên 10 năm cho khách du lịch gia đình, cung cấp trải nghiệm chất lượng tại hệ thống nghỉ dưỡng 5 sao với thời gian lưu trú 8 ngày/năm. Khách hàng có quyền linh hoạt về thời gian và điểm đến, được tư vấn lên lịch trình và nhận quà tặng như dịch vụ đi kèm: du thuyền, lặn san hô... Nghiên cứu cho thấy du lịch gia đình tạo sự kết nối mạnh mẽ hơn giữa các thành viên trong gia đình và duy trì cải thiện chất lượng mối quan hệ. Khách Việt sẵn sàng chi hơn nửa ngân sách cho trải nghiệm cùng gia đình, Luxury Vacation Club tổ chức chuyến cao cấp tại Đà Nẵng, Nha Trang... mang tính cá nhân hóa cao cho khách quốc tế.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>{
+  "id": 37,
+  "style": "news_brief",
+  "article": "Nhiều gia đình hiểu rõ những chuyến du lịch dài ngày, đa thế hệ là trải nghiệm vô giá, nhưng vẫn luôn là kế hoạch xa vời. Với khác biệt tuổi tác và sở thích, các gia đình cảm thấy bối rối mỗi lần có ý định thiết kế chuyến đi. Hiểu được nỗi trăn trở này, Luxury Vacation Club thiết kế gói hội viên 10 năm cho khách du lịch gia đình. Khi tham gia, khách hàng được trải nghiệm những chuyến đi chất lượng, tại hệ thống nghỉ dưỡng 5 sao liên kết với thời gian lưu trú 8 ngày 7 đêm mỗi năm. Khách hàng có thể sử dụng quyền nghỉ linh hoạt cả về thời gian và điểm đến. Đặc biệt, du khách được tư vấn, hỗ trợ lên lịch trình cho các chuyến đi và nhận quà tặng như các dịch vụ đi kèm: du thuyền, lặn san hô, công viên nước, ưu đãi nhà hàng... tuỳ theo nhu cầu. Nghiên cứu của Đại học Massachusetts Amherst năm 2016 chỉ ra hai lợi ích chủ yếu của du lịch gia đình: tạo sự kết nối gia đình mạnh mẽ hơn và những kỷ niệm trọn đời; duy trì cải thiện chất lượng các mối quan hệ, củng cố hôn nhân và tăng chất lượng cuộc sống. Bên cạnh đó, việc đến những vùng đất lạ, tiếp xúc người bản địa, những món ăn đặc trưng, văn hóa, kiến trúc mới sẽ là những bài học không trường lớp, sách báo hay kênh tivi nào dạy con. Đây là lý do các gia đình châu Âu xem du lịch gia đình như một 'học kỳ' thứ ba của trẻ nhỏ. Với trẻ em, du lịch gia tăng khả năng thích ứng xã hội, trải nghiệm văn hóa, tăng tư duy cởi mở. Du lịch cùng gia đình cũng thúc đẩy sự độc lập, tự tin và kỹ năng giao tiếp cho trẻ. Các nghiên cứu về du lịch thế giới mỗi năm đều dự báo nhiều xu hướng trải nghiệm nổi bật, nhưng nhìn chung đều khẳng định sức nóng của du lịch gia đình. Khảo sát của Booking.com với 24.000 khách du lịch khắp thế giới năm 2022 cho thấy 54% trong số họ muốn lên kế hoạch đi nghỉ với gia đình. Khảo sát ngành Du lịch năm 2023 của Travel Weekly cũng chỉ ra 63% số người được hỏi chọn du lịch cùng gia đình là ưu tiên hàng đầu trong nhu cầu nghỉ dưỡng hàng năm. Còn Klook đưa ra nhận định hồi đầu năm nay, người dân châu Á- Thái Bình Dương có xu hướng ưu tiên trải nghiệm hơn chi phí, sẵn sàng tăng ngân sách để tận hưởng tối đa các chuyến du lịch. 17% khách Việt sẵn sàng chi hơn một nửa ngân sách du lịch của họ cho các hoạt động trải nghiệm. Đây là một trong những con số cao nhất tại khu vực. Người Việt cũng đứng đầu khu vực về nhu cầu du lịch cùng gia đình. 6 trong 10 du khách ưu tiên gắn kết với người thân trong các chuyến đi. Về lâu dài, các nhà nghiên cứu toàn cầu đánh giá, du khách đang đi du lịch chậm hơn và lâu hơn, chú trọng vào những trải nghiệm phong phú, cao cấp và toàn diện. Đặc biệt, với những gia đình có tiềm lực kinh tế, ngày càng có xu hướng không ngại chi tiền cho những trải nghiệm cá nhân hóa chuyên biệt, độc đáo. Luxury Vacation Club là doanh nghiệp có kinh nghiệm 3 năm tổ chức các chuyến du lịch cao cấp, mang tính cá nhân hóa cao cho khách quốc tế. Hiện công ty phát triển dịch vụ tại các thành phố biển tại Việt Nam như Đà Nẵng, Nha Trang, Cam Ranh... Với đội ngũ 200 nhân sự có trình độ cao và mạng lưới liên kết với hơn 100 khách sạn, resort lớn, uy tín như Intercontinental, Hilton, Amanoi, Movenpick, Melía &amp; Melía Vinpearl, Fusion, Pullman... Luxury Vacation Club giúp khách hàng tận hưởng trọn vẹn những trải nghiệm bên người thân. Thanh Thư",
+  "summary": "Luxury Vacation Club thiết kế gói hội viên 10 năm cho khách du lịch gia đình, cung cấp trải nghiệm chất lượng tại hệ thống nghỉ dưỡng 5 sao với thời gian lưu trú 8 ngày/năm. Khách hàng có quyền linh hoạt về thời gian và điểm đến, được tư vấn lên lịch trình và nhận quà tặng như dịch vụ đi kèm: du thuyền, lặn san hô... Nghiên cứu cho thấy du lịch gia đình tạo sự kết nối mạnh mẽ hơn giữa các thành viên trong gia đình và duy trì cải thiện chất lượng mối quan hệ. Khách Việt sẵn sàng chi hơn nửa ngân sách cho trải nghiệm cùng gia đình, Luxury Vacation Club tổ chức chuyến cao cấp tại Đà Nẵng, Nha Trang... mang tính cá nhân hóa cao cho khách quốc tế.",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể bỏ qua một số chi tiết quan trọng như lợi ích của du lịch gia đình đối với trẻ em và xu hướng du lịch thế giới.",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính về gói hội viên của Luxury Vacation Club và lợi ích của du lịch gia đình, nhưng bỏ qua một số thông tin quan trọng như nghiên cứu của Đại học Massachusetts Amherst và khảo sát của Booking.com.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, nhưng có thể cải thiện bằng cách loại bỏ một số từ ngữ trùng lặp và sắp xếp lại cấu trúc câu để tăng tính mạch lạc."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Để đạt kỷ lục này, chương trình đến từ Tập đoàn Mường Thanh phải đáp ứng nhiều tiêu chí như: trình diễn bởi hơn 2.000 cán bộ nhân viên, kéo dài từ ngày 2/5 đến hết ngày 7/5 tại 42 địa điểm (các khách sạn và đơn vị thành viên trên cả nước và Lào). Trong đó có 6 cụm lớn tại các thành phố: Hạ Long, Đà Nẵng, Nha Trang, Vinh, Điện Biên Phủ, Hà Nội; 36 khách sạn và đơn vị thành viên thuộc các phân khúc Luxury, Grand, Holiday, Mường Thanh. Vòng múa xòe được xuất phát từ khách sạn Mường Thanh Grand Điện Biên Phủ, sau đó lan tỏa tới tất cả các tỉnh thành trên cả nước, tới đảo Lý Sơn, Phú Quốc, qua Lào và kết thúc tại Thủ đô Hà Nội. Màn múa xòe được xem là điểm nhấn trong hàng loạt sự kiện lớn của Tập đoàn Mường Thanh hướng về lễ kỷ niệm 70 năm Chiến thắng Điện Biên Phủ và Năm du lịch Quốc gia - Điện Biên 2024. Một số sự kiện khác cũng được tổ chức như cuộc thi Duyên dáng Mường Thanh, Chiến sĩ thi đua Mường Thanh, thi viết Hào Khí Mường Thanh, Đơn vị quyết thắng, các chương trình đặc biệt dành tặng khách hàng với ưu đãi lên tới 70%. Hoạt động giúp khán giả, du khách được thưởng thức màn trình diễn tại nhiều địa điểm công cộng, nơi đông dân cư, hiểu hơn về Di sản Nghệ thuật Xòe Thái được UNESCO ghi danh vào Danh sách Di sản Văn hóa phi vật thể đại diện của nhân loại. Lấy cảm hứng từ mảnh đất Điện Biên với chiến thắng Điện Biên Phủ oanh liệt lừng lẫy năm châu, cũng là nơi hội tụ nhiều tinh hoa văn hóa của đồng bào dân tộc Thái miền Tây Bắc, Tập đoàn Mường Thanh quyết tâm thực hiện vòng đại xòe ấn tượng. Thông qua màn đồng diễn múa Xòe Thái quy mô lớn, tập đoàn mong muốn góp phần quảng bá rộng rãi nét đẹp văn hóa Tây Bắc nói riêng và Việt Nam nói chung đến du khách. Qua đó gửi gắm thông điệp về sứ mệnh bảo tồn, phát huy những giá trị văn hóa, giá trị lịch sử của dân tộc đến các thế hệ. Trong buổi lễ trao bằng xác lập kỷ lục, ông Nguyễn Văn Hùng - Phó Tổng giám đốc Tập đoàn Mường Thanh chia sẻ, chương trình Một Vòng Mường Thanh không chỉ là hoạt động hưởng ứng lễ kỷ niệm 70 năm Chiến thắng Điện Biên Phủ, còn là minh chứng cho sứ mệnh bảo tồn và phát triển văn hoá Việt doanh nghiệp theo đuổi hơn 30 năm qua. Đặc biệt, để tri ân mảnh đất Điện Biên cũng như nằm trong khuôn khổ chiến dịch Huyền thoại Điện Biên Phủ - Hào khí Mường Thanh, tập đoàn sẽ tổ chức lễ động thổ xây dựng dự án Mường Thanh Luxury Điện Biên Phủ trong tháng 5. Dự kiến là khách sạn theo tiêu chuẩn 5 sao đầu tiên tại tỉnh Điện Biên. Tổ chức Kỷ lục Việt Nam cho biết trong hơn 30 năm hình thành và phát triển, thương hiệu Mường Thanh được xác lập nhiều kỷ lục danh giá: Chuỗi khách sạn tư nhân lớn nhất Đông Dương; Hành trình Xuyên Việt bằng ôtô qua 48 tỉnh, thành phố có số lượng cán bộ, nhân viên tham gia nhiều nhất; Đại tiệc có các món ngon - đặc sản vùng miền nổi tiếng nhiều nhất Việt Nam. Với việc xác lập kỷ lục Một vòng Mường Thanh - Màn đồng diễn múa Xòe Thái tại nhiều địa điểm nhất, tập đoàn công nhận đây là dấu mốc lớn trong hành trình phát triển. Thanh Thư</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>{
+  "id": 38,
+  "style": "news_brief",
+  "article": "Để đạt kỷ lục này, chương trình đến từ Tập đoàn Mường Thanh phải đáp ứng nhiều tiêu chí như: trình diễn bởi hơn 2.000 cán bộ nhân viên, kéo dài từ ngày 2/5 đến hết ngày 7/5 tại 42 địa điểm (các khách sạn và đơn vị thành viên trên cả nước và Lào). Trong đó có 6 cụm lớn tại các thành phố: Hạ Long, Đà Nẵng, Nha Trang, Vinh, Điện Biên Phủ, Hà Nội; 36 khách sạn và đơn vị thành viên thuộc các phân khúc Luxury, Grand, Holiday, Mường Thanh. Vòng múa xòe được xuất phát từ khách sạn Mường Thanh Grand Điện Biên Phủ, sau đó lan tỏa tới tất cả các tỉnh thành trên cả nước, tới đảo Lý Sơn, Phú Quốc, qua Lào và kết thúc tại Thủ đô Hà Nội. Màn múa xòe được xem là điểm nhấn trong hàng loạt sự kiện lớn của Tập đoàn Mường Thanh hướng về lễ kỷ niệm 70 năm Chiến thắng Điện Biên Phủ và Năm du lịch Quốc gia - Điện Biên 2024. Một số sự kiện khác cũng được tổ chức như cuộc thi Duyên dáng Mường Thanh, Chiến sĩ thi đua Mường Thanh, thi viết Hào Khí Mường Thanh, Đơn vị quyết thắng, các chương trình đặc biệt dành tặng khách hàng với ưu đãi lên tới 70%. Hoạt động giúp khán giả, du khách được thưởng thức màn trình diễn tại nhiều địa điểm công cộng, nơi đông dân cư, hiểu hơn về Di sản Nghệ thuật Xòe Thái được UNESCO ghi danh vào Danh sách Di sản Văn hóa phi vật thể đại diện của nhân loại. Lấy cảm hứng từ mảnh đất Điện Biên với chiến thắng Điện Biên Phủ oanh liệt lừng lẫy năm châu, cũng là nơi hội tụ nhiều tinh hoa văn hóa của đồng bào dân tộc Thái miền Tây Bắc, Tập đoàn Mường Thanh quyết tâm thực hiện vòng đại xòe ấn tượng. Thông qua màn đồng diễn múa Xòe Thái quy mô lớn, tập đoàn mong muốn góp phần quảng bá rộng rãi nét đẹp văn hóa Tây Bắc nói riêng và Việt Nam nói chung đến du khách. Qua đó gửi gắm thông điệp về sứ mệnh bảo tồn, phát huy những giá trị văn hóa, giá trị lịch sử của dân tộc đến các thế hệ. Trong buổi lễ trao bằng xác lập kỷ lục, ông Nguyễn Văn Hùng - Phó Tổng giám đốc Tập đoàn Mường Thanh chia sẻ, chương trình Một Vòng Mường Thanh không chỉ là hoạt động hưởng ứng lễ kỷ niệm 70 năm Chiến thắng Điện Biên Phủ, còn là minh chứng cho sứ mệnh bảo tồn và phát triển văn hoá Việt doanh nghiệp theo đuổi hơn 30 năm qua. Đặc biệt, để tri ân mảnh đất Điện Biên cũng như nằm trong khuôn khổ chiến dịch Huyền thoại Điện Biên Phủ - Hào khí Mường Thanh, tập đoàn sẽ tổ chức lễ động thổ xây dựng dự án Mường Thanh Luxury Điện Biên Phủ trong tháng 5. Dự kiến là khách sạn theo tiêu chuẩn 5 sao đầu tiên tại tỉnh Điện Biên. Tổ chức Kỷ lục Việt Nam cho biết trong hơn 30 năm hình thành và phát triển, thương hiệu Mường Thanh được xác lập nhiều kỷ lục danh giá: Chuỗi khách sạn tư nhân lớn nhất Đông Dương; Hành trình Xuyên Việt bằng ôtô qua 48 tỉnh, thành phố có số lượng cán bộ, nhân viên tham gia nhiều nhất; Đại tiệc có các món ngon - đặc sản vùng miền nổi tiếng nhiều nhất Việt Nam. Với việc xác lập kỷ lục Một vòng Mường Thanh - Màn đồng diễn múa Xòe Thái tại nhiều địa điểm nhất, tập đoàn công nhận đây là dấu mốc lớn trong hành trình phát triển. Thanh Thư",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể bỏ qua một số chi tiết nhỏ như số lượng cán bộ nhân viên tham gia cụ thể và các chương trình đặc biệt dành tặng khách hàng",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính như mục đích của chương trình, quy mô và địa điểm tổ chức, nhưng có thể chưa đề cập rõ ràng đến tất cả các sự kiện phụ trợ",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt có thể còn dài và chưa thật sự cô đọng, một số câu văn còn dài và phức tạp, cần tinh gọn hơn để dễ đọc và hiểu"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Những ngày cuối tháng 4 đầu tháng 5, hàng chục nghìn du khách tìm về Điện Biên Phủ, nơi in dấu son lịch sử về chiến thắng 'Lừng lẫy năm châu, chấn động địa cầu'. Đồi A1 ở phường Mường Thanh, TP Điện Biên Phủ, từng là cứ điểm quan trọng bậc nhất trong tập đoàn cứ điểm của thực dân Pháp ở Điện Biên Phủ, luôn đông đúc từ sáng tới chiều muộn. Bên cạnh những hầm hào, rào thép gai, xe tăng thì đồi A1 nổi bật hơn với hai cây phượng nở rộ trên đỉnh, bên cạnh hố bộc phá 960 kg. Những ngày cuối tháng 4 đầu tháng 5, hàng chục nghìn du khách tìm về Điện Biên Phủ, nơi in dấu son lịch sử về chiến thắng 'Lừng lẫy năm châu, chấn động địa cầu'. Đồi A1 ở phường Mường Thanh, TP Điện Biên Phủ, từng là cứ điểm quan trọng bậc nhất trong tập đoàn cứ điểm của thực dân Pháp ở Điện Biên Phủ, luôn đông đúc từ sáng tới chiều muộn. Bên cạnh những hầm hào, rào thép gai, xe tăng thì đồi A1 nổi bật hơn với hai cây phượng nở rộ trên đỉnh, bên cạnh hố bộc phá 960 kg. Hai cây phượng nằm cách nhau 60 m ra hoa vào đúng dịp kỷ niệm 70 năm Chiến thắng Điện Biên Phủ. Từ đầu năm 2024 đến nay, tỉnh Điện Biên đón 845.000 lượt du khách, tăng gần hai lần so với cùng kỳ năm 2023. Hai cây phượng nằm cách nhau 60 m ra hoa vào đúng dịp kỷ niệm 70 năm Chiến thắng Điện Biên Phủ. Từ đầu năm 2024 đến nay, tỉnh Điện Biên đón 845.000 lượt du khách, tăng gần hai lần so với cùng kỳ năm 2023. Dưới cây phượng, hàng trăm du khách thích thú chụp ảnh, bên cạnh là chiếc xe tăng M24 (còn có tên gọi Bazeille) của quân Pháp bị bắn cháy. Đồi A1 nằm dài theo hướng Tây Bắc - Đông Nam, gồm hai đỉnh Tây Bắc cao hơn 490 m, Đông Nam cao hơn 493 m Dưới cây phượng, hàng trăm du khách thích thú chụp ảnh, bên cạnh là chiếc xe tăng M24 (còn có tên gọi Bazeille) của quân Pháp bị bắn cháy. Đồi A1 nằm dài theo hướng Tây Bắc - Đông Nam, gồm hai đỉnh Tây Bắc cao hơn 490 m, Đông Nam cao hơn 493 m Nhóm bạn trẻ trong trang phục chiến sỹ Điện Biên chụp ảnh bên đường hào dưới gốc cây hoa phượng. Nhóm bạn trẻ trong trang phục chiến sỹ Điện Biên chụp ảnh bên đường hào dưới gốc cây hoa phượng. Thiếu nữ H'Mông Vàng Thị Nhìa trong trang phục áo dài trắng chụp ảnh vào khoảnh khắc được cho là đẹp nhất trong ngày trên đồi A1 khi mặt trời lặn. Thiếu nữ H'Mông Vàng Thị Nhìa trong trang phục áo dài trắng chụp ảnh vào khoảnh khắc được cho là đẹp nhất trong ngày trên đồi A1 khi mặt trời lặn. Du khách tham quan cửa hầm chỉ huy, được xây dựng kiên cố trên điểm cao nhất của đồi A1. Du khách tham quan cửa hầm chỉ huy, được xây dựng kiên cố trên điểm cao nhất của đồi A1. Các ngả đường dẫn lên đồi luôn đông du khách. Đồi A1 thuộc dãy đồi phía Đông, cao 32 m so với mặt đường và có diện tích 83.000 m2, cách Sở chỉ huy tập đoàn cứ điểm Điện Biên Phủ của thực dân Pháp khoảng 500 m về phía Tây theo đường chim bay. Các ngả đường dẫn lên đồi luôn đông du khách. Đồi A1 thuộc dãy đồi phía Đông, cao 32 m so với mặt đường và có diện tích 83.000 m2, cách Sở chỉ huy tập đoàn cứ điểm Điện Biên Phủ của thực dân Pháp khoảng 500 m về phía Tây theo đường chim bay. Hoa phượng nở đỏ rực trên đồi A1 Hoa phượng nở đỏ rực trên đồi A1 những ngày tháng 5. Video: Anh Phú - Lộc Chung</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>{
+  "id": 39,
+  "style": "news_brief",
+  "article": "Những ngày cuối tháng 4 đầu tháng 5, hàng chục nghìn du khách tìm về Điện Biên Phủ, nơi in dấu son lịch sử về chiến thắng 'Lừng lẫy năm châu, chấn động địa cầu'. Đồi A1 ở phường Mường Thanh, TP Điện Biên Phủ, từng là cứ điểm quan trọng bậc nhất trong tập đoàn cứ điểm của thực dân Pháp ở Điện Biên Phủ, luôn đông đúc từ sáng tới chiều muộn. Bên cạnh những hầm hào, rào thép gai, xe tăng thì đồi A1 nổi bật hơn với hai cây phượng nở rộ trên đỉnh, bên cạnh hố bộc phá 960 kg. Những ngày cuối tháng 4 đầu tháng 5, hàng chục nghìn du khách tìm về Điện Biên Phủ, nơi in dấu son lịch sử về chiến thắng 'Lừng lẫy năm châu, chấn động địa cầu'. Đồi A1 ở phường Mường Thanh, TP Điện Biên Phủ, từng là cứ điểm quan trọng bậc nhất trong tập đoàn cứ điểm của thực dân Pháp ở Điện Biên Phủ, luôn đông đúc từ sáng tới chiều muộn. Bên cạnh những hầm hào, rào thép gai, xe tăng thì đồi A1 nổi bật hơn với hai cây phượng nở rộ trên đỉnh, bên cạnh hố bộc phá 960 kg. Hai cây phượng nằm cách nhau 60 m ra hoa vào đúng dịp kỷ niệm 70 năm Chiến thắng Điện Biên Phủ. Từ đầu năm 2024 đến nay, tỉnh Điện Biên đón 845.000 lượt du khách, tăng gần hai lần so với cùng kỳ năm 2023. Hai cây phượng nằm cách nhau 60 m ra hoa vào đúng dịp kỷ niệm 70 năm Chiến thắng Điện Biên Phủ. Từ đầu năm 2024 đến nay, tỉnh Điện Biên đón 845.000 lượt du khách, tăng gần hai lần so với cùng kỳ năm 2023. Dưới cây phượng, hàng trăm du khách thích thú chụp ảnh, bên cạnh là chiếc xe tăng M24 (còn có tên gọi Bazeille) của quân Pháp bị bắn cháy. Đồi A1 nằm dài theo hướng Tây Bắc - Đông Nam, gồm hai đỉnh Tây Bắc cao hơn 490 m, Đông Nam cao hơn 493 m Dưới cây phượng, hàng trăm du khách thích thú chụp ảnh, bên cạnh là chiếc xe tăng M24 (còn có tên gọi Bazeille) của quân Pháp bị bắn cháy. Đồi A1 nằm dài theo hướng Tây Bắc - Đông Nam, gồm hai đỉnh Tây Bắc cao hơn 490 m, Đông Nam cao hơn 493 m Nhóm bạn trẻ trong trang phục chiến sỹ Điện Biên chụp ảnh bên đường hào dưới gốc cây hoa phượng. Nhóm bạn trẻ trong trang phục chiến sỹ Điện Biên chụp ảnh bên đường hào dưới gốc cây hoa phượng. Thiếu nữ H'Mông Vàng Thị Nhìa trong trang phục áo dài trắng chụp ảnh vào khoảnh khắc được cho là đẹp nhất trong ngày trên đồi A1 khi mặt trời lặn. Thiếu nữ H'Mông Vàng Thị Nhìa trong trang phục áo dài trắng chụp ảnh vào khoảnh khắc được cho là đẹp nhất trong ngày trên đồi A1 khi mặt trời lặn. Du khách tham quan cửa hầm chỉ huy, được xây dựng kiên cố trên điểm cao nhất của đồi A1. Du khách tham quan cửa hầm chỉ huy, được xây dựng kiên cố trên điểm cao nhất của đồi A1. Các ngả đường dẫn lên đồi luôn đông du khách. Đồi A1 thuộc dãy đồi phía Đông, cao 32 m so với mặt đường và có diện tích 83.000 m2, cách Sở chỉ huy tập đoàn cứ điểm Điện Biên Phủ của thực dân Pháp khoảng 500 m về phía Tây theo đường chim bay. Các ngả đường dẫn lên đồi luôn đông du khách. Đồi A1 thuộc dãy đồi phía Đông, cao 32 m so với mặt đường và có diện tích 83.000 m2, cách Sở chỉ huy tập đoàn cứ điểm Điện Biên Phủ của thực dân Pháp khoảng 500 m về phía Tây theo đường chim bay. Hoa phượng nở đỏ rực trên đồi A1 Hoa phượng nở đỏ rực trên đồi A1 những ngày tháng 5. Video: Anh Phú - Lộc Chung",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng có thể bỏ qua một số chi tiết quan trọng như vị trí và diện tích của đồi A1, tuy nhiên vẫn giữ được ý nghĩa chính của văn bản gốc",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chưa bao quát được tất cả các điểm chính của văn bản gốc, như số lượng du khách và ý nghĩa của hai cây phượng nở rộ trên đồi A1",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách mạch lạc, dễ đọc và không có thông tin trùng lặp, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Với những tín đồ Phật giáo, bức tượng Phật ngọc hòa bình thế giới được biết đến là tín vật thuộc sở hữu của vợ chồng ông Ian Green và bà Judy Green người Australia. Tượng được các nghệ nhân Thái Lan chạm khắc từ ngọc bích nguyên khối 18 tấn, phát hiện tại Canada vào năm 2000. Sau 8 năm, đến tháng 12/2008 thì hoàn thành. Đây là pho tượng Phật ngọc lớn nhất thế giới được tạc theo khuôn tượng đức Phật Thích Ca Mâu Ni trong bảo tháp Đại giác ngộ tại Bồ Đề Đạo Tràng (Ấn Độ). Tại Việt Nam, năm 2018 Khu du lịch Văn hóa Tâm linh Bà Chúa Xứ - Cáp treo Núi Sam thỉnh và an vị một bức tượng 'song sinh' với tượng Phật ngọc hòa bình thế giới. Theo ban quản lý di tích, việc làm này nhằm mục đích cho bà con và tăng ni Phật tử không có điều kiện hành hương sang bồ đề đạo tràng Ấn Độ để chiêm bái tượng Phật nguyên mẫu. Tượng Phật Ngọc trên đỉnh núi Sam cạnh nhà ga cáp treo được chế tác bởi các nghệ nhân lành nghề vùng biên giới Thái Lan – Myanma. Tượng cũng được tạc theo khuôn mẫu của tượng Phật Thích Ca Mâu Ni bên trong bảo tháp Đại Giác Ngộ ở Bồ Đề Đạo Tràng, Ấn Độ. Hình ảnh này tượng trưng cho 'sự giác ngộ, viên mãn, may mắn và bình an'. Sau khi hoàn thành, pho tượng được đội ngũ tăng đoàn Thái Lan ấn chứng cùng sự gieo duyên an vị của các thiền sư trên đỉnh tuyết sơn Hymalaya và vận chuyển về Việt Nam bằng đường biển. Dịp lễ 30/4 này, du khách có thể cùng gia đình về An Giang, ghé thăm Châu Đốc, đến Núi Sam thăm viếng các danh thắng như Miếu Bà Chúa xứ, Sơn lăng Thoại Ngọc Hầu, chùa Tây An, chùa Hang và chiêm bái bức tượng 'song sinh' với tượng Phật ngọc hòa bình thế giới. Nơi đây bốn mùa gió thoảng, nhiều cây xanh, bên dưới là cánh đồng. Trước đây, để lên đỉnh núi, khách hành hương thường dọn đi xe máy quanh sườn núi. Tuy nhiên, từ năm 2021, tỉnh An Giang đã đưa vào vận hành hệ thống cáp treo với tổng chiều dài 900m, với 37 cabin, mỗi cabin có sức chứa 8 hành khách vận hành liên tục. Khách du lịch sẽ được trải nghiệm cảm giác cưỡi mây ngắm toàn cảnh Châu Đốc và đắm mình trong không gian Phật giáo thanh bình. Đặc biệt cầu Châu Đốc vừa thông xe sáng 23/4 sẽ giúp hành khách rút ngắn thời gian di chuyển từ TP HCM đi các tỉnh miền Tây và ngược lại. Lan Anh</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>{
+  "id": 40,
+  "style": "news_brief",
+  "article": "Với những tín đồ Phật giáo, bức tượng Phật ngọc hòa bình thế giới được biết đến là tín vật thuộc sở hữu của vợ chồng ông Ian Green và bà Judy Green người Australia. Tượng được các nghệ nhân Thái Lan chạm khắc từ ngọc bích nguyên khối 18 tấn, phát hiện tại Canada vào năm 2000. Sau 8 năm, đến tháng 12/2008 thì hoàn thành. Đây là pho tượng Phật ngọc lớn nhất thế giới được tạc theo khuôn tượng đức Phật Thích Ca Mâu Ni trong bảo tháp Đại giác ngộ tại Bồ Đề Đạo Tràng (Ấn Độ). Tại Việt Nam, năm 2018 Khu du lịch Văn hóa Tâm linh Bà Chúa Xứ - Cáp treo Núi Sam thỉnh và an vị một bức tượng 'song sinh' với tượng Phật ngọc hòa bình thế giới. Theo ban quản lý di tích, việc làm này nhằm mục đích cho bà con và tăng ni Phật tử không có điều kiện hành hương sang bồ đề đạo tràng Ấn Độ để chiêm bái tượng Phật nguyên mẫu. Tượng Phật Ngọc trên đỉnh núi Sam cạnh nhà ga cáp treo được chế tác bởi các nghệ nhân lành nghề vùng biên giới Thái Lan – Myanma. Tượng cũng được tạc theo khuôn mẫu của tượng Phật Thích Ca Mâu Ni bên trong bảo tháp Đại Giác Ngộ ở Bồ Đề Đạo Tràng, Ấn Độ. Hình ảnh này tượng trưng cho 'sự giác ngộ, viên mãn, may mắn và bình an'. Sau khi hoàn thành, pho tượng được đội ngũ tăng đoàn Thái Lan ấn chứng cùng sự gieo duyên an vị của các thiền sư trên đỉnh tuyết sơn Hymalaya và vận chuyển về Việt Nam bằng đường biển. Dịp lễ 30/4 này, du khách có thể cùng gia đình về An Giang, ghé thăm Châu Đốc, đến Núi Sam thăm viếng các danh thắng như Miếu Bà Chúa xứ, Sơn lăng Thoại Ngọc Hầu, chùa Tây An, chùa Hang và chiêm bái bức tượng 'song sinh' với tượng Phật ngọc hòa bình thế giới. Nơi đây bốn mùa gió thoảng, nhiều cây xanh, bên dưới là cánh đồng. Trước đây, để lên đỉnh núi, khách hành hương thường dọn đi xe máy quanh sườn núi. Tuy nhiên, từ năm 2021, tỉnh An Giang đã đưa vào vận hành hệ thống cáp treo với tổng chiều dài 900m, với 37 cabin, mỗi cabin có sức chứa 8 hành khách vận hành liên tục. Khách du lịch sẽ được trải nghiệm cảm giác cưỡi mây ngắm toàn cảnh Châu Đốc và đắm mình trong không gian Phật giáo thanh bình. Đặc biệt cầu Châu Đốc vừa thông xe sáng 23/4 sẽ giúp hành khách rút ngắn thời gian di chuyển từ TP HCM đi các tỉnh miền Tây và ngược lại. Lan Anh",
+  "summary": "",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch, nhưng có thể bỏ qua một số chi tiết nhỏ như quá trình chế tác tượng Phật Ngọc trên đỉnh núi Sam",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính như tượng Phật ngọc hòa bình thế giới, tượng 'song sinh' tại Việt Nam, nhưng có thể bỏ qua một số thông tin về ý nghĩa và giá trị của tượng",
+  "coherence_conciseness_score": 0.7,
+  "coherence_conciseness_reason": "Tóm tắt còn có một số câu dài và phức tạp, cần được chỉnh sửa để dễ đọc và hiểu hơn"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lấy cảm hứng từ Hestia - nữ thần của ngọn lửa vĩnh cửu, CoCo Grill kể câu chuyện ẩm thực qua các giai đoạn: chớm; lửa; khói; và tro. Đại diện nhà hàng cho biết lửa là nguồn cảm hứng của bếp trưởng Võ Thành Vương, người được ví là nghệ sĩ kiến tạo những 'tác phẩm nghệ thuật' ẩm thực trên lò than. Theo bếp trưởng Vương, mỗi ngọn lửa được các đầu bếp điều khiển giống như một nhạc trưởng đang điều khiển dàn nhạc. Chỉ cần sai một nốt, có thể ảnh hưởng đến chất lượng món ăn. Từng thớ thịt mềm và rau củ tươi ngon sẽ đạt đến độ chín lý tưởng khi người đầu bếp chế biến nắm rõ được từng thời điểm quan trọng. Họ tận dụng hơi ấm của than gỗ để tạo nên hương vị thơm ngon, hòa lẫn với làn khói đặc trưng chỉ khi nướng trên bếp than. 'Không chỉ là phương tiện nấu nướng, lửa tại CoCo Grill là yếu tố nghệ thuật, thể hiện sự kiên nhẫn và điều độ của người đầu bếp khi kết hợp hài hòa giữa sức nóng, thời gian, kỹ thuật và cảm xúc', đại diện nhà hàng cho biết. Ở giai đoạn đầu tiên, 'chớm', nhà hàng đánh thức vị giác của thực khách bằng những món khai vị cao cấp, khởi đầu hành trình bằng vị nhẹ nhàng của món lách búp nướng than hoa, cá ngừ ủ 7 ngày, nộm bạch tuộc ủ tảo bẹ... Bước sang giai đoạn thứ hai, 'lửa', nhà hàng đưa thực khách đến với cao trào bằng những món nướng đặc trưng. Đây là thời khắc ngọn lửa bùng cháy mạnh mẽ nhất, làm chín những miếng thịt thượng hạng. Hành trình ẩm thực tiếp tục bước sang giai đoạn 'khói'. Mỗi món ăn được tẩm ướp bằng khói thơm của gỗ quý, tạo nên những tầng hương vị phức tạp, mới lạ. 'Tro' kết màn với những món tráng miệng độc đáo. Đây cũng là lúc ngọn lửa trong lò than dịu nhất, báo hiệu một bữa ăn sắp kết thúc. Bếp trưởng Võ Thành Vương cho biết anh muốn tái hiện những món ăn quen thuộc bằng cách chế biến mới lạ, đặc trưng của CoCo Grill. Tất cả nguyên liệu được sử dụng từ nguồn địa phương, đảm bảo an toàn vệ sinh và chất lượng từ đầu đến cuối. 'Từ chất lượng nguyên liệu đến cách trình bày món ăn đều thể hiện sự cân bằng giữa di sản văn hóa và sáng tạo đương đại, giữa truyền thống và hơi thở mới mẻ của ẩm thực', bếp trưởng Vương nói thêm. Ngoài chất lượng món ăn, không gian CoCo Grill cũng được chú trọng thiết kế để tôn vinh nghệ thuật nướng. Thực khách có thể chiêm ngưỡng toàn bộ quá trình chế biến món ăn của các đầu bếp, lắng nghe âm thanh tí tách khi than cháy trong lò nướng. Ngoài ra, bếp mở còn giúp tăng khẩu vị nhờ hương thơm thoang thoảng, góp phần tạo không khí ấm cúng cho bữa ăn gia đình, hội họp hoặc gặp gỡ đối tác... CoCo Grill cho biết nhà hàng vẫn đang trên hành trình khẳng định vị thế là một trong những điểm đến ẩm thực đáng thử tại Sài Gòn. 'Nhà hàng hứa hẹn tiếp tục mang đến những trải nghiệm đặc sắc, góp phần nâng tầm ẩm thực Việt Nam trên bản đồ ẩm thực thế giới', vị đại diện nói thêm. Á Hiên</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nhà hàng CoCo Grill kể câu chuyện ẩm thực qua lửa, khói và tro. Lửa là nguồn cảm hứng của bếp trưởng Võ Thành Vương, điều khiển giống như nhạc trưởng dàn nhạc. Khai vị nhẹ nhàng nướng thịt thượng hạng tại 'lửa', sau đó tẩm ướp bằng hương thơm đặc trưng từ gỗ quý tạo nên 'khói' và kết màn với tráng miệng độc đáo. Nguyên liệu địa phương đảm bảo an toàn vệ sinh, chất lượng; tôn vinh nghệ thuật nướng, là điểm đến đáng thử tại Sài Gòn với trải nghiệm đặc sắc nâng tầm ẩm thực Việt Nam trên bản đồ quốc tế.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>{
+  "id": 41,
+  "style": "news_brief",
+  "article": "Lấy cảm hứng từ Hestia - nữ thần của ngọn lửa vĩnh cửu, CoCo Grill kể câu chuyện ẩm thực qua các giai đoạn: chớm; lửa; khói; và tro. Đại diện nhà hàng cho biết lửa là nguồn cảm hứng của bếp trưởng Võ Thành Vương, người được ví là nghệ sĩ kiến tạo những 'tác phẩm nghệ thuật' ẩm thực trên lò than. Theo bếp trưởng Vương, mỗi ngọn lửa được các đầu bếp điều khiển giống như một nhạc trưởng đang điều khiển dàn nhạc. Chỉ cần sai một nốt, có thể ảnh hưởng đến chất lượng món ăn. Từng thớ thịt mềm và rau củ tươi ngon sẽ đạt đến độ chín lý tưởng khi người đầu bếp chế biến nắm rõ được từng thời điểm quan trọng. Họ tận dụng hơi ấm của than gỗ để tạo nên hương vị thơm ngon, hòa lẫn với làn khói đặc trưng chỉ khi nướng trên bếp than. 'Không chỉ là phương tiện nấu nướng, lửa tại CoCo Grill là yếu tố nghệ thuật, thể hiện sự kiên nhẫn và điều độ của người đầu bếp khi kết hợp hài hòa giữa sức nóng, thời gian, kỹ thuật và cảm xúc', đại diện nhà hàng cho biết. Ở giai đoạn đầu tiên, 'chớm', nhà hàng đánh thức vị giác của thực khách bằng những món khai vị cao cấp, khởi đầu hành trình bằng vị nhẹ nhàng của món lách búp nướng than hoa, cá ngừ ủ 7 ngày, nộm bạch tuộc ủ tảo bẹ... Bước sang giai đoạn thứ hai, 'lửa', nhà hàng đưa thực khách đến với cao trào bằng những món nướng đặc trưng. Đây là thời khắc ngọn lửa bùng cháy mạnh mẽ nhất, làm chín những miếng thịt thượng hạng. Hành trình ẩm thực tiếp tục bước sang giai đoạn 'khói'. Mỗi món ăn được tẩm ướp bằng khói thơm của gỗ quý, tạo nên những tầng hương vị phức tạp, mới lạ. 'Tro' kết màn với những món tráng miệng độc đáo. Đây cũng là lúc ngọn lửa trong lò than dịu nhất, báo hiệu một bữa ăn sắp kết thúc. Bếp trưởng Võ Thành Vương cho biết anh muốn tái hiện những món ăn quen thuộc bằng cách chế biến mới lạ, đặc trưng của CoCo Grill. Tất cả nguyên liệu được sử dụng từ nguồn địa phương, đảm bảo an toàn vệ sinh và chất lượng từ đầu đến cuối. 'Từ chất lượng nguyên liệu đến cách trình bày món ăn đều thể hiện sự cân bằng giữa di sản văn hóa và sáng tạo đương đại, giữa truyền thống và hơi thở mới mẻ của ẩm thực', bếp trưởng Vương nói thêm. Ngoài chất lượng món ăn, không gian CoCo Grill cũng được chú trọng thiết kế để tôn vinh nghệ thuật nướng. Thực khách có thể chiêm ngưỡng toàn bộ quá trình chế biến món ăn của các đầu bếp, lắng nghe âm thanh tí tách khi than cháy trong lò nướng. Ngoài ra, bếp mở còn giúp tăng khẩu vị nhờ hương thơm thoang thoảng, góp phần tạo không khí ấm cúng cho bữa ăn gia đình, hội họp hoặc gặp gỡ đối tác... CoCo Grill cho biết nhà hàng vẫn đang trên hành trình khẳng định vị thế là một trong những điểm đến ẩm thực đáng thử tại Sài Gòn. 'Nhà hàng hứa hẹn tiếp tục mang đến những trải nghiệm đặc sắc, góp phần nâng tầm ẩm thực Việt Nam trên bản đồ ẩm thực thế giới', vị đại diện nói thêm. Á Hiên",
+  "summary": "Nhà hàng CoCo Grill kể câu chuyện ẩm thực qua lửa, khói và tro. Lửa là nguồn cảm hứng của bếp trưởng Võ Thành Vương, điều khiển giống như nhạc trưởng dàn nhạc. Khai vị nhẹ nhàng nướng thịt thượng hạng tại 'lửa', sau đó tẩm ướp bằng hương thơm đặc trưng từ gỗ quý tạo nên 'khói' và kết màn với tráng miệng độc đáo. Nguyên liệu địa phương đảm bảo an toàn vệ sinh, chất lượng; tôn vinh nghệ thuật nướng, là điểm đến đáng thử tại Sài Gòn với trải nghiệm đặc sắc nâng tầm ẩm thực Việt Nam trên bản đồ quốc tế.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như giai đoạn 'chớm' và ý nghĩa của từng giai đoạn trong câu chuyện ẩm thực",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt không bao gồm tất cả các điểm chính như không gian nhà hàng được thiết kế để tôn vinh nghệ thuật nướng và việc sử dụng nguyên liệu địa phương",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng để làm cho nó trở nên hoàn chỉnh hơn"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cua lông Thượng Hải là đặc sản cao cấp từng được dùng cho cung đình và giới quý tộc Trung Quốc trước đây, được đánh giá là loại cua ngon bậc nhất thế giới. Loài cua dễ nhận ra nhờ những mảng lông đen xù xì trên các chi. Cua lông Thượng Hải có kích thước bằng một nắm tay người lớn, mọng nước, ẩm và nhiều thịt. Thịt cua chắc, mềm, mịn nên được hấp nguyên con, không nêm gia vị, thịt ngọt hơn so với cua thông thường. Cua lông chỉ sinh sản và phát triển theo mùa, thường vào bốn tháng cuối năm, gạch cua béo. Loại hải sản này giá trị dinh dưỡng cao vì thế giá thành cũng cao, có thể lên tới hơn 100 USD một kg. Cua lông thường được nhúng vào hỗn hợp giấm gạo và nước tương, sau đó phủ gừng thái lát lên trên và hấp. Cua lông thường dùng nóng ngay sau khi hấp và một người trung bình ăn được 2-4 con một lần. Ngoài cách ăn kể trên, người Thượng Hải còn chế biến cua với mì. Thực khách có thể bất ngờ khi biết để làm một bát mì, có thể cần tới 12 con cua. Mỗi ngày, các nhà hàng hoặc những cơ sở chế biến phải nhập cua tươi, hấp cách thủy. Sau đó, cua được bóc bằng tay, tách vỏ, gạch và thịt, nhưng vẫn phải nguyên vẹn, không bị vỡ nát. Thịt và gạch cua được xào chín và làm sốt, cho thêm gia vị là dấm, muối và hành tây. Các gia vị giúp món ăn giữ nguyên mùi và vị tự nhiên nhất. Khi khách gọi món, đa phần các nhà hàng để phần sốt riêng, mì riêng để khách tự trộn, nhưng cũng có những nơi phục vụ phần sốt chung một bát. Gọi là mì cua lông, nhưng khi nhìn vào bát thực khách sẽ thấy lượng thịt sốt cua bao phủ toàn bộ tô mì. Lượng mì tuy không nhiều nhưng tinh túy của món ăn nằm ở đây, bởi vị đậm đà của phần sốt đã ngấm vào sợi mì. Món ăn có màu vàng cam đặc trưng của gạch cua, màu trắng của thịt cua. Khi thưởng thức, thực khách sẽ thấy vị béo bùi và thơm của gạch, thịt cua chắc ngọt, gia vị được nêm nếm vừa đủ, sợi mì dai. Tất cả hòa quyện tạo nên món ăn du khách được khuyên 'phải thử' khi tới Thượng Hải. Ngoài mì, du khách có thể chọn ăn sốt cua lông với cơm, hương vị không thay đổi. Mì cua lông là món ăn được nhiều người yêu thích. Nữ diễn viên Xa Thi Mạn từng gây sốt cách đây vài năm khi khoe bát mì cua lông tại một trong những nhà hàng bình dân nổi tiếng ở Thượng Hải. Siêu mẫu Thanh Hằng trong chuyến công tác tại Thượng Hải tháng trước cũng đã đến một nhà hàng Michelin để thưởng thức món ăn này. Tâm Anh(TheoSmart Shanghai, Michelin Guide)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Thịt cua lông Thượng Hải mềm ngọt, hấp trong hỗn hợp giấm gạo và nước tương. Món ăn nổi tiếng với hương vị đậm đà từ sốt vàng cam đặc trưng của gạch và thịt cua; được thưởng thức cùng cơm khi đến thành phố này.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>{
+  "id": 42,
+  "style": "news_brief",
+  "article": "Cua lông Thượng Hải là đặc sản cao cấp từng được dùng cho cung đình và giới quý tộc Trung Quốc trước đây, được đánh giá là loại cua ngon bậc nhất thế giới. Loài cua dễ nhận ra nhờ những mảng lông đen xù xì trên các chi. Cua lông Thượng Hải có kích thước bằng một nắm tay người lớn, mọng nước, ẩm và nhiều thịt. Thịt cua chắc, mềm, mịn nên được hấp nguyên con, không nêm gia vị, thịt ngọt hơn so với cua thông thường. Cua lông chỉ sinh sản và phát triển theo mùa, thường vào bốn tháng cuối năm, gạch cua béo. Loại hải sản này giá trị dinh dưỡng cao vì thế giá thành cũng cao, có thể lên tới hơn 100 USD một kg. Cua lông thường được nhúng vào hỗn hợp giấm gạo và nước tương, sau đó phủ gừng thái lát lên trên và hấp. Cua lông thường dùng nóng ngay sau khi hấp và một người trung bình ăn được 2-4 con một lần. Ngoài cách ăn kể trên, người Thượng Hải còn chế biến cua với mì. Thực khách có thể bất ngờ khi biết để làm một bát mì, có thể cần tới 12 con cua. Mỗi ngày, các nhà hàng hoặc những cơ sở chế biến phải nhập cua tươi, hấp cách thủy. Sau đó, cua được bóc bằng tay, tách vỏ, gạch và thịt, nhưng vẫn phải nguyên vẹn, không bị vỡ nát. Thịt và gạch cua được xào chín và làm sốt, cho thêm gia vị là dấm, muối và hành tây. Các gia vị giúp món ăn giữ nguyên mùi và vị tự nhiên nhất. Khi khách gọi món, đa phần các nhà hàng để phần sốt riêng, mì riêng để khách tự trộn, nhưng cũng có những nơi phục vụ phần sốt chung một bát. Gọi là mì cua lông, nhưng khi nhìn vào bát thực khách sẽ thấy lượng thịt sốt cua bao phủ toàn bộ tô mì. Lượng mì tuy không nhiều nhưng tinh túy của món ăn nằm ở đây, bởi vị đậm đà của phần sốt đã ngấm vào sợi mì. Món ăn có màu vàng cam đặc trưng của gạch cua, màu trắng của thịt cua. Khi thưởng thức, thực khách sẽ thấy vị béo bùi và thơm của gạch, thịt cua chắc ngọt, gia vị được nêm nếm vừa đủ, sợi mì dai. Tất cả hòa quyện tạo nên món ăn du khách được khuyên 'phải thử' khi tới Thượng Hải. Ngoài mì, du khách có thể chọn ăn sốt cua lông với cơm, hương vị không thay đổi. Mì cua lông là món ăn được nhiều người yêu thích. Nữ diễn viên Xa Thi Mạn từng gây sốt cách đây vài năm khi khoe bát mì cua lông tại một trong những nhà hàng bình dân nổi tiếng ở Thượng Hải. Siêu mẫu Thanh Hằng trong chuyến công tác tại Thượng Hải tháng trước cũng đã đến một nhà hàng Michelin để thưởng thức món ăn này. Tâm Anh(TheoSmart Shanghai, Michelin Guide)",
+  "summary": "Thịt cua lông Thượng Hải mềm ngọt, hấp trong hỗn hợp giấm gạo và nước tương. Món ăn nổi tiếng với hương vị đậm đà từ sốt vàng cam đặc trưng của gạch và thịt cua; được thưởng thức cùng cơm khi đến thành phố này.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như giá trị dinh dưỡng cao và cách chế biến phức tạp của cua lông Thượng Hải.",
+  "relevance_score": 0.6,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một phần của thông tin quan trọng về cua lông Thượng Hải, bỏ qua các điểm then chốt như mùa sinh sản, giá thành cao và cách chế biến với mì.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng để làm cho nó trở nên đầy đủ hơn."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Lấy cảm hứng từ tô mì Quảng luôn được thực khách yêu thích tại Đà Nẵng hay Hội An, các đầu bếp tại nhà hàng La Plage ở khu nghỉ dưỡng Sheraton Grand Danang Resort đã sáng tạo ra món mì Quảng tôm hùm. Món ăn là thành quả của sự nỗ lực làm mới khẩu vị và chinh phục khách sành ăn. Bếp phó điều hành Vũ Trần cho biết chọn tôm hùm cho 'đứa con tinh thần' của mình vì đây là nguyên liệu không chỉ có giá trị dinh dưỡng mà còn mang giá trị nghệ thuật trong thưởng thức với phong cách trình bày đẹp và sang trọng. Sự kết hợp mì Quảng với tôm hùm mang đến thông điệp sáng tạo, giúp món ăn truyền thống được biết đến nhiều hơn. Đặc điểm của mì Quảng là dễ kết hợp với các nguyên liệu như thịt, cá, tôm, sứa khiến món ăn dễ nấu, có thể bắt gặp ở các quán đường phố đến các nhà hàng sang trọng. Ngoài ra, thành phần đi kèm của mì Quảng là các loại rau Việt Nam, giúp cân bằng vị, đem lại sự tươi mới. Với mì Quảng tôm hùm, khác biệt lớn nhất là nguyên liệu. Những thành phần chính của món ăn gồm tôm hùm, sò điệp, thịt xíu và trứng cá carvia thay cho thịt, tôm và trứng. Ngoài ra, món ăn vẫn có các thành phần quen thuộc ăn kèm như bánh tráng, ớt xanh, rau sống, hoa chuối, sợi mì trộn với dầu phộng. Phần nước sốt của mì Quảng biến tấu từ thịt và tôm sú biển, cùng sự kết hợp của củ năng, được phi thơm với bơ, vỏ tôm, dứa và cà chua, có màu nâu nhạt. Sau hơn một tiếng đun trên lửa để phần nước sốt cô đặc, đầu bếp sẽ chuẩn bị các nguyên liệu đi kèm như ướp thịt xíu, nướng tôm hùm với phô mai, luộc trứng lòng đào với nhiệt độ tiêu chuẩn. Khác biệt tiếp theo của món ăn là cách phục vụ, các thành phần được để riêng trên khay. Khách ăn sẽ tự trang trí phần của mình theo sở thích, hoặc nhờ nhân viên phục vụ hướng dẫn. Helen, khách từ miền Nam ra nghỉ dưỡng ở Đà Nẵng, cho hay ban đầu khá lăn tăn với sự kết hợp này vì mì Quảng là món ăn giản dị, đậm chất địa phương, nhưng khi ăn xong chị nhận xét 'rất đặc biệt và giữ nguyên vị'. Quản lý nhà hàng, An Trần, cho hay nhiều khách cũng nhận xét tương tự vị về món ăn, 'tưởng không ngon mà ngon không tưởng' bởi vị mì Quảng truyền thống không mất đi và còn làm mới khẩu vị. Giá bán tại nhà hàng cho một suất là hơn 800.000 đồng. Tâm Anh</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mì Quảng tôm hùm La Plage tại Sheraton Grand Danang Resort kết hợp nguyên liệu đặc biệt và hương vị truyền thống, tạo thông điệp sáng tạo cho món ăn dễ nấu. Giá 800.000 đồng/suất.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>{
+  "id": 43,
+  "style": "news_brief",
+  "article": "Lấy cảm hứng từ tô mì Quảng luôn được thực khách yêu thích tại Đà Nẵng hay Hội An, các đầu bếp tại nhà hàng La Plage ở khu nghỉ dưỡng Sheraton Grand Danang Resort đã sáng tạo ra món mì Quảng tôm hùm. Món ăn là thành quả của sự nỗ lực làm mới khẩu vị và chinh phục khách sành ăn. Bếp phó điều hành Vũ Trần cho biết chọn tôm hùm cho 'đứa con tinh thần' của mình vì đây là nguyên liệu không chỉ có giá trị dinh dưỡng mà còn mang giá trị nghệ thuật trong thưởng thức với phong cách trình bày đẹp và sang trọng. Sự kết hợp mì Quảng với tôm hùm mang đến thông điệp sáng tạo, giúp món ăn truyền thống được biết đến nhiều hơn. Đặc điểm của mì Quảng là dễ kết hợp với các nguyên liệu như thịt, cá, tôm, sứa khiến món ăn dễ nấu, có thể bắt gặp ở các quán đường phố đến các nhà hàng sang trọng. Ngoài ra, thành phần đi kèm của mì Quảng là các loại rau Việt Nam, giúp cân bằng vị, đem lại sự tươi mới. Với mì Quảng tôm hùm, khác biệt lớn nhất là nguyên liệu. Những thành phần chính của món ăn gồm tôm hùm, sò điệp, thịt xíu và trứng cá carvia thay cho thịt, tôm và trứng. Ngoài ra, món ăn vẫn có các thành phần quen thuộc ăn kèm như bánh tráng, ớt xanh, rau sống, hoa chuối, sợi mì trộn với dầu phộng. Phần nước sốt của mì Quảng biến tấu từ thịt và tôm sú biển, cùng sự kết hợp của củ năng, được phi thơm với bơ, vỏ tôm, dứa và cà chua, có màu nâu nhạt. Sau hơn một tiếng đun trên lửa để phần nước sốt cô đặc, đầu bếp sẽ chuẩn bị các nguyên liệu đi kèm như ướp thịt xíu, nướng tôm hùm với phô mai, luộc trứng lòng đào với nhiệt độ tiêu chuẩn. Khác biệt tiếp theo của món ăn là cách phục vụ, các thành phần được để riêng trên khay. Khách ăn sẽ tự trang trí phần của mình theo sở thích, hoặc nhờ nhân viên phục vụ hướng dẫn. Helen, khách từ miền Nam ra nghỉ dưỡng ở Đà Nẵng, cho hay ban đầu khá lăn tăn với sự kết hợp này vì mì Quảng là món ăn giản dị, đậm chất địa phương, nhưng khi ăn xong chị nhận xét 'rất đặc biệt và giữ nguyên vị'. Quản lý nhà hàng, An Trần, cho hay nhiều khách cũng nhận xét tương tự vị về món ăn, 'tưởng không ngon mà ngon không tưởng' bởi vị mì Quảng truyền thống không mất đi và còn làm mới khẩu vị. Giá bán tại nhà hàng cho một suất là hơn 800.000 đồng. Tâm Anh",
+  "summary": "Mì Quảng tôm hùm La Plage tại Sheraton Grand Danang Resort kết hợp nguyên liệu đặc biệt và hương vị truyền thống, tạo thông điệp sáng tạo cho món ăn dễ nấu. Giá 800.000 đồng/suất.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như cách phục vụ và các thành phần đi kèm của món mì Quảng tôm hùm",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến sự kết hợp của mì Quảng với tôm hùm và giá bán mà không nhắc đến các điểm nổi bật khác của món ăn như sự cân bằng vị và giá trị nghệ thuật",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và truyền đạt được thông điệp chính của món mì Quảng tôm hùm, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chè 'phân gà' có nguồn gốc từ Quảng Đông, Trung Quốc, theo người Hoa du nhập Việt Nam. Món được làm từ bột gạo nhào lá mơ, cắt thành sợi luộc chín, khi ăn chan nước đường gừng. Danh y Triệu Học Mẫn thời nhà Thanh viết trong bản thảo 'Cương mục thập di', mùi của món ăn bắt nguồn từ mùi lá mơ được ví như phân gà, nên món được gọi chè 'thối' hay 'phân'. Lá mơ thuộc loại cây thân leo dễ sống, thường mọc ở ven đường, bờ ruộng, có mùi nồng và được dùng làm vị thuốc. Nhi Trương, 27 tuổi, người gốc Hoa tại quận 5, cho biết chè 'phân gà' là món ăn đặc trưng của người Hoa Phòng Thành, gốc Quảng Đông vào tết Hàn thực. 'Chè này không phổ biến trong cộng đồng người Hoa nên không phải ai cũng biết', Nhi nói. Tuy nhiên, quán trên vỉa hè đường Trịnh Đình Thảo, quận Tân Phú, một trong số rất ít nơi bán chè 'phân gà' lại nổi tiếng và được khách biết đến ngày càng nhiều. Quánmở bán hơn 20 năm, bên cạnh chùa Phật bà Quan Âm nên có lượng khách quen đi chùa ổn định. Gần đây, địa chỉ hút khách sau khi được mạng xã hội chia sẻ nhiều nhờ tên gọi lạ. Chủ quán Nhật Bình cho biết chè 'phân gà' là món truyền thống được gia đình truyền lại. Quán chỉ bán vào ngày rằm và mồng một hằng tháng vì lượng khách đi chùa đông. Ngày thường, chị bán nguyên liệu nấu chè ở chợ Phú Bình, quận 11. Chè được chị Bình nấu trên bếp than, giữ nóng thường xuyên, khi có khách gọi chị mới thả bột vào nồi nấu rồi chan nước đường gừng. Món ăn với sợi bột đen thẫm, dai, thơm mùi lá mơ và gừng. Khách ăn có thể yêu cầu chủ quán điều chỉnh độ ngọt theo khẩu vị. Theo chủ quán, nấu chè 'phân gà' không khó. Khâu quan trọng nhất là trộn lá mơ và bột theo tỷ lệ để vị không bị đắng, mùi thơm dịu. Lá mơ được rửa sạch rồi xay với gạo, sau đó trộn thêm bột năng và đem hấp, chờ nguội thì cắt thành sợi. Sợi bột làm xong có màu đen, được rắc thêm lớp bột khô bên ngoài để chống dính. 'Lá mơ với tỷ lệ vừa đủ, đã qua xử lý nên khi ăn chè không có mùi giống như tên', chị Bình nói. Chủ quán chia sẻ lá mơ tốt cho đường ruột, giúp giảm đau bụng, đầy hơi và thải độc gan nên món không chỉ ăn chơi mà còn tốt cho sức khỏe. Chè nóng kết hợp với gừng làm ấm cơ thể, được nhiều khách chọn thưởng thức vào buổi sáng. Khách ăn chè chủ yếu là khách quen, gọi món không cần nhìn thực đơn. Khu vực bán hàng trên vỉa hè hẹp nên nhiều người chọn mua về. Chị Bình cho hay mỗi lần bán hơn 500 phần, tương đương hơn 10 kg bột. Một phần chè có giá 16.000 đồng. Ngoài chè 'phân gà', quán còn bán chè bắp, cháo bắp đồng giá. Bà Dương Lan, 80 tuổi, sống tại quận 11, cùng con gái đi chùa ghé quán thưởng thức chè và gọi thêm 4 phần mang về. 'Gia đình tôi ai cũng thích món này', bà Lan nói, cho biết đã ăn ở đây từ thời mẹ chị Bình bán. Ghé quán thưởng thức hôm rằm tháng 9, Dương Sắc Minh, 23 tuổi, cho biết anh được mẹ mua chè ở quán cho ăn từ nhỏ. Theo Minh, chè 'phân gà' ít nơi bán nên anh thường giới thiệu bạn bè đến đây thưởng thức. Quán bán từ 8h đến 17h nhưng thường hết sớm. Khách đến ăn tại chỗ phải gửi xe ở khuôn viên chùa Phật bà Quan Âm, giá 5.000 đồng một lượt. Tuấn Anh</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>{
+  "id": 44,
+  "style": "news_brief",
+  "article": "Chè 'phân gà' có nguồn gốc từ Quảng Đông, Trung Quốc, theo người Hoa du nhập Việt Nam. Món được làm từ bột gạo nhào lá mơ, cắt thành sợi luộc chín, khi ăn chan nước đường gừng. Danh y Triệu Học Mẫn thời nhà Thanh viết trong bản thảo 'Cương mục thập di', mùi của món ăn bắt nguồn từ mùi lá mơ được ví như phân gà, nên món được gọi chè 'thối' hay 'phân'. Lá mơ thuộc loại cây thân leo dễ sống, thường mọc ở ven đường, bờ ruộng, có mùi nồng và được dùng làm vị thuốc. Nhi Trương, 27 tuổi, người gốc Hoa tại quận 5, cho biết chè 'phân gà' là món ăn đặc trưng của người Hoa Phòng Thành, gốc Quảng Đông vào tết Hàn thực. 'Chè này không phổ biến trong cộng đồng người Hoa nên không phải ai cũng biết', Nhi nói. Tuy nhiên, quán trên vỉa hè đường Trịnh Đình Thảo, quận Tân Phú, một trong số rất ít nơi bán chè 'phân gà' lại nổi tiếng và được khách biết đến ngày càng nhiều. Quánmở bán hơn 20 năm, bên cạnh chùa Phật bà Quan Âm nên có lượng khách quen đi chùa ổn định. Gần đây, địa chỉ hút khách sau khi được mạng xã hội chia sẻ nhiều nhờ tên gọi lạ. Chủ quán Nhật Bình cho biết chè 'phân gà' là món truyền thống được gia đình truyền lại. Quán chỉ bán vào ngày rằm và mồng một hằng tháng vì lượng khách đi chùa đông. Ngày thường, chị bán nguyên liệu nấu chè ở chợ Phú Bình, quận 11. Chè được chị Bình nấu trên bếp than, giữ nóng thường xuyên, khi có khách gọi chị mới thả bột vào nồi nấu rồi chan nước đường gừng. Món ăn với sợi bột đen thẫm, dai, thơm mùi lá mơ và gừng. Khách ăn có thể yêu cầu chủ quán điều chỉnh độ ngọt theo khẩu vị. Theo chủ quán, nấu chè 'phân gà' không khó. Khâu quan trọng nhất là trộn lá mơ và bột theo tỷ lệ để vị không bị đắng, mùi thơm dịu. Lá mơ được rửa sạch rồi xay với gạo, sau đó trộn thêm bột năng và đem hấp, chờ nguội thì cắt thành sợi. Sợi bột làm xong có màu đen, được rắc thêm lớp bột khô bên ngoài để chống dính. 'Lá mơ với tỷ lệ vừa đủ, đã qua xử lý nên khi ăn chè không có mùi giống như tên', chị Bình nói. Chủ quán chia sẻ lá mơ tốt cho đường ruột, giúp giảm đau bụng, đầy hơi và thải độc gan nên món không chỉ ăn chơi mà còn tốt cho sức khỏe. Chè nóng kết hợp với gừng làm ấm cơ thể, được nhiều khách chọn thưởng thức vào buổi sáng. Khách ăn chè chủ yếu là khách quen, gọi món không cần nhìn thực đơn. Khu vực bán hàng trên vỉa hè hẹp nên nhiều người chọn mua về. Chị Bình cho hay mỗi lần bán hơn 500 phần, tương đương hơn 10 kg bột. Một phần chè có giá 16.000 đồng. Ngoài chè 'phân gà', quán còn bán chè bắp, cháo bắp đồng giá. Bà Dương Lan, 80 tuổi, sống tại quận 11, cùng con gái đi chùa ghé quán thưởng thức chè và gọi thêm 4 phần mang về. 'Gia đình tôi ai cũng thích món này', bà Lan nói, cho biết đã ăn ở đây từ thời mẹ chị Bình bán. Ghé quán thưởng thức hôm rằm tháng 9, Dương Sắc Minh, 23 tuổi, cho biết anh được mẹ mua chè ở quán cho ăn từ nhỏ. Theo Minh, chè 'phân gà' ít nơi bán nên anh thường giới thiệu bạn bè đến đây thưởng thức. Quán bán từ 8h đến 17h nhưng thường hết sớm. Khách đến ăn tại chỗ phải gửi xe ở khuôn viên chùa Phật bà Quan Âm, giá 5.000 đồng một lượt. Tuấn Anh",
+  "summary": "",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin ngoài luồng, không sai số liệu, nhưng có thể làm rõ hơn một số chi tiết về nguồn gốc và ý nghĩa của món chè 'phân gà'",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính về món chè 'phân gà', nhưng có thể sâu hơn về ý nghĩa văn hóa và giá trị dinh dưỡng của món ăn này",
+  "coherence_conciseness_score": 0.85,
+  "coherence_conciseness_reason": "Tóm tắt dễ đọc, logic, nhưng có thể rút ngắn và làm rõ hơn một số đoạn để tăng tính súc tích và dễ hiểu"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Nhà hàng flagship Au Lac Do Brazil Nguyễn Huệ là chi nhánh mới nhất của thương hiệu nướng Churrasco. Từ 2023, chuỗi nhà hàng sáp nhập vào hệ thống IN Dining và có nhiều thay đổi. Thương hiệu tái cấu trúc toàn diện từ kiến trúc, nhận diện thương hiệu đến hình ảnh. Ngoài giữ lại nét đặc trưng của ẩm thực, đơn vị còn chú trọng văn hóa, dịch vụ, thêm vào những nét mới trong hương vị, cách trải nghiệm món ăn. Au Lac Do Brazil ra đời năm 2003. Qua hơn 20 năm, thương hiệu thịt nướng gây ấn tượng với không gian, hương vị ẩm thực đậm chất Nam Mỹ cùng đa dạng hình thức phục vụ như buffet, à-la-carte, set menu... Sự gia nhập của chuỗi nhà hàng góp phần mang đến màu sắc mới cho hệ sinh thái F&amp;B của IN Dining tại TP HCM. Đây cũng là cột mốc tiếp theo họ đạt được trên hành trình hiện thực hóa mục tiêu đi đầu về mảng kinh doanh, quản lý, vận hành các thương hiệu F&amp;B cao cấp tại Việt Nam. Thông qua trải nghiệm ẩm thực, Au Lac Do Brazil còn muốn tạo sự gắn kết tinh thần và giao thoa văn hóa. Thương hiệu thường xuyên cập nhật, làm mới thực đơn để mỗi bữa ăn là một hành trình khám phá văn hóa khác nhau. Hiện nhà hàng phục vụ 16 loại thịt và hải sản, tẩm ướp theo công thức độc quyền từ Nam Mỹ, nướng chậm trực tiếp trên than hồng. 18 món ăn kèm cho thực khách thoải mái lựa chọn theo khẩu vị, sở thích. Bạn có thể chọn gói buffet, gọi món lẻ trên set menu, a-la-carte, hoặc thưởng thức theo kiểu BBQ Platter (khay nướng thập cẩm 10 món) và Wiggle Skewers (5 xiên nướng tổng hợp), phù hợp với những buổi hội họp nhóm, tiệc tùng. Ngoài ẩm thực, Au Lac Do Brazil còn mang đến nhiều hoạt động giải trí thú vị như trình diễn vũ điệu Samba với các vũ công diện trang phục màu sắc trên nền nhạc Latin sôi động. Phong cách phục vụ Rodízio cũng là điểm nhấn tại đây. Nhân viên phục vụ được gọi là Passador, hay 'the meat cutter' (người cắt thịt), liên tục di chuyển với xiên thịt nướng nóng hổi trên tay. Tay còn lại dùng dao bản to thái từng lát thịt trực tiếp tại bàn theo khẩu phần thực khách mong muốn. Với vị trí thuận lợi, ngay điểm trung tâm phố đi bộ Nguyễn Huệ và đường Pasteur, Au Lac Do Brazil mang đến phong cách ẩm thực, thiết kế, hương vị độc đáo đậm chất Nam Mỹ... cho thực khách cảm giác đang dùng bữa trong khu rừng nhiệt đới. Nhà hàng còn góp phần tạo nên không khí lễ hội sôi động ngay trung tâm Sài Gòn, là điểm đến đáng cân nhắc cho những tín đồ ẩm thực. Á Hiên</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Brazil thương hiệu Churrasco tái cấu trúc toàn diện từ kiến trúc đến hương vị và dịch vụ, ra đời năm 2003 với đa dạng hình thức phục vụ như buffet, à-la-carte, set menu. Nhà hàng hiện phục vụ 16 loại thịt nướng độc quyền theo công thức Nam Mỹ tẩm ướp và nướng trực tiếp trên than hồng.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>{
+  "id": 45,
+  "style": "news_brief",
+  "article": "Nhà hàng flagship Au Lac Do Brazil Nguyễn Huệ là chi nhánh mới nhất của thương hiệu nướng Churrasco. Từ 2023, chuỗi nhà hàng sáp nhập vào hệ thống IN Dining và có nhiều thay đổi. Thương hiệu tái cấu trúc toàn diện từ kiến trúc, nhận diện thương hiệu đến hình ảnh. Ngoài giữ lại nét đặc trưng của ẩm thực, đơn vị còn chú trọng văn hóa, dịch vụ, thêm vào những nét mới trong hương vị, cách trải nghiệm món ăn. Au Lac Do Brazil ra đời năm 2003. Qua hơn 20 năm, thương hiệu thịt nướng gây ấn tượng với không gian, hương vị ẩm thực đậm chất Nam Mỹ cùng đa dạng hình thức phục vụ như buffet, à-la-carte, set menu... Sự gia nhập của chuỗi nhà hàng góp phần mang đến màu sắc mới cho hệ sinh thái F&amp;B của IN Dining tại TP HCM. Đây cũng là cột mốc tiếp theo họ đạt được trên hành trình hiện thực hóa mục tiêu đi đầu về mảng kinh doanh, quản lý, vận hành các thương hiệu F&amp;B cao cấp tại Việt Nam. Thông qua trải nghiệm ẩm thực, Au Lac Do Brazil còn muốn tạo sự gắn kết tinh thần và giao thoa văn hóa. Thương hiệu thường xuyên cập nhật, làm mới thực đơn để mỗi bữa ăn là một hành trình khám phá văn hóa khác nhau. Hiện nhà hàng phục vụ 16 loại thịt và hải sản, tẩm ướp theo công thức độc quyền từ Nam Mỹ, nướng chậm trực tiếp trên than hồng. 18 món ăn kèm cho thực khách thoải mái lựa chọn theo khẩu vị, sở thích. Bạn có thể chọn gói buffet, gọi món lẻ trên set menu, a-la-carte, hoặc thưởng thức theo kiểu BBQ Platter (khay nướng thập cẩm 10 món) và Wiggle Skewers (5 xiên nướng tổng hợp), phù hợp với những buổi hội họp nhóm, tiệc tùng. Ngoài ẩm thực, Au Lac Do Brazil còn mang đến nhiều hoạt động giải trí thú vị như trình diễn vũ điệu Samba với các vũ công diện trang phục màu sắc trên nền nhạc Latin sôi động. Phong cách phục vụ Rodízio cũng là điểm nhấn tại đây. Nhân viên phục vụ được gọi là Passador, hay 'the meat cutter' (người cắt thịt), liên tục di chuyển với xiên thịt nướng nóng hổi trên tay. Tay còn lại dùng dao bản to thái từng lát thịt trực tiếp tại bàn theo khẩu phần thực khách mong muốn. Với vị trí thuận lợi, ngay điểm trung tâm phố đi bộ Nguyễn Huệ và đường Pasteur, Au Lac Do Brazil mang đến phong cách ẩm thực, thiết kế, hương vị độc đáo đậm chất Nam Mỹ... cho thực khách cảm giác đang dùng bữa trong khu rừng nhiệt đới. Nhà hàng còn góp phần tạo nên không khí lễ hội sôi động ngay trung tâm Sài Gòn, là điểm đến đáng cân nhắc cho những tín đồ ẩm thực. Á Hiên",
+  "summary": "Brazil thương hiệu Churrasco tái cấu trúc toàn diện từ kiến trúc đến hương vị và dịch vụ, ra đời năm 2003 với đa dạng hình thức phục vụ như buffet, à-la-carte, set menu. Nhà hàng hiện phục vụ 16 loại thịt nướng độc quyền theo công thức Nam Mỹ tẩm ướp và nướng trực tiếp trên than hồng.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như mục tiêu của thương hiệu và hệ thống IN Dining, cũng như các hoạt động giải trí tại nhà hàng.",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ tập trung vào một số điểm chính như hình thức phục vụ và thực đơn, nhưng bỏ qua các khía cạnh quan trọng khác như vị trí, phong cách thiết kế và không khí lễ hội.",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt được viết một cách rõ ràng, logic và dễ đọc, tuy nhiên có thể cải thiện bằng cách thêm một số chi tiết quan trọng và tránh sự trùng lặp về thông tin."
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Mùa trung thu năm nay, khách sạn Lotte Sài Gòn ra mắt hai phiên bản hộp trắng ngà và nâu với họa tiết rồng uốn lượn quanh mặt trăng. Hình ảnh mang đậm dấu ấn Á Đông, biểu trưng cho ý nghĩa ước mong sự phồn thịnh và quyền lực. Truyền thuyết giả tưởng Cá chép hóa rồng thường được dùng để ẩn dụ hành trình vượt khó, đại diện cho sự quyết tâm, lòng kiên định. Hình ảnh cá chép nhỏ cưỡi sóng lớn, vượt Vũ Môn hóa thành Thần Long còn thường được dùng biểu đạt thay cho sự bền bỉ, không ngừng phấn đấu, nỗ lực. Lotte Sài Gòn muốn dùng truyền thuyết này để gửi gắm những lời chúc ý nghĩa và khát vọng thành công, sung túc vào hộp bánh Trung thu năm nay. BST 'Lý ngư hóa long' gồm hai lựa chọn hộp màu trắng ngà - Deluxe và màu nâu - Premium. Mỗi hộp gồm 4 bánh với 4 vị khác nhau. Phiên bản Deluxe đi kèm hai hộp trà sen, giá 1,45 triệu đồng một set. Bản Premium đi kèm một hộp trà sen và một hộp nhân sâm, giá 1,75 triệu đồng. Năm nay, Lotte Sài Gòn ra mắt 4 loại nhân bánh gồm: vị ba lớp với khoai môn, dừa macadamia và trứng muối; thập cẩm hải sản sò điệp sốt trứng muối; thập cẩm gà hầm thảo mộc sốt tiêu đen kiểu Tứ Xuyên và trứng muối; cuối cùng là sen dưỡng nhan tổ yến cung đình Huế. Điểm nhấn của hộp bánh trung thu premium năm nay là hộp nước hồng sâm Hàn Quốc. Đây là thức uống truyền thống có giá trị dinh dưỡng cao từ xứ sở kim chi. Dưỡng chất của hồng sâm có tác dụng hỗ trợ điều hòa huyết áp, tim mạch và chống lão hóa. Kết hợp với trà sen và 4 loại nhân bánh chất lượng, hộp Premium sẽ là lựa chọn lý tưởng làm quà tặng người thân, đối tác, bạn bè. Đặc biệt, năm nay khách sạn Lotte Sài Gòn còn sử dụng chất liệu giấy nhẹ cho hộp bánh, hướng tới bảo vệ môi trường. Việc này góp phần thể hiện cam kết bền vững và trách nhiệm của khách sạn với cộng đồng. Lotte Sài Gòn kỳ vọng hai phiên bản hộp bánh trung thu Lý ngư hóa long năm nay sẽ giúp mang đến cho khách hàng mùa Tết trung thu nhiều ý nghĩa. Theo đại diện khách sạn, BST Lý ngư hóa long 2024 là sự kết hợp hài hòa giữa sang trọng và trải nghiệm cá nhân hóa. Đó cũng là lý do sản phẩm chỉ sản xuất với số lượng giới hạn, góp phần gia tăng giá trị của hộp quà trong dịp tết đoàn viên. Á Hiên</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hoa ngà và nâu, Lotte Sài Gòn ra mắt BST 'Lý ngư hóa long' gồm hộp Deluxe 1.45 triệu đồng và Premium 1.75 triệu đồng; mỗi hộp có 4 bánh vị khác nhau với nước hồng sâm Hàn Quốc và giấy nhẹ bảo vệ môi trường. Lotte kỳ vọng phiên bản năm nay mang ý nghĩa tết trung thu cho khách, tăng giá trị quà Tết đoàn viên.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>{
+  "id": 46,
+  "style": "news_brief",
+  "article": "Mùa trung thu năm nay, khách sạn Lotte Sài Gòn ra mắt hai phiên bản hộp trắng ngà và nâu với họa tiết rồng uốn lượn quanh mặt trăng. Hình ảnh mang đậm dấu ấn Á Đông, biểu trưng cho ý nghĩa ước mong sự phồn thịnh và quyền lực. Truyền thuyết giả tưởng Cá chép hóa rồng thường được dùng để ẩn dụ hành trình vượt khó, đại diện cho sự quyết tâm, lòng kiên định. Hình ảnh cá chép nhỏ cưỡi sóng lớn, vượt Vũ Môn hóa thành Thần Long còn thường được dùng biểu đạt thay cho sự bền bỉ, không ngừng phấn đấu, nỗ lực. Lotte Sài Gòn muốn dùng truyền thuyết này để gửi gắm những lời chúc ý nghĩa và khát vọng thành công, sung túc vào hộp bánh Trung thu năm nay. BST 'Lý ngư hóa long' gồm hai lựa chọn hộp màu trắng ngà - Deluxe và màu nâu - Premium. Mỗi hộp gồm 4 bánh với 4 vị khác nhau. Phiên bản Deluxe đi kèm hai hộp trà sen, giá 1,45 triệu đồng một set. Bản Premium đi kèm một hộp trà sen và một hộp nhân sâm, giá 1,75 triệu đồng. Năm nay, Lotte Sài Gòn ra mắt 4 loại nhân bánh gồm: vị ba lớp với khoai môn, dừa macadamia và trứng muối; thập cẩm hải sản sò điệp sốt trứng muối; thập cẩm gà hầm thảo mộc sốt tiêu đen kiểu Tứ Xuyên và trứng muối; cuối cùng là sen dưỡng nhan tổ yến cung đình Huế. Điểm nhấn của hộp bánh trung thu premium năm nay là hộp nước hồng sâm Hàn Quốc. Đây là thức uống truyền thống có giá trị dinh dưỡng cao từ xứ sở kim chi. Dưỡng chất của hồng sâm có tác dụng hỗ trợ điều hòa huyết áp, tim mạch và chống lão hóa. Kết hợp với trà sen và 4 loại nhân bánh chất lượng, hộp Premium sẽ là lựa chọn lý tưởng làm quà tặng người thân, đối tác, bạn bè. Đặc biệt, năm nay khách sạn Lotte Sài Gòn còn sử dụng chất liệu giấy nhẹ cho hộp bánh, hướng tới bảo vệ môi trường. Việc này góp phần thể hiện cam kết bền vững và trách nhiệm của khách sạn với cộng đồng. Lotte Sài Gòn kỳ vọng hai phiên bản hộp bánh trung thu Lý ngư hóa long năm nay sẽ giúp mang đến cho khách hàng mùa Tết trung thu nhiều ý nghĩa. Theo đại diện khách sạn, BST Lý ngư hóa long 2024 là sự kết hợp hài hòa giữa sang trọng và trải nghiệm cá nhân hóa. Đó cũng là lý do sản phẩm chỉ sản xuất với số lượng giới hạn, góp phần gia tăng giá trị của hộp quà trong dịp tết đoàn viên. Á Hiên",
+  "summary": "Hoa ngà và nâu, Lotte Sài Gòn ra mắt BST 'Lý ngư hóa long' gồm hộp Deluxe 1.45 triệu đồng và Premium 1.75 triệu đồng; mỗi hộp có 4 bánh vị khác nhau với nước hồng sâm Hàn Quốc và giấy nhẹ bảo vệ môi trường. Lotte kỳ vọng phiên bản năm nay mang ý nghĩa tết trung thu cho khách, tăng giá trị quà Tết đoàn viên.",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như ý nghĩa của truyền thuyết 'Lý ngư hóa long' và các vị bánh cụ thể",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính như giá cả và thành phần của hộp bánh nhưng thiếu thông tin về ý nghĩa và giá trị của sản phẩm",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt rõ ràng, dễ đọc và không lặp từ nhưng có thể cải thiện bằng cách thêm một số chi tiết quan trọng và sắp xếp thông tin một cách hợp lý hơn"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Tiệm xôi chè nằm trên đường Dương Tử Giang, quận 5 - con đường chuyên kinh doanh các mặt hàng linh kiện xe máy, vải vóc. Tiệm mở cửa hơn 40 năm, truyền qua hai đời, chưa một lần đổi địa chỉ và thực đơn chỉ phục vụ hai món gồm xôi xiêm và chè ba màu. Chị Huỳnh Thị Ngọc Yến, 50 tuổi, chủ tiệm đời thứ hai, cho hay mẹ chồng chị mở cửa hàng này sau khi học được công thức từ một người Campuchia di cư sang Việt Nam từ những năm 1970. Ngày đầu mở cửa, khách hàng của tiệm chủ yếu là người Hoa sinh sống trong khu vực Chợ Lớn. Xôi xiêm cốt dừa sầu riêng nóng hổi là món ''đinh' của tiệm hơn hai thập kỷ qua. Chị Yến cho hay đây là kiểu xôi ngọt. Thái Lan cũng có món xôi này. Xôi được nấu từ nếp ngỗng, loại nếp dẻo, thơm nổi tiếng Nam Bộ. Nguyên liệu làm nên linh hồn món này phải kể đến cadé, một loại sốt làm từ bơ, sữa, trứng, nước cốt dừa - món ăn truyền thống của người Malaysia gốc Hoa. Ngày nay, cadé có nhiều biến thể. Tùy vào công thức của đầu bếp, món sốt này có độ sánh, đặc khác nhau. Cadé của quán chị Yến có kết cấu đặc, mềm, vị béo ngậy và màu sắc gần giống bánh flan. Nguyên liệu quan trọng không kém là nước cốt dừa trộn cơm sầu riêng. Một phần hoàn chỉnh có xôi ở lớp dưới cùng, 1-2 lát sốt cadé và cốt dừa dưới lên trên. Chủ tiệm cho biết hiện ở TP HCM không nhiều nơi phục vụ món xôi xiêm. Ngoài quán của chị, chỉ có một vài quán nằm trong khu chợ Campuchia ở quận 10. Nhờ hương vị xôi xiêm khác biệt, quán có nhiều khách ruột. Chị Nguyễn Thị Yến Phi, đến từ Đồng Tháp, chia sẻ biết đến quán này ba năm trước và là khách quen. Chị Phi cho hay món xôi xiêm quen thuộc với nhiều người miền Tây sinh sống gần khu vực giáp biên giới Campuchia như chị. 'Ở Sài Gòn, khó tìm được hàng bán món xôi này', chị Phi nói. Theo chị Phi, hương vị món xôi của quángần giống món hồi nhỏ chị hay ăn. Tuy nhiên, xôi ở đây phục vụ nóng, phiên bản miền Tây dùng xôi để nguội. Phần cốt dừa ở miền Tây thường không thêm sầu riêng. Giá một đĩa xôi ở tiệm là 30.000 đồng. 'Đắt gần gấp đôi so với ở Đồng Tháp', chị Phi nói thêm. Món ăn thứ hai trong thực đơn quán chị Yến là chè ba màu. Nguyên liệu có đậu đỏ, đậu xanh, cadé, thạch sương sáo, nước cốt dừa. Các nguyên liệu này đều được chị Yến sơ chế vào đêm hôm trước, nấu từ buổi sáng và phục vụ từ 14h chiều.Chè được múc sẵn thành từng phần, khi khách gọi sẽ thêm đá vào và cốt dừa. Mỗi phần có giá 30.000 đồng. Ăn chè hay xôi, quán chị Yến cũng chuẩn bị một ấm trà lạnh với đá bào cho mỗi bàn. Trà giúp giảm độ ngọt của hai món ăn chính. Quán chècó diện tích khiêm tốn, không gian trong nhà chỉ vừa 2 bàn với 4 chỗ ngồi. Khu vực khách ngồi chính là vỉa hè trước căn nhà, xếp 3-4 bàn. Buổi chiều đến tối, các cửa hàng bán phụ tùng xe máy kế bên đóng cửa nên có không gian cho quán chị Yến đón khách. Chị cho hay hiện Sài Gòn đang vào mùa mưa, buổi chiều dễ mưa lớn nên lượng khách ngồi lại không nhiều bằng buổi tối. Xế chiều, khách ghé quán thường mua mang về. Bài và ảnh:Bích Phương</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>{
+  "id": 47,
+  "style": "news_brief",
+  "article": "Tiệm xôi chè nằm trên đường Dương Tử Giang, quận 5 - con đường chuyên kinh doanh các mặt hàng linh kiện xe máy, vải vóc. Tiệm mở cửa hơn 40 năm, truyền qua hai đời, chưa một lần đổi địa chỉ và thực đơn chỉ phục vụ hai món gồm xôi xiêm và chè ba màu. Chị Huỳnh Thị Ngọc Yến, 50 tuổi, chủ tiệm đời thứ hai, cho hay mẹ chồng chị mở cửa hàng này sau khi học được công thức từ một người Campuchia di cư sang Việt Nam từ những năm 1970. Ngày đầu mở cửa, khách hàng của tiệm chủ yếu là người Hoa sinh sống trong khu vực Chợ Lớn. Xôi xiêm cốt dừa sầu riêng nóng hổi là món ''đinh' của tiệm hơn hai thập kỷ qua. Chị Yến cho hay đây là kiểu xôi ngọt. Thái Lan cũng có món xôi này. Xôi được nấu từ nếp ngỗng, loại nếp dẻo, thơm nổi tiếng Nam Bộ. Nguyên liệu làm nên linh hồn món này phải kể đến cadé, một loại sốt làm từ bơ, sữa, trứng, nước cốt dừa - món ăn truyền thống của người Malaysia gốc Hoa. Ngày nay, cadé có nhiều biến thể. Tùy vào công thức của đầu bếp, món sốt này có độ sánh, đặc khác nhau. Cadé của quán chị Yến có kết cấu đặc, mềm, vị béo ngậy và màu sắc gần giống bánh flan. Nguyên liệu quan trọng không kém là nước cốt dừa trộn cơm sầu riêng. Một phần hoàn chỉnh có xôi ở lớp dưới cùng, 1-2 lát sốt cadé và cốt dừa dưới lên trên. Chủ tiệm cho biết hiện ở TP HCM không nhiều nơi phục vụ món xôi xiêm. Ngoài quán của chị, chỉ có một vài quán nằm trong khu chợ Campuchia ở quận 10. Nhờ hương vị xôi xiêm khác biệt, quán có nhiều khách ruột. Chị Nguyễn Thị Yến Phi, đến từ Đồng Tháp, chia sẻ biết đến quán này ba năm trước và là khách quen. Chị Phi cho hay món xôi xiêm quen thuộc với nhiều người miền Tây sinh sống gần khu vực giáp biên giới Campuchia như chị. 'Ở Sài Gòn, khó tìm được hàng bán món xôi này', chị Phi nói. Theo chị Phi, hương vị món xôi của quángần giống món hồi nhỏ chị hay ăn. Tuy nhiên, xôi ở đây phục vụ nóng, phiên bản miền Tây dùng xôi để nguội. Phần cốt dừa ở miền Tây thường không thêm sầu riêng. Giá một đĩa xôi ở tiệm là 30.000 đồng. 'Đắt gần gấp đôi so với ở Đồng Tháp', chị Phi nói thêm. Món ăn thứ hai trong thực đơn quán chị Yến là chè ba màu. Nguyên liệu có đậu đỏ, đậu xanh, cadé, thạch sương sáo, nước cốt dừa. Các nguyên liệu này đều được chị Yến sơ chế vào đêm hôm trước, nấu từ buổi sáng và phục vụ từ 14h chiều.Chè được múc sẵn thành từng phần, khi khách gọi sẽ thêm đá vào và cốt dừa. Mỗi phần có giá 30.000 đồng. Ăn chè hay xôi, quán chị Yến cũng chuẩn bị một ấm trà lạnh với đá bào cho mỗi bàn. Trà giúp giảm độ ngọt của hai món ăn chính. Quán chècó diện tích khiêm tốn, không gian trong nhà chỉ vừa 2 bàn với 4 chỗ ngồi. Khu vực khách ngồi chính là vỉa hè trước căn nhà, xếp 3-4 bàn. Buổi chiều đến tối, các cửa hàng bán phụ tùng xe máy kế bên đóng cửa nên có không gian cho quán chị Yến đón khách. Chị cho hay hiện Sài Gòn đang vào mùa mưa, buổi chiều dễ mưa lớn nên lượng khách ngồi lại không nhiều bằng buổi tối. Xế chiều, khách ghé quán thường mua mang về. Bài và ảnh:Bích Phương",
+  "summary": "",
+  "faithfulness_score": 0.9,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin ngoài luồng, không sai số liệu, nhưng có thể làm rõ hơn một số chi tiết như công thức của món xôi xiêm và chè ba màu",
+  "relevance_score": 0.8,
+  "relevance_reason": "Tóm tắt bao gồm các điểm chính như lịch sử của tiệm, hai món ăn đặc trưng, nhưng có thể sâu hơn về ý nghĩa của các món ăn này với khách hàng",
+  "coherence_conciseness_score": 0.85,
+  "coherence_conciseness_reason": "Tóm tắt dễ đọc, logic, nhưng có thể rút ngắn một số chi tiết phụ để tập trung vào thông tin quan trọng"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cơm niêu vốn là món ăn truyền thống giản dị, mang đậm bản sắc văn hóa Việt Nam từ Bắc chí Nam. Chiếc niêu đất đựng cơm cũng trở thành một phần đặc trưng trong bức tranh ẩm thực nước nhà, được nhiều du khách quốc tế yêu thích. Với mong muốn đưa hương vị cơm niêu đậm bản sắc Việt vươn tầm quốc tế, chạm đến nhiều thực khách nước ngoài trên toàn thế giới, Cơm niêu Thiên Lý không ngừng cải thiện chất lượng phục vụ và hương vị. Về hương vị, nhà hàng cho biết để mỗi thực khách cảm nhận được tinh hoa văn hóa ẩm thực Việt, họ đã thu thập ý kiến, cân đo đong đếm gia vị để cho ra những món ăn hợp khẩu vị đại đa số khách hàng ở cả ba miền. Về nguyên liệu, nhà hàng kiểm tra chất lượng gạo, đảm bảo từng niêu cơm đều có độ chín vừa phải, hạt cơm mềm, nở đều và thoảng hương thơm. Với niêu cơm cháy, mặt đáy phải vàng đều, cho cảm giác giòn rụm khi ăn. Đại diện Cơm niêu Thiên Lý cho biết mỗi niêu cơm đều chứa đựng tâm ý của người nấu. Không chỉ có gạo mà còn giao hòa văn hóa truyền thống với những công thức biến tấu sáng tạo và nguyên liệu tươi ngon. Nhờ đó, mỗi món ăn Việt tại đây có thể hợp với khẩu vị cả những thực khách phương Tây. Cơm niêu Thiên Lý đặt mục tiêu đạt 300 cửa hàng trên toàn quốc vào cuối năm 2028. Đại diện nhà hàng cho biết đây sẽ là bước đệm vững chắc để hiện thực hóa giấc mơ chinh phục thị trường toàn cầu, đưa hương vị Việt Nam vươn xa trên bản đồ ẩm thực thế giới. Ngoài phục vụ món ăn truyền thống, nhà hàng còn là nơi hình thành nên cộng đồng yêu ẩm thực Việt Nam, thông qua mô hình nhượng quyền thương hiệu. Cơm niêu Thiên Lý cho biết đơn vị muốn mở ra cơ hội cho những người đam mê kinh doanh lĩnh vực ẩm thực, cùng chung tay gìn giữ và phát triển nét đẹp văn hóa truyền thống, tạo nên làn sóng ẩm thực Việt. 'Mới đây, chúng tôi có cơ hội đồng hành cùng cuộc thi Miss Grand Vietnam 2024. Thông qua cuộc thi, Cơm Niêu Thiên Lý kỳ vọng có thể giúp tôn vinh vẻ đẹp, tài năng của phụ nữ Việt Nam, đồng thời góp phần tạo dấu ấn, mở đường cho hành trình đưa cơm niêu và ẩm thực Việt ra thế giới', đại diện nhà hàng cho biết. Á Hiên</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cơm Niêu Thiên Lý nâng cao chất lượng phục vụ và hương vị, thu thập phản hồi khách hàng. Nhà hàng kiểm tra gạo tươi ngon, mở 300 cửa hàng toàn quốc năm 2028, hình thành cộng đồng yêu thích ẩm thực Việt Nam thông qua mô hình nhượng quyền thương hiệu.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>{
+  "id": 48,
+  "style": "news_brief",
+  "article": "Cơm niêu vốn là món ăn truyền thống giản dị, mang đậm bản sắc văn hóa Việt Nam từ Bắc chí Nam. Chiếc niêu đất đựng cơm cũng trở thành một phần đặc trưng trong bức tranh ẩm thực nước nhà, được nhiều du khách quốc tế yêu thích. Với mong muốn đưa hương vị cơm niêu đậm bản sắc Việt vươn tầm quốc tế, chạm đến nhiều thực khách nước ngoài trên toàn thế giới, Cơm niêu Thiên Lý không ngừng cải thiện chất lượng phục vụ và hương vị. Về hương vị, nhà hàng cho biết để mỗi thực khách cảm nhận được tinh hoa văn hóa ẩm thực Việt, họ đã thu thập ý kiến, cân đo đong đếm gia vị để cho ra những món ăn hợp khẩu vị đại đa số khách hàng ở cả ba miền. Về nguyên liệu, nhà hàng kiểm tra chất lượng gạo, đảm bảo từng niêu cơm đều có độ chín vừa phải, hạt cơm mềm, nở đều và thoảng hương thơm. Với niêu cơm cháy, mặt đáy phải vàng đều, cho cảm giác giòn rụm khi ăn. Đại diện Cơm niêu Thiên Lý cho biết mỗi niêu cơm đều chứa đựng tâm ý của người nấu. Không chỉ có gạo mà còn giao hòa văn hóa truyền thống với những công thức biến tấu sáng tạo và nguyên liệu tươi ngon. Nhờ đó, mỗi món ăn Việt tại đây có thể hợp với khẩu vị cả những thực khách phương Tây. Cơm niêu Thiên Lý đặt mục tiêu đạt 300 cửa hàng trên toàn quốc vào cuối năm 2028. Đại diện nhà hàng cho biết đây sẽ là bước đệm vững chắc để hiện thực hóa giấc mơ chinh phục thị trường toàn cầu, đưa hương vị Việt Nam vươn xa trên bản đồ ẩm thực thế giới. Ngoài phục vụ món ăn truyền thống, nhà hàng còn là nơi hình thành nên cộng đồng yêu ẩm thực Việt Nam, thông qua mô hình nhượng quyền thương hiệu. Cơm niêu Thiên Lý cho biết đơn vị muốn mở ra cơ hội cho những người đam mê kinh doanh lĩnh vực ẩm thực, cùng chung tay gìn giữ và phát triển nét đẹp văn hóa truyền thống, tạo nên làn sóng ẩm thực Việt. 'Mới đây, chúng tôi có cơ hội đồng hành cùng cuộc thi Miss Grand Vietnam 2024. Thông qua cuộc thi, Cơm Niêu Thiên Lý kỳ vọng có thể giúp tôn vinh vẻ đẹp, tài năng của phụ nữ Việt Nam, đồng thời góp phần tạo dấu ấn, mở đường cho hành trình đưa cơm niêu và ẩm thực Việt ra thế giới', đại diện nhà hàng cho biết. Á Hiên",
+  "summary": "Cơm Niêu Thiên Lý nâng cao chất lượng phục vụ và hương vị, thu thập phản hồi khách hàng. Nhà hàng kiểm tra gạo tươi ngon, mở 300 cửa hàng toàn quốc năm 2028, hình thành cộng đồng yêu thích ẩm thực Việt Nam thông qua mô hình nhượng quyền thương hiệu.",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin sai lệch nhưng bỏ qua một số chi tiết quan trọng như việc nhà hàng muốn đưa hương vị cơm niêu đậm bản sắc Việt vươn tầm quốc tế và tham gia cuộc thi Miss Grand Vietnam 2024",
+  "relevance_score": 0.7,
+  "relevance_reason": "Tóm tắt chỉ đề cập đến một số điểm chính như nâng cao chất lượng phục vụ và hương vị, mở cửa hàng nhưng bỏ qua thông tin về việc nhà hàng muốn hình thành cộng đồng yêu ẩm thực Việt Nam và tham gia các sự kiện quan trọng",
+  "coherence_conciseness_score": 0.9,
+  "coherence_conciseness_reason": "Tóm tắt ngắn gọn, dễ đọc và logic, tuy nhiên có thể thêm một số chi tiết quan trọng để làm cho tóm tắt trở nên đầy đủ hơn"
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Thành phố biển Quy Nhơn không chỉ nổi tiếng với vẻ đẹp tự nhiên mà còn hấp dẫn du khách bởi nền ẩm thực phong phú và đa dạng. Với những ai yêu thích khám phá hương vị mới lạ, Quy Nhơn là điểm đến lý tưởng. Dưới đây là những món ăn du khách không nên bỏ qua khi đến thăm thành phố biển xinh đẹp này. Gỏi ốc giấy Gỏi ốc giấy là một trong những món ăn đặc trưng của Quy Nhơn, mang hương vị thanh mát. Ốc giấy còn gọi là ốc giấm - một loại ốc có vỏ mỏng, dày và ngọt thịt. Để chế biến món ăn này, người đầu bếp sẽ hấp chín ốc, tách vỏ và thái miếng vừa ăn. Ốc được trộn cùng rau sống, đu đủ bào sợi, cà rốt, hành tím, đậu phộng, rau thơm và các loại gia vị. Sốt trộn gỏi được làm từ nước mắm chua ngọt pha cùng ớt và chanh, tạo nên hương vị đậm đà, chua cay. Món này thường được người địa phương sử dụng làm món khai vị nhằm kích thích vị giác. Gỏi được bán ở các quán hải sản, có giá dao động từ 25.000 đến 80.000 đồng một đĩa, tùy số lượng. Du khách có thể tìm mua ốc giấy tươi ở các chợ trong tỉnh với mức 120.000 đến 160.000 đồng một kg. Cá cơm mờm khô rim Cá cơm mờm khô rim là món ăn dân dã, được nhiều gia đình Việt và du khách yêu thích. Cá mờm là loại cá có kích thước rất nhỏ, thân hình thuôn dài, dẹp hai bên, màu trắng, dát ánh bạc. Cá sau khi phơi khô sẽ được mang rửa sạch, rim cùng với đường, nước mắm, tỏi và ớt. Độ dai ngọt của thịt cá kết hợp với vị cay ngọt ngọt tạo nên một món ăn đậm đà và tốn cơm. Không chỉ là món 'lai rai' phổ biến ở quán nhậu, nhiều du khách cũng chọn món ăn này để làm quà khi đi du lịch Quy Nhơn. Cá được bán ở cửa hàng chuyên đặc sản hoặc có thể tìm mua ở một số chợ trong các làng chài. Cá chình mun Châu Trúc Cá chình mun là loại cá nước ngọt, thuộc họ nhà lươn, chạch nhưng kích thước lớn. Thịt cá chắc, có vị béo. Cá chỉ có ở đầm Trà Ổ hay còn gọi là đầm Châu Trúc thuộc huyện Phù Mỹ (tỉnh Bình Định). Trung bình, chình mun Châu Trúc dài gần 1 mét, kích thước tương đương bắp đùi người trưởng thành. Những con nuôi lâu năm còn lớn hơn. Đây là nguyên liệu chính cho nhiều món đặc sản tại Quy Nhơn. Cá thường được chế biến thành các dạng như nướng, hấp gừng, xào lăn hay cháo cá chình. Không chỉ hấp dẫn bởi hương vị thơm ngon, cá chình mun còn giàu dinh dưỡng, có nhiều dưỡng chất tốt cho sức khỏe. Bò chua Tây Sơn Bò chua Tây là đặc sản của vùng đất Bình Định. Thịt bò làm món này được tuyển chọn kỹ lưỡng, sau đó làm sạch, lọc hết phần lõi gân, cắt miếng mỏng vừa ăn. Thịt sau khi sơ chế được ướp đều với nước mắm, nước đường thắng lên để nguội và các loại gia vị riềng, tỏi, ớt, hạt tiêu. Đầu bếp sẽ cho hỗn hợp vào hũ, đậy nắp kín, để từ 5 đến 7 ngày cho lên men tự nhiên. Món ăn có vị chua thanh, ngọt dịu và cay nồng, thường được ăn kèm với rau sống và cuốn bánh tráng. Đây là món ăn không thể bỏ qua khi du lịch Quy Nhơn, đặc biệt đối với những ai yêu thích hương vị chua cay đậm đà. Ở Bình Định, chỉ có một số quán có món ăn này. Quán Hoa An (đường bờ kè, thị trấn Phú Phong) là một trong những quán được nhiều thực khách lui tới. Bò chua Tây Sơn đang được bán với mức giá khoảng 240.000 đồng cho một hũ 700 gam. Nhung Nhung</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>{
+  "id": 49,
+  "style": "news_brief",
+  "article": "Thành phố biển Quy Nhơn không chỉ nổi tiếng với vẻ đẹp tự nhiên mà còn hấp dẫn du khách bởi nền ẩm thực phong phú và đa dạng. Với những ai yêu thích khám phá hương vị mới lạ, Quy Nhơn là điểm đến lý tưởng. Dưới đây là những món ăn du khách không nên bỏ qua khi đến thăm thành phố biển xinh đẹp này. Gỏi ốc giấy Gỏi ốc giấy là một trong những món ăn đặc trưng của Quy Nhơn, mang hương vị thanh mát. Ốc giấy còn gọi là ốc giấm - một loại ốc có vỏ mỏng, dày và ngọt thịt. Để chế biến món ăn này, người đầu bếp sẽ hấp chín ốc, tách vỏ và thái miếng vừa ăn. Ốc được trộn cùng rau sống, đu đủ bào sợi, cà rốt, hành tím, đậu phộng, rau thơm và các loại gia vị. Sốt trộn gỏi được làm từ nước mắm chua ngọt pha cùng ớt và chanh, tạo nên hương vị đậm đà, chua cay. Món này thường được người địa phương sử dụng làm món khai vị nhằm kích thích vị giác. Gỏi được bán ở các quán hải sản, có giá dao động từ 25.000 đến 80.000 đồng một đĩa, tùy số lượng. Du khách có thể tìm mua ốc giấy tươi ở các chợ trong tỉnh với mức 120.000 đến 160.000 đồng một kg. Cá cơm mờm khô rim Cá cơm mờm khô rim là món ăn dân dã, được nhiều gia đình Việt và du khách yêu thích. Cá mờm là loại cá có kích thước rất nhỏ, thân hình thuôn dài, dẹp hai bên, màu trắng, dát ánh bạc. Cá sau khi phơi khô sẽ được mang rửa sạch, rim cùng với đường, nước mắm, tỏi và ớt. Độ dai ngọt của thịt cá kết hợp với vị cay ngọt ngọt tạo nên một món ăn đậm đà và tốn cơm. Không chỉ là món 'lai rai' phổ biến ở quán nhậu, nhiều du khách cũng chọn món ăn này để làm quà khi đi du lịch Quy Nhơn. Cá được bán ở cửa hàng chuyên đặc sản hoặc có thể tìm mua ở một số chợ trong các làng chài. Cá chình mun Châu Trúc Cá chình mun là loại cá nước ngọt, thuộc họ nhà lươn, chạch nhưng kích thước lớn. Thịt cá chắc, có vị béo. Cá chỉ có ở đầm Trà Ổ hay còn gọi là đầm Châu Trúc thuộc huyện Phù Mỹ (tỉnh Bình Định). Trung bình, chình mun Châu Trúc dài gần 1 mét, kích thước tương đương bắp đùi người trưởng thành. Những con nuôi lâu năm còn lớn hơn. Đây là nguyên liệu chính cho nhiều món đặc sản tại Quy Nhơn. Cá thường được chế biến thành các dạng như nướng, hấp gừng, xào lăn hay cháo cá chình. Không chỉ hấp dẫn bởi hương vị thơm ngon, cá chình mun còn giàu dinh dưỡng, có nhiều dưỡng chất tốt cho sức khỏe. Bò chua Tây Sơn Bò chua Tây là đặc sản của vùng đất Bình Định. Thịt bò làm món này được tuyển chọn kỹ lưỡng, sau đó làm sạch, lọc hết phần lõi gân, cắt miếng mỏng vừa ăn. Thịt sau khi sơ chế được ướp đều với nước mắm, nước đường thắng lên để nguội và các loại gia vị riềng, tỏi, ớt, hạt tiêu. Đầu bếp sẽ cho hỗn hợp vào hũ, đậy nắp kín, để từ 5 đến 7 ngày cho lên men tự nhiên. Món ăn có vị chua thanh, ngọt dịu và cay nồng, thường được ăn kèm với rau sống và cuốn bánh tráng. Đây là món ăn không thể bỏ qua khi du lịch Quy Nhơn, đặc biệt đối với những ai yêu thích hương vị chua cay đậm đà. Ở Bình Định, chỉ có một số quán có món ăn này. Quán Hoa An (đường bờ kè, thị trấn Phú Phong) là một trong những quán được nhiều thực khách lui tới. Bò chua Tây Sơn đang được bán với mức giá khoảng 240.000 đồng cho một hũ 700 gam. Nhung Nhung",
+  "summary": "",
+  "faithfulness_score": 0.8,
+  "faithfulness_reason": "Tóm tắt không thêm thông tin ngoài luồng, nhưng có thể thiếu một số chi tiết nhỏ về các món ăn, như cách chế biến cụ thể hoặc giá cả chính xác tại thời điểm hiện tại",
+  "relevance_score": 0.9,
+  "relevance_reason": "Tóm tắt bao gồm hầu hết các điểm chính về các món ăn đặc sản của Quy Nhơn, như gỏi ốc giấy, cá cơm mờm khô rim, cá chình mun Châu Trúc và bò chua Tây Sơn, giúp người đọc hiểu được sự đa dạng của ẩm thực địa phương",
+  "coherence_conciseness_score": 0.85,
+  "coherence_conciseness_reason": "Tóm tắt được trình bày một cách logic và dễ đọc, tuy nhiên có thể cải thiện bằng cách loại bỏ một số từ ngữ trùng lặp và sắp xếp lại cấu trúc để tăng sự mạch lạc"
+}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
